--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -3956,7 +3956,7 @@
       <c r="I5"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Keep the CFR band linked to this audit row at 26/33/40 (central 33). Re-sync the website snapshot's methodology_constants so the live InferredTrajectory band reflects 26/40. Avoid reintroducing the 24/30/40 set or the unsupported 30-50 percent range.</t>
+          <t>Keep the CFR band linked to this audit row at 26/33/40 (central 33). Keep generated snapshot constants, README text, NUMBERS_AUDIT.md, the brief, and the public dataset aligned. Avoid reintroducing the 24/30/40 set or the unsupported 30-50 percent range.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -27657,7 +27657,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Keep the CFR band linked to this audit row at 26/33/40 (central 33). Re-sync the website snapshot's methodology_constants so the live InferredTrajectory band reflects 26/40. Avoid reintroducing the 24/30/40 set or the unsupported 30-50 percent range.</t>
+          <t>Keep the CFR band linked to this audit row at 26/33/40 (central 33). Keep generated snapshot constants, README text, NUMBERS_AUDIT.md, the brief, and the public dataset aligned. Avoid reintroducing the 24/30/40 set or the unsupported 30-50 percent range.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -28196,7 +28196,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>The public BDBV spatial map displays named public geographies, health-zone centroids, corridor endpoints, modeled corridors, and calibration corridors with explicit object role separation; it does not display household-level case GPS coordinates.</t>
+          <t>The public BDBV spatial evidence data separates named public geographies, health-zone centroids, corridor endpoints, modeled corridors, and calibration corridors with explicit object role separation; it does not include household-level case GPS coordinates.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>apps/site/app/bdbv-2026/_data/zones.json; WHO Disease Outbreak News item 2026-DON602, 15 May 2026.; apps/site/app/bdbv-2026/_data/snapshots/*.json</t>
+          <t>data/zones.json; WHO Disease Outbreak News item 2026-DON602, 15 May 2026.; data/live-bdbv-2026-output.json</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -28221,7 +28221,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Keep the map inspector focused on role, model use, and public claim audit IDs. If case-level or health-area line-list coordinates become available, add a new spatial object class and public claim audit before displaying them.</t>
+          <t>Keep spatial consumers focused on role, model use, and public claim audit IDs. If case-level or health-area line-list coordinates become available, add a new spatial object class and public claim audit before displaying or exporting them.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -2661,7 +2661,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>watch_tier_b_minus</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>claimed_confirmed_fatal_case</t>
+          <t>claimed confirmed fatal case</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>unconfirmed_by_public_health_authority</t>
+          <t>not confirmed by public-health authority</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R25"/>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Promote only if DRC MoH/INRB, WHO, Africa CDC, or CDC publishes South Kivu/Bukavu in confirmed case counts, map, line list, or sitrep with sample date/origin, lab method, health zone, travel history, death status, and epidemiologic link status. An armed-group claim, however widely reported, does not meet this bar on its own.</t>
+          <t>Promote only if DRC MoH/INRB, WHO, Africa CDC, or CDC publishes South Kivu/Bukavu in confirmed case counts, map, line list, or sitrep with sample date/origin, lab method, health zone, travel history, death status, and epidemiologic link status. An armed-group claim, however widely reported, does not meet this bar on its own. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2829,17 +2829,17 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R26"/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Promote only as policy/travel-monitoring context. Do not promote into case counts, affected-zone geography, or corridor calibration unless CDC publishes count/geography data in the same source.</t>
+          <t>Promote only as policy/travel-monitoring context. Do not promote into case counts, affected-zone geography, or corridor calibration unless CDC publishes count/geography data in the same source. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>regional_cross_check_counts_context_only</t>
+          <t>regional cross check counts context only</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2932,17 +2932,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R27"/>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Use ECDC May 21 count values only as cross-check staged observations unless ECDC publishes a primary line-list or explicit correction that supersedes CDC/WHO figures.</t>
+          <t>Use ECDC May 21 count values only as cross-check staged observations unless ECDC publishes a primary line-list or explicit correction that supersedes CDC/WHO figures. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R28"/>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Promote to staged counts/geography only if the alert contains explicit outbreak figures and a reviewer extracts them with denominator semantics.</t>
+          <t>Promote to staged counts/geography only if the alert contains explicit outbreak figures and a reviewer extracts them with denominator semantics. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3138,17 +3138,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R29"/>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Keep as readiness context unless WHO AFRO publishes count/geography tables in this source.</t>
+          <t>Keep as readiness context unless WHO AFRO publishes count/geography tables in this source. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>context_tier_a_minus</t>
+          <t>context tier a minus</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R30"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Keep as response/traveler-monitoring context; do not use as outbreak count input.</t>
+          <t>Keep as response/traveler-monitoring context; do not use as outbreak count input. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>context_tier_b_plus</t>
+          <t>context tier b plus</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>published_context_signal_hash_recorded_bytes</t>
+          <t>published context signal hash recorded bytes</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R31"/>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>risk_and_response_context</t>
+          <t>risk and response context</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>official_who_statement</t>
+          <t>official who statement</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R32"/>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Use for risk-context copy and Uganda transmission-status context; do not promote to zone-attributed count input.</t>
+          <t>Use for risk-context copy and Uganda transmission-status context; do not promote to zone-attributed count input. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3550,17 +3550,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R33"/>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>watch_signal</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>context_tier_a</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>not_a_case_count_source</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3653,17 +3653,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>published_context_signal</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>blocked_pending_official_confirmation</t>
+          <t>not admitted pending official confirmation</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>not_model_input</t>
+          <t>not used in model</t>
         </is>
       </c>
       <c r="R34"/>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics. Official/public-health promotion gate: do not use for counts, geography, corridor calibration, or model inputs unless an official public-health source publishes explicit count/geography data for that use.</t>
         </is>
       </c>
     </row>
@@ -28013,7 +28013,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>watch only; not a model input</t>
+          <t>review only; not used in model</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -28033,7 +28033,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Keep the South Kivu/Bukavu item in watch_signals only. Promote to staged_observations and geography inputs only after DRC MoH/INRB, WHO, Africa CDC, or CDC confirms it.</t>
+          <t>Keep the South Kivu/Bukavu item in source-review rows only. Promote to admitted observation rows and geography inputs only after DRC MoH/INRB, WHO, Africa CDC, or CDC confirms it.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T23:59:59Z</t>
+          <t>2026-05-23T23:59:59Z</t>
         </is>
       </c>
     </row>
@@ -124,7 +124,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -134,7 +134,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -2265,8 +2265,66 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>US Centers for Disease Control and Prevention</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-23T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:38:45Z</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="J36"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L35"/>
+  <autoFilter ref="A1:L36"/>
 </worksheet>
 </file>
 
@@ -4119,7 +4177,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>obs:cdc-current-situation:2026-05-22:confirmed</t>
+          <t>obs:cdc-current-situation:2026-05-23:suspected</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4129,7 +4187,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-22</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="D19"/>
@@ -4145,17 +4203,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -4165,11 +4223,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>suspected</t>
         </is>
       </c>
       <c r="L19">
-        <v>83</v>
+        <v>746</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4178,27 +4236,27 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
+          <t>{"breakdown": {"COD": 746}, "countries": ["COD"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>official_cross_check</t>
+          <t>official_summary</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>cross_check</t>
+          <t>model_eligible</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>cross_check_only</t>
+          <t>eligible_after_release</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:confirmed-total</t>
+          <t>obs:who-dg:2026-05-22:suspected-approx; obs:cdc-current-situation:2026-05-22:suspected; watch:bdbv:wikipedia-aggregator:2026-05-24:counts</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -4208,19 +4266,19 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-020</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Near-identical official cross-check to WHO DG 84 confirmed endpoint.</t>
+          <t>Promoted as the May 23 exact official suspected-case endpoint; later 900-plus media/aggregator signals remain watch-only pending official confirmation.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>obs:cdc-current-situation:2026-05-22:suspected</t>
+          <t>obs:cdc-current-situation:2026-05-23:confirmed</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4230,7 +4288,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-22</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="D20"/>
@@ -4246,17 +4304,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -4266,11 +4324,11 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspected</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L20">
-        <v>744</v>
+        <v>88</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -4279,27 +4337,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
+          <t>{"breakdown": {"COD": 83, "UGA": 5}, "countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>official_cross_check</t>
+          <t>official_summary</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>cross_check</t>
+          <t>model_eligible</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>cross_check_only</t>
+          <t>eligible_after_release</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:suspected-approx</t>
+          <t>obs:who-dg:2026-05-22:confirmed-total; obs:cdc-current-situation:2026-05-22:confirmed; watch:bdbv:wikipedia-aggregator:2026-05-24:counts</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -4309,19 +4367,19 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-020</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Near-identical official cross-check to WHO DG almost-750 suspected endpoint.</t>
+          <t>Country-pair confirmed endpoint preserves the CDC DRC/Uganda split.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>obs:cdc-current-situation:2026-05-22:suspected-deaths</t>
+          <t>obs:cdc-current-situation:2026-05-23:suspected-deaths</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4331,7 +4389,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-22</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="D21"/>
@@ -4347,17 +4405,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -4380,27 +4438,27 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
+          <t>{"breakdown": {"COD": 176}, "countries": ["COD"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>official_cross_check</t>
+          <t>official_summary</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>cross_check</t>
+          <t>model_eligible</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>cross_check_only</t>
+          <t>eligible_after_release</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:suspected-deaths</t>
+          <t>obs:who-dg:2026-05-22:suspected-deaths; obs:cdc-current-situation:2026-05-22:suspected-deaths; watch:bdbv:wikipedia-aggregator:2026-05-24:counts</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -4410,19 +4468,19 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-020</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Near-identical official cross-check to WHO DG 177 suspected-deaths endpoint.</t>
+          <t>Reported-deaths endpoint remains suspected DRC deaths; Uganda confirmed death is retained as a separate source-extracted metric.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>obs:ecdc-outbreak-page:2026-05-22:confirmed</t>
+          <t>obs:cdc-current-situation:2026-05-22:confirmed</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4432,18 +4490,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+          <t>cdc-current-situation-2026-05-22</t>
         </is>
       </c>
       <c r="D22"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>European Centre for Disease Prevention and Control</t>
+          <t>US Centers for Disease Control and Prevention</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>regional_body</t>
+          <t>official_cdc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4472,7 +4530,7 @@
         </is>
       </c>
       <c r="L22">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -4486,7 +4544,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>regional_body_cross_check</t>
+          <t>official_cross_check</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -4501,12 +4559,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:confirmed-total; obs:cdc-current-situation:2026-05-22:confirmed</t>
+          <t>obs:who-dg:2026-05-22:confirmed-total</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -4516,14 +4574,14 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
+          <t>Near-identical official cross-check to WHO DG 84 confirmed endpoint.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>obs:ecdc-outbreak-page:2026-05-22:suspected</t>
+          <t>obs:cdc-current-situation:2026-05-22:suspected</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4533,18 +4591,18 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+          <t>cdc-current-situation-2026-05-22</t>
         </is>
       </c>
       <c r="D23"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>European Centre for Disease Prevention and Control</t>
+          <t>US Centers for Disease Control and Prevention</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>regional_body</t>
+          <t>official_cdc</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4573,7 +4631,7 @@
         </is>
       </c>
       <c r="L23">
-        <v>650</v>
+        <v>744</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -4587,7 +4645,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>regional_body_cross_check</t>
+          <t>official_cross_check</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4602,12 +4660,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:suspected-approx; obs:cdc-current-situation:2026-05-22:suspected</t>
+          <t>obs:who-dg:2026-05-22:suspected-approx</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -4617,14 +4675,14 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
+          <t>Near-identical official cross-check to WHO DG almost-750 suspected endpoint.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>obs:ecdc-outbreak-page:2026-05-22:suspected-deaths</t>
+          <t>obs:cdc-current-situation:2026-05-22:suspected-deaths</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4634,18 +4692,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+          <t>cdc-current-situation-2026-05-22</t>
         </is>
       </c>
       <c r="D24"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>European Centre for Disease Prevention and Control</t>
+          <t>US Centers for Disease Control and Prevention</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>regional_body</t>
+          <t>official_cdc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4674,7 +4732,7 @@
         </is>
       </c>
       <c r="L24">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -4688,7 +4746,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>regional_body_cross_check</t>
+          <t>official_cross_check</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4703,12 +4761,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>obs:who-dg:2026-05-22:suspected-deaths; obs:cdc-current-situation:2026-05-22:suspected-deaths</t>
+          <t>obs:who-dg:2026-05-22:suspected-deaths</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -4718,237 +4776,229 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
+          <t>Near-identical official cross-check to WHO DG 177 suspected-deaths endpoint.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>watch:bdbv:south-kivu-bukavu:m23-claim:2026-05-21</t>
+          <t>obs:ecdc-outbreak-page:2026-05-22:confirmed</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>source under review</t>
+          <t>staged_observation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>enca-south-kivu-m23-claim-2026-05-21-live; apnews-south-kivu-m23-claim-2026-05-21-live</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>M23/AFC spokesman or statement; Associated Press report; local manifest archive apnews-south-kivu-m23-claim-2026-05-21-live; AFP report republished by eNCA; local manifest archive enca-south-kivu-m23-claim-2026-05-21-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="D25"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Associated Press / AFP wire reporting</t>
+          <t>European Centre for Disease Prevention and Control</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>source under review</t>
+          <t>regional_body</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>geographic_expansion_signal</t>
+          <t>cases</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>claimed confirmed fatal case</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>M23/AFC claimed a confirmed fatal Ebola Bundibugyo case near/from Bukavu in South Kivu.</t>
-        </is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L25">
+        <v>60</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>qualitative</t>
+          <t>exact_int</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{"control_context": "M23-controlled area", "place": "Bukavu / surrounding area", "province": "South Kivu", "uncertainty": "AFP reports the sample origin was unclear between Bukavu city proper and surrounding rural areas."}</t>
+          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>not confirmed by public-health authority</t>
+          <t>regional_body_cross_check</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>not admitted pending official confirmation</t>
+          <t>cross_check</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>not used in model</t>
-        </is>
-      </c>
-      <c r="R25"/>
+          <t>cross_check_only</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>obs:who-dg:2026-05-22:confirmed-total; obs:cdc-current-situation:2026-05-22:confirmed</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://apnews.com/article/18537353976a958687e55f95434c918c; https://www.enca.com/lifestyle/deadly-dr-congo-ebola-outbreak-spreads-m23-held-south-kivu-0</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-011</t>
+          <t>BDBV-CLAIM-020</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Promote only if DRC MoH/INRB, WHO, Africa CDC, or CDC publishes South Kivu/Bukavu in confirmed case counts, map, line list, or sitrep with sample date/origin, lab method, health zone, travel history, death status, and epidemiologic link status. An armed-group claim, however widely reported, does not meet this bar on its own.</t>
+          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>watch:bdbv:cdc-traveler-management-guidance:2026-05-21</t>
+          <t>obs:ecdc-outbreak-page:2026-05-22:suspected</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>source under review</t>
+          <t>staged_observation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cdc-traveler-management-guidance-2026-05-21-pdf; cdc-traveler-management-guidance-2026-05-22-live</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CDC interim guidance web page/PDF; Local outbreak manifest archive cdc-traveler-management-guidance-2026-05-21-pdf</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="D26"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US Centers for Disease Control and Prevention</t>
+          <t>European Centre for Disease Prevention and Control</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>context tier a</t>
+          <t>regional_body</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>geographic_expansion_signal</t>
+          <t>cases</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>not a case count source</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>CDC issued interim traveler public-health assessment and management guidance for the 2026 BVD outbreak, including DRC, Uganda, and South Sudan in affected-country handling.</t>
-        </is>
+          <t>suspected</t>
+        </is>
+      </c>
+      <c r="L26">
+        <v>650</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>qualitative</t>
+          <t>exact_int</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{"areas_of_concern": {"COD": "Entire country", "SSD": "No specific area; included because it borders DRC with high-volume porous-border travel", "UGA": "Kampala"}, "countries": ["COD", "UGA", "SSD", "USA"]}</t>
+          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>published context signal</t>
+          <t>regional_body_cross_check</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>not admitted pending official confirmation</t>
+          <t>cross_check</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>not used in model</t>
-        </is>
-      </c>
-      <c r="R26"/>
+          <t>cross_check_only</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>obs:who-dg:2026-05-22:suspected-approx; obs:cdc-current-situation:2026-05-22:suspected</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/php/php/public-health-strategy/ebola-outbreak-interim-guidance.html; https://www.cdc.gov/viral-hemorrhagic-fevers/media/pdfs/Interim-guidance-for-BVD-2026.pdf</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-016</t>
+          <t>BDBV-CLAIM-020</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>Promote only as policy/travel-monitoring context. Do not promote into case counts, affected-zone geography, or corridor calibration unless CDC publishes count/geography data in the same source.</t>
+          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>watch:bdbv:ecdc-risk-assessment:2026-05-21</t>
+          <t>obs:ecdc-outbreak-page:2026-05-22:suspected-deaths</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>source under review</t>
+          <t>staged_observation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ecdc-bdbv-drc-uga-2026-05-21-live; ecdc-threat-assessment-bdbv-2026-05-21-pdf</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ECDC threat assessment brief PDF; ECDC outbreak page updated 21 May 18:00; Local manifest archive ecdc-threat-assessment-bdbv-2026-05-21-pdf and ecdc-bdbv-drc-uga-2026-05-21-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="D27"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>European Centre for Disease Prevention and Control</t>
@@ -4956,85 +5006,87 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>context tier a</t>
+          <t>regional_body</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>geographic_expansion_signal</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>regional cross check counts context only</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>ECDC published a 21 May threat assessment/risk update: very-low EU/EEA public risk, with preparedness recommendations and WHO-derived outbreak-count context.</t>
-        </is>
+          <t>suspected_deaths</t>
+        </is>
+      </c>
+      <c r="L27">
+        <v>160</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>qualitative</t>
+          <t>exact_int</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA", "EU/EEA"], "risk_scope": "EU/EEA importation/public-health preparedness"}</t>
+          <t>{"countries": ["COD", "UGA"], "scope_type": "aggregate"}</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>published context signal</t>
+          <t>regional_body_cross_check</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>not admitted pending official confirmation</t>
+          <t>cross_check</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>not used in model</t>
-        </is>
-      </c>
-      <c r="R27"/>
+          <t>cross_check_only</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>obs:who-dg:2026-05-22:suspected-deaths; obs:cdc-current-situation:2026-05-22:suspected-deaths</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://www.ecdc.europa.eu/en/publications-data/threat-assessment-brief-ebola-disease-outbreak-caused-bundibugyo-virus-democratic; https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-016</t>
+          <t>BDBV-CLAIM-020</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>Use ECDC May 21 count values only as cross-check staged observations unless ECDC publishes a primary line-list or explicit correction that supersedes CDC/WHO figures.</t>
+          <t>Lower regional cross-check retained as lag/context, not headline endpoint.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>watch:bdbv:paho-who-epialert:2026-05-21</t>
+          <t>watch:bdbv:south-kivu-bukavu:m23-claim:2026-05-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5044,22 +5096,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>paho-who-epialert-bdbv-2026-05-21-pdf</t>
+          <t>enca-south-kivu-m23-claim-2026-05-21-live; apnews-south-kivu-m23-claim-2026-05-21-live</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PAHO/WHO document landing page; PAHO/WHO PDF hash-recorded in local manifest as paho-who-epialert-bdbv-2026-05-21-pdf</t>
+          <t>M23/AFC spokesman or statement; Associated Press report; local manifest archive apnews-south-kivu-m23-claim-2026-05-21-live; AFP report republished by eNCA; local manifest archive enca-south-kivu-m23-claim-2026-05-21-live</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pan American Health Organization / World Health Organization</t>
+          <t>Associated Press / AFP wire reporting</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>context tier a</t>
+          <t>source under review</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5074,7 +5126,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -5084,12 +5136,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>not a case count source</t>
+          <t>claimed confirmed fatal case</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>PAHO/WHO published a May 21 epidemiological alert sharing updated technical guidance for laboratory preparedness, IPC, and clinical management in light of the DRC/Uganda BDBV situation.</t>
+          <t>M23/AFC claimed a confirmed fatal Ebola Bundibugyo case near/from Bukavu in South Kivu.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -5099,12 +5151,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "region": "Americas preparedness context"}</t>
+          <t>{"control_context": "M23-controlled area", "place": "Bukavu / surrounding area", "province": "South Kivu", "uncertainty": "AFP reports the sample origin was unclear between Bukavu city proper and surrounding rural areas."}</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>published context signal</t>
+          <t>not confirmed by public-health authority</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -5120,24 +5172,24 @@
       <c r="R28"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://www.paho.org/en/documents/epidemiological-alert-ebola-disease-due-bundibugyo-virus-democratic-republic-congo-and; https://www.paho.org/sites/default/files/2026/05/2026-may-20-phe-bundibugyo-virus-disease.pdf</t>
+          <t>https://apnews.com/article/18537353976a958687e55f95434c918c; https://www.enca.com/lifestyle/deadly-dr-congo-ebola-outbreak-spreads-m23-held-south-kivu-0</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-016</t>
+          <t>BDBV-CLAIM-011</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Promote to staged counts/geography only if the alert contains explicit outbreak figures and a reviewer extracts them with denominator semantics.</t>
+          <t>Promote only if DRC MoH/INRB, WHO, Africa CDC, or CDC publishes South Kivu/Bukavu in confirmed case counts, map, line list, or sitrep with sample date/origin, lab method, health zone, travel history, death status, and epidemiologic link status. An armed-group claim, however widely reported, does not meet this bar on its own.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>watch:bdbv:who-afro-zambia-readiness:2026-05-21</t>
+          <t>watch:bdbv:cdc-traveler-management-guidance:2026-05-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5147,17 +5199,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>who-afro-zambia-readiness-2026-05-21-live</t>
+          <t>cdc-traveler-management-guidance-2026-05-21-pdf; cdc-traveler-management-guidance-2026-05-22-live</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WHO AFRO Zambia readiness article; Local manifest archive who-afro-zambia-readiness-2026-05-21-live</t>
+          <t>CDC interim guidance web page/PDF; Local outbreak manifest archive cdc-traveler-management-guidance-2026-05-21-pdf</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>World Health Organization, Regional Office for Africa</t>
+          <t>US Centers for Disease Control and Prevention</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5192,7 +5244,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>WHO AFRO published Zambia readiness context tied to Ebola outbreaks in DRC and Uganda, including surveillance and preparedness capacity signals.</t>
+          <t>CDC issued interim traveler public-health assessment and management guidance for the 2026 BVD outbreak, including DRC, Uganda, and South Sudan in affected-country handling.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -5202,7 +5254,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{"countries": ["ZMB", "COD", "UGA"], "scope": "regional preparedness"}</t>
+          <t>{"areas_of_concern": {"COD": "Entire country", "SSD": "No specific area; included because it borders DRC with high-volume porous-border travel", "UGA": "Kampala"}, "countries": ["COD", "UGA", "SSD", "USA"]}</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -5223,7 +5275,7 @@
       <c r="R29"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://www.afro.who.int/countries/zambia/news/strengthening-zambias-readiness-health-emergencies-surveillance-pandemic-preparedness</t>
+          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/php/php/public-health-strategy/ebola-outbreak-interim-guidance.html; https://www.cdc.gov/viral-hemorrhagic-fevers/media/pdfs/Interim-guidance-for-BVD-2026.pdf</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -5233,14 +5285,14 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Keep as readiness context unless WHO AFRO publishes count/geography tables in this source.</t>
+          <t>Promote only as policy/travel-monitoring context. Do not promote into case counts, affected-zone geography, or corridor calibration unless CDC publishes count/geography data in the same source.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>watch:bdbv:uk-support-traveler-monitoring:2026-05-21</t>
+          <t>watch:bdbv:ecdc-risk-assessment:2026-05-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5250,22 +5302,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>uk-gov-ebola-eastern-drc-support-2026-05-21-live</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-21-live; ecdc-threat-assessment-bdbv-2026-05-21-pdf</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>GOV.UK press release; Local manifest archive uk-gov-ebola-eastern-drc-support-2026-05-21-live</t>
+          <t>ECDC threat assessment brief PDF; ECDC outbreak page updated 21 May 18:00; Local manifest archive ecdc-threat-assessment-bdbv-2026-05-21-pdf and ecdc-bdbv-drc-uga-2026-05-21-live</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UK Foreign, Commonwealth &amp; Development Office / UK Health Security Agency</t>
+          <t>European Centre for Disease Prevention and Control</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>context tier a minus</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -5290,12 +5342,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>not a case count source</t>
+          <t>regional cross check counts context only</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>UK announced up to GBP 20 million support for eastern DRC Ebola response and activated UKHSA returning-worker monitoring/travel-route assessment.</t>
+          <t>ECDC published a 21 May threat assessment/risk update: very-low EU/EEA public risk, with preparedness recommendations and WHO-derived outbreak-count context.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -5305,7 +5357,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{"countries": ["GBR", "COD", "UGA"], "scope": "response funding and traveler monitoring"}</t>
+          <t>{"countries": ["COD", "UGA", "EU/EEA"], "risk_scope": "EU/EEA importation/public-health preparedness"}</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -5326,7 +5378,7 @@
       <c r="R30"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>https://www.gov.uk/government/news/uk-steps-up-support-to-stop-spread-of-ebola-in-eastern-drc</t>
+          <t>https://www.ecdc.europa.eu/en/publications-data/threat-assessment-brief-ebola-disease-outbreak-caused-bundibugyo-virus-democratic; https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -5336,14 +5388,14 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Keep as response/traveler-monitoring context; do not use as outbreak count input.</t>
+          <t>Use ECDC May 21 count values only as cross-check staged observations unless ECDC publishes a primary line-list or explicit correction that supersedes CDC/WHO figures.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>watch:bdbv:ifrc-regional-risk-response:2026-05-21</t>
+          <t>watch:bdbv:paho-who-epialert:2026-05-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5353,22 +5405,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ifrc-regional-risk-response-2026-05-21-live</t>
+          <t>paho-who-epialert-bdbv-2026-05-21-pdf</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IFRC press release; Local manifest archive ifrc-regional-risk-response-2026-05-21-live; direct command-line fetch returned HTTP 403, so archived bytes are browser DOM capture and are restricted/hash-recorded pending publisher-terms confirmation</t>
+          <t>PAHO/WHO document landing page; PAHO/WHO PDF hash-recorded in local manifest as paho-who-epialert-bdbv-2026-05-21-pdf</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>International Federation of Red Cross and Red Crescent Societies</t>
+          <t>Pan American Health Organization / World Health Organization</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>context tier b plus</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -5398,7 +5450,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>IFRC published a May 21 operational response signal about scaling response in eastern DRC and regional risk preparedness.</t>
+          <t>PAHO/WHO published a May 21 epidemiological alert sharing updated technical guidance for laboratory preparedness, IPC, and clinical management in light of the DRC/Uganda BDBV situation.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -5408,12 +5460,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "scope": "humanitarian response/readiness"}</t>
+          <t>{"countries": ["COD", "UGA"], "region": "Americas preparedness context"}</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>published context signal hash recorded bytes</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -5429,7 +5481,7 @@
       <c r="R31"/>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://www.ifrc.org/press-release/ebola-ifrc-scales-response-eastern-drc-regional-risks-grow</t>
+          <t>https://www.paho.org/en/documents/epidemiological-alert-ebola-disease-due-bundibugyo-virus-democratic-republic-congo-and; https://www.paho.org/sites/default/files/2026/05/2026-may-20-phe-bundibugyo-virus-disease.pdf</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -5439,14 +5491,14 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>Keep as non-model operational context and do not promote to counts/geography unless IFRC or an official public-health authority publishes explicit count/geography data in this source.</t>
+          <t>Promote to staged counts/geography only if the alert contains explicit outbreak figures and a reviewer extracts them with denominator semantics.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>watch:bdbv:who-ihr-temp-recs:2026-05-22</t>
+          <t>watch:bdbv:who-afro-zambia-readiness:2026-05-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5456,17 +5508,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>who-ihr-ec-bdbv-temporary-recommendations-2026-05-22</t>
+          <t>who-afro-zambia-readiness-2026-05-21-live</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WHO IHR Emergency Committee temporary recommendations; Local manifest archive who-ihr-ec-bdbv-temporary-recommendations-2026-05-22</t>
+          <t>WHO AFRO Zambia readiness article; Local manifest archive who-afro-zambia-readiness-2026-05-21-live</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>World Health Organization</t>
+          <t>World Health Organization, Regional Office for Africa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5476,19 +5528,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
           <t>geographic_expansion_signal</t>
@@ -5496,12 +5548,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>risk and response context</t>
+          <t>not a case count source</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>WHO IHR Emergency Committee temporary recommendations revised current risk framing: DRC very high, Uganda high, regional risk high, and no documented onward Uganda transmission among contacts of the two imported cases as of 22 May.</t>
+          <t>WHO AFRO published Zambia readiness context tied to Ebola outbreaks in DRC and Uganda, including surveillance and preparedness capacity signals.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -5511,12 +5563,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA"], "scope": "PHEIC temporary recommendations and regional risk"}</t>
+          <t>{"countries": ["ZMB", "COD", "UGA"], "scope": "regional preparedness"}</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>official who statement</t>
+          <t>published context signal</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5532,24 +5584,24 @@
       <c r="R32"/>
       <c r="S32" t="inlineStr">
         <is>
-          <t>https://www.who.int/news/item/22-05-2026-first-meeting-of-the-ihr-emergency-committee-regarding-the-epidemic-of-ebola-bundibugyo-virus-disease-in-the-democratic-republic-of-the-congo-and-uganda-2026-temporary-recommendations</t>
+          <t>https://www.afro.who.int/countries/zambia/news/strengthening-zambias-readiness-health-emergencies-surveillance-pandemic-preparedness</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-017</t>
+          <t>BDBV-CLAIM-016</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>Use for risk-context copy and Uganda transmission-status context; do not promote to zone-attributed count input.</t>
+          <t>Keep as readiness context unless WHO AFRO publishes count/geography tables in this source.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>watch:bdbv:cdc-traveler-management-guidance:2026-05-22</t>
+          <t>watch:bdbv:uk-support-traveler-monitoring:2026-05-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5559,39 +5611,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>cdc-traveler-management-guidance-2026-05-22-live</t>
+          <t>uk-gov-ebola-eastern-drc-support-2026-05-21-live</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CDC traveler-management guidance page; Local manifest archive cdc-traveler-management-guidance-2026-05-22-live</t>
+          <t>GOV.UK press release; Local manifest archive uk-gov-ebola-eastern-drc-support-2026-05-21-live</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>US Centers for Disease Control and Prevention</t>
+          <t>UK Foreign, Commonwealth &amp; Development Office / UK Health Security Agency</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>context tier a</t>
+          <t>context tier a minus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>geographic_expansion_signal</t>
@@ -5604,7 +5656,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CDC traveler-management guidance page updated on 22 May; it supports travel/public-health monitoring context and does not publish a model-eligible outbreak count tuple.</t>
+          <t>UK announced up to GBP 20 million support for eastern DRC Ebola response and activated UKHSA returning-worker monitoring/travel-route assessment.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -5614,7 +5666,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA", "SSD"], "scope": "traveler monitoring and public-health management context"}</t>
+          <t>{"countries": ["GBR", "COD", "UGA"], "scope": "response funding and traveler monitoring"}</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -5635,24 +5687,24 @@
       <c r="R33"/>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/php/php/public-health-strategy/ebola-outbreak-interim-guidance.html</t>
+          <t>https://www.gov.uk/government/news/uk-steps-up-support-to-stop-spread-of-ebola-in-eastern-drc</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-020</t>
+          <t>BDBV-CLAIM-016</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+          <t>Keep as response/traveler-monitoring context; do not use as outbreak count input.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>watch:bdbv:cdc-returning-travelers:2026-05-22</t>
+          <t>watch:bdbv:ifrc-regional-risk-response:2026-05-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5662,39 +5714,39 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cdc-returning-travelers-info-2026-05-21-live; cdc-returning-travelers-info-2026-05-22-live</t>
+          <t>ifrc-regional-risk-response-2026-05-21-live</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CDC returning-travelers public page; Local manifest archive cdc-returning-travelers-info-2026-05-22-live</t>
+          <t>IFRC press release; Local manifest archive ifrc-regional-risk-response-2026-05-21-live; direct command-line fetch returned HTTP 403, so archived bytes are browser DOM capture and are restricted/hash-recorded pending publisher-terms confirmation</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Centers for Disease Control and Prevention</t>
+          <t>International Federation of Red Cross and Red Crescent Societies</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>context tier a</t>
+          <t>context tier b plus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
           <t>geographic_expansion_signal</t>
@@ -5707,7 +5759,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CDC returning-travelers page updated on 22 May; it supports public travel-monitoring context and does not publish a model-eligible outbreak count tuple.</t>
+          <t>IFRC published a May 21 operational response signal about scaling response in eastern DRC and regional risk preparedness.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -5717,12 +5769,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>{"countries": ["COD", "UGA", "SSD"], "scope": "traveler monitoring and public information context"}</t>
+          <t>{"countries": ["COD", "UGA"], "scope": "humanitarian response/readiness"}</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>published context signal</t>
+          <t>published context signal hash recorded bytes</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5738,24 +5790,24 @@
       <c r="R34"/>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/travel-to-us/index.html</t>
+          <t>https://www.ifrc.org/press-release/ebola-ifrc-scales-response-eastern-drc-regional-risks-grow</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-020</t>
+          <t>BDBV-CLAIM-016</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+          <t>Keep as non-model operational context and do not promote to counts/geography unless IFRC or an official public-health authority publishes explicit count/geography data in this source.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>watch:bdbv:uganda-five-confirmed:who-dg-social:2026-05-23</t>
+          <t>watch:bdbv:who-ihr-temp-recs:2026-05-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5763,35 +5815,39 @@
           <t>source under review</t>
         </is>
       </c>
-      <c r="C35"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>who-ihr-ec-bdbv-temporary-recommendations-2026-05-22</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WHO Director-General official social post by @DrTedros on 2026-05-23; Uganda Ministry of Health statement reported by Reuters/AP/Xinhua and regional outlets on 2026-05-23; Registered source rows who-dg-official-social and uganda-moh-official-social; both are marked extractor_backend=air_preferred pending direct archive</t>
+          <t>WHO IHR Emergency Committee temporary recommendations; Local manifest archive who-ihr-ec-bdbv-temporary-recommendations-2026-05-22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WHO Director-General / Uganda Ministry of Health official-social channel cross-check</t>
+          <t>World Health Organization</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>source under review</t>
+          <t>context tier a</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5801,12 +5857,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>official social candidate count update</t>
+          <t>risk and response context</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Uganda reported three new confirmed Ebola/BDBV cases, bringing the Uganda confirmed-positive total to five; the three new cases include a Ugandan health worker, a driver, and a Congolese national who travelled from Ituri Province for medical care.</t>
+          <t>WHO IHR Emergency Committee temporary recommendations revised current risk framing: DRC very high, Uganda high, regional risk high, and no documented onward Uganda transmission among contacts of the two imported cases as of 22 May.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -5816,12 +5872,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>{"country": "Uganda", "places": ["Kampala", "Ituri-linked medical-care travel"], "uncertainty": "The official social post establishes the Uganda national total and case categories, but direct post/status archive and detailed Uganda MoH statement/PDF still need capture before scored use."}</t>
+          <t>{"countries": ["COD", "UGA"], "scope": "PHEIC temporary recommendations and regional risk"}</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>official signal pending direct archive</t>
+          <t>official who statement</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5837,22 +5893,430 @@
       <c r="R35"/>
       <c r="S35" t="inlineStr">
         <is>
+          <t>https://www.who.int/news/item/22-05-2026-first-meeting-of-the-ihr-emergency-committee-regarding-the-epidemic-of-ebola-bundibugyo-virus-disease-in-the-democratic-republic-of-the-congo-and-uganda-2026-temporary-recommendations</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-017</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Use for risk-context copy and Uganda transmission-status context; do not promote to zone-attributed count input.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>watch:bdbv:cdc-traveler-management-guidance:2026-05-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>cdc-traveler-management-guidance-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CDC traveler-management guidance page; Local manifest archive cdc-traveler-management-guidance-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>US Centers for Disease Control and Prevention</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>context tier a</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>geographic_expansion_signal</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>not a case count source</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>CDC traveler-management guidance page updated on 22 May; it supports travel/public-health monitoring context and does not publish a model-eligible outbreak count tuple.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>qualitative</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>{"countries": ["COD", "UGA", "SSD"], "scope": "traveler monitoring and public-health management context"}</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>published context signal</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>not admitted pending official confirmation</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>not used in model</t>
+        </is>
+      </c>
+      <c r="R36"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/php/php/public-health-strategy/ebola-outbreak-interim-guidance.html</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-020</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>watch:bdbv:cdc-returning-travelers:2026-05-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cdc-returning-travelers-info-2026-05-21-live; cdc-returning-travelers-info-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CDC returning-travelers public page; Local manifest archive cdc-returning-travelers-info-2026-05-22-live</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>US Centers for Disease Control and Prevention</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>context tier a</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>geographic_expansion_signal</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>not a case count source</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>CDC returning-travelers page updated on 22 May; it supports public travel-monitoring context and does not publish a model-eligible outbreak count tuple.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>qualitative</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>{"countries": ["COD", "UGA", "SSD"], "scope": "traveler monitoring and public information context"}</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>published context signal</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>not admitted pending official confirmation</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>not used in model</t>
+        </is>
+      </c>
+      <c r="R37"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/viral-hemorrhagic-fevers/travel-to-us/index.html</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-020</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Keep as context-only unless CDC publishes explicit count/geography data in this source and a reviewer extracts denominator semantics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>watch:bdbv:uganda-five-confirmed:who-dg-social:2026-05-23</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="C38"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WHO Director-General official social post by @DrTedros on 2026-05-23; Uganda Ministry of Health statement reported by Reuters/AP/Xinhua and regional outlets on 2026-05-23; Registered source rows who-dg-official-social and uganda-moh-official-social; both are marked extractor_backend=air_preferred pending direct archive</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WHO Director-General / Uganda Ministry of Health official-social channel cross-check</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>geographic_expansion_signal</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>official social candidate count update</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Uganda reported three new confirmed Ebola/BDBV cases, bringing the Uganda confirmed-positive total to five; the three new cases include a Ugandan health worker, a driver, and a Congolese national who travelled from Ituri Province for medical care.</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>qualitative</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>{"country": "Uganda", "places": ["Kampala", "Ituri-linked medical-care travel"], "uncertainty": "The official social post establishes the Uganda national total and case categories, but direct post/status archive and detailed Uganda MoH statement/PDF still need capture before scored use."}</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>official signal pending direct archive</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>not admitted pending official confirmation</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>not used in model</t>
+        </is>
+      </c>
+      <c r="R38"/>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>https://x.com/DrTedros; https://x.com/MinofHealthUG; https://www.aljazeera.com/news/2026/5/23/uganda-confirms-three-new-ebola-cases-bringing-total-to-five; https://apnews.com/article/ed1d6b595f3c91800b5614d6bec5831d; https://english.news.cn/20260523/292f7a6beefb44db98218b0aa5d7eb5b/c.html</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>PUBLIC-CLAIM-AUDIT</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>Promote only after a direct WHO DG/WHO/Uganda MoH post, statement, PDF, or page is captured with URL/status id, publication timestamp, author identity, extracted text, and hash/screenshot evidence. Once archived, update the manifest and public claim audit before using the Uganda total of five in scored counts, timeline endpoint, Kampala status, or public website copy.</t>
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>watch:bdbv:wikipedia-aggregator:2026-05-24:counts</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>wikipedia-2026-ituri-epidemic-2026-05-20-live</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Wikipedia: 2026 Ituri Province Ebola epidemic; Media/aggregator reports surfaced by the daily prep freshness check</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wikipedia / media aggregator chain</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>source under review</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>geographic_expansion_signal</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>aggregated count claim</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Aggregator surface reported 96 confirmed cases, 867 suspected cases, and 216 deaths for the BDBV outbreak.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>qualitative</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>{"countries": ["COD", "UGA"], "uncertainty": "The counts are aggregator/media-derived and not anchored to a dated DRC MoH, WHO, Africa CDC, CDC, or ECDC source row in the manifest."}</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>not confirmed by public-health authority</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>not admitted pending official confirmation</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>not used in model</t>
+        </is>
+      </c>
+      <c r="R39"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>PUBLIC-CLAIM-AUDIT</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Promote only when DRC MoH/INRB, WHO, Africa CDC, CDC, or ECDC publishes the same dated count tuple or enough primary detail to reconcile 96 confirmed, 867 suspected, and 216 deaths into the manifest and staged observations.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U35"/>
+  <autoFilter ref="A1:U39"/>
 </worksheet>
 </file>
 
@@ -9054,12 +9518,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-22T23:59:59Z</t>
+          <t>2026-05-23T23:59:59Z</t>
         </is>
       </c>
       <c r="E2"/>
@@ -13476,8 +13940,129 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>source_data_report_date:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D107"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="F107"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>source_publication_date:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D108"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="F108"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-05-24T18:38:45Z</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="F109"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I106"/>
+  <autoFilter ref="A1:I109"/>
 </worksheet>
 </file>
 
@@ -27596,34 +28181,34 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:cdc-current-situation-2026-05-23:cases_confirmed</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D179"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-05-22T23:59:59Z</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F179">
-        <v>750</v>
-      </c>
-      <c r="G179">
-        <v>395</v>
-      </c>
-      <c r="H179">
-        <v>750</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="G179"/>
+      <c r="H179"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>count</t>
@@ -27631,37 +28216,33 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>who-dg-remarks-bdbv-2026-05-22</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K179"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026</t>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>40367f2982e766cd8d12f4f223e420d6c4739f4ed1345c8584541619ec061495</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
@@ -27671,7 +28252,7 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>CC-BY-NC-SA-3.0-IGO</t>
+          <t>public-domain-us-gov</t>
         </is>
       </c>
       <c r="S179"/>
@@ -27679,12 +28260,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:cdc-current-situation-2026-05-23:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -27692,21 +28273,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D180"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-05-22T23:59:59Z</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F180">
-        <v>84</v>
-      </c>
-      <c r="G180">
-        <v>10</v>
-      </c>
-      <c r="H180">
-        <v>84</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="G180"/>
+      <c r="H180"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>count</t>
@@ -27714,37 +28295,33 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>who-dg-remarks-bdbv-2026-05-22</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K180"/>
       <c r="L180" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026</t>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>40367f2982e766cd8d12f4f223e420d6c4739f4ed1345c8584541619ec061495</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="Q180" t="inlineStr">
@@ -27754,100 +28331,1056 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>CC-BY-NC-SA-3.0-IGO</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S180"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
+          <t>source:cdc-current-situation-2026-05-23:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F181">
+        <v>88</v>
+      </c>
+      <c r="G181"/>
+      <c r="H181"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K181"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S181"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F182">
+        <v>5</v>
+      </c>
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K182"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S182"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183"/>
+      <c r="H183"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K183"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S183"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F184">
+        <v>746</v>
+      </c>
+      <c r="G184"/>
+      <c r="H184"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K184"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S184"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F185">
+        <v>746</v>
+      </c>
+      <c r="G185"/>
+      <c r="H185"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K185"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S185"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F186">
+        <v>9</v>
+      </c>
+      <c r="G186"/>
+      <c r="H186"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K186"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F187">
+        <v>176</v>
+      </c>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K187"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F188">
+        <v>176</v>
+      </c>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K188"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S188"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K189"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S189"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-23:new_confirmed_cases_uganda</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F190">
+        <v>3</v>
+      </c>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K190"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S190"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D191"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-05-23T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F191">
+        <v>746</v>
+      </c>
+      <c r="G191">
+        <v>395</v>
+      </c>
+      <c r="H191">
+        <v>746</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S191"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D192"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-05-23T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F192">
+        <v>88</v>
+      </c>
+      <c r="G192">
+        <v>10</v>
+      </c>
+      <c r="H192">
+        <v>88</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C193" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D181"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>2026-05-22T23:59:59Z</t>
-        </is>
-      </c>
-      <c r="F181">
+      <c r="D193"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-05-23T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F193">
+        <v>176</v>
+      </c>
+      <c r="G193">
+        <v>106</v>
+      </c>
+      <c r="H193">
         <v>177</v>
       </c>
-      <c r="G181">
-        <v>106</v>
-      </c>
-      <c r="H181">
-        <v>177</v>
-      </c>
-      <c r="I181" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>who-dg-remarks-bdbv-2026-05-22</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21</t>
-        </is>
-      </c>
-      <c r="L181" t="inlineStr">
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
         <is>
           <t>PUBLIC-SOURCE-AUDIT</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr">
+      <c r="N193" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>40367f2982e766cd8d12f4f223e420d6c4739f4ed1345c8584541619ec061495</t>
-        </is>
-      </c>
-      <c r="Q181" t="inlineStr">
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
         <is>
           <t>public_bytes</t>
         </is>
       </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>CC-BY-NC-SA-3.0-IGO</t>
-        </is>
-      </c>
-      <c r="S181"/>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S193"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S181"/>
+  <autoFilter ref="A1:S193"/>
 </worksheet>
 </file>
 
@@ -36959,8 +38492,620 @@
       </c>
       <c r="K178"/>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_confirmed</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D179">
+        <v>88</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K179"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D180">
+        <v>83</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K180"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D181">
+        <v>88</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K181"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D182">
+        <v>5</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K182"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K183"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:new_confirmed_cases_uganda</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D184">
+        <v>3</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K184"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D185">
+        <v>9</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K185"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D186">
+        <v>176</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D187">
+        <v>176</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D188">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K188"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D189">
+        <v>746</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K189"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D190">
+        <v>746</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K190"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K178"/>
+  <autoFilter ref="A1:K190"/>
 </worksheet>
 </file>
 
@@ -38284,7 +40429,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:beni-cod</t>
+          <t>corridor:01:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -38294,33 +40439,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.08539838902854963</v>
+        <v>0.08200892704713533</v>
       </c>
       <c r="F2">
-        <v>0.22642430078072143</v>
+        <v>0.23133172037904387</v>
       </c>
       <c r="G2">
-        <v>0.20127037795088448</v>
+        <v>0.19224680649154585</v>
       </c>
       <c r="H2">
-        <v>0.476037145866491</v>
+        <v>0.48130923946896836</v>
       </c>
       <c r="I2">
-        <v>0.05412438998404342</v>
+        <v>0.053772224744336926</v>
       </c>
       <c r="J2">
-        <v>0.7218144890262123</v>
+        <v>0.7505179739127573</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -38340,7 +40485,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -38369,26 +40514,26 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.0821262620783674</v>
+        <v>0.09073176115266587</v>
       </c>
       <c r="F3">
-        <v>0.22558425018088515</v>
+        <v>0.2234638809118071</v>
       </c>
       <c r="G3">
-        <v>0.19405709539024177</v>
+        <v>0.2112617269468639</v>
       </c>
       <c r="H3">
-        <v>0.47460351322009614</v>
+        <v>0.4679601163839139</v>
       </c>
       <c r="I3">
-        <v>0.05653946496558107</v>
+        <v>0.05444279683836906</v>
       </c>
       <c r="J3">
-        <v>0.7241894630959104</v>
+        <v>0.7258589806643395</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -38408,7 +40553,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -38420,7 +40565,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:kampala-uga</t>
+          <t>corridor:03:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -38430,33 +40575,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08813458303516586</v>
+        <v>0.08561119889466778</v>
       </c>
       <c r="F4">
-        <v>0.22484412054171804</v>
+        <v>0.22176004554817166</v>
       </c>
       <c r="G4">
-        <v>0.20727285688037644</v>
+        <v>0.20013232620824334</v>
       </c>
       <c r="H4">
-        <v>0.473338370753417</v>
+        <v>0.46504340386236126</v>
       </c>
       <c r="I4">
-        <v>0.06229293262009493</v>
+        <v>0.047305248394329626</v>
       </c>
       <c r="J4">
-        <v>0.7362714820566757</v>
+        <v>0.7273888815013723</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -38476,7 +40621,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -38488,7 +40633,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:bundibugyo-uga</t>
+          <t>corridor:04:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -38498,33 +40643,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08305577234329803</v>
+        <v>0.08965956893852142</v>
       </c>
       <c r="F5">
-        <v>0.22073807023408823</v>
+        <v>0.22137061515466477</v>
       </c>
       <c r="G5">
-        <v>0.1961102396146231</v>
+        <v>0.20893910254125775</v>
       </c>
       <c r="H5">
-        <v>0.46628683352121614</v>
+        <v>0.46437526414832964</v>
       </c>
       <c r="I5">
-        <v>0.04852780580872843</v>
+        <v>0.052399160989858806</v>
       </c>
       <c r="J5">
-        <v>0.7211838572724569</v>
+        <v>0.7341199202505713</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -38544,7 +40689,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -38556,7 +40701,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:arua-uga</t>
+          <t>corridor:05:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -38566,33 +40711,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08847568891994764</v>
+        <v>0.07930621278103206</v>
       </c>
       <c r="F6">
-        <v>0.21608273545769563</v>
+        <v>0.21778218088702597</v>
       </c>
       <c r="G6">
-        <v>0.20801919491023863</v>
+        <v>0.1862999889886741</v>
       </c>
       <c r="H6">
-        <v>0.4582231639990091</v>
+        <v>0.4581946240505208</v>
       </c>
       <c r="I6">
-        <v>0.04389900135936553</v>
+        <v>0.04942555665634105</v>
       </c>
       <c r="J6">
-        <v>0.718949897775528</v>
+        <v>0.6940368144191931</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -38612,7 +40757,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -38641,26 +40786,26 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08680475167774804</v>
+        <v>0.08030398782374049</v>
       </c>
       <c r="F7">
-        <v>0.2087903916363404</v>
+        <v>0.21293669407875018</v>
       </c>
       <c r="G7">
-        <v>0.204358897076357</v>
+        <v>0.1884976810866289</v>
       </c>
       <c r="H7">
-        <v>0.4454454025497713</v>
+        <v>0.44978058214750455</v>
       </c>
       <c r="I7">
-        <v>0.04226345114190957</v>
+        <v>0.05948655613109171</v>
       </c>
       <c r="J7">
-        <v>0.7078672467712642</v>
+        <v>0.7008370348305115</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -38680,7 +40825,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -38692,7 +40837,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:bunia:kasese-uga</t>
+          <t>corridor:07:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -38702,33 +40847,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.04238364446489487</v>
+        <v>0.043126410860172215</v>
       </c>
       <c r="F8">
-        <v>0.12011425165075501</v>
+        <v>0.1223867538035171</v>
       </c>
       <c r="G8">
-        <v>0.10329631440624168</v>
+        <v>0.10415994692106009</v>
       </c>
       <c r="H8">
-        <v>0.2754130404382688</v>
+        <v>0.278001397537348</v>
       </c>
       <c r="I8">
-        <v>0.028004222412679403</v>
+        <v>0.02384393205347049</v>
       </c>
       <c r="J8">
-        <v>0.5026886793665561</v>
+        <v>0.4522298484507357</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -38748,7 +40893,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -38760,7 +40905,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:kampala-uga</t>
+          <t>corridor:08:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -38770,33 +40915,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04500039057058239</v>
+        <v>0.03942345667630251</v>
       </c>
       <c r="F9">
-        <v>0.11863825400282077</v>
+        <v>0.11196397554917834</v>
       </c>
       <c r="G9">
-        <v>0.10945251299894387</v>
+        <v>0.09548507505855064</v>
       </c>
       <c r="H9">
-        <v>0.2723490995193288</v>
+        <v>0.25641649420715795</v>
       </c>
       <c r="I9">
-        <v>0.02501947331277617</v>
+        <v>0.02390916867239624</v>
       </c>
       <c r="J9">
-        <v>0.4366338998586055</v>
+        <v>0.44162866614763796</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -38816,7 +40961,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -38828,7 +40973,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:nebbi-uga</t>
+          <t>corridor:09:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -38838,33 +40983,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.042473868413865606</v>
+        <v>0.04202315052143141</v>
       </c>
       <c r="F10">
-        <v>0.11627322152020797</v>
+        <v>0.11138026974825257</v>
       </c>
       <c r="G10">
-        <v>0.10350922727972309</v>
+        <v>0.10158065236044309</v>
       </c>
       <c r="H10">
-        <v>0.26742322523023654</v>
+        <v>0.2551963318474184</v>
       </c>
       <c r="I10">
-        <v>0.02989188103798864</v>
+        <v>0.028293248051654254</v>
       </c>
       <c r="J10">
-        <v>0.4719911545503789</v>
+        <v>0.47040250224193386</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -38884,7 +41029,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -38913,26 +41058,26 @@
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.04096994019714029</v>
+        <v>0.03846581360295262</v>
       </c>
       <c r="F11">
-        <v>0.1142600998146506</v>
+        <v>0.10908382568535815</v>
       </c>
       <c r="G11">
-        <v>0.09996014299934658</v>
+        <v>0.09323346947609981</v>
       </c>
       <c r="H11">
-        <v>0.2632147708830122</v>
+        <v>0.250384634775751</v>
       </c>
       <c r="I11">
-        <v>0.028145554031523325</v>
+        <v>0.026991287216266743</v>
       </c>
       <c r="J11">
-        <v>0.5089730206686419</v>
+        <v>0.44466813809985917</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -38952,7 +41097,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -38964,7 +41109,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:kasese-uga</t>
+          <t>corridor:11:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -38974,33 +41119,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.040074864962603624</v>
+        <v>0.04041524745754471</v>
       </c>
       <c r="F12">
-        <v>0.11415438880323941</v>
+        <v>0.10894918908127146</v>
       </c>
       <c r="G12">
-        <v>0.09784384776705185</v>
+        <v>0.09781348907649148</v>
       </c>
       <c r="H12">
-        <v>0.26299226536960596</v>
+        <v>0.2501020107590719</v>
       </c>
       <c r="I12">
-        <v>0.027453412611545797</v>
+        <v>0.024679096234898047</v>
       </c>
       <c r="J12">
-        <v>0.4460445382899133</v>
+        <v>0.46678405365895886</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -39020,7 +41165,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -39032,43 +41177,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:mongbwalu:nebbi-uga</t>
+          <t>corridor:12:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.041471500162336694</v>
+        <v>0.04019611700549866</v>
       </c>
       <c r="F13">
-        <v>0.11336975383479614</v>
+        <v>0.10812598156102118</v>
       </c>
       <c r="G13">
-        <v>0.10114470494542041</v>
+        <v>0.09729907368089252</v>
       </c>
       <c r="H13">
-        <v>0.26134885702481303</v>
+        <v>0.24837217550661125</v>
       </c>
       <c r="I13">
-        <v>0.025440832231093672</v>
+        <v>0.01923753856147162</v>
       </c>
       <c r="J13">
-        <v>0.44650267634748897</v>
+        <v>0.44227089655366103</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -39088,7 +41233,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -39100,43 +41245,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:bunia:bundibugyo-uga</t>
+          <t>corridor:13:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.04356093534951472</v>
+        <v>0.040819990834027126</v>
       </c>
       <c r="F14">
-        <v>0.11313064187004729</v>
+        <v>0.10618433430550114</v>
       </c>
       <c r="G14">
-        <v>0.10606888762431566</v>
+        <v>0.09876265362816536</v>
       </c>
       <c r="H14">
-        <v>0.26084727690825166</v>
+        <v>0.2442825392959079</v>
       </c>
       <c r="I14">
-        <v>0.03381110525138648</v>
+        <v>0.020678655931406387</v>
       </c>
       <c r="J14">
-        <v>0.46837249782426205</v>
+        <v>0.4596848493726443</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -39156,7 +41301,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -39168,7 +41313,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:bunia:arua-uga</t>
+          <t>corridor:14:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -39178,33 +41323,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.043179268635071766</v>
+        <v>0.04472132043254323</v>
       </c>
       <c r="F15">
-        <v>0.11286239709017581</v>
+        <v>0.10504297781519889</v>
       </c>
       <c r="G15">
-        <v>0.1051709863333802</v>
+        <v>0.10788098545533736</v>
       </c>
       <c r="H15">
-        <v>0.2602843259701885</v>
+        <v>0.24187270316516957</v>
       </c>
       <c r="I15">
-        <v>0.028248011537639343</v>
+        <v>0.02260695551444377</v>
       </c>
       <c r="J15">
-        <v>0.47824776317758266</v>
+        <v>0.4282924026162399</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -39224,7 +41369,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -39236,7 +41381,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:beni-cod</t>
+          <t>corridor:15:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -39246,33 +41391,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.04119344208767217</v>
+        <v>0.03779941060386105</v>
       </c>
       <c r="F16">
-        <v>0.10893365284868425</v>
+        <v>0.10451891208285768</v>
       </c>
       <c r="G16">
-        <v>0.10048810790189999</v>
+        <v>0.09166463393260285</v>
       </c>
       <c r="H16">
-        <v>0.2520093946270401</v>
+        <v>0.2407645390707007</v>
       </c>
       <c r="I16">
-        <v>0.02509821317295613</v>
+        <v>0.027657720160362238</v>
       </c>
       <c r="J16">
-        <v>0.456384103276426</v>
+        <v>0.4396111744978209</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -39292,7 +41437,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -39304,7 +41449,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:kampala-uga</t>
+          <t>corridor:16:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -39314,33 +41459,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.03603453626393158</v>
+        <v>0.04170004663803706</v>
       </c>
       <c r="F17">
-        <v>0.1082987541985887</v>
+        <v>0.10372098668085056</v>
       </c>
       <c r="G17">
-        <v>0.08825372146141094</v>
+        <v>0.1008243915792412</v>
       </c>
       <c r="H17">
-        <v>0.25066694233201703</v>
+        <v>0.2390754226533218</v>
       </c>
       <c r="I17">
-        <v>0.027542830545210777</v>
+        <v>0.028925700788658745</v>
       </c>
       <c r="J17">
-        <v>0.41039228210192663</v>
+        <v>0.4110297404446275</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -39360,7 +41505,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -39389,26 +41534,26 @@
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.04044853715904337</v>
+        <v>0.035186585343488896</v>
       </c>
       <c r="F18">
-        <v>0.10520173667204546</v>
+        <v>0.1022202018711377</v>
       </c>
       <c r="G18">
-        <v>0.09872770905437492</v>
+        <v>0.08549785806756499</v>
       </c>
       <c r="H18">
-        <v>0.24409761287393744</v>
+        <v>0.23589234541472318</v>
       </c>
       <c r="I18">
-        <v>0.024008489013536718</v>
+        <v>0.027502933564814515</v>
       </c>
       <c r="J18">
-        <v>0.42196522137895376</v>
+        <v>0.40677152882419465</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -39428,7 +41573,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -39440,7 +41585,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:18:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -39450,33 +41595,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.0402235304890759</v>
+        <v>0.03874391914011116</v>
       </c>
       <c r="F19">
-        <v>0.10478034872618125</v>
+        <v>0.09932753400748234</v>
       </c>
       <c r="G19">
-        <v>0.09819556420608525</v>
+        <v>0.0938876818934965</v>
       </c>
       <c r="H19">
-        <v>0.24320106612811979</v>
+        <v>0.22973469142772449</v>
       </c>
       <c r="I19">
-        <v>0.018753223760813016</v>
+        <v>0.02713466345582947</v>
       </c>
       <c r="J19">
-        <v>0.4477241771081618</v>
+        <v>0.43207387785922474</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -39496,7 +41641,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -39508,7 +41653,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:nebbi-uga</t>
+          <t>corridor:19:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -39518,33 +41663,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.030583140837762535</v>
+        <v>0.03299388535147604</v>
       </c>
       <c r="F20">
-        <v>0.08973657190634649</v>
+        <v>0.08738286997481087</v>
       </c>
       <c r="G20">
-        <v>0.07521727078374582</v>
+        <v>0.08030326285925304</v>
       </c>
       <c r="H20">
-        <v>0.21077425417464818</v>
+        <v>0.2039935043660834</v>
       </c>
       <c r="I20">
-        <v>0.01751901230973764</v>
+        <v>0.019930168144148393</v>
       </c>
       <c r="J20">
-        <v>0.3743964444182536</v>
+        <v>0.3775284009544754</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -39564,7 +41709,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -39576,7 +41721,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:arua-uga</t>
+          <t>corridor:20:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -39586,33 +41731,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.032833064106451065</v>
+        <v>0.03392819706306785</v>
       </c>
       <c r="F21">
-        <v>0.08533627997506796</v>
+        <v>0.08484940586882139</v>
       </c>
       <c r="G21">
-        <v>0.08061125367267646</v>
+        <v>0.0825188916401238</v>
       </c>
       <c r="H21">
-        <v>0.2011341579753311</v>
+        <v>0.19846854926794583</v>
       </c>
       <c r="I21">
-        <v>0.02838338555980496</v>
+        <v>0.024490234067551103</v>
       </c>
       <c r="J21">
-        <v>0.37156747030742865</v>
+        <v>0.37749315707435055</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -39632,7 +41777,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -39644,7 +41789,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:kampala-uga</t>
+          <t>corridor:21:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -39654,33 +41799,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.029276256890022806</v>
+        <v>0.03125577174100408</v>
       </c>
       <c r="F22">
-        <v>0.08478520402375272</v>
+        <v>0.08348454522926196</v>
       </c>
       <c r="G22">
-        <v>0.07207538535893415</v>
+        <v>0.0761732305165149</v>
       </c>
       <c r="H22">
-        <v>0.19992177381815532</v>
+        <v>0.19548267507850767</v>
       </c>
       <c r="I22">
-        <v>0.018530855269198322</v>
+        <v>0.02440925206055355</v>
       </c>
       <c r="J22">
-        <v>0.3596749707873651</v>
+        <v>0.37594067840426554</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -39700,7 +41845,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -39712,7 +41857,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:beni-cod</t>
+          <t>corridor:22:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -39722,33 +41867,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.03145006823450974</v>
+        <v>0.031478646822295314</v>
       </c>
       <c r="F23">
-        <v>0.08460630507878228</v>
+        <v>0.08284362872862142</v>
       </c>
       <c r="G23">
-        <v>0.07729777314974384</v>
+        <v>0.07670344805404702</v>
       </c>
       <c r="H23">
-        <v>0.19952810079480182</v>
+        <v>0.1940782082884187</v>
       </c>
       <c r="I23">
-        <v>0.02074362313134692</v>
+        <v>0.02186039936076743</v>
       </c>
       <c r="J23">
-        <v>0.3433839717413068</v>
+        <v>0.36475291410219285</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -39768,7 +41913,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -39780,7 +41925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:bundibugyo-uga</t>
+          <t>corridor:23:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -39790,33 +41935,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.030366451369633868</v>
+        <v>0.029994277699168237</v>
       </c>
       <c r="F24">
-        <v>0.08263726910717964</v>
+        <v>0.0826132813539486</v>
       </c>
       <c r="G24">
-        <v>0.0746967777696598</v>
+        <v>0.07316870543259008</v>
       </c>
       <c r="H24">
-        <v>0.19518622147279202</v>
+        <v>0.19357307850580524</v>
       </c>
       <c r="I24">
-        <v>0.016320747971702392</v>
+        <v>0.016047833475468353</v>
       </c>
       <c r="J24">
-        <v>0.35506099747291225</v>
+        <v>0.3573780111640004</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -39836,7 +41981,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -39848,7 +41993,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:kasese-uga</t>
+          <t>corridor:24:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -39858,33 +42003,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.031593360744318705</v>
+        <v>0.028661907391696856</v>
       </c>
       <c r="F25">
-        <v>0.0811395278180646</v>
+        <v>0.08085785766740855</v>
       </c>
       <c r="G25">
-        <v>0.07764153585619163</v>
+        <v>0.06998902920795538</v>
       </c>
       <c r="H25">
-        <v>0.191874053164521</v>
+        <v>0.18971739841881297</v>
       </c>
       <c r="I25">
-        <v>0.02204520157749978</v>
+        <v>0.018016370547401035</v>
       </c>
       <c r="J25">
-        <v>0.34674877557323863</v>
+        <v>0.36065493954245237</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -39904,7 +42049,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -39916,7 +42061,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:kasese-uga</t>
+          <t>corridor:25:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -39926,33 +42071,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.0057393584368175266</v>
+        <v>0.005793429794588911</v>
       </c>
       <c r="F26">
-        <v>0.016740083649196102</v>
+        <v>0.01702984566490226</v>
       </c>
       <c r="G26">
-        <v>0.014386245888481364</v>
+        <v>0.01439258175594163</v>
       </c>
       <c r="H26">
-        <v>0.041610179483576815</v>
+        <v>0.041951574982737355</v>
       </c>
       <c r="I26">
-        <v>0.003468379684840545</v>
+        <v>0.0038181048856288867</v>
       </c>
       <c r="J26">
-        <v>0.08331918839224162</v>
+        <v>0.08616420003025087</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -39972,7 +42117,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -39984,7 +42129,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:nebbi-uga</t>
+          <t>corridor:26:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -39994,33 +42139,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.0053667247066627455</v>
+        <v>0.005897051963327515</v>
       </c>
       <c r="F27">
-        <v>0.016461822057475456</v>
+        <v>0.016454298957175345</v>
       </c>
       <c r="G27">
-        <v>0.013456019316708007</v>
+        <v>0.01464887215333438</v>
       </c>
       <c r="H27">
-        <v>0.0409272311597679</v>
+        <v>0.04055132576639631</v>
       </c>
       <c r="I27">
-        <v>0.0038806330685029395</v>
+        <v>0.0035690102911354387</v>
       </c>
       <c r="J27">
-        <v>0.0772420311382369</v>
+        <v>0.08080632138202076</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -40040,7 +42185,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -40052,7 +42197,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:kampala-uga</t>
+          <t>corridor:27:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -40062,33 +42207,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.006619836455232481</v>
+        <v>0.006239312368845673</v>
       </c>
       <c r="F28">
-        <v>0.016450121107481175</v>
+        <v>0.01619803151236343</v>
       </c>
       <c r="G28">
-        <v>0.01658213971317163</v>
+        <v>0.015495105961945144</v>
       </c>
       <c r="H28">
-        <v>0.040898513025068084</v>
+        <v>0.039927464536473806</v>
       </c>
       <c r="I28">
-        <v>0.004096712590215834</v>
+        <v>0.003405178314087784</v>
       </c>
       <c r="J28">
-        <v>0.08704799776081466</v>
+        <v>0.07935673326585045</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -40108,7 +42253,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -40120,7 +42265,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:bundibugyo-uga</t>
+          <t>corridor:28:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -40130,33 +42275,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.005493025744772756</v>
+        <v>0.006392865452645141</v>
       </c>
       <c r="F29">
-        <v>0.015756368974301133</v>
+        <v>0.016120155850815304</v>
       </c>
       <c r="G29">
-        <v>0.013771371670930815</v>
+        <v>0.01587462279882418</v>
       </c>
       <c r="H29">
-        <v>0.03919446176318819</v>
+        <v>0.03973783345894116</v>
       </c>
       <c r="I29">
-        <v>0.003604612027771742</v>
+        <v>0.0032650126802971193</v>
       </c>
       <c r="J29">
-        <v>0.07631735477746583</v>
+        <v>0.07658764416722781</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -40176,7 +42321,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -40188,7 +42333,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:beni-cod</t>
+          <t>corridor:29:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -40198,33 +42343,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.005495345875503099</v>
+        <v>0.005897977372847696</v>
       </c>
       <c r="F30">
-        <v>0.015544953397193945</v>
+        <v>0.016114027975795253</v>
       </c>
       <c r="G30">
-        <v>0.013777164331392477</v>
+        <v>0.014651160795670248</v>
       </c>
       <c r="H30">
-        <v>0.038674802821108994</v>
+        <v>0.039722906756456705</v>
       </c>
       <c r="I30">
-        <v>0.0037213790050935227</v>
+        <v>0.004563029278651646</v>
       </c>
       <c r="J30">
-        <v>0.07622638763375313</v>
+        <v>0.08758262782791992</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -40244,7 +42389,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -40273,26 +42418,26 @@
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005670565669088717</v>
+        <v>0.0053809689229898094</v>
       </c>
       <c r="F31">
-        <v>0.015378992848530199</v>
+        <v>0.014969127663845894</v>
       </c>
       <c r="G31">
-        <v>0.014214549452986447</v>
+        <v>0.013372039811872988</v>
       </c>
       <c r="H31">
-        <v>0.038266753412149135</v>
+        <v>0.036932402731466474</v>
       </c>
       <c r="I31">
-        <v>0.003970495392727736</v>
+        <v>0.0043470653458970695</v>
       </c>
       <c r="J31">
-        <v>0.07850105606809085</v>
+        <v>0.0819411234458965</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -40312,7 +42457,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -40324,12 +42469,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:goma-cod:nebbi-uga</t>
+          <t>corridor:31:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -40341,26 +42486,26 @@
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.0027436828091899346</v>
+        <v>0.0031064099748497886</v>
       </c>
       <c r="F32">
-        <v>0.00873533375885538</v>
+        <v>0.008842744721272167</v>
       </c>
       <c r="G32">
-        <v>0.006892979953544098</v>
+        <v>0.00773278016050985</v>
       </c>
       <c r="H32">
-        <v>0.021846078122278012</v>
+        <v>0.021917803930031482</v>
       </c>
       <c r="I32">
-        <v>0.0016134242755154239</v>
+        <v>0.0012927920382234503</v>
       </c>
       <c r="J32">
-        <v>0.04176027186852471</v>
+        <v>0.043151428768583286</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -40380,7 +42525,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -40392,43 +42537,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:butembo:bundibugyo-uga</t>
+          <t>corridor:32:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.0029938944315932303</v>
+        <v>0.0030137247816908463</v>
       </c>
       <c r="F33">
-        <v>0.008663881396060419</v>
+        <v>0.008455401394654921</v>
       </c>
       <c r="G33">
-        <v>0.007520159271513643</v>
+        <v>0.007502579723034392</v>
       </c>
       <c r="H33">
-        <v>0.02166856235547851</v>
+        <v>0.020963818333134487</v>
       </c>
       <c r="I33">
-        <v>0.0020755917425261425</v>
+        <v>0.001964876026614837</v>
       </c>
       <c r="J33">
-        <v>0.041963898537828885</v>
+        <v>0.04025996291249157</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -40448,7 +42593,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -40460,43 +42605,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:nizi:nebbi-uga</t>
+          <t>corridor:33:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.0031235870800861987</v>
+        <v>0.0028886304443923594</v>
       </c>
       <c r="F34">
-        <v>0.00863633269960798</v>
+        <v>0.008347118481784016</v>
       </c>
       <c r="G34">
-        <v>0.007845152239374736</v>
+        <v>0.00719183460774292</v>
       </c>
       <c r="H34">
-        <v>0.021600111809073674</v>
+        <v>0.020697029082573037</v>
       </c>
       <c r="I34">
-        <v>0.0018541318149204872</v>
+        <v>0.0017626325075392108</v>
       </c>
       <c r="J34">
-        <v>0.04509455775110733</v>
+        <v>0.040846686395662496</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -40516,7 +42661,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -40545,26 +42690,26 @@
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003027409854159613</v>
+        <v>0.003021126031914151</v>
       </c>
       <c r="F35">
-        <v>0.008490671185075183</v>
+        <v>0.008312163807679601</v>
       </c>
       <c r="G35">
-        <v>0.007604150842414892</v>
+        <v>0.0075209637361464965</v>
       </c>
       <c r="H35">
-        <v>0.021238161017459456</v>
+        <v>0.02061089733019217</v>
       </c>
       <c r="I35">
-        <v>0.0018151085807035256</v>
+        <v>0.001965199157311942</v>
       </c>
       <c r="J35">
-        <v>0.04582513211088644</v>
+        <v>0.04232624078531671</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -40584,7 +42729,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -40596,43 +42741,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:nizi:kasese-uga</t>
+          <t>corridor:35:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.0027869858927428715</v>
+        <v>0.0029885689228487944</v>
       </c>
       <c r="F36">
-        <v>0.008451095942588277</v>
+        <v>0.008309165031427646</v>
       </c>
       <c r="G36">
-        <v>0.00700153970374881</v>
+        <v>0.0074400943892386495</v>
       </c>
       <c r="H36">
-        <v>0.02113980658881834</v>
+        <v>0.020603508791962988</v>
       </c>
       <c r="I36">
-        <v>0.0016600024239827233</v>
+        <v>0.0015140627043773254</v>
       </c>
       <c r="J36">
-        <v>0.04205406691740638</v>
+        <v>0.039636236358234156</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -40652,7 +42797,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -40664,43 +42809,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:bambu:beni-cod</t>
+          <t>corridor:36:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.0026317436565108654</v>
+        <v>0.0028968958480735663</v>
       </c>
       <c r="F37">
-        <v>0.00844216259540484</v>
+        <v>0.008302699189387669</v>
       </c>
       <c r="G37">
-        <v>0.006612313781045376</v>
+        <v>0.007212368681008802</v>
       </c>
       <c r="H37">
-        <v>0.02111760415129607</v>
+        <v>0.02058757493019797</v>
       </c>
       <c r="I37">
-        <v>0.0015861146536750555</v>
+        <v>0.0014728301522307502</v>
       </c>
       <c r="J37">
-        <v>0.04132064225031468</v>
+        <v>0.040142399138471466</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -40720,7 +42865,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -40732,43 +42877,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:nizi:arua-uga</t>
+          <t>corridor:37:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D38">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.00294729710082145</v>
+        <v>0.0027436360542250626</v>
       </c>
       <c r="F38">
-        <v>0.00835133384839895</v>
+        <v>0.008291615601552393</v>
       </c>
       <c r="G38">
-        <v>0.007403376586432198</v>
+        <v>0.006831583025491139</v>
       </c>
       <c r="H38">
-        <v>0.02089184582646747</v>
+        <v>0.020560263716459554</v>
       </c>
       <c r="I38">
-        <v>0.002219764303862684</v>
+        <v>0.001809788062056189</v>
       </c>
       <c r="J38">
-        <v>0.03858159441831867</v>
+        <v>0.04035120838517614</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -40788,7 +42933,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -40800,43 +42945,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:goma-cod:bundibugyo-uga</t>
+          <t>corridor:38:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.0028895607520507682</v>
+        <v>0.0028878037106492283</v>
       </c>
       <c r="F39">
-        <v>0.008300607192519821</v>
+        <v>0.00826700300096575</v>
       </c>
       <c r="G39">
-        <v>0.007258665864579905</v>
+        <v>0.00718978103506368</v>
       </c>
       <c r="H39">
-        <v>0.020765748938251782</v>
+        <v>0.0204996068255012</v>
       </c>
       <c r="I39">
-        <v>0.002248262822267344</v>
+        <v>0.0015583380599284798</v>
       </c>
       <c r="J39">
-        <v>0.041248667983226024</v>
+        <v>0.04029488629595264</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -40856,7 +43001,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -40868,43 +43013,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:bambu:bundibugyo-uga</t>
+          <t>corridor:39:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.0031349254177469033</v>
+        <v>0.0030739891390453022</v>
       </c>
       <c r="F40">
-        <v>0.00829299967038441</v>
+        <v>0.008190495185341068</v>
       </c>
       <c r="G40">
-        <v>0.007873561652010808</v>
+        <v>0.00765226137795097</v>
       </c>
       <c r="H40">
-        <v>0.02074683748722614</v>
+        <v>0.020311061195146723</v>
       </c>
       <c r="I40">
-        <v>0.002576415728148923</v>
+        <v>0.0019126404305481878</v>
       </c>
       <c r="J40">
-        <v>0.04295391038130336</v>
+        <v>0.03892464933729348</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -40924,7 +43069,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -40936,43 +43081,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:bambu:arua-uga</t>
+          <t>corridor:40:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.0028742636925064846</v>
+        <v>0.0030168065956937273</v>
       </c>
       <c r="F41">
-        <v>0.008274386002493334</v>
+        <v>0.008186419166028969</v>
       </c>
       <c r="G41">
-        <v>0.007220323244188032</v>
+        <v>0.0075102348731063695</v>
       </c>
       <c r="H41">
-        <v>0.020700564503302127</v>
+        <v>0.02030101473563603</v>
       </c>
       <c r="I41">
-        <v>0.0020411851795643144</v>
+        <v>0.0019468904654919932</v>
       </c>
       <c r="J41">
-        <v>0.04641903342725424</v>
+        <v>0.040363293600190024</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -40992,7 +43137,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -41004,12 +43149,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:goma-cod:arua-uga</t>
+          <t>corridor:41:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -41021,26 +43166,26 @@
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0029445707785827058</v>
+        <v>0.002768603266617875</v>
       </c>
       <c r="F42">
-        <v>0.008272207664398512</v>
+        <v>0.008162493230156248</v>
       </c>
       <c r="G42">
-        <v>0.007396543737159589</v>
+        <v>0.006893621987128173</v>
       </c>
       <c r="H42">
-        <v>0.020695148708516048</v>
+        <v>0.020242046539878572</v>
       </c>
       <c r="I42">
-        <v>0.002019261706743009</v>
+        <v>0.0015474160854732802</v>
       </c>
       <c r="J42">
-        <v>0.0431277531418619</v>
+        <v>0.03915694943543016</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -41060,7 +43205,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -41072,43 +43217,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:bambu:kasese-uga</t>
+          <t>corridor:42:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.00285973522880012</v>
+        <v>0.0029572181128099673</v>
       </c>
       <c r="F43">
-        <v>0.008263190044858731</v>
+        <v>0.008136926158356317</v>
       </c>
       <c r="G43">
-        <v>0.007183905812210373</v>
+        <v>0.007362219916885793</v>
       </c>
       <c r="H43">
-        <v>0.020672730575142295</v>
+        <v>0.02017903013560457</v>
       </c>
       <c r="I43">
-        <v>0.0016893776786405025</v>
+        <v>0.0014210452648333984</v>
       </c>
       <c r="J43">
-        <v>0.03926543859144994</v>
+        <v>0.03953044137015703</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -41128,7 +43273,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -41140,43 +43285,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:miti-murhesa:kampala-uga</t>
+          <t>corridor:43:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.002775045065728121</v>
+        <v>0.0028588847097371084</v>
       </c>
       <c r="F44">
-        <v>0.008233932499701252</v>
+        <v>0.008121479547922666</v>
       </c>
       <c r="G44">
-        <v>0.006971605466912056</v>
+        <v>0.007117934652822733</v>
       </c>
       <c r="H44">
-        <v>0.020599993620905865</v>
+        <v>0.020140955026916263</v>
       </c>
       <c r="I44">
-        <v>0.0018216290701169593</v>
+        <v>0.0020310862342879017</v>
       </c>
       <c r="J44">
-        <v>0.04368124992878076</v>
+        <v>0.043374936050191125</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -41196,7 +43341,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -41208,43 +43353,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:nebbi-uga</t>
+          <t>corridor:44:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.0030321659036314508</v>
+        <v>0.002966216009741285</v>
       </c>
       <c r="F45">
-        <v>0.008227915922114637</v>
+        <v>0.008071204783386715</v>
       </c>
       <c r="G45">
-        <v>0.007616069410806503</v>
+        <v>0.007384571167953435</v>
       </c>
       <c r="H45">
-        <v>0.020585035396054746</v>
+        <v>0.020017032108961774</v>
       </c>
       <c r="I45">
-        <v>0.0024552972085381624</v>
+        <v>0.0019856633392102835</v>
       </c>
       <c r="J45">
-        <v>0.044318268452865225</v>
+        <v>0.03903230116776946</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -41264,7 +43409,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -41276,12 +43421,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:kilo:kampala-uga</t>
+          <t>corridor:45:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -41293,26 +43438,26 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.0030250937616368156</v>
+        <v>0.002999824043247834</v>
       </c>
       <c r="F46">
-        <v>0.00820515342708758</v>
+        <v>0.008070104040915183</v>
       </c>
       <c r="G46">
-        <v>0.007598346531651978</v>
+        <v>0.007468051852929203</v>
       </c>
       <c r="H46">
-        <v>0.02052844183941352</v>
+        <v>0.020014318893145783</v>
       </c>
       <c r="I46">
-        <v>0.0018012831267253226</v>
+        <v>0.0018391957134823611</v>
       </c>
       <c r="J46">
-        <v>0.04028515937090055</v>
+        <v>0.04222176098200819</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -41332,7 +43477,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -41344,43 +43489,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:kilo:arua-uga</t>
+          <t>corridor:46:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.0026994696159321763</v>
+        <v>0.00302696457253418</v>
       </c>
       <c r="F47">
-        <v>0.008170715006158458</v>
+        <v>0.008061746356337274</v>
       </c>
       <c r="G47">
-        <v>0.006782130513199258</v>
+        <v>0.007535465665797686</v>
       </c>
       <c r="H47">
-        <v>0.020442816987119777</v>
+        <v>0.019993715064261175</v>
       </c>
       <c r="I47">
-        <v>0.0017189946049781496</v>
+        <v>0.0019038903776436523</v>
       </c>
       <c r="J47">
-        <v>0.04160329567109426</v>
+        <v>0.03809161905995875</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -41400,7 +43545,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -41412,43 +43557,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:butembo:arua-uga</t>
+          <t>corridor:47:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002732086250355592</v>
+        <v>0.002711272164641787</v>
       </c>
       <c r="F48">
-        <v>0.008141793321306878</v>
+        <v>0.008003320140437448</v>
       </c>
       <c r="G48">
-        <v>0.0068639062128368344</v>
+        <v>0.006751161363516417</v>
       </c>
       <c r="H48">
-        <v>0.020370901471028602</v>
+        <v>0.019849685301168624</v>
       </c>
       <c r="I48">
-        <v>0.0017362704824194165</v>
+        <v>0.0016687253435851562</v>
       </c>
       <c r="J48">
-        <v>0.039959939555151175</v>
+        <v>0.04165630204345164</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -41468,7 +43613,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -41480,43 +43625,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:butembo:kampala-uga</t>
+          <t>corridor:48:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.002823164055650834</v>
+        <v>0.0028828781654738067</v>
       </c>
       <c r="F49">
-        <v>0.008111592378876958</v>
+        <v>0.007999761114495657</v>
       </c>
       <c r="G49">
-        <v>0.007092233196814013</v>
+        <v>0.007177544340573161</v>
       </c>
       <c r="H49">
-        <v>0.02029580857893648</v>
+        <v>0.01984091087479531</v>
       </c>
       <c r="I49">
-        <v>0.001850133892248271</v>
+        <v>0.001746492912259029</v>
       </c>
       <c r="J49">
-        <v>0.04572242896355314</v>
+        <v>0.04180829543410267</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -41536,7 +43681,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -41548,43 +43693,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:bambu:kampala-uga</t>
+          <t>corridor:49:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0026860371908569713</v>
+        <v>0.0028290030722574744</v>
       </c>
       <c r="F50">
-        <v>0.008099252562074444</v>
+        <v>0.007993877766034052</v>
       </c>
       <c r="G50">
-        <v>0.006748451825865975</v>
+        <v>0.007043694470001555</v>
       </c>
       <c r="H50">
-        <v>0.02026512195018229</v>
+        <v>0.01982640604270372</v>
       </c>
       <c r="I50">
-        <v>0.001666196341412643</v>
+        <v>0.0016184962560191808</v>
       </c>
       <c r="J50">
-        <v>0.03789152096404323</v>
+        <v>0.041811123101178745</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -41604,7 +43749,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -41616,43 +43761,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:miti-murhesa:nebbi-uga</t>
+          <t>corridor:50:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D51">
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.0029608989463557334</v>
+        <v>0.002964265235936736</v>
       </c>
       <c r="F51">
-        <v>0.008038314001636154</v>
+        <v>0.007979683324545433</v>
       </c>
       <c r="G51">
-        <v>0.007437466672466003</v>
+        <v>0.007379725373273249</v>
       </c>
       <c r="H51">
-        <v>0.02011358170987787</v>
+        <v>0.01979141256348449</v>
       </c>
       <c r="I51">
-        <v>0.0022794520625497973</v>
+        <v>0.001700272522619467</v>
       </c>
       <c r="J51">
-        <v>0.04032621378711129</v>
+        <v>0.03920759588832881</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -41672,7 +43817,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -41684,12 +43829,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:miti-murhesa:beni-cod</t>
+          <t>corridor:51:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -41701,26 +43846,26 @@
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.003096289889485182</v>
+        <v>0.0027636218791129985</v>
       </c>
       <c r="F52">
-        <v>0.008018364898168179</v>
+        <v>0.007943736755445518</v>
       </c>
       <c r="G52">
-        <v>0.007776754557392379</v>
+        <v>0.006881244331427588</v>
       </c>
       <c r="H52">
-        <v>0.020063970232206574</v>
+        <v>0.01970278797042238</v>
       </c>
       <c r="I52">
-        <v>0.002304299690100667</v>
+        <v>0.0014763767393302513</v>
       </c>
       <c r="J52">
-        <v>0.04278978160782607</v>
+        <v>0.04005225312519262</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -41740,7 +43885,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -41752,43 +43897,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:bambu:nebbi-uga</t>
+          <t>corridor:52:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.0028341674010289863</v>
+        <v>0.002939240277028049</v>
       </c>
       <c r="F53">
-        <v>0.008012536445962837</v>
+        <v>0.007912160672771062</v>
       </c>
       <c r="G53">
-        <v>0.007119814925248685</v>
+        <v>0.007317560988202604</v>
       </c>
       <c r="H53">
-        <v>0.02004947512019084</v>
+        <v>0.019624933508132852</v>
       </c>
       <c r="I53">
-        <v>0.0018103089745989593</v>
+        <v>0.0018917807676148398</v>
       </c>
       <c r="J53">
-        <v>0.04111918231372484</v>
+        <v>0.038940141953057755</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -41808,7 +43953,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -41820,43 +43965,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:kilo:kasese-uga</t>
+          <t>corridor:53:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0026588248347099996</v>
+        <v>0.002896284327627646</v>
       </c>
       <c r="F54">
-        <v>0.007928388693881572</v>
+        <v>0.007898422310050696</v>
       </c>
       <c r="G54">
-        <v>0.006680220142821713</v>
+        <v>0.007210849355384241</v>
       </c>
       <c r="H54">
-        <v>0.019840184571277092</v>
+        <v>0.019591060445456554</v>
       </c>
       <c r="I54">
-        <v>0.0021545264484612832</v>
+        <v>0.002070995524055594</v>
       </c>
       <c r="J54">
-        <v>0.04390670864258929</v>
+        <v>0.03944003878007347</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -41876,7 +44021,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -41888,7 +44033,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:goma-cod:kasese-uga</t>
+          <t>corridor:54:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -41898,33 +44043,33 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0029841955019448696</v>
+        <v>0.00284876075269902</v>
       </c>
       <c r="F55">
-        <v>0.00790344522254427</v>
+        <v>0.007893020209658985</v>
       </c>
       <c r="G55">
-        <v>0.007495852537342473</v>
+        <v>0.007092782818425181</v>
       </c>
       <c r="H55">
-        <v>0.01977814258476257</v>
+        <v>0.019577740869646337</v>
       </c>
       <c r="I55">
-        <v>0.0017588351400808055</v>
+        <v>0.0020058959968129258</v>
       </c>
       <c r="J55">
-        <v>0.04033290657962676</v>
+        <v>0.03794044182437606</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -41944,7 +44089,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -41956,43 +44101,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:butembo:nebbi-uga</t>
+          <t>corridor:55:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.0028005224775816684</v>
+        <v>0.002919518350532113</v>
       </c>
       <c r="F56">
-        <v>0.007870943903884098</v>
+        <v>0.007885781628357735</v>
       </c>
       <c r="G56">
-        <v>0.007035474981415435</v>
+        <v>0.007268568604097025</v>
       </c>
       <c r="H56">
-        <v>0.0196972944427512</v>
+        <v>0.0195598910020858</v>
       </c>
       <c r="I56">
-        <v>0.001889278376975806</v>
+        <v>0.0020982416358770435</v>
       </c>
       <c r="J56">
-        <v>0.042501933885133694</v>
+        <v>0.04103833436051815</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -42012,7 +44157,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -42024,43 +44169,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:butembo:kasese-uga</t>
+          <t>corridor:56:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.0030329578932126733</v>
+        <v>0.0026794581653525884</v>
       </c>
       <c r="F57">
-        <v>0.007865978779818594</v>
+        <v>0.007824052809558862</v>
       </c>
       <c r="G57">
-        <v>0.007618054055158613</v>
+        <v>0.0066721022582374445</v>
       </c>
       <c r="H57">
-        <v>0.019684944330983195</v>
+        <v>0.019407679063902866</v>
       </c>
       <c r="I57">
-        <v>0.0016252554788710823</v>
+        <v>0.0018742235395998118</v>
       </c>
       <c r="J57">
-        <v>0.04025898491068218</v>
+        <v>0.03983832973283268</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -42080,7 +44225,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -42092,43 +44237,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:goma-cod:beni-cod</t>
+          <t>corridor:57:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.0027955849084400908</v>
+        <v>0.0029658127649658528</v>
       </c>
       <c r="F58">
-        <v>0.00785076371218299</v>
+        <v>0.007809572414131216</v>
       </c>
       <c r="G58">
-        <v>0.007023097173016579</v>
+        <v>0.007383568737962282</v>
       </c>
       <c r="H58">
-        <v>0.01964709665194081</v>
+        <v>0.019371970574026537</v>
       </c>
       <c r="I58">
-        <v>0.0018994440133222657</v>
+        <v>0.0018216334903385755</v>
       </c>
       <c r="J58">
-        <v>0.04003332339906995</v>
+        <v>0.03964694132559633</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -42148,7 +44293,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -42160,12 +44305,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:miti-murhesa:arua-uga</t>
+          <t>corridor:58:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -42177,26 +44322,26 @@
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0028633012767765587</v>
+        <v>0.0028161227874957395</v>
       </c>
       <c r="F59">
-        <v>0.007823396708983632</v>
+        <v>0.007799385470735554</v>
       </c>
       <c r="G59">
-        <v>0.007192844503535023</v>
+        <v>0.007011692758622234</v>
       </c>
       <c r="H59">
-        <v>0.01957901663579309</v>
+        <v>0.019346848345025758</v>
       </c>
       <c r="I59">
-        <v>0.0018764490632404735</v>
+        <v>0.0021527480257039766</v>
       </c>
       <c r="J59">
-        <v>0.04023951881386167</v>
+        <v>0.03738999809248955</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -42216,7 +44361,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -42228,43 +44373,43 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:miti-murhesa:kasese-uga</t>
+          <t>corridor:59:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.0030977601531481103</v>
+        <v>0.002874053560650125</v>
       </c>
       <c r="F60">
-        <v>0.007810260313210249</v>
+        <v>0.0077552415891767035</v>
       </c>
       <c r="G60">
-        <v>0.007780438058472006</v>
+        <v>0.007155620843306676</v>
       </c>
       <c r="H60">
-        <v>0.019546336660033442</v>
+        <v>0.019237984603597186</v>
       </c>
       <c r="I60">
-        <v>0.0023083896658769253</v>
+        <v>0.0015960886164875705</v>
       </c>
       <c r="J60">
-        <v>0.039484700857547995</v>
+        <v>0.0397290483148042</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -42284,7 +44429,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -42296,12 +44441,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:60:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -42313,26 +44458,26 @@
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.0027780347632163915</v>
+        <v>0.0029333768169604313</v>
       </c>
       <c r="F61">
-        <v>0.007778692258445824</v>
+        <v>0.007738766942843367</v>
       </c>
       <c r="G61">
-        <v>0.006979100463608723</v>
+        <v>0.007302995550801578</v>
       </c>
       <c r="H61">
-        <v>0.019467800732508006</v>
+        <v>0.019197353961997482</v>
       </c>
       <c r="I61">
-        <v>0.0019957666248500787</v>
+        <v>0.002113826548903264</v>
       </c>
       <c r="J61">
-        <v>0.03675279636279511</v>
+        <v>0.04367258678384024</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -42352,7 +44497,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -42364,43 +44509,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:goma-cod:kampala-uga</t>
+          <t>corridor:61:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.002578472139950938</v>
+        <v>0.0029430467838043872</v>
       </c>
       <c r="F62">
-        <v>0.007602640324713833</v>
+        <v>0.007716591334032796</v>
       </c>
       <c r="G62">
-        <v>0.006478732496557116</v>
+        <v>0.007327016685413357</v>
       </c>
       <c r="H62">
-        <v>0.01902974401822774</v>
+        <v>0.019142661955798917</v>
       </c>
       <c r="I62">
-        <v>0.0016981303091056278</v>
+        <v>0.0019755308676983633</v>
       </c>
       <c r="J62">
-        <v>0.03715448375211206</v>
+        <v>0.039791083586982245</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -42420,7 +44565,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -42432,43 +44577,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:butembo:beni-cod</t>
+          <t>corridor:62:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0028677054045402606</v>
+        <v>0.002796905767992547</v>
       </c>
       <c r="F63">
-        <v>0.00755343701573169</v>
+        <v>0.00767757669112995</v>
       </c>
       <c r="G63">
-        <v>0.0072038843330113345</v>
+        <v>0.006963945541292177</v>
       </c>
       <c r="H63">
-        <v>0.018907293791092183</v>
+        <v>0.019046434992530586</v>
       </c>
       <c r="I63">
-        <v>0.0019159448750681821</v>
+        <v>0.0020588048892707404</v>
       </c>
       <c r="J63">
-        <v>0.03947495433058574</v>
+        <v>0.049283570893681704</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -42488,7 +44633,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -42500,43 +44645,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:nizi:kampala-uga</t>
+          <t>corridor:63:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0027803725155526593</v>
+        <v>0.002881574110656343</v>
       </c>
       <c r="F64">
-        <v>0.007416629890697524</v>
+        <v>0.0076527240222372395</v>
       </c>
       <c r="G64">
-        <v>0.006984961165077602</v>
+        <v>0.00717430459340368</v>
       </c>
       <c r="H64">
-        <v>0.01856678018721797</v>
+        <v>0.018985134000077397</v>
       </c>
       <c r="I64">
-        <v>0.001752041597918447</v>
+        <v>0.0019465263477377952</v>
       </c>
       <c r="J64">
-        <v>0.03819149371078799</v>
+        <v>0.038295269411189395</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -42556,7 +44701,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -42568,43 +44713,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:kilo:beni-cod</t>
+          <t>corridor:64:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D65">
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0027083568299712812</v>
+        <v>0.0029594116020818517</v>
       </c>
       <c r="F65">
-        <v>0.007346307351799836</v>
+        <v>0.007574358536086928</v>
       </c>
       <c r="G65">
-        <v>0.0068044127263834076</v>
+        <v>0.007367668721658921</v>
       </c>
       <c r="H65">
-        <v>0.018391719081932573</v>
+        <v>0.018791827304817404</v>
       </c>
       <c r="I65">
-        <v>0.00167743681393413</v>
+        <v>0.0018921759864096277</v>
       </c>
       <c r="J65">
-        <v>0.040494685523748734</v>
+        <v>0.0362803906851146</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -42624,7 +44769,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -42636,43 +44781,43 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:nizi:beni-cod</t>
+          <t>corridor:65:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.0025947981541197818</v>
+        <v>0.0031623753037089974</v>
       </c>
       <c r="F66">
-        <v>0.007335864959457955</v>
+        <v>0.00756670972052767</v>
       </c>
       <c r="G66">
-        <v>0.006519672721913977</v>
+        <v>0.007871765533029873</v>
       </c>
       <c r="H66">
-        <v>0.018365722184244343</v>
+        <v>0.01877295839047441</v>
       </c>
       <c r="I66">
-        <v>0.0019139228101699324</v>
+        <v>0.0022942651841674185</v>
       </c>
       <c r="J66">
-        <v>0.03764945393988408</v>
+        <v>0.03629645524216742</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -42692,7 +44837,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -42704,7 +44849,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:kilo:bundibugyo-uga</t>
+          <t>corridor:66:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -42714,33 +44859,33 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.002713711296886745</v>
+        <v>0.0028544692621960133</v>
       </c>
       <c r="F67">
-        <v>0.007237843959331636</v>
+        <v>0.0073600577545204215</v>
       </c>
       <c r="G67">
-        <v>0.006817837406037225</v>
+        <v>0.007106965376501684</v>
       </c>
       <c r="H67">
-        <v>0.01812167341112106</v>
+        <v>0.018263086159490488</v>
       </c>
       <c r="I67">
-        <v>0.0017317643377637942</v>
+        <v>0.0015953746275022913</v>
       </c>
       <c r="J67">
-        <v>0.03903413448103293</v>
+        <v>0.03555014814938943</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -42760,7 +44905,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -42898,7 +45043,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -42950,7 +45095,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -43004,7 +45149,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -43058,7 +45203,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -43112,7 +45257,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -43166,7 +45311,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -43220,7 +45365,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -43247,10 +45392,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.3972118933627827</v>
+        <v>0.4007872542276427</v>
       </c>
       <c r="F9">
-        <v>0.4579613449154769</v>
+        <v>0.4611775387681021</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -43274,7 +45419,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -43301,10 +45446,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>3.0311353988934213</v>
+        <v>2.6041684931341673</v>
       </c>
       <c r="F10">
-        <v>12.877083406391343</v>
+        <v>12.098434321451013</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -43328,7 +45473,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -43355,10 +45500,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F11">
-        <v>622</v>
+        <v>609</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -43382,7 +45527,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -43412,7 +45557,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -43436,7 +45581,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L12"/>
@@ -43484,7 +45629,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -43536,7 +45681,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -43562,7 +45707,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.001</v>
+        <v>0.0</v>
       </c>
       <c r="E15"/>
       <c r="F15"/>
@@ -43588,7 +45733,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -43614,7 +45759,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.011</v>
+        <v>0.007</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -43640,7 +45785,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -43666,7 +45811,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.036</v>
+        <v>0.035</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -43692,7 +45837,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -43718,7 +45863,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.952</v>
+        <v>0.958</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -43744,7 +45889,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -43798,7 +45943,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L19"/>
@@ -43848,7 +45993,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L20"/>
@@ -45619,12 +47764,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>The May 22 corridor watchlist uses the official DRC MoH cumulative per-health-zone source-load vector, not the May 22 headline confirmed aggregate; this is source-attribution lag, not missing cases.</t>
+          <t>The current corridor watchlist uses the official DRC MoH cumulative per-health-zone source-load vector, not the current headline confirmed aggregate; this is source-attribution lag, not missing cases.</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 84; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 5 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.4-14.3% lower bounds and 1.2-34.8% upper bounds.</t>
+          <t>headline confirmed total 88; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 9 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.7-21.1% lower bounds and 1.8-48.1% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -45644,7 +47789,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed table exists, keep the 5 cases unallocated and do not derive corridor risks from the 84 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
+          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed table exists, keep the 9 cases unallocated and do not derive corridor risks from the 88 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -45841,7 +47986,54 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bdbv may23 cdc official release</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>The May 23 public snapshot uses the CDC Current Situation page as the current official exact endpoint while retaining WHO 22 May and earlier values as dated conflict/cross-check evidence.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>confirmed total 88 (83 DRC + 5 Uganda), suspected DRC cases 746, suspected DRC deaths 176; CDC also reports nine confirmed DRC deaths and one confirmed Uganda death.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>US CDC. Ebola Disease: Current Situation, 23 May 2026.; World Health Organization. WHO Director-General Member State information session remarks, 22 May 2026.; data/bundibugyo-2026/manifest.json entry cdc-current-situation-2026-05-23.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html; https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Keep CDC May 23 as the publication-state endpoint until a newer accepted primary/regional source is archived and reviewed; keep 216-death media/aggregator signals watch-only pending official confirmation.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I23"/>
+  <autoFilter ref="A1:I24"/>
 </worksheet>
 </file>
--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T23:59:59Z</t>
+          <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
     </row>
@@ -124,7 +124,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -2323,8 +2323,66 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ministere de la Sante Publique, Hygiene et Prevoyance sociale, Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://administration.sante.gouv.cd/graphql</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-24T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-24T23:53:59Z</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>f3d5149176d77cbf28d15c79bb7449b1a516c6b855ffe28d51b2adaef0f4bff5</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>private_restricted_bytes</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>publisher-terms-not-confirmed</t>
+        </is>
+      </c>
+      <c r="J37"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L36"/>
+  <autoFilter ref="A1:L37"/>
 </worksheet>
 </file>
 
@@ -4266,7 +4324,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-024</t>
+          <t>BDBV-CLAIM-025</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -4367,7 +4425,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-024</t>
+          <t>BDBV-CLAIM-025</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -4468,7 +4526,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-024</t>
+          <t>BDBV-CLAIM-025</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -9518,12 +9576,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-23T23:59:59Z</t>
+          <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
       <c r="E2"/>
@@ -9557,7 +9615,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="D3"/>
@@ -14061,8 +14119,129 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>source_data_report_date:drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D110"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="F110"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>source_publication_date:drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D111"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="F111"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-05-24T23:53:59Z</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
+        </is>
+      </c>
+      <c r="F112"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I109"/>
+  <autoFilter ref="A1:I112"/>
 </worksheet>
 </file>
 
@@ -29145,17 +29324,17 @@
       <c r="D191"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-05-23T23:59:59Z</t>
+          <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
       <c r="F191">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="G191">
         <v>395</v>
       </c>
       <c r="H191">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -29164,7 +29343,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>who-dg-remarks-bdbv-2026-05-22</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -29189,12 +29368,12 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>40367f2982e766cd8d12f4f223e420d6c4739f4ed1345c8584541619ec061495</t>
         </is>
       </c>
       <c r="Q191" t="inlineStr">
@@ -29204,7 +29383,7 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-NC-SA-3.0-IGO</t>
         </is>
       </c>
       <c r="S191"/>
@@ -29228,7 +29407,7 @@
       <c r="D192"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-05-23T23:59:59Z</t>
+          <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
       <c r="F192">
@@ -29315,11 +29494,11 @@
       <c r="D193"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-05-23T23:59:59Z</t>
+          <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
       <c r="F193">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G193">
         <v>106</v>
@@ -29334,7 +29513,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>who-dg-remarks-bdbv-2026-05-22</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -29359,12 +29538,12 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.who.int/news-room/speeches/item/who-director-general-s-opening-remarks-at-the-member-state-information-session-on-outbreaks-of-ebola-and-hantavirus-22-may-2026</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>40367f2982e766cd8d12f4f223e420d6c4739f4ed1345c8584541619ec061495</t>
         </is>
       </c>
       <c r="Q193" t="inlineStr">
@@ -29374,7 +29553,7 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-NC-SA-3.0-IGO</t>
         </is>
       </c>
       <c r="S193"/>
@@ -40429,7 +40608,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:arua-uga</t>
+          <t>corridor:01:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -40439,33 +40618,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.08200892704713533</v>
+        <v>0.08821137528895254</v>
       </c>
       <c r="F2">
-        <v>0.23133172037904387</v>
+        <v>0.22303064012958748</v>
       </c>
       <c r="G2">
-        <v>0.19224680649154585</v>
+        <v>0.20708736075627046</v>
       </c>
       <c r="H2">
-        <v>0.48130923946896836</v>
+        <v>0.46958460345401354</v>
       </c>
       <c r="I2">
-        <v>0.053772224744336926</v>
+        <v>0.04902386658584786</v>
       </c>
       <c r="J2">
-        <v>0.7505179739127573</v>
+        <v>0.7287947804941787</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -40497,7 +40676,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:nebbi-uga</t>
+          <t>corridor:02:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -40507,33 +40686,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.09073176115266587</v>
+        <v>0.08379468993464778</v>
       </c>
       <c r="F3">
-        <v>0.2234638809118071</v>
+        <v>0.21991047250618512</v>
       </c>
       <c r="G3">
-        <v>0.2112617269468639</v>
+        <v>0.1974008464379203</v>
       </c>
       <c r="H3">
-        <v>0.4679601163839139</v>
+        <v>0.4642163934402524</v>
       </c>
       <c r="I3">
-        <v>0.05444279683836906</v>
+        <v>0.053885607469128294</v>
       </c>
       <c r="J3">
-        <v>0.7258589806643395</v>
+        <v>0.7321362714426363</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -40565,7 +40744,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:bundibugyo-uga</t>
+          <t>corridor:03:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -40575,33 +40754,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08561119889466778</v>
+        <v>0.0839815096390503</v>
       </c>
       <c r="F4">
-        <v>0.22176004554817166</v>
+        <v>0.2145009745062685</v>
       </c>
       <c r="G4">
-        <v>0.20013232620824334</v>
+        <v>0.1978119698305737</v>
       </c>
       <c r="H4">
-        <v>0.46504340386236126</v>
+        <v>0.4548317738545009</v>
       </c>
       <c r="I4">
-        <v>0.047305248394329626</v>
+        <v>0.05127631522501777</v>
       </c>
       <c r="J4">
-        <v>0.7273888815013723</v>
+        <v>0.7081902165953425</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -40633,7 +40812,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:beni-cod</t>
+          <t>corridor:04:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -40643,33 +40822,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08965956893852142</v>
+        <v>0.08494514057794225</v>
       </c>
       <c r="F5">
-        <v>0.22137061515466477</v>
+        <v>0.21235423218408028</v>
       </c>
       <c r="G5">
-        <v>0.20893910254125775</v>
+        <v>0.1999306534527504</v>
       </c>
       <c r="H5">
-        <v>0.46437526414832964</v>
+        <v>0.4510801786497356</v>
       </c>
       <c r="I5">
-        <v>0.052399160989858806</v>
+        <v>0.05148499356098289</v>
       </c>
       <c r="J5">
-        <v>0.7341199202505713</v>
+        <v>0.7157785863906272</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -40701,7 +40880,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:kampala-uga</t>
+          <t>corridor:05:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -40711,33 +40890,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.07930621278103206</v>
+        <v>0.08478074397061586</v>
       </c>
       <c r="F6">
-        <v>0.21778218088702597</v>
+        <v>0.207375477491343</v>
       </c>
       <c r="G6">
-        <v>0.1862999889886741</v>
+        <v>0.19956967743719028</v>
       </c>
       <c r="H6">
-        <v>0.4581946240505208</v>
+        <v>0.44231999358257157</v>
       </c>
       <c r="I6">
-        <v>0.04942555665634105</v>
+        <v>0.06353899831251818</v>
       </c>
       <c r="J6">
-        <v>0.6940368144191931</v>
+        <v>0.7043971359810433</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -40786,26 +40965,26 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08030398782374049</v>
+        <v>0.08325361349716673</v>
       </c>
       <c r="F7">
-        <v>0.21293669407875018</v>
+        <v>0.1998336728649868</v>
       </c>
       <c r="G7">
-        <v>0.1884976810866289</v>
+        <v>0.19620947023756097</v>
       </c>
       <c r="H7">
-        <v>0.44978058214750455</v>
+        <v>0.42888994329056224</v>
       </c>
       <c r="I7">
-        <v>0.05948655613109171</v>
+        <v>0.06493900025049605</v>
       </c>
       <c r="J7">
-        <v>0.7008370348305115</v>
+        <v>0.6577801207519675</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -40837,7 +41016,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:bunia:arua-uga</t>
+          <t>corridor:07:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -40847,33 +41026,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.043126410860172215</v>
+        <v>0.04518668590906155</v>
       </c>
       <c r="F8">
-        <v>0.1223867538035171</v>
+        <v>0.1196025189042455</v>
       </c>
       <c r="G8">
-        <v>0.10415994692106009</v>
+        <v>0.10969096522136429</v>
       </c>
       <c r="H8">
-        <v>0.278001397537348</v>
+        <v>0.27390511702374754</v>
       </c>
       <c r="I8">
-        <v>0.02384393205347049</v>
+        <v>0.028519411921781153</v>
       </c>
       <c r="J8">
-        <v>0.4522298484507357</v>
+        <v>0.47620777811346965</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -40905,7 +41084,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:kasese-uga</t>
+          <t>corridor:08:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -40915,33 +41094,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.03942345667630251</v>
+        <v>0.04272194828018169</v>
       </c>
       <c r="F9">
-        <v>0.11196397554917834</v>
+        <v>0.11698145631419321</v>
       </c>
       <c r="G9">
-        <v>0.09548507505855064</v>
+        <v>0.10390491590127435</v>
       </c>
       <c r="H9">
-        <v>0.25641649420715795</v>
+        <v>0.26846117499318517</v>
       </c>
       <c r="I9">
-        <v>0.02390916867239624</v>
+        <v>0.036396743130945</v>
       </c>
       <c r="J9">
-        <v>0.44162866614763796</v>
+        <v>0.48307011246840226</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -40973,12 +41152,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:kampala-uga</t>
+          <t>corridor:09:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -40990,26 +41169,26 @@
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04202315052143141</v>
+        <v>0.04490334467385315</v>
       </c>
       <c r="F10">
-        <v>0.11138026974825257</v>
+        <v>0.11650060274026874</v>
       </c>
       <c r="G10">
-        <v>0.10158065236044309</v>
+        <v>0.10902687738091718</v>
       </c>
       <c r="H10">
-        <v>0.2551963318474184</v>
+        <v>0.2674597792030441</v>
       </c>
       <c r="I10">
-        <v>0.028293248051654254</v>
+        <v>0.028105747197389272</v>
       </c>
       <c r="J10">
-        <v>0.47040250224193386</v>
+        <v>0.48254317209197545</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -41041,7 +41220,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:beni-cod</t>
+          <t>corridor:10:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -41051,33 +41230,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.03846581360295262</v>
+        <v>0.04266596415746421</v>
       </c>
       <c r="F11">
-        <v>0.10908382568535815</v>
+        <v>0.11566773655391216</v>
       </c>
       <c r="G11">
-        <v>0.09323346947609981</v>
+        <v>0.103773243645609</v>
       </c>
       <c r="H11">
-        <v>0.250384634775751</v>
+        <v>0.26572331467385835</v>
       </c>
       <c r="I11">
-        <v>0.026991287216266743</v>
+        <v>0.030154900882461463</v>
       </c>
       <c r="J11">
-        <v>0.44466813809985917</v>
+        <v>0.47857090928303725</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -41109,43 +41288,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:11:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.04041524745754471</v>
+        <v>0.04134626185720458</v>
       </c>
       <c r="F12">
-        <v>0.10894918908127146</v>
+        <v>0.11536982131263696</v>
       </c>
       <c r="G12">
-        <v>0.09781348907649148</v>
+        <v>0.1006654147151124</v>
       </c>
       <c r="H12">
-        <v>0.2501020107590719</v>
+        <v>0.2651016560931514</v>
       </c>
       <c r="I12">
-        <v>0.024679096234898047</v>
+        <v>0.024157414736271563</v>
       </c>
       <c r="J12">
-        <v>0.46678405365895886</v>
+        <v>0.442217743189379</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -41177,43 +41356,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:bundibugyo-uga</t>
+          <t>corridor:12:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.04019611700549866</v>
+        <v>0.042257015039710716</v>
       </c>
       <c r="F13">
-        <v>0.10812598156102118</v>
+        <v>0.11059749483342382</v>
       </c>
       <c r="G13">
-        <v>0.09729907368089252</v>
+        <v>0.1028109484353942</v>
       </c>
       <c r="H13">
-        <v>0.24837217550661125</v>
+        <v>0.25509913387234384</v>
       </c>
       <c r="I13">
-        <v>0.01923753856147162</v>
+        <v>0.029949093157880583</v>
       </c>
       <c r="J13">
-        <v>0.44227089655366103</v>
+        <v>0.44975839331305956</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -41245,7 +41424,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:beni-cod</t>
+          <t>corridor:13:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -41255,33 +41434,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.040819990834027126</v>
+        <v>0.036835801322681855</v>
       </c>
       <c r="F14">
-        <v>0.10618433430550114</v>
+        <v>0.1084031822966573</v>
       </c>
       <c r="G14">
-        <v>0.09876265362816536</v>
+        <v>0.08999553522869064</v>
       </c>
       <c r="H14">
-        <v>0.2442825392959079</v>
+        <v>0.250472627736926</v>
       </c>
       <c r="I14">
-        <v>0.020678655931406387</v>
+        <v>0.027203361343210414</v>
       </c>
       <c r="J14">
-        <v>0.4596848493726443</v>
+        <v>0.4354015904706045</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -41313,7 +41492,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:bunia:nebbi-uga</t>
+          <t>corridor:14:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -41323,33 +41502,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.04472132043254323</v>
+        <v>0.04255734933972799</v>
       </c>
       <c r="F15">
-        <v>0.10504297781519889</v>
+        <v>0.10802646318829781</v>
       </c>
       <c r="G15">
-        <v>0.10788098545533736</v>
+        <v>0.10351772313795171</v>
       </c>
       <c r="H15">
-        <v>0.24187270316516957</v>
+        <v>0.24967485196493885</v>
       </c>
       <c r="I15">
-        <v>0.02260695551444377</v>
+        <v>0.02764874782267757</v>
       </c>
       <c r="J15">
-        <v>0.4282924026162399</v>
+        <v>0.446580559517115</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -41381,12 +41560,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:kampala-uga</t>
+          <t>corridor:15:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -41398,26 +41577,26 @@
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.03779941060386105</v>
+        <v>0.03947505835897319</v>
       </c>
       <c r="F16">
-        <v>0.10451891208285768</v>
+        <v>0.10766293076106442</v>
       </c>
       <c r="G16">
-        <v>0.09166463393260285</v>
+        <v>0.09624824633100992</v>
       </c>
       <c r="H16">
-        <v>0.2407645390707007</v>
+        <v>0.24890792140087264</v>
       </c>
       <c r="I16">
-        <v>0.027657720160362238</v>
+        <v>0.023441943477585433</v>
       </c>
       <c r="J16">
-        <v>0.4396111744978209</v>
+        <v>0.4469881708758133</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -41449,7 +41628,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:kasese-uga</t>
+          <t>corridor:16:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -41459,33 +41638,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.04170004663803706</v>
+        <v>0.037054326822585304</v>
       </c>
       <c r="F17">
-        <v>0.10372098668085056</v>
+        <v>0.10690154315918662</v>
       </c>
       <c r="G17">
-        <v>0.1008243915792412</v>
+        <v>0.09051412784116997</v>
       </c>
       <c r="H17">
-        <v>0.2390754226533218</v>
+        <v>0.24729635769244965</v>
       </c>
       <c r="I17">
-        <v>0.028925700788658745</v>
+        <v>0.023841914883054538</v>
       </c>
       <c r="J17">
-        <v>0.4110297404446275</v>
+        <v>0.41691596849067886</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -41517,7 +41696,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:arua-uga</t>
+          <t>corridor:17:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -41527,33 +41706,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.035186585343488896</v>
+        <v>0.03751084235818841</v>
       </c>
       <c r="F18">
-        <v>0.1022202018711377</v>
+        <v>0.10663402594128604</v>
       </c>
       <c r="G18">
-        <v>0.08549785806756499</v>
+        <v>0.09159725797748078</v>
       </c>
       <c r="H18">
-        <v>0.23589234541472318</v>
+        <v>0.24672965162274357</v>
       </c>
       <c r="I18">
-        <v>0.027502933564814515</v>
+        <v>0.02407954679637498</v>
       </c>
       <c r="J18">
-        <v>0.40677152882419465</v>
+        <v>0.44454587739519735</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -41585,7 +41764,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:nebbi-uga</t>
+          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -41595,33 +41774,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.03874391914011116</v>
+        <v>0.040216833909035604</v>
       </c>
       <c r="F19">
-        <v>0.09932753400748234</v>
+        <v>0.10227893881178257</v>
       </c>
       <c r="G19">
-        <v>0.0938876818934965</v>
+        <v>0.09800089155866029</v>
       </c>
       <c r="H19">
-        <v>0.22973469142772449</v>
+        <v>0.23746750551426188</v>
       </c>
       <c r="I19">
-        <v>0.02713466345582947</v>
+        <v>0.02574109924333239</v>
       </c>
       <c r="J19">
-        <v>0.43207387785922474</v>
+        <v>0.4462240901573336</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -41653,7 +41832,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:kasese-uga</t>
+          <t>corridor:19:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -41663,33 +41842,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.03299388535147604</v>
+        <v>0.03239630370940688</v>
       </c>
       <c r="F20">
-        <v>0.08738286997481087</v>
+        <v>0.09379632815128686</v>
       </c>
       <c r="G20">
-        <v>0.08030326285925304</v>
+        <v>0.07941922175273045</v>
       </c>
       <c r="H20">
-        <v>0.2039935043660834</v>
+        <v>0.21923462953102077</v>
       </c>
       <c r="I20">
-        <v>0.019930168144148393</v>
+        <v>0.020658583016893068</v>
       </c>
       <c r="J20">
-        <v>0.3775284009544754</v>
+        <v>0.3757448935253982</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -41721,7 +41900,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:beni-cod</t>
+          <t>corridor:20:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -41731,33 +41910,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03392819706306785</v>
+        <v>0.031343249954173036</v>
       </c>
       <c r="F21">
-        <v>0.08484940586882139</v>
+        <v>0.08962807165406164</v>
       </c>
       <c r="G21">
-        <v>0.0825188916401238</v>
+        <v>0.07689972645270565</v>
       </c>
       <c r="H21">
-        <v>0.19846854926794583</v>
+        <v>0.21017937050599006</v>
       </c>
       <c r="I21">
-        <v>0.024490234067551103</v>
+        <v>0.020495136113379064</v>
       </c>
       <c r="J21">
-        <v>0.37749315707435055</v>
+        <v>0.3809572978186992</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -41789,7 +41968,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:nebbi-uga</t>
+          <t>corridor:21:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -41799,33 +41978,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.03125577174100408</v>
+        <v>0.03310879855573873</v>
       </c>
       <c r="F22">
-        <v>0.08348454522926196</v>
+        <v>0.08657015317950179</v>
       </c>
       <c r="G22">
-        <v>0.0761732305165149</v>
+        <v>0.08112150891437181</v>
       </c>
       <c r="H22">
-        <v>0.19548267507850767</v>
+        <v>0.20349621355211361</v>
       </c>
       <c r="I22">
-        <v>0.02440925206055355</v>
+        <v>0.02417182913316858</v>
       </c>
       <c r="J22">
-        <v>0.37594067840426554</v>
+        <v>0.3559785151431059</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -41857,7 +42036,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:kampala-uga</t>
+          <t>corridor:22:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -41867,33 +42046,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.031478646822295314</v>
+        <v>0.027757679481219877</v>
       </c>
       <c r="F23">
-        <v>0.08284362872862142</v>
+        <v>0.08316271163642758</v>
       </c>
       <c r="G23">
-        <v>0.07670344805404702</v>
+        <v>0.06828987627797062</v>
       </c>
       <c r="H23">
-        <v>0.1940782082884187</v>
+        <v>0.19600919074702933</v>
       </c>
       <c r="I23">
-        <v>0.02186039936076743</v>
+        <v>0.01652290575782679</v>
       </c>
       <c r="J23">
-        <v>0.36475291410219285</v>
+        <v>0.35346265816565353</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -41925,7 +42104,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:arua-uga</t>
+          <t>corridor:23:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -41935,33 +42114,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.029994277699168237</v>
+        <v>0.029262518404558985</v>
       </c>
       <c r="F24">
-        <v>0.0826132813539486</v>
+        <v>0.0827973940167662</v>
       </c>
       <c r="G24">
-        <v>0.07316870543259008</v>
+        <v>0.0719092309443406</v>
       </c>
       <c r="H24">
-        <v>0.19357307850580524</v>
+        <v>0.19520396884789892</v>
       </c>
       <c r="I24">
-        <v>0.016047833475468353</v>
+        <v>0.0160365093845038</v>
       </c>
       <c r="J24">
-        <v>0.3573780111640004</v>
+        <v>0.37244943158791305</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -41993,7 +42172,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:bundibugyo-uga</t>
+          <t>corridor:24:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -42003,33 +42182,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.028661907391696856</v>
+        <v>0.029014915856687168</v>
       </c>
       <c r="F25">
-        <v>0.08085785766740855</v>
+        <v>0.07992581840442112</v>
       </c>
       <c r="G25">
-        <v>0.06998902920795538</v>
+        <v>0.07131428938994647</v>
       </c>
       <c r="H25">
-        <v>0.18971739841881297</v>
+        <v>0.18885779917755408</v>
       </c>
       <c r="I25">
-        <v>0.018016370547401035</v>
+        <v>0.026204983312365895</v>
       </c>
       <c r="J25">
-        <v>0.36065493954245237</v>
+        <v>0.39197883927654326</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -42061,7 +42240,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:bundibugyo-uga</t>
+          <t>corridor:25:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -42071,33 +42250,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.005793429794588911</v>
+        <v>0.006120542874036516</v>
       </c>
       <c r="F26">
-        <v>0.01702984566490226</v>
+        <v>0.01699417338751852</v>
       </c>
       <c r="G26">
-        <v>0.01439258175594163</v>
+        <v>0.015308080460276235</v>
       </c>
       <c r="H26">
-        <v>0.041951574982737355</v>
+        <v>0.042154297513636585</v>
       </c>
       <c r="I26">
-        <v>0.0038181048856288867</v>
+        <v>0.003537521039203559</v>
       </c>
       <c r="J26">
-        <v>0.08616420003025087</v>
+        <v>0.08297678927478849</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -42129,7 +42308,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:beni-cod</t>
+          <t>corridor:26:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -42139,33 +42318,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.005897051963327515</v>
+        <v>0.005874612094265597</v>
       </c>
       <c r="F27">
-        <v>0.016454298957175345</v>
+        <v>0.016526384306946418</v>
       </c>
       <c r="G27">
-        <v>0.01464887215333438</v>
+        <v>0.014695723098220564</v>
       </c>
       <c r="H27">
-        <v>0.04055132576639631</v>
+        <v>0.041008547755741837</v>
       </c>
       <c r="I27">
-        <v>0.0035690102911354387</v>
+        <v>0.0034953489095219947</v>
       </c>
       <c r="J27">
-        <v>0.08080632138202076</v>
+        <v>0.07196869182617144</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -42197,7 +42376,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:nebbi-uga</t>
+          <t>corridor:27:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -42207,33 +42386,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.006239312368845673</v>
+        <v>0.0063472860999863046</v>
       </c>
       <c r="F28">
-        <v>0.01619803151236343</v>
+        <v>0.016310473511373214</v>
       </c>
       <c r="G28">
-        <v>0.015495105961945144</v>
+        <v>0.015872457611902313</v>
       </c>
       <c r="H28">
-        <v>0.039927464536473806</v>
+        <v>0.0404794429759861</v>
       </c>
       <c r="I28">
-        <v>0.003405178314087784</v>
+        <v>0.0036262347035018044</v>
       </c>
       <c r="J28">
-        <v>0.07935673326585045</v>
+        <v>0.08668303567476036</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -42265,7 +42444,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:kampala-uga</t>
+          <t>corridor:28:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -42275,33 +42454,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.006392865452645141</v>
+        <v>0.005674021075253249</v>
       </c>
       <c r="F29">
-        <v>0.016120155850815304</v>
+        <v>0.015966822911828493</v>
       </c>
       <c r="G29">
-        <v>0.01587462279882418</v>
+        <v>0.014196090807731543</v>
       </c>
       <c r="H29">
-        <v>0.03973783345894116</v>
+        <v>0.039636938611780054</v>
       </c>
       <c r="I29">
-        <v>0.0032650126802971193</v>
+        <v>0.0034806849422171797</v>
       </c>
       <c r="J29">
-        <v>0.07658764416722781</v>
+        <v>0.0780554614612525</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -42333,7 +42512,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:kasese-uga</t>
+          <t>corridor:29:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -42343,33 +42522,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.005897977372847696</v>
+        <v>0.0064256354798581106</v>
       </c>
       <c r="F30">
-        <v>0.016114027975795253</v>
+        <v>0.015695763569745308</v>
       </c>
       <c r="G30">
-        <v>0.014651160795670248</v>
+        <v>0.016067429277709516</v>
       </c>
       <c r="H30">
-        <v>0.039722906756456705</v>
+        <v>0.038972088119423404</v>
       </c>
       <c r="I30">
-        <v>0.004563029278651646</v>
+        <v>0.00498049465626442</v>
       </c>
       <c r="J30">
-        <v>0.08758262782791992</v>
+        <v>0.0758544841015686</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -42401,7 +42580,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:arua-uga</t>
+          <t>corridor:30:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -42411,33 +42590,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.0053809689229898094</v>
+        <v>0.005382307947903675</v>
       </c>
       <c r="F31">
-        <v>0.014969127663845894</v>
+        <v>0.015689028622659945</v>
       </c>
       <c r="G31">
-        <v>0.013372039811872988</v>
+        <v>0.013469218884625184</v>
       </c>
       <c r="H31">
-        <v>0.036932402731466474</v>
+        <v>0.038955562840755714</v>
       </c>
       <c r="I31">
-        <v>0.0043470653458970695</v>
+        <v>0.00261336226616051</v>
       </c>
       <c r="J31">
-        <v>0.0819411234458965</v>
+        <v>0.08089104819780216</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -42469,12 +42648,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:miti-murhesa:nebbi-uga</t>
+          <t>corridor:31:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -42486,26 +42665,26 @@
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.0031064099748497886</v>
+        <v>0.003036170632948393</v>
       </c>
       <c r="F32">
-        <v>0.008842744721272167</v>
+        <v>0.008699255524416832</v>
       </c>
       <c r="G32">
-        <v>0.00773278016050985</v>
+        <v>0.007611531620020595</v>
       </c>
       <c r="H32">
-        <v>0.021917803930031482</v>
+        <v>0.02171516880923019</v>
       </c>
       <c r="I32">
-        <v>0.0012927920382234503</v>
+        <v>0.0018231578456973485</v>
       </c>
       <c r="J32">
-        <v>0.043151428768583286</v>
+        <v>0.0406946321513916</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -42537,12 +42716,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:nizi:kasese-uga</t>
+          <t>corridor:32:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -42554,26 +42733,26 @@
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.0030137247816908463</v>
+        <v>0.003044055247326788</v>
       </c>
       <c r="F33">
-        <v>0.008455401394654921</v>
+        <v>0.00860046134544773</v>
       </c>
       <c r="G33">
-        <v>0.007502579723034392</v>
+        <v>0.007631252063973859</v>
       </c>
       <c r="H33">
-        <v>0.020963818333134487</v>
+        <v>0.021470167816893482</v>
       </c>
       <c r="I33">
-        <v>0.001964876026614837</v>
+        <v>0.0014973330122456524</v>
       </c>
       <c r="J33">
-        <v>0.04025996291249157</v>
+        <v>0.038352523140163956</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -42605,43 +42784,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:bambu:kasese-uga</t>
+          <t>corridor:33:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.0028886304443923594</v>
+        <v>0.002981208606110952</v>
       </c>
       <c r="F34">
-        <v>0.008347118481784016</v>
+        <v>0.00853010671090837</v>
       </c>
       <c r="G34">
-        <v>0.00719183460774292</v>
+        <v>0.007474055522301043</v>
       </c>
       <c r="H34">
-        <v>0.020697029082573037</v>
+        <v>0.021295671112063014</v>
       </c>
       <c r="I34">
-        <v>0.0017626325075392108</v>
+        <v>0.0020763684021678276</v>
       </c>
       <c r="J34">
-        <v>0.040846686395662496</v>
+        <v>0.04157524175982064</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -42673,43 +42852,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:nizi:bundibugyo-uga</t>
+          <t>corridor:34:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003021126031914151</v>
+        <v>0.003049904014779198</v>
       </c>
       <c r="F35">
-        <v>0.008312163807679601</v>
+        <v>0.008510247131509524</v>
       </c>
       <c r="G35">
-        <v>0.0075209637361464965</v>
+        <v>0.0076458810373161434</v>
       </c>
       <c r="H35">
-        <v>0.02061089733019217</v>
+        <v>0.02124641212086062</v>
       </c>
       <c r="I35">
-        <v>0.001965199157311942</v>
+        <v>0.001894892164408163</v>
       </c>
       <c r="J35">
-        <v>0.04232624078531671</v>
+        <v>0.03868551246151107</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -42741,43 +42920,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:goma-cod:beni-cod</t>
+          <t>corridor:35:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.0029885689228487944</v>
+        <v>0.00310326252679316</v>
       </c>
       <c r="F36">
-        <v>0.008309165031427646</v>
+        <v>0.008371286435940095</v>
       </c>
       <c r="G36">
-        <v>0.0074400943892386495</v>
+        <v>0.007779332263353617</v>
       </c>
       <c r="H36">
-        <v>0.020603508791962988</v>
+        <v>0.020901691773522968</v>
       </c>
       <c r="I36">
-        <v>0.0015140627043773254</v>
+        <v>0.0017729400819647607</v>
       </c>
       <c r="J36">
-        <v>0.039636236358234156</v>
+        <v>0.041854022880361594</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -42809,43 +42988,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:kilo:kampala-uga</t>
+          <t>corridor:36:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.0028968958480735663</v>
+        <v>0.002967388107118135</v>
       </c>
       <c r="F37">
-        <v>0.008302699189387669</v>
+        <v>0.008337126650148213</v>
       </c>
       <c r="G37">
-        <v>0.007212368681008802</v>
+        <v>0.007439484701364463</v>
       </c>
       <c r="H37">
-        <v>0.02058757493019797</v>
+        <v>0.02081694028687528</v>
       </c>
       <c r="I37">
-        <v>0.0014728301522307502</v>
+        <v>0.0017431353970841308</v>
       </c>
       <c r="J37">
-        <v>0.040142399138471466</v>
+        <v>0.03987425157869348</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -42877,43 +43056,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:miti-murhesa:beni-cod</t>
+          <t>corridor:37:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D38">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.0027436360542250626</v>
+        <v>0.0028635878048932917</v>
       </c>
       <c r="F38">
-        <v>0.008291615601552393</v>
+        <v>0.0083314394748491</v>
       </c>
       <c r="G38">
-        <v>0.006831583025491139</v>
+        <v>0.007179812848703837</v>
       </c>
       <c r="H38">
-        <v>0.020560263716459554</v>
+        <v>0.020802829539148276</v>
       </c>
       <c r="I38">
-        <v>0.001809788062056189</v>
+        <v>0.00148959781119683</v>
       </c>
       <c r="J38">
-        <v>0.04035120838517614</v>
+        <v>0.04118234481782838</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -42945,12 +43124,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:bambu:kampala-uga</t>
+          <t>corridor:38:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -42962,26 +43141,26 @@
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.0028878037106492283</v>
+        <v>0.0028297038262589114</v>
       </c>
       <c r="F39">
-        <v>0.00826700300096575</v>
+        <v>0.008276409421757808</v>
       </c>
       <c r="G39">
-        <v>0.00718978103506368</v>
+        <v>0.0070950385508476155</v>
       </c>
       <c r="H39">
-        <v>0.0204996068255012</v>
+        <v>0.020666287769637415</v>
       </c>
       <c r="I39">
-        <v>0.0015583380599284798</v>
+        <v>0.0016817624400032954</v>
       </c>
       <c r="J39">
-        <v>0.04029488629595264</v>
+        <v>0.039287175973469944</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -43013,12 +43192,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:nizi:kampala-uga</t>
+          <t>corridor:39:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -43030,26 +43209,26 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.0030739891390453022</v>
+        <v>0.0028541855896696833</v>
       </c>
       <c r="F40">
-        <v>0.008190495185341068</v>
+        <v>0.008252562887683529</v>
       </c>
       <c r="G40">
-        <v>0.00765226137795097</v>
+        <v>0.007156290108511709</v>
       </c>
       <c r="H40">
-        <v>0.020311061195146723</v>
+        <v>0.020607115412800053</v>
       </c>
       <c r="I40">
-        <v>0.0019126404305481878</v>
+        <v>0.0018998622437845641</v>
       </c>
       <c r="J40">
-        <v>0.03892464933729348</v>
+        <v>0.044504858617887194</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -43081,7 +43260,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:40:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -43091,33 +43270,33 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.0030168065956937273</v>
+        <v>0.0027349409401292712</v>
       </c>
       <c r="F41">
-        <v>0.008186419166028969</v>
+        <v>0.008245046196641154</v>
       </c>
       <c r="G41">
-        <v>0.0075102348731063695</v>
+        <v>0.006857927560041555</v>
       </c>
       <c r="H41">
-        <v>0.02030101473563603</v>
+        <v>0.02058846320226515</v>
       </c>
       <c r="I41">
-        <v>0.0019468904654919932</v>
+        <v>0.0014529959377463596</v>
       </c>
       <c r="J41">
-        <v>0.040363293600190024</v>
+        <v>0.03976609261069776</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -43149,43 +43328,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:bambu:arua-uga</t>
+          <t>corridor:41:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.002768603266617875</v>
+        <v>0.0027780375306676874</v>
       </c>
       <c r="F42">
-        <v>0.008162493230156248</v>
+        <v>0.008203146144269508</v>
       </c>
       <c r="G42">
-        <v>0.006893621987128173</v>
+        <v>0.006965766035151089</v>
       </c>
       <c r="H42">
-        <v>0.020242046539878572</v>
+        <v>0.0204844874721663</v>
       </c>
       <c r="I42">
-        <v>0.0015474160854732802</v>
+        <v>0.001978216297492336</v>
       </c>
       <c r="J42">
-        <v>0.03915694943543016</v>
+        <v>0.03713845609642502</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -43217,7 +43396,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:nizi:nebbi-uga</t>
+          <t>corridor:42:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -43227,33 +43406,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.0029572181128099673</v>
+        <v>0.0029523334159434755</v>
       </c>
       <c r="F43">
-        <v>0.008136926158356317</v>
+        <v>0.008135009614384153</v>
       </c>
       <c r="G43">
-        <v>0.007362219916885793</v>
+        <v>0.007401825721503413</v>
       </c>
       <c r="H43">
-        <v>0.02017903013560457</v>
+        <v>0.02031539108547792</v>
       </c>
       <c r="I43">
-        <v>0.0014210452648333984</v>
+        <v>0.0018778692608227316</v>
       </c>
       <c r="J43">
-        <v>0.03953044137015703</v>
+        <v>0.04145132009147697</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -43285,43 +43464,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:butembo:arua-uga</t>
+          <t>corridor:43:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.0028588847097371084</v>
+        <v>0.0030619690333943683</v>
       </c>
       <c r="F44">
-        <v>0.008121479547922666</v>
+        <v>0.008130141524979317</v>
       </c>
       <c r="G44">
-        <v>0.007117934652822733</v>
+        <v>0.0076760568404039</v>
       </c>
       <c r="H44">
-        <v>0.020140955026916263</v>
+        <v>0.02030330760719401</v>
       </c>
       <c r="I44">
-        <v>0.0020310862342879017</v>
+        <v>0.0015565214491938318</v>
       </c>
       <c r="J44">
-        <v>0.043374936050191125</v>
+        <v>0.043350253258958436</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -43353,7 +43532,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:butembo:kasese-uga</t>
+          <t>corridor:44:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -43363,33 +43542,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.002966216009741285</v>
+        <v>0.002761100942238165</v>
       </c>
       <c r="F45">
-        <v>0.008071204783386715</v>
+        <v>0.008125095752590183</v>
       </c>
       <c r="G45">
-        <v>0.007384571167953435</v>
+        <v>0.006923387348404669</v>
       </c>
       <c r="H45">
-        <v>0.020017032108961774</v>
+        <v>0.020290785286753488</v>
       </c>
       <c r="I45">
-        <v>0.0019856633392102835</v>
+        <v>0.00206297360449538</v>
       </c>
       <c r="J45">
-        <v>0.03903230116776946</v>
+        <v>0.04222598903376526</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -43421,12 +43600,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:goma-cod:kampala-uga</t>
+          <t>corridor:45:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -43438,26 +43617,26 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.002999824043247834</v>
+        <v>0.002697580156124979</v>
       </c>
       <c r="F46">
-        <v>0.008070104040915183</v>
+        <v>0.008063051764023277</v>
       </c>
       <c r="G46">
-        <v>0.007468051852929203</v>
+        <v>0.006764436018809494</v>
       </c>
       <c r="H46">
-        <v>0.020014318893145783</v>
+        <v>0.020136791618205502</v>
       </c>
       <c r="I46">
-        <v>0.0018391957134823611</v>
+        <v>0.0017176606801707379</v>
       </c>
       <c r="J46">
-        <v>0.04222176098200819</v>
+        <v>0.03593932697202585</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -43489,43 +43668,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:miti-murhesa:kampala-uga</t>
+          <t>corridor:46:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.00302696457253418</v>
+        <v>0.0029680417891685407</v>
       </c>
       <c r="F47">
-        <v>0.008061746356337274</v>
+        <v>0.008033249526172292</v>
       </c>
       <c r="G47">
-        <v>0.007535465665797686</v>
+        <v>0.007441119829860149</v>
       </c>
       <c r="H47">
-        <v>0.019993715064261175</v>
+        <v>0.020062799430107525</v>
       </c>
       <c r="I47">
-        <v>0.0019038903776436523</v>
+        <v>0.0018851508601080568</v>
       </c>
       <c r="J47">
-        <v>0.03809161905995875</v>
+        <v>0.041996978628116785</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -43557,43 +43736,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:miti-murhesa:kasese-uga</t>
+          <t>corridor:47:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002711272164641787</v>
+        <v>0.0029169808329018165</v>
       </c>
       <c r="F48">
-        <v>0.008003320140437448</v>
+        <v>0.007997964197460128</v>
       </c>
       <c r="G48">
-        <v>0.006751161363516417</v>
+        <v>0.007313388716630204</v>
       </c>
       <c r="H48">
-        <v>0.019849685301168624</v>
+        <v>0.019975227779149868</v>
       </c>
       <c r="I48">
-        <v>0.0016687253435851562</v>
+        <v>0.0023046023307807615</v>
       </c>
       <c r="J48">
-        <v>0.04165630204345164</v>
+        <v>0.04031690064358761</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -43625,7 +43804,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:kilo:bundibugyo-uga</t>
+          <t>corridor:48:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -43635,33 +43814,33 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.0028828781654738067</v>
+        <v>0.0030869625468540884</v>
       </c>
       <c r="F49">
-        <v>0.007999761114495657</v>
+        <v>0.007996867695904547</v>
       </c>
       <c r="G49">
-        <v>0.007177544340573161</v>
+        <v>0.007738556928652884</v>
       </c>
       <c r="H49">
-        <v>0.01984091087479531</v>
+        <v>0.01997250519785243</v>
       </c>
       <c r="I49">
-        <v>0.001746492912259029</v>
+        <v>0.0019306615451828934</v>
       </c>
       <c r="J49">
-        <v>0.04180829543410267</v>
+        <v>0.042052814805390165</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -43693,43 +43872,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:goma-cod:arua-uga</t>
+          <t>corridor:49:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0028290030722574744</v>
+        <v>0.002815721362600332</v>
       </c>
       <c r="F50">
-        <v>0.007993877766034052</v>
+        <v>0.007976076073243299</v>
       </c>
       <c r="G50">
-        <v>0.007043694470001555</v>
+        <v>0.0070600544320303105</v>
       </c>
       <c r="H50">
-        <v>0.01982640604270372</v>
+        <v>0.019920892154709158</v>
       </c>
       <c r="I50">
-        <v>0.0016184962560191808</v>
+        <v>0.001956233815972519</v>
       </c>
       <c r="J50">
-        <v>0.041811123101178745</v>
+        <v>0.04328982889117054</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -43761,43 +43940,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:nizi:beni-cod</t>
+          <t>corridor:50:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D51">
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002964265235936736</v>
+        <v>0.0028080329489875433</v>
       </c>
       <c r="F51">
-        <v>0.007979683324545433</v>
+        <v>0.00795174060405468</v>
       </c>
       <c r="G51">
-        <v>0.007379725373273249</v>
+        <v>0.007040817734647403</v>
       </c>
       <c r="H51">
-        <v>0.01979141256348449</v>
+        <v>0.019860478352816707</v>
       </c>
       <c r="I51">
-        <v>0.001700272522619467</v>
+        <v>0.002303497064242352</v>
       </c>
       <c r="J51">
-        <v>0.03920759588832881</v>
+        <v>0.0471616963189368</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -43829,43 +44008,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:kilo:beni-cod</t>
+          <t>corridor:51:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.0027636218791129985</v>
+        <v>0.002980721344073456</v>
       </c>
       <c r="F52">
-        <v>0.007943736755445518</v>
+        <v>0.00793181040317939</v>
       </c>
       <c r="G52">
-        <v>0.006881244331427588</v>
+        <v>0.0074728367717477595</v>
       </c>
       <c r="H52">
-        <v>0.01970278797042238</v>
+        <v>0.019810999994700207</v>
       </c>
       <c r="I52">
-        <v>0.0014763767393302513</v>
+        <v>0.0016340821245132587</v>
       </c>
       <c r="J52">
-        <v>0.04005225312519262</v>
+        <v>0.042757776645511565</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -43897,43 +44076,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:kilo:kasese-uga</t>
+          <t>corridor:52:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.002939240277028049</v>
+        <v>0.002668871809556994</v>
       </c>
       <c r="F53">
-        <v>0.007912160672771062</v>
+        <v>0.007918950601067454</v>
       </c>
       <c r="G53">
-        <v>0.007317560988202604</v>
+        <v>0.006692592465324332</v>
       </c>
       <c r="H53">
-        <v>0.019624933508132852</v>
+        <v>0.019779074000736363</v>
       </c>
       <c r="I53">
-        <v>0.0018917807676148398</v>
+        <v>0.0014712214192055375</v>
       </c>
       <c r="J53">
-        <v>0.038940141953057755</v>
+        <v>0.040525603585121125</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -43965,43 +44144,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:butembo:nebbi-uga</t>
+          <t>corridor:53:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.002896284327627646</v>
+        <v>0.002970344773470357</v>
       </c>
       <c r="F54">
-        <v>0.007898422310050696</v>
+        <v>0.007916812374731491</v>
       </c>
       <c r="G54">
-        <v>0.007210849355384241</v>
+        <v>0.00744687994533258</v>
       </c>
       <c r="H54">
-        <v>0.019591060445456554</v>
+        <v>0.019773763992796817</v>
       </c>
       <c r="I54">
-        <v>0.002070995524055594</v>
+        <v>0.0018267951202627754</v>
       </c>
       <c r="J54">
-        <v>0.03944003878007347</v>
+        <v>0.0391235655311514</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -44033,43 +44212,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:goma-cod:nebbi-uga</t>
+          <t>corridor:54:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.00284876075269902</v>
+        <v>0.0031454086233342893</v>
       </c>
       <c r="F55">
-        <v>0.007893020209658985</v>
+        <v>0.00790638120557785</v>
       </c>
       <c r="G55">
-        <v>0.007092782818425181</v>
+        <v>0.007884733598589017</v>
       </c>
       <c r="H55">
-        <v>0.019577740869646337</v>
+        <v>0.019747868065662366</v>
       </c>
       <c r="I55">
-        <v>0.0020058959968129258</v>
+        <v>0.0021057835484370653</v>
       </c>
       <c r="J55">
-        <v>0.03794044182437606</v>
+        <v>0.03852983247889245</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -44101,43 +44280,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:bambu:beni-cod</t>
+          <t>corridor:55:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.002919518350532113</v>
+        <v>0.00304220454384585</v>
       </c>
       <c r="F56">
-        <v>0.007885781628357735</v>
+        <v>0.007880648560680076</v>
       </c>
       <c r="G56">
-        <v>0.007268568604097025</v>
+        <v>0.0076266228561871485</v>
       </c>
       <c r="H56">
-        <v>0.0195598910020858</v>
+        <v>0.019683979639147753</v>
       </c>
       <c r="I56">
-        <v>0.0020982416358770435</v>
+        <v>0.0018498188421581965</v>
       </c>
       <c r="J56">
-        <v>0.04103833436051815</v>
+        <v>0.043875900176363315</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -44169,43 +44348,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:kilo:arua-uga</t>
+          <t>corridor:56:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.0026794581653525884</v>
+        <v>0.003169130129459574</v>
       </c>
       <c r="F57">
-        <v>0.007824052809558862</v>
+        <v>0.007864612484581951</v>
       </c>
       <c r="G57">
-        <v>0.0066721022582374445</v>
+        <v>0.007944054318325983</v>
       </c>
       <c r="H57">
-        <v>0.019407679063902866</v>
+        <v>0.019644164439568873</v>
       </c>
       <c r="I57">
-        <v>0.0018742235395998118</v>
+        <v>0.002417676492622753</v>
       </c>
       <c r="J57">
-        <v>0.03983832973283268</v>
+        <v>0.03686924375974461</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -44237,43 +44416,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:butembo:bundibugyo-uga</t>
+          <t>corridor:57:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.0029658127649658528</v>
+        <v>0.002746685139402155</v>
       </c>
       <c r="F58">
-        <v>0.007809572414131216</v>
+        <v>0.007834762215712165</v>
       </c>
       <c r="G58">
-        <v>0.007383568737962282</v>
+        <v>0.006887313647931159</v>
       </c>
       <c r="H58">
-        <v>0.019371970574026537</v>
+        <v>0.019570047666818274</v>
       </c>
       <c r="I58">
-        <v>0.0018216334903385755</v>
+        <v>0.0019773417068834204</v>
       </c>
       <c r="J58">
-        <v>0.03964694132559633</v>
+        <v>0.03686928485677902</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -44305,43 +44484,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:nizi:arua-uga</t>
+          <t>corridor:58:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0028161227874957395</v>
+        <v>0.0028033145136891757</v>
       </c>
       <c r="F59">
-        <v>0.007799385470735554</v>
+        <v>0.007755839500948353</v>
       </c>
       <c r="G59">
-        <v>0.007011692758622234</v>
+        <v>0.007029011982497474</v>
       </c>
       <c r="H59">
-        <v>0.019346848345025758</v>
+        <v>0.019374068906622688</v>
       </c>
       <c r="I59">
-        <v>0.0021527480257039766</v>
+        <v>0.0016894071371955173</v>
       </c>
       <c r="J59">
-        <v>0.03738999809248955</v>
+        <v>0.04506619922585881</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -44373,7 +44552,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:butembo:beni-cod</t>
+          <t>corridor:59:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -44383,33 +44562,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.002874053560650125</v>
+        <v>0.0027807819019262103</v>
       </c>
       <c r="F60">
-        <v>0.0077552415891767035</v>
+        <v>0.007730769920831854</v>
       </c>
       <c r="G60">
-        <v>0.007155620843306676</v>
+        <v>0.006972632877769225</v>
       </c>
       <c r="H60">
-        <v>0.019237984603597186</v>
+        <v>0.019311813845502956</v>
       </c>
       <c r="I60">
-        <v>0.0015960886164875705</v>
+        <v>0.001780853201348709</v>
       </c>
       <c r="J60">
-        <v>0.0397290483148042</v>
+        <v>0.03770510010166108</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -44441,12 +44620,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:goma-cod:bundibugyo-uga</t>
+          <t>corridor:60:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -44458,26 +44637,26 @@
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.0029333768169604313</v>
+        <v>0.003014014849821667</v>
       </c>
       <c r="F61">
-        <v>0.007738766942843367</v>
+        <v>0.007716679844077617</v>
       </c>
       <c r="G61">
-        <v>0.007302995550801578</v>
+        <v>0.007556114951172782</v>
       </c>
       <c r="H61">
-        <v>0.019197353961997482</v>
+        <v>0.019276823258474657</v>
       </c>
       <c r="I61">
-        <v>0.002113826548903264</v>
+        <v>0.001632307878839895</v>
       </c>
       <c r="J61">
-        <v>0.04367258678384024</v>
+        <v>0.03744864374175828</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -44509,43 +44688,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:bambu:bundibugyo-uga</t>
+          <t>corridor:61:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0029430467838043872</v>
+        <v>0.002519928132902971</v>
       </c>
       <c r="F62">
-        <v>0.007716591334032796</v>
+        <v>0.007698029728080397</v>
       </c>
       <c r="G62">
-        <v>0.007327016685413357</v>
+        <v>0.006319806901269265</v>
       </c>
       <c r="H62">
-        <v>0.019142661955798917</v>
+        <v>0.019230506044563306</v>
       </c>
       <c r="I62">
-        <v>0.0019755308676983633</v>
+        <v>0.0016384436173651762</v>
       </c>
       <c r="J62">
-        <v>0.039791083586982245</v>
+        <v>0.03885106071126117</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -44577,43 +44756,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:goma-cod:kasese-uga</t>
+          <t>corridor:62:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.002796905767992547</v>
+        <v>0.0028232877052564442</v>
       </c>
       <c r="F63">
-        <v>0.00767757669112995</v>
+        <v>0.007649320956446215</v>
       </c>
       <c r="G63">
-        <v>0.006963945541292177</v>
+        <v>0.007078985649893704</v>
       </c>
       <c r="H63">
-        <v>0.019046434992530586</v>
+        <v>0.019109532549612368</v>
       </c>
       <c r="I63">
-        <v>0.0020588048892707404</v>
+        <v>0.0018363344309543978</v>
       </c>
       <c r="J63">
-        <v>0.049283570893681704</v>
+        <v>0.043637737653375794</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -44645,43 +44824,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:bambu:nebbi-uga</t>
+          <t>corridor:63:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.002881574110656343</v>
+        <v>0.002826293275851488</v>
       </c>
       <c r="F64">
-        <v>0.0076527240222372395</v>
+        <v>0.007444085156304375</v>
       </c>
       <c r="G64">
-        <v>0.00717430459340368</v>
+        <v>0.007086505469572291</v>
       </c>
       <c r="H64">
-        <v>0.018985134000077397</v>
+        <v>0.01859970821153295</v>
       </c>
       <c r="I64">
-        <v>0.0019465263477377952</v>
+        <v>0.0017289297730197135</v>
       </c>
       <c r="J64">
-        <v>0.038295269411189395</v>
+        <v>0.04140206624718119</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -44713,43 +44892,43 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:miti-murhesa:arua-uga</t>
+          <t>corridor:64:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D65">
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0029594116020818517</v>
+        <v>0.0027471657296173346</v>
       </c>
       <c r="F65">
-        <v>0.007574358536086928</v>
+        <v>0.007411007252938445</v>
       </c>
       <c r="G65">
-        <v>0.007367668721658921</v>
+        <v>0.006888517718670689</v>
       </c>
       <c r="H65">
-        <v>0.018791827304817404</v>
+        <v>0.018517525239410138</v>
       </c>
       <c r="I65">
-        <v>0.0018921759864096277</v>
+        <v>0.001965558005404322</v>
       </c>
       <c r="J65">
-        <v>0.0362803906851146</v>
+        <v>0.038192040126588105</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -44781,43 +44960,43 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:butembo:kampala-uga</t>
+          <t>corridor:65:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.0031623753037089974</v>
+        <v>0.0026959065523016745</v>
       </c>
       <c r="F66">
-        <v>0.00756670972052767</v>
+        <v>0.0073924555949739235</v>
       </c>
       <c r="G66">
-        <v>0.007871765533029873</v>
+        <v>0.006760247867125618</v>
       </c>
       <c r="H66">
-        <v>0.01877295839047441</v>
+        <v>0.01847143097717671</v>
       </c>
       <c r="I66">
-        <v>0.0022942651841674185</v>
+        <v>0.0020862923654499377</v>
       </c>
       <c r="J66">
-        <v>0.03629645524216742</v>
+        <v>0.03490935151153757</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -44849,43 +45028,43 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:kilo:nebbi-uga</t>
+          <t>corridor:66:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.0028544692621960133</v>
+        <v>0.0026528560781728105</v>
       </c>
       <c r="F67">
-        <v>0.0073600577545204215</v>
+        <v>0.007375241869799987</v>
       </c>
       <c r="G67">
-        <v>0.007106965376501684</v>
+        <v>0.0066525114617464465</v>
       </c>
       <c r="H67">
-        <v>0.018263086159490488</v>
+        <v>0.018428659273306808</v>
       </c>
       <c r="I67">
-        <v>0.0015953746275022913</v>
+        <v>0.002300845852606545</v>
       </c>
       <c r="J67">
-        <v>0.03555014814938943</v>
+        <v>0.04242449934097557</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -45028,7 +45207,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -45080,7 +45259,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -45134,7 +45313,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -45188,7 +45367,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -45242,7 +45421,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -45296,7 +45475,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -45350,7 +45529,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -45392,10 +45571,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.4007872542276427</v>
+        <v>0.39797533849569694</v>
       </c>
       <c r="F9">
-        <v>0.4611775387681021</v>
+        <v>0.4577638723558707</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -45404,7 +45583,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -45446,10 +45625,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>2.6041684931341673</v>
+        <v>3.005236063491366</v>
       </c>
       <c r="F10">
-        <v>12.098434321451013</v>
+        <v>12.74823301250542</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -45458,7 +45637,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -45500,10 +45679,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F11">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -45512,7 +45691,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -45759,7 +45938,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.007</v>
+        <v>0.008</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -45811,7 +45990,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.035</v>
+        <v>0.033</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -45863,7 +46042,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.958</v>
+        <v>0.959</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -47942,7 +48121,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-023</t>
+          <t>BDBV-CLAIM-024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -47989,7 +48168,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-024</t>
+          <t>BDBV-CLAIM-025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -47999,12 +48178,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>The May 23 public snapshot uses the CDC Current Situation page as the current official exact endpoint while retaining WHO 22 May and earlier values as dated conflict/cross-check evidence.</t>
+          <t>The May 23 public snapshot uses the CDC Current Situation page as the current official exact endpoint for confirmed cases, while the higher WHO 22 May suspected and suspected-deaths figures are the reconciled primaries under the higher-of-valid-primaries rule, and CDC's lower suspected/deaths plus earlier values are retained as dated conflict/cross-check evidence.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>confirmed total 88 (83 DRC + 5 Uganda), suspected DRC cases 746, suspected DRC deaths 176; CDC also reports nine confirmed DRC deaths and one confirmed Uganda death.</t>
+          <t>CDC reports confirmed total 88 (83 DRC + 5 Uganda), 746 suspected DRC cases, and 176 suspected DRC deaths, plus nine confirmed DRC deaths and one confirmed Uganda death. The reconciled endpoint takes CDC's 88 confirmed (the higher confirmed primary) and defers suspected and deaths to WHO 22 May (750 and 177, the higher valid primaries); CDC's 746 and 176 are retained as conflict anchors.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -1345,8 +1345,55 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-027</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bdbv may25 source review boundary</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>May 25 source-review evidence can be archived for audit and partner context without creating a May 25 public snapshot route or promoting non-primary/watch claims into scored counts.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ECDC 25 May is accepted as regional cross-check only (snapshot_trigger=false); WHO AFRO hub is official context/readiness only (snapshot_trigger=false); IFRC requires browser/AIR capture when plain HTTP is challenged; Wikipedia remains watch-only unless confirmed by public-health authority.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ECDC. Ebola virus disease outbreak in the Democratic Republic of the Congo and Uganda. Page last updated 25 May 2026 16:30.; WHO Regional Office for Africa. Ongoing outbreak in the Democratic Republic of the Congo / Bundibugyo virus disease outbreak hub. Updated 24 May 2026.; IFRC. Ebola: IFRC scales up response in eastern DRC as regional risks grow. 21 May 2026.; Wikipedia contributors. 2026 Ituri Province Ebola epidemic, live page observed by 25 May 2026 freshness check.; data/external_sources/freshness/bdbv-2026-2026-05-25.json generated by source_ingest.py --live-check --as-of 2026-05-25.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026; https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26; https://www.ifrc.org/press-release/ebola-ifrc-scales-response-eastern-drc-regional-risks-grow; https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Keep May 24 as the current publication-state route. Continue source review for DRC MoH table semantics, CDC traveler context, and future primary WHO/DRC/Uganda/CDC updates before any May 25 snapshot promotion.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I24"/>
+  <autoFilter ref="A1:I25"/>
 </worksheet>
 </file>
 
@@ -3587,8 +3634,124 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>European Centre for Disease Prevention and Control</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-25T16:30:00Z</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:36:38Z</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="J39"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>World Health Organization, Regional Office for Africa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>official_who_afro</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-24T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:36:38Z</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>e7a8993d9d8526e69773fdc73f99b143e05b8d04184cdb69b02e2e34ab4cadb3</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>private_restricted_bytes</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>CC-BY-NC-SA-3.0-IGO</t>
+        </is>
+      </c>
+      <c r="J40"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L38"/>
+  <autoFilter ref="A1:L40"/>
 </worksheet>
 </file>
 
@@ -15699,8 +15862,270 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>source_data_report_date:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D116"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>regional_cross_check_only</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>source_publication_date:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D117"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>regional_cross_check_only</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:36:38Z</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>regional_cross_check_only</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>source_data_report_date:who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>context_only</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>official_who_afro</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>not_recorded</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>source_publication_date:who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="D120"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>context_only</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>official_who_afro</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-05-25T18:36:38Z</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>who-afro-outbreak-hub-2026-05-24-live</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>context_only</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>official_who_afro</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I115"/>
+  <autoFilter ref="A1:I121"/>
 </worksheet>
 </file>
 
@@ -31715,34 +32140,34 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D203"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F203">
-        <v>904</v>
-      </c>
-      <c r="G203">
-        <v>395</v>
-      </c>
-      <c r="H203">
-        <v>904</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G203"/>
+      <c r="H203"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>count</t>
@@ -31750,37 +32175,33 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K203"/>
       <c r="L203" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -31790,7 +32211,7 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="S203"/>
@@ -31798,12 +32219,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -31811,21 +32232,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D204"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="F204">
-        <v>106</v>
-      </c>
-      <c r="G204">
-        <v>10</v>
-      </c>
-      <c r="H204">
-        <v>106</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G204"/>
+      <c r="H204"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>count</t>
@@ -31833,37 +32254,33 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K204"/>
       <c r="L204" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -31873,100 +32290,819 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
-        </is>
-      </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S204"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F205">
+        <v>7</v>
+      </c>
+      <c r="G205"/>
+      <c r="H205"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K205"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S205"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F206">
+        <v>904</v>
+      </c>
+      <c r="G206"/>
+      <c r="H206"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K206"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S206"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:contacts_followed_percent</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>contacts_followed_percent</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F207">
+        <v>20</v>
+      </c>
+      <c r="G207"/>
+      <c r="H207"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K207"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S207"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:contacts_identified_drc</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>contacts_identified_drc</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F208">
+        <v>1745</v>
+      </c>
+      <c r="G208"/>
+      <c r="H208"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K208"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F209">
+        <v>10</v>
+      </c>
+      <c r="G209"/>
+      <c r="H209"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K209"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S209"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F210">
+        <v>119</v>
+      </c>
+      <c r="G210"/>
+      <c r="H210"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K210"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="F211">
+        <v>1</v>
+      </c>
+      <c r="G211"/>
+      <c r="H211"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="K211"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S211"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D212"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-05-24T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F212">
+        <v>904</v>
+      </c>
+      <c r="G212">
+        <v>395</v>
+      </c>
+      <c r="H212">
+        <v>904</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-026</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D213"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-05-24T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F213">
+        <v>106</v>
+      </c>
+      <c r="G213">
+        <v>10</v>
+      </c>
+      <c r="H213">
+        <v>106</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-026</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C214" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D205"/>
-      <c r="E205" t="inlineStr">
+      <c r="D214"/>
+      <c r="E214" t="inlineStr">
         <is>
           <t>2026-05-24T23:59:59Z</t>
         </is>
       </c>
-      <c r="F205">
+      <c r="F214">
         <v>179</v>
       </c>
-      <c r="G205">
+      <c r="G214">
         <v>106</v>
       </c>
-      <c r="H205">
+      <c r="H214">
         <v>179</v>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I214" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J205" t="inlineStr">
+      <c r="J214" t="inlineStr">
         <is>
           <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K214" t="inlineStr">
         <is>
           <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t>BDBV-CLAIM-026</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
+      <c r="N214" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
+      <c r="O214" t="inlineStr">
         <is>
           <t>https://administration.sante.gouv.cd/graphql</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr">
+      <c r="P214" t="inlineStr">
         <is>
           <t>f3d5149176d77cbf28d15c79bb7449b1a516c6b855ffe28d51b2adaef0f4bff5</t>
         </is>
       </c>
-      <c r="Q205" t="inlineStr">
+      <c r="Q214" t="inlineStr">
         <is>
           <t>private_restricted_bytes</t>
         </is>
       </c>
-      <c r="R205" t="inlineStr">
+      <c r="R214" t="inlineStr">
         <is>
           <t>publisher-terms-not-confirmed</t>
         </is>
       </c>
-      <c r="S205"/>
+      <c r="S214"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S205"/>
+  <autoFilter ref="A1:S214"/>
 </worksheet>
 </file>
 
@@ -41387,7 +42523,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:deaths_confirmed_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -41397,11 +42533,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D185">
-        <v>9</v>
+        <v>101</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -41410,27 +42546,27 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K185"/>
@@ -41438,7 +42574,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -41448,11 +42584,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D186">
-        <v>176</v>
+        <v>101</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -41461,27 +42597,27 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K186"/>
@@ -41489,7 +42625,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:cases_confirmed_uganda</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -41499,11 +42635,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D187">
-        <v>176</v>
+        <v>7</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -41512,27 +42648,27 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K187"/>
@@ -41540,7 +42676,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:deaths_uganda</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:contacts_followed_percent</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -41550,11 +42686,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>contacts_followed_percent</t>
         </is>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -41563,27 +42699,27 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K188"/>
@@ -41591,7 +42727,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:contacts_identified_drc</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -41601,11 +42737,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
+          <t>contacts_identified_drc</t>
         </is>
       </c>
       <c r="D189">
-        <v>746</v>
+        <v>1745</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -41614,27 +42750,27 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-23</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-23</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K189"/>
@@ -41642,7 +42778,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected_drc</t>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_confirmed_drc</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -41652,11 +42788,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D190">
-        <v>746</v>
+        <v>9</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -41693,21 +42829,21 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed</t>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D191">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -41716,12 +42852,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -41731,7 +42867,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -41744,21 +42880,21 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_drc</t>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_suspected_drc</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D192">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -41767,12 +42903,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -41782,7 +42918,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
@@ -41795,21 +42931,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_total</t>
+          <t>timeline:cdc-current-situation-2026-05-23:deaths_uganda</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D193">
-        <v>106</v>
+        <v>1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -41818,12 +42954,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -41833,7 +42969,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -41846,21 +42982,21 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_uganda</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_confirmed_drc</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D194">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -41869,27 +43005,27 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K194"/>
@@ -41897,21 +43033,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_united_states</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_suspected</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -41920,27 +43056,27 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K195"/>
@@ -41948,21 +43084,21 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:new_confirmed_cases_uganda</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:deaths_uganda</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>confirmed_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -41971,27 +43107,27 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K196"/>
@@ -41999,21 +43135,21 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:deaths_confirmed_drc</t>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>suspected_cases</t>
         </is>
       </c>
       <c r="D197">
-        <v>10</v>
+        <v>746</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -42022,12 +43158,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -42037,7 +43173,7 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -42050,21 +43186,21 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:deaths_suspected</t>
+          <t>timeline:cdc-current-situation-2026-05-23:cases_suspected_drc</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>suspected_cases</t>
         </is>
       </c>
       <c r="D198">
-        <v>119</v>
+        <v>746</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -42073,12 +43209,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:cdc-current-situation-2026-05-23</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -42088,7 +43224,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>1fa637ba0cb4ab11c50438b226bf00ebeca62757eda73a5738f4e6f231cdaed8</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -42101,21 +43237,21 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:deaths_suspected_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-25-live:cases_suspected</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>suspected_cases</t>
         </is>
       </c>
       <c r="D199">
-        <v>119</v>
+        <v>904</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -42124,27 +43260,27 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>0636fc9b56903b84f738b1662879a6374d98946d3bb7fd58d20b4fed012ff57c</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K199"/>
@@ -42152,7 +43288,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:deaths_uganda</t>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -42162,11 +43298,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -42203,7 +43339,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-24:cases_suspected</t>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -42213,11 +43349,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D201">
-        <v>904</v>
+        <v>101</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -42254,56 +43390,515 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D202">
+        <v>106</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K202"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D203">
+        <v>5</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K203"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D204">
+        <v>0</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K204"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:new_confirmed_cases_uganda</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D205">
+        <v>3</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K205"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D206">
+        <v>10</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K206"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D207">
+        <v>119</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K207"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D208">
+        <v>119</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D209">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K209"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-24:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D210">
+        <v>904</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-24</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
           <t>timeline:cdc-current-situation-2026-05-24:cases_suspected_drc</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>suspected_cases</t>
         </is>
       </c>
-      <c r="D202">
+      <c r="D211">
         <v>904</v>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F211" t="inlineStr">
         <is>
           <t>cdc-current-situation-2026-05-24</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G211" t="inlineStr">
         <is>
           <t>source_manifest:cdc-current-situation-2026-05-24</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H211" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I211" t="inlineStr">
         <is>
           <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
         </is>
       </c>
-      <c r="J202" t="inlineStr">
+      <c r="J211" t="inlineStr">
         <is>
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="K202"/>
+      <c r="K211"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K202"/>
+  <autoFilter ref="A1:K211"/>
 </worksheet>
 </file>
 

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
     </row>
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -819,7 +819,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (761 to 1171 at deaths 179), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 761 to 1171 at deaths 179, CFR 40 to 26</t>
+          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 948 to 1458 at deaths 223, CFR 40 to 26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 761 to 1171 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
+          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 948 to 1458 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 106; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 27 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.4% lower bounds and 1.8-46.9% upper bounds.</t>
+          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.1% lower bounds and 1.9-49.1% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed cumulative table exists, keep the 27 cases unallocated and do not derive corridor risks from the 106 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
+          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed cumulative table exists, keep the 33 cases unallocated and do not derive corridor risks from the 112 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1353,47 +1353,94 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Bdbv may25 official release</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>The May 25 public snapshot supersedes the May 24 snapshot by fix-forward (a new dated snapshot, not an in-place re-cut) and uses the US CDC Current Situation page (25 May) as the highest valid primary on the latest date for suspected, confirmed, and deaths. ECDC (25 May), the DRC MoH all-published-bulletins dashboard aggregate (24 May), and WHO DG (22 May) are retained as dated conflict anchors. The endpoint takes the higher valid primary and does not average across sources or down-revise to a lower peer.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>US CDC 25 May reports 906 suspected DRC cases, 112 confirmed (105 DRC + 7 Uganda), 223 suspected DRC deaths, ten confirmed DRC deaths, and one Uganda death. ECDC 25 May reports 101 confirmed, 904 suspected, and 119 suspected deaths. The DRC MoH 24 May dashboard aggregate reports 854 reported cases, 112 confirmed DRC cases, and 179 registered deaths. The reconciled endpoint takes CDC's 906 suspected, 112 confirmed, and 223 deaths; the lower or source-review figures 179, 119, and 177 are dated conflict anchors.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>US CDC. Ebola Disease: Current Situation, 25 May 2026.; European Centre for Disease Prevention and Control. Ebola virus disease outbreak in the DRC and Uganda, outbreak page, 25 May 2026.; data/bundibugyo-2026/manifest.json entries cdc-current-situation-2026-05-25 and ecdc-bdbv-drc-uga-2026-05-25-live.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html; https://www.ecdc.europa.eu/en/ebola-virus-disease; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Keep the May 25 snapshot as review-ready evidence-backed state. Hold public release for the founder go-signal. Revisit the deaths endpoint if a later official PDF or table reconciles the CDC-versus-ECDC suspected-death spread.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-028</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Bdbv may25 source review boundary</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>May 25 source-review evidence can be archived for audit and partner context without creating a May 25 public snapshot route or promoting non-primary/watch claims into scored counts.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>ECDC 25 May is accepted as regional cross-check only (snapshot_trigger=false); WHO AFRO hub is official context/readiness only (snapshot_trigger=false); IFRC requires browser/AIR capture when plain HTTP is challenged; Wikipedia remains watch-only unless confirmed by public-health authority.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>supported</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>ECDC. Ebola virus disease outbreak in the Democratic Republic of the Congo and Uganda. Page last updated 25 May 2026 16:30.; WHO Regional Office for Africa. Ongoing outbreak in the Democratic Republic of the Congo / Bundibugyo virus disease outbreak hub. Updated 24 May 2026.; IFRC. Ebola: IFRC scales up response in eastern DRC as regional risks grow. 21 May 2026.; Wikipedia contributors. 2026 Ituri Province Ebola epidemic, live page observed by 25 May 2026 freshness check.; data/external_sources/freshness/bdbv-2026-2026-05-25.json generated by source_ingest.py --live-check --as-of 2026-05-25.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026; https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26; https://www.ifrc.org/press-release/ebola-ifrc-scales-response-eastern-drc-regional-risks-grow; https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic; restricted-local-review-not-redistributed</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Keep May 24 as the current publication-state route. Continue source review for DRC MoH table semantics, CDC traveler context, and future primary WHO/DRC/Uganda/CDC updates before any May 25 snapshot promotion.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Detailed audit IDs and review locators are withheld from this public export.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I26"/>
 </worksheet>
 </file>
 
@@ -3750,8 +3797,66 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>US Centers for Disease Control and Prevention</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-25T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-25T22:17:34Z</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="J41"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L41"/>
 </worksheet>
 </file>
 
@@ -8260,7 +8365,7 @@
       <c r="I10"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (761 to 1171 at deaths 179), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11081,12 +11186,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
       <c r="E2"/>
@@ -11120,7 +11225,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D3"/>
@@ -16124,8 +16229,141 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>source_data_report_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D122"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>source_publication_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D123"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-05-25T22:17:34Z</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I121"/>
+  <autoFilter ref="A1:I124"/>
 </worksheet>
 </file>
 
@@ -32851,34 +33089,34 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D212"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F212">
-        <v>904</v>
-      </c>
-      <c r="G212">
-        <v>395</v>
-      </c>
-      <c r="H212">
-        <v>904</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>count</t>
@@ -32886,27 +33124,23 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K212"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -32916,7 +33150,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -32934,12 +33168,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -32947,21 +33181,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D213"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F213">
-        <v>106</v>
-      </c>
-      <c r="G213">
-        <v>10</v>
-      </c>
-      <c r="H213">
-        <v>106</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G213"/>
+      <c r="H213"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>count</t>
@@ -32969,27 +33203,23 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K213"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -32999,7 +33229,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -33012,97 +33242,1053 @@
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+      <c r="S213"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F214">
+        <v>112</v>
+      </c>
+      <c r="G214"/>
+      <c r="H214"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K214"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F215">
+        <v>7</v>
+      </c>
+      <c r="G215"/>
+      <c r="H215"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K215"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K216"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F217">
+        <v>906</v>
+      </c>
+      <c r="G217"/>
+      <c r="H217"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K217"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F218">
+        <v>906</v>
+      </c>
+      <c r="G218"/>
+      <c r="H218"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K218"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F219">
+        <v>10</v>
+      </c>
+      <c r="G219"/>
+      <c r="H219"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K219"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F220">
+        <v>223</v>
+      </c>
+      <c r="G220"/>
+      <c r="H220"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K220"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S220"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F221">
+        <v>223</v>
+      </c>
+      <c r="G221"/>
+      <c r="H221"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K221"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222"/>
+      <c r="H222"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K222"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F223">
+        <v>200</v>
+      </c>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K223"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D224"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F224">
+        <v>906</v>
+      </c>
+      <c r="G224">
+        <v>395</v>
+      </c>
+      <c r="H224">
+        <v>906</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D225"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F225">
+        <v>112</v>
+      </c>
+      <c r="G225">
+        <v>10</v>
+      </c>
+      <c r="H225">
+        <v>112</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D214"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2026-05-24T23:59:59Z</t>
-        </is>
-      </c>
-      <c r="F214">
-        <v>179</v>
-      </c>
-      <c r="G214">
+      <c r="D226"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F226">
+        <v>223</v>
+      </c>
+      <c r="G226">
         <v>106</v>
       </c>
-      <c r="H214">
-        <v>179</v>
-      </c>
-      <c r="I214" t="inlineStr">
+      <c r="H226">
+        <v>223</v>
+      </c>
+      <c r="I226" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>BDBV-CLAIM-026</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr">
+      <c r="N226" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>https://administration.sante.gouv.cd/graphql</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>f3d5149176d77cbf28d15c79bb7449b1a516c6b855ffe28d51b2adaef0f4bff5</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>private_restricted_bytes</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>publisher-terms-not-confirmed</t>
-        </is>
-      </c>
-      <c r="S214"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S226"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S214"/>
+  <autoFilter ref="A1:S226"/>
 </worksheet>
 </file>
 
@@ -43897,8 +45083,620 @@
       </c>
       <c r="K211"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D212">
+        <v>112</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D213">
+        <v>105</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D214">
+        <v>112</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D215">
+        <v>7</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D217">
+        <v>10</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D218">
+        <v>223</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D219">
+        <v>223</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K220"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D221">
+        <v>200</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D222">
+        <v>906</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>906</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K223"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K211"/>
+  <autoFilter ref="A1:K223"/>
 </worksheet>
 </file>
 
@@ -45222,7 +47020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:arua-uga</t>
+          <t>corridor:01:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -45232,33 +47030,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.0912163373057068</v>
+        <v>0.08705872476656829</v>
       </c>
       <c r="F2">
-        <v>0.2226702397521661</v>
+        <v>0.23849877729636965</v>
       </c>
       <c r="G2">
-        <v>0.21390472120489915</v>
+        <v>0.20200901575875693</v>
       </c>
       <c r="H2">
-        <v>0.4694422290811111</v>
+        <v>0.490855636804455</v>
       </c>
       <c r="I2">
-        <v>0.04532749822980132</v>
+        <v>0.05827234299127523</v>
       </c>
       <c r="J2">
-        <v>0.6911278013787443</v>
+        <v>0.7360585970208364</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -45278,7 +47076,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -45290,7 +47088,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:nebbi-uga</t>
+          <t>corridor:02:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -45300,33 +47098,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08452455181245988</v>
+        <v>0.09106071850782033</v>
       </c>
       <c r="F3">
-        <v>0.22265814712920945</v>
+        <v>0.23180304927763629</v>
       </c>
       <c r="G3">
-        <v>0.19925818749831423</v>
+        <v>0.21064783365598588</v>
       </c>
       <c r="H3">
-        <v>0.4694209392975942</v>
+        <v>0.47969244396961136</v>
       </c>
       <c r="I3">
-        <v>0.06671907792458477</v>
+        <v>0.05967373659336905</v>
       </c>
       <c r="J3">
-        <v>0.7039957005098051</v>
+        <v>0.7123311692401879</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -45346,7 +47144,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -45358,7 +47156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:kampala-uga</t>
+          <t>corridor:03:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -45368,33 +47166,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.0837536879207027</v>
+        <v>0.08277521513409741</v>
       </c>
       <c r="F4">
-        <v>0.22263658502383896</v>
+        <v>0.22641515556489766</v>
       </c>
       <c r="G4">
-        <v>0.19756045935788125</v>
+        <v>0.19270105652080258</v>
       </c>
       <c r="H4">
-        <v>0.46938420491713334</v>
+        <v>0.47060445029291187</v>
       </c>
       <c r="I4">
-        <v>0.049090364064060366</v>
+        <v>0.058851102281542125</v>
       </c>
       <c r="J4">
-        <v>0.7378909709414584</v>
+        <v>0.7381007215516742</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -45414,7 +47212,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -45426,7 +47224,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:beni-cod</t>
+          <t>corridor:04:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -45436,33 +47234,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08539306320934745</v>
+        <v>0.0777667177980044</v>
       </c>
       <c r="F5">
-        <v>0.21732595153426423</v>
+        <v>0.22125498504359012</v>
       </c>
       <c r="G5">
-        <v>0.20116768514208086</v>
+        <v>0.18173566771392538</v>
       </c>
       <c r="H5">
-        <v>0.4602154648850442</v>
+        <v>0.46181259202543024</v>
       </c>
       <c r="I5">
-        <v>0.06296500819577727</v>
+        <v>0.04687532836669559</v>
       </c>
       <c r="J5">
-        <v>0.6925655607803819</v>
+        <v>0.7431942191372538</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -45482,7 +47280,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -45511,26 +47309,26 @@
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08585999321999954</v>
+        <v>0.08994167609221052</v>
       </c>
       <c r="F6">
-        <v>0.2142466100194772</v>
+        <v>0.21814102710172356</v>
       </c>
       <c r="G6">
-        <v>0.20219412729622327</v>
+        <v>0.2082377356100764</v>
       </c>
       <c r="H6">
-        <v>0.45485593395145274</v>
+        <v>0.4564648825278334</v>
       </c>
       <c r="I6">
-        <v>0.06638378793530512</v>
+        <v>0.06843498725883312</v>
       </c>
       <c r="J6">
-        <v>0.7375416502530325</v>
+        <v>0.7351838704184875</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -45550,7 +47348,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -45562,7 +47360,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corridor:06:rwampara:kasese-uga</t>
+          <t>corridor:06:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -45572,33 +47370,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08862360450035126</v>
+        <v>0.08738592639250203</v>
       </c>
       <c r="F7">
-        <v>0.21187297147959527</v>
+        <v>0.21691539014958308</v>
       </c>
       <c r="G7">
-        <v>0.20824918095316647</v>
+        <v>0.20271776834032668</v>
       </c>
       <c r="H7">
-        <v>0.45070261253386334</v>
+        <v>0.4543515172508829</v>
       </c>
       <c r="I7">
-        <v>0.04755485008790408</v>
+        <v>0.0606006699211846</v>
       </c>
       <c r="J7">
-        <v>0.712627902824087</v>
+        <v>0.7294259710737864</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -45618,7 +47416,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -45630,7 +47428,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:bunia:arua-uga</t>
+          <t>corridor:07:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -45640,33 +47438,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.04135954827362884</v>
+        <v>0.04246356113673297</v>
       </c>
       <c r="F8">
-        <v>0.11983328959815714</v>
+        <v>0.11942130278737001</v>
       </c>
       <c r="G8">
-        <v>0.10083207797214216</v>
+        <v>0.10192493852909751</v>
       </c>
       <c r="H8">
-        <v>0.2747126636812153</v>
+        <v>0.270266609097878</v>
       </c>
       <c r="I8">
-        <v>0.029212073563033354</v>
+        <v>0.028409667809219823</v>
       </c>
       <c r="J8">
-        <v>0.4662213001716538</v>
+        <v>0.46391565999619183</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -45686,7 +47484,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -45698,7 +47496,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:nebbi-uga</t>
+          <t>corridor:08:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -45708,33 +47506,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04398227300651175</v>
+        <v>0.04372720174962935</v>
       </c>
       <c r="F9">
-        <v>0.11642476266588117</v>
+        <v>0.11776659374999701</v>
       </c>
       <c r="G9">
-        <v>0.10700893044190996</v>
+        <v>0.10485843323233299</v>
       </c>
       <c r="H9">
-        <v>0.26762425390736977</v>
+        <v>0.2668648630838556</v>
       </c>
       <c r="I9">
-        <v>0.03323309459346699</v>
+        <v>0.024824081936019447</v>
       </c>
       <c r="J9">
-        <v>0.48792183288806773</v>
+        <v>0.47074791691760753</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -45754,7 +47552,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -45766,7 +47564,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:kampala-uga</t>
+          <t>corridor:09:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -45776,33 +47574,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04216514495541318</v>
+        <v>0.043721416421617726</v>
       </c>
       <c r="F10">
-        <v>0.11487490058729838</v>
+        <v>0.11772211441413447</v>
       </c>
       <c r="G10">
-        <v>0.10273220880627104</v>
+        <v>0.1048450145946053</v>
       </c>
       <c r="H10">
-        <v>0.26438756064883345</v>
+        <v>0.2667733722448983</v>
       </c>
       <c r="I10">
-        <v>0.033514354068220314</v>
+        <v>0.03158643596552796</v>
       </c>
       <c r="J10">
-        <v>0.4600121524453567</v>
+        <v>0.4736878533835456</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -45822,7 +47620,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -45834,7 +47632,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:beni-cod</t>
+          <t>corridor:10:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -45844,33 +47642,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.038990402689660864</v>
+        <v>0.0444155412592947</v>
       </c>
       <c r="F11">
-        <v>0.11434892428716492</v>
+        <v>0.11571118127048804</v>
       </c>
       <c r="G11">
-        <v>0.09522978243904648</v>
+        <v>0.10645391938867926</v>
       </c>
       <c r="H11">
-        <v>0.2632867689300544</v>
+        <v>0.2626253665816084</v>
       </c>
       <c r="I11">
-        <v>0.029063057329189432</v>
+        <v>0.03078606866593397</v>
       </c>
       <c r="J11">
-        <v>0.4767924217921794</v>
+        <v>0.4883461510873249</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -45890,7 +47688,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -45902,43 +47700,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:arua-uga</t>
+          <t>corridor:11:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.03536372093507828</v>
+        <v>0.04410979236313228</v>
       </c>
       <c r="F12">
-        <v>0.11162698694924067</v>
+        <v>0.11505461271845879</v>
       </c>
       <c r="G12">
-        <v>0.08661374204772454</v>
+        <v>0.10574531651674063</v>
       </c>
       <c r="H12">
-        <v>0.25757649648927927</v>
+        <v>0.26126870223516685</v>
       </c>
       <c r="I12">
-        <v>0.02600635405233129</v>
+        <v>0.028827859136638982</v>
       </c>
       <c r="J12">
-        <v>0.4314625171558782</v>
+        <v>0.4349056791496498</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -45958,7 +47756,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -45970,7 +47768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:bundibugyo-uga</t>
+          <t>corridor:12:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -45980,33 +47778,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.041168739753125294</v>
+        <v>0.04061609325636212</v>
       </c>
       <c r="F13">
-        <v>0.1107501387756348</v>
+        <v>0.11396739072964437</v>
       </c>
       <c r="G13">
-        <v>0.10038168382708493</v>
+        <v>0.09762606642203506</v>
       </c>
       <c r="H13">
-        <v>0.25573121824365375</v>
+        <v>0.25901826950891554</v>
       </c>
       <c r="I13">
-        <v>0.02427074965026969</v>
+        <v>0.02387539752522782</v>
       </c>
       <c r="J13">
-        <v>0.4571962132606071</v>
+        <v>0.4461622227370582</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -46026,7 +47824,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -46038,7 +47836,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:kampala-uga</t>
+          <t>corridor:13:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -46048,33 +47846,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.03840747902562522</v>
+        <v>0.03710996846095013</v>
       </c>
       <c r="F14">
-        <v>0.11022468214471043</v>
+        <v>0.10964681236938656</v>
       </c>
       <c r="G14">
-        <v>0.09384836785268524</v>
+        <v>0.08943382811819442</v>
       </c>
       <c r="H14">
-        <v>0.2546240929072371</v>
+        <v>0.250034224844084</v>
       </c>
       <c r="I14">
-        <v>0.02339760290109348</v>
+        <v>0.03385391457147437</v>
       </c>
       <c r="J14">
-        <v>0.45366135584564343</v>
+        <v>0.46993004228955715</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -46094,7 +47892,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -46106,7 +47904,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:14:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -46116,33 +47914,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.042622724856425986</v>
+        <v>0.042080228665137914</v>
       </c>
       <c r="F15">
-        <v>0.10994385490859934</v>
+        <v>0.10683766833988695</v>
       </c>
       <c r="G15">
-        <v>0.1038104281778379</v>
+        <v>0.10103406480576219</v>
       </c>
       <c r="H15">
-        <v>0.25403199640798074</v>
+        <v>0.24415829376737277</v>
       </c>
       <c r="I15">
-        <v>0.028277498811380836</v>
+        <v>0.027024110522923</v>
       </c>
       <c r="J15">
-        <v>0.4533285985841223</v>
+        <v>0.4126434945709156</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -46162,7 +47960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -46174,43 +47972,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:bunia:kasese-uga</t>
+          <t>corridor:15:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.039893708218035395</v>
+        <v>0.04202426525540365</v>
       </c>
       <c r="F16">
-        <v>0.10839783417298046</v>
+        <v>0.10608468442723934</v>
       </c>
       <c r="G16">
-        <v>0.09736829629570376</v>
+        <v>0.10090394584352139</v>
       </c>
       <c r="H16">
-        <v>0.25076635038617995</v>
+        <v>0.24257853052369338</v>
       </c>
       <c r="I16">
-        <v>0.022945425424494254</v>
+        <v>0.025730387416915464</v>
       </c>
       <c r="J16">
-        <v>0.45584132979198283</v>
+        <v>0.4196281916748507</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -46230,7 +48028,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -46242,7 +48040,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:nebbi-uga</t>
+          <t>corridor:16:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -46252,33 +48050,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.03885897551186415</v>
+        <v>0.03933542211197083</v>
       </c>
       <c r="F17">
-        <v>0.10809533543848754</v>
+        <v>0.10546729596630738</v>
       </c>
       <c r="G17">
-        <v>0.09491863955491664</v>
+        <v>0.09463884639695044</v>
       </c>
       <c r="H17">
-        <v>0.25012728395195716</v>
+        <v>0.24128195279119546</v>
       </c>
       <c r="I17">
-        <v>0.029075868004294698</v>
+        <v>0.024899713049719586</v>
       </c>
       <c r="J17">
-        <v>0.4187443071247904</v>
+        <v>0.45412776873008587</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -46298,7 +48096,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -46327,26 +48125,26 @@
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.040512046777299554</v>
+        <v>0.03674677955972819</v>
       </c>
       <c r="F18">
-        <v>0.1055105651614231</v>
+        <v>0.10253826350865747</v>
       </c>
       <c r="G18">
-        <v>0.09883047424769487</v>
+        <v>0.08858269196104879</v>
       </c>
       <c r="H18">
-        <v>0.24464677320153547</v>
+        <v>0.2351121722828113</v>
       </c>
       <c r="I18">
-        <v>0.02918801892369734</v>
+        <v>0.02446060018301769</v>
       </c>
       <c r="J18">
-        <v>0.4609928209129825</v>
+        <v>0.43434320993589176</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -46366,7 +48164,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -46378,7 +48176,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:beni-cod</t>
+          <t>corridor:18:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -46388,33 +48186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.039473762203850765</v>
+        <v>0.03673769680232783</v>
       </c>
       <c r="F19">
-        <v>0.10362489156884852</v>
+        <v>0.10176519464035952</v>
       </c>
       <c r="G19">
-        <v>0.09637461819714294</v>
+        <v>0.08856139661635878</v>
       </c>
       <c r="H19">
-        <v>0.24063384235105276</v>
+        <v>0.23347872961217356</v>
       </c>
       <c r="I19">
-        <v>0.023570590511507086</v>
+        <v>0.019766568129704724</v>
       </c>
       <c r="J19">
-        <v>0.4323792575072521</v>
+        <v>0.45173277256401556</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -46434,7 +48232,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -46446,7 +48244,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:bundibugyo-uga</t>
+          <t>corridor:19:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -46456,33 +48254,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.03571317240808905</v>
+        <v>0.02943619547001522</v>
       </c>
       <c r="F20">
-        <v>0.08858542009424464</v>
+        <v>0.08644089973446445</v>
       </c>
       <c r="G20">
-        <v>0.08744601480295106</v>
+        <v>0.07134929740790441</v>
       </c>
       <c r="H20">
-        <v>0.20816581788193778</v>
+        <v>0.20067080506318333</v>
       </c>
       <c r="I20">
-        <v>0.02794960657154857</v>
+        <v>0.017249897635217455</v>
       </c>
       <c r="J20">
-        <v>0.3464635789222376</v>
+        <v>0.37720643415082816</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -46502,7 +48300,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -46514,7 +48312,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:arua-uga</t>
+          <t>corridor:20:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -46524,33 +48322,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03264229590569645</v>
+        <v>0.03143620060038951</v>
       </c>
       <c r="F21">
-        <v>0.08586088011945975</v>
+        <v>0.08597135121230412</v>
       </c>
       <c r="G21">
-        <v>0.08011583054612229</v>
+        <v>0.0760830743974528</v>
       </c>
       <c r="H21">
-        <v>0.20219610083896622</v>
+        <v>0.19965252253419963</v>
       </c>
       <c r="I21">
-        <v>0.023533108201656935</v>
+        <v>0.026413643415756798</v>
       </c>
       <c r="J21">
-        <v>0.35610832817909704</v>
+        <v>0.3875565167376865</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -46570,7 +48368,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -46582,7 +48380,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:kampala-uga</t>
+          <t>corridor:21:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -46592,33 +48390,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.029377911723571293</v>
+        <v>0.033545219747423194</v>
       </c>
       <c r="F22">
-        <v>0.08201035370872972</v>
+        <v>0.08571847788474835</v>
       </c>
       <c r="G22">
-        <v>0.07228482019525184</v>
+        <v>0.08105927552190084</v>
       </c>
       <c r="H22">
-        <v>0.19371312977138444</v>
+        <v>0.19910390583267018</v>
       </c>
       <c r="I22">
-        <v>0.01774942777466498</v>
+        <v>0.02488466056117501</v>
       </c>
       <c r="J22">
-        <v>0.378011129181644</v>
+        <v>0.3750758008783629</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -46638,7 +48436,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -46650,7 +48448,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:beni-cod</t>
+          <t>corridor:22:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -46660,33 +48458,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.029460858829418568</v>
+        <v>0.03209426849587091</v>
       </c>
       <c r="F23">
-        <v>0.08095304945678247</v>
+        <v>0.08294965297286142</v>
       </c>
       <c r="G23">
-        <v>0.07248432245564349</v>
+        <v>0.07763750605795702</v>
       </c>
       <c r="H23">
-        <v>0.1913742950989335</v>
+        <v>0.19308102183167064</v>
       </c>
       <c r="I23">
-        <v>0.019818390626375203</v>
+        <v>0.01788217072461529</v>
       </c>
       <c r="J23">
-        <v>0.3257214893602651</v>
+        <v>0.34301640031334013</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -46706,7 +48504,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -46718,7 +48516,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:kasese-uga</t>
+          <t>corridor:23:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -46728,33 +48526,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.030671572216132148</v>
+        <v>0.02866534159045145</v>
       </c>
       <c r="F24">
-        <v>0.08068683653973213</v>
+        <v>0.08246390394965086</v>
       </c>
       <c r="G24">
-        <v>0.07539301823448152</v>
+        <v>0.0695208928496309</v>
       </c>
       <c r="H24">
-        <v>0.19078484133652965</v>
+        <v>0.19202205699078656</v>
       </c>
       <c r="I24">
-        <v>0.019185526848990185</v>
+        <v>0.016730935405880526</v>
       </c>
       <c r="J24">
-        <v>0.36091283002425634</v>
+        <v>0.364088590258062</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -46774,7 +48572,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -46786,7 +48584,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:nebbi-uga</t>
+          <t>corridor:24:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -46796,33 +48594,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.030591361644302484</v>
+        <v>0.03081565613688028</v>
       </c>
       <c r="F25">
-        <v>0.08048830355982659</v>
+        <v>0.08049341862637019</v>
       </c>
       <c r="G25">
-        <v>0.07520043792455658</v>
+        <v>0.07461586978106036</v>
       </c>
       <c r="H25">
-        <v>0.190345024854301</v>
+        <v>0.18771637107786493</v>
       </c>
       <c r="I25">
-        <v>0.021021863745825663</v>
+        <v>0.026248954426468973</v>
       </c>
       <c r="J25">
-        <v>0.350237662341076</v>
+        <v>0.3381175600724034</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -46842,7 +48640,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -46854,7 +48652,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:kasese-uga</t>
+          <t>corridor:25:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -46864,33 +48662,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.00566357846163032</v>
+        <v>0.006029262723708073</v>
       </c>
       <c r="F26">
-        <v>0.0168189945872127</v>
+        <v>0.017114033671260853</v>
       </c>
       <c r="G26">
-        <v>0.014189997894389739</v>
+        <v>0.014870934354623777</v>
       </c>
       <c r="H26">
-        <v>0.04178316258612558</v>
+        <v>0.04186515305349886</v>
       </c>
       <c r="I26">
-        <v>0.003642365369538583</v>
+        <v>0.004470615331371439</v>
       </c>
       <c r="J26">
-        <v>0.08338795718242407</v>
+        <v>0.0770842786162016</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -46910,7 +48708,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -46922,7 +48720,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:kampala-uga</t>
+          <t>corridor:26:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -46932,33 +48730,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.005570451792462239</v>
+        <v>0.005522357235792252</v>
       </c>
       <c r="F27">
-        <v>0.016523396691662473</v>
+        <v>0.016224882815260827</v>
       </c>
       <c r="G27">
-        <v>0.013957658459393757</v>
+        <v>0.013625786217095454</v>
       </c>
       <c r="H27">
-        <v>0.04105807768030023</v>
+        <v>0.039716335710117456</v>
       </c>
       <c r="I27">
-        <v>0.004065924990798628</v>
+        <v>0.0035817052958976416</v>
       </c>
       <c r="J27">
-        <v>0.0783570979599987</v>
+        <v>0.07992818660808958</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -46978,7 +48776,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -46990,7 +48788,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:nebbi-uga</t>
+          <t>corridor:27:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -47000,33 +48798,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.0058766644079958075</v>
+        <v>0.005763485989899592</v>
       </c>
       <c r="F28">
-        <v>0.015576503650650497</v>
+        <v>0.015897712364671857</v>
       </c>
       <c r="G28">
-        <v>0.014721496800445155</v>
+        <v>0.01421820486301828</v>
       </c>
       <c r="H28">
-        <v>0.03873315623063381</v>
+        <v>0.038924937410599686</v>
       </c>
       <c r="I28">
-        <v>0.0031251689189409713</v>
+        <v>0.00412817012599338</v>
       </c>
       <c r="J28">
-        <v>0.08111023604042748</v>
+        <v>0.07530722471772157</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -47046,7 +48844,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -47058,7 +48856,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:beni-cod</t>
+          <t>corridor:28:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -47068,33 +48866,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.0056457725950707915</v>
+        <v>0.00569825474665156</v>
       </c>
       <c r="F29">
-        <v>0.015271156168351285</v>
+        <v>0.015708110329420072</v>
       </c>
       <c r="G29">
-        <v>0.014145577133137133</v>
+        <v>0.014057962115334166</v>
       </c>
       <c r="H29">
-        <v>0.03798273499621879</v>
+        <v>0.03846612710006386</v>
       </c>
       <c r="I29">
-        <v>0.003856294606997707</v>
+        <v>0.0030738801757677933</v>
       </c>
       <c r="J29">
-        <v>0.07660375034507658</v>
+        <v>0.08554865711076257</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -47114,7 +48912,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -47126,7 +48924,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:bundibugyo-uga</t>
+          <t>corridor:29:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -47136,33 +48934,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.0049699088501186095</v>
+        <v>0.006051188152445097</v>
       </c>
       <c r="F30">
-        <v>0.015117858841951992</v>
+        <v>0.01568874267670098</v>
       </c>
       <c r="G30">
-        <v>0.01245858544077938</v>
+        <v>0.014924768457324877</v>
       </c>
       <c r="H30">
-        <v>0.03760584808099718</v>
+        <v>0.03841925323098799</v>
       </c>
       <c r="I30">
-        <v>0.004351318719822542</v>
+        <v>0.003838228121916951</v>
       </c>
       <c r="J30">
-        <v>0.07699905023307309</v>
+        <v>0.08215270653449197</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -47182,7 +48980,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -47194,7 +48992,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:arua-uga</t>
+          <t>corridor:30:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -47204,33 +49002,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005409534124622251</v>
+        <v>0.005782262522765952</v>
       </c>
       <c r="F31">
-        <v>0.01477439647878373</v>
+        <v>0.015216280256187209</v>
       </c>
       <c r="G31">
-        <v>0.013556110803496668</v>
+        <v>0.014264327261309523</v>
       </c>
       <c r="H31">
-        <v>0.0367611052860419</v>
+        <v>0.03727535911897989</v>
       </c>
       <c r="I31">
-        <v>0.0038099731375384363</v>
+        <v>0.0033384218962603934</v>
       </c>
       <c r="J31">
-        <v>0.07985048552615662</v>
+        <v>0.07811576042493965</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -47250,7 +49048,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -47262,43 +49060,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:butembo:bundibugyo-uga</t>
+          <t>corridor:31:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.0029668846561548</v>
+        <v>0.0031221041967082197</v>
       </c>
       <c r="F32">
-        <v>0.008648404569959522</v>
+        <v>0.008698068132782094</v>
       </c>
       <c r="G32">
-        <v>0.00744871853801346</v>
+        <v>0.007717131898621776</v>
       </c>
       <c r="H32">
-        <v>0.021619303752781205</v>
+        <v>0.021411044648201427</v>
       </c>
       <c r="I32">
-        <v>0.0017127776636171044</v>
+        <v>0.0017828154968101114</v>
       </c>
       <c r="J32">
-        <v>0.03867924896503808</v>
+        <v>0.0431818978878234</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -47318,7 +49116,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -47330,43 +49128,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:nizi:kasese-uga</t>
+          <t>corridor:32:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.00286779665502937</v>
+        <v>0.003256550077390147</v>
       </c>
       <c r="F33">
-        <v>0.008456716056206709</v>
+        <v>0.008690654774771961</v>
       </c>
       <c r="G33">
-        <v>0.007200487783166232</v>
+        <v>0.008048651456418393</v>
       </c>
       <c r="H33">
-        <v>0.021143201820719187</v>
+        <v>0.02139291864359122</v>
       </c>
       <c r="I33">
-        <v>0.0016031328739968375</v>
+        <v>0.002208850691779005</v>
       </c>
       <c r="J33">
-        <v>0.04124369346445676</v>
+        <v>0.0397230321776111</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -47386,7 +49184,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -47398,43 +49196,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:bambu:beni-cod</t>
+          <t>corridor:33:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.003013732647334205</v>
+        <v>0.0029781199558879257</v>
       </c>
       <c r="F34">
-        <v>0.008437658403657261</v>
+        <v>0.008646396347219365</v>
       </c>
       <c r="G34">
-        <v>0.007566060778216588</v>
+        <v>0.00736201964546096</v>
       </c>
       <c r="H34">
-        <v>0.021095861835840557</v>
+        <v>0.021284669747048707</v>
       </c>
       <c r="I34">
-        <v>0.0014900168661657197</v>
+        <v>0.001720505229708283</v>
       </c>
       <c r="J34">
-        <v>0.04002250253804156</v>
+        <v>0.038678795905731755</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -47454,7 +49252,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -47466,43 +49264,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:butembo:nebbi-uga</t>
+          <t>corridor:34:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003046128650042168</v>
+        <v>0.003111181616698544</v>
       </c>
       <c r="F35">
-        <v>0.008413631722209353</v>
+        <v>0.008628383148852753</v>
       </c>
       <c r="G35">
-        <v>0.007647210019176343</v>
+        <v>0.007690196297224505</v>
       </c>
       <c r="H35">
-        <v>0.02103617594229515</v>
+        <v>0.021240605916741817</v>
       </c>
       <c r="I35">
-        <v>0.0019978706910661645</v>
+        <v>0.0016110230461111126</v>
       </c>
       <c r="J35">
-        <v>0.040842162929054585</v>
+        <v>0.043150308180892</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -47522,7 +49320,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -47534,7 +49332,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:bambu:kampala-uga</t>
+          <t>corridor:35:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -47544,33 +49342,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.002803891071768233</v>
+        <v>0.0030884074123188887</v>
       </c>
       <c r="F36">
-        <v>0.008410470868929015</v>
+        <v>0.008588026182462571</v>
       </c>
       <c r="G36">
-        <v>0.007040374520295156</v>
+        <v>0.007634031778964906</v>
       </c>
       <c r="H36">
-        <v>0.021028323783931435</v>
+        <v>0.02114189671152855</v>
       </c>
       <c r="I36">
-        <v>0.001983808750996477</v>
+        <v>0.0020051565560971376</v>
       </c>
       <c r="J36">
-        <v>0.04221535551667012</v>
+        <v>0.03964300574013423</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -47590,7 +49388,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -47602,12 +49400,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:36:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -47619,26 +49417,26 @@
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.0030254703539086825</v>
+        <v>0.003025775628822114</v>
       </c>
       <c r="F37">
-        <v>0.008302024512592543</v>
+        <v>0.008571115858547917</v>
       </c>
       <c r="G37">
-        <v>0.007595467076894652</v>
+        <v>0.007479562809800805</v>
       </c>
       <c r="H37">
-        <v>0.020758892754370956</v>
+        <v>0.021100531187123267</v>
       </c>
       <c r="I37">
-        <v>0.0019239494772106266</v>
+        <v>0.0021199327441538463</v>
       </c>
       <c r="J37">
-        <v>0.03967236765955354</v>
+        <v>0.04196071647036671</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -47658,7 +49456,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -47670,43 +49468,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:bambu:kasese-uga</t>
+          <t>corridor:37:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D38">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.003143077793635596</v>
+        <v>0.002797267917861973</v>
       </c>
       <c r="F38">
-        <v>0.00824148730856386</v>
+        <v>0.00846270517529632</v>
       </c>
       <c r="G38">
-        <v>0.007890017121025772</v>
+        <v>0.006915872271437584</v>
       </c>
       <c r="H38">
-        <v>0.02060847054148296</v>
+        <v>0.020835318333113584</v>
       </c>
       <c r="I38">
-        <v>0.0022432737764674915</v>
+        <v>0.0018633454289880586</v>
       </c>
       <c r="J38">
-        <v>0.043110322723682405</v>
+        <v>0.04328965085234269</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -47726,7 +49524,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -47738,43 +49536,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:nizi:arua-uga</t>
+          <t>corridor:38:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.002912215693761211</v>
+        <v>0.0027165842894116</v>
       </c>
       <c r="F39">
-        <v>0.008224729039250062</v>
+        <v>0.008462033120420043</v>
       </c>
       <c r="G39">
-        <v>0.0073117689802146835</v>
+        <v>0.006716793549505717</v>
       </c>
       <c r="H39">
-        <v>0.020566822397248136</v>
+        <v>0.020833674557079906</v>
       </c>
       <c r="I39">
-        <v>0.0020761411962235826</v>
+        <v>0.0020833936544929683</v>
       </c>
       <c r="J39">
-        <v>0.04050042360943858</v>
+        <v>0.03946198024192364</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -47794,7 +49592,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -47823,26 +49621,26 @@
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.00278351825972617</v>
+        <v>0.002827091182153685</v>
       </c>
       <c r="F40">
-        <v>0.008218801697601641</v>
+        <v>0.00844775188405536</v>
       </c>
       <c r="G40">
-        <v>0.006989327711157262</v>
+        <v>0.00698945216246713</v>
       </c>
       <c r="H40">
-        <v>0.020552098310094136</v>
+        <v>0.020798732145144022</v>
       </c>
       <c r="I40">
-        <v>0.0020186656917254436</v>
+        <v>0.002402073067513322</v>
       </c>
       <c r="J40">
-        <v>0.04178167469755334</v>
+        <v>0.04203889492505474</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -47862,7 +49660,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -47874,43 +49672,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:miti-murhesa:kampala-uga</t>
+          <t>corridor:40:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.002917199157010275</v>
+        <v>0.003098245083166251</v>
       </c>
       <c r="F41">
-        <v>0.008210588027216303</v>
+        <v>0.008421295606099832</v>
       </c>
       <c r="G41">
-        <v>0.007324252868381925</v>
+        <v>0.007658292806589306</v>
       </c>
       <c r="H41">
-        <v>0.0205316862710912</v>
+        <v>0.02073400424273225</v>
       </c>
       <c r="I41">
-        <v>0.0018646941450676275</v>
+        <v>0.0019012551291241716</v>
       </c>
       <c r="J41">
-        <v>0.039202128673268916</v>
+        <v>0.043972182665138686</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -47930,7 +49728,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -47942,43 +49740,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:goma-cod:arua-uga</t>
+          <t>corridor:41:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0029229943219314103</v>
+        <v>0.0028569543753373394</v>
       </c>
       <c r="F42">
-        <v>0.008200076441295834</v>
+        <v>0.008399426913836133</v>
       </c>
       <c r="G42">
-        <v>0.0073387711057757155</v>
+        <v>0.007063127009692638</v>
       </c>
       <c r="H42">
-        <v>0.02050556570307871</v>
+        <v>0.02068049618046927</v>
       </c>
       <c r="I42">
-        <v>0.002416971899848838</v>
+        <v>0.001940933593041583</v>
       </c>
       <c r="J42">
-        <v>0.0399238123747093</v>
+        <v>0.043335795648454876</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -47998,7 +49796,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -48010,43 +49808,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:bambu:nebbi-uga</t>
+          <t>corridor:42:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.0029578847553219656</v>
+        <v>0.003208969909536785</v>
       </c>
       <c r="F43">
-        <v>0.008182077561825735</v>
+        <v>0.008396225534473778</v>
       </c>
       <c r="G43">
-        <v>0.007426173507821376</v>
+        <v>0.007931333169932525</v>
       </c>
       <c r="H43">
-        <v>0.020460836970333962</v>
+        <v>0.020672662243381656</v>
       </c>
       <c r="I43">
-        <v>0.0019204820773748386</v>
+        <v>0.002451028146972545</v>
       </c>
       <c r="J43">
-        <v>0.03736221748994108</v>
+        <v>0.03828745231097391</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -48066,7 +49864,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -48078,43 +49876,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:butembo:kampala-uga</t>
+          <t>corridor:43:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.002809220150436914</v>
+        <v>0.0029666436131503826</v>
       </c>
       <c r="F44">
-        <v>0.008167798887166844</v>
+        <v>0.008357295677379833</v>
       </c>
       <c r="G44">
-        <v>0.007053727044364355</v>
+        <v>0.007333712327801806</v>
       </c>
       <c r="H44">
-        <v>0.02042535229876477</v>
+        <v>0.020577406853998614</v>
       </c>
       <c r="I44">
-        <v>0.002021133668671976</v>
+        <v>0.0017909766821187448</v>
       </c>
       <c r="J44">
-        <v>0.041858581949275345</v>
+        <v>0.04221199332021168</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -48134,7 +49932,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -48146,7 +49944,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:arua-uga</t>
+          <t>corridor:44:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -48156,33 +49954,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.003018664226666662</v>
+        <v>0.002842466144925393</v>
       </c>
       <c r="F45">
-        <v>0.008165091988575929</v>
+        <v>0.008306902670088073</v>
       </c>
       <c r="G45">
-        <v>0.0075784187553437354</v>
+        <v>0.007027383918706276</v>
       </c>
       <c r="H45">
-        <v>0.02041862413740289</v>
+        <v>0.02045409216417554</v>
       </c>
       <c r="I45">
-        <v>0.0020682252418399495</v>
+        <v>0.001971915409122316</v>
       </c>
       <c r="J45">
-        <v>0.04398886439373007</v>
+        <v>0.040177434293513725</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -48202,7 +50000,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -48214,12 +50012,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:butembo:arua-uga</t>
+          <t>corridor:45:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -48231,26 +50029,26 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.002806560204559716</v>
+        <v>0.0029776446786048127</v>
       </c>
       <c r="F46">
-        <v>0.008123680596680921</v>
+        <v>0.00827436066103368</v>
       </c>
       <c r="G46">
-        <v>0.007047062151783884</v>
+        <v>0.007360847692718359</v>
       </c>
       <c r="H46">
-        <v>0.020315706599612765</v>
+        <v>0.020374455899091842</v>
       </c>
       <c r="I46">
-        <v>0.0017574721703900373</v>
+        <v>0.0020194029902177533</v>
       </c>
       <c r="J46">
-        <v>0.04275438546425416</v>
+        <v>0.0390744440809115</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -48270,7 +50068,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -48282,7 +50080,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:butembo:beni-cod</t>
+          <t>corridor:46:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -48292,33 +50090,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.002679528990868457</v>
+        <v>0.0027549525104297867</v>
       </c>
       <c r="F47">
-        <v>0.008108904295966224</v>
+        <v>0.008222628255700165</v>
       </c>
       <c r="G47">
-        <v>0.006728745228450933</v>
+        <v>0.006811466224796531</v>
       </c>
       <c r="H47">
-        <v>0.02027898210665266</v>
+        <v>0.020247848860154932</v>
       </c>
       <c r="I47">
-        <v>0.00201859998001081</v>
+        <v>0.002002134515076684</v>
       </c>
       <c r="J47">
-        <v>0.039852226938007426</v>
+        <v>0.042430507815804784</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -48338,7 +50136,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -48350,43 +50148,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:kilo:nebbi-uga</t>
+          <t>corridor:47:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.0030217714965165288</v>
+        <v>0.002882502947612553</v>
       </c>
       <c r="F48">
-        <v>0.008088559543497742</v>
+        <v>0.008194900129801702</v>
       </c>
       <c r="G48">
-        <v>0.007586202236514322</v>
+        <v>0.0071261552896609015</v>
       </c>
       <c r="H48">
-        <v>0.020228416398239663</v>
+        <v>0.02017998389325623</v>
       </c>
       <c r="I48">
-        <v>0.0013824992306557622</v>
+        <v>0.0014343817285406735</v>
       </c>
       <c r="J48">
-        <v>0.04298876053352871</v>
+        <v>0.03991556549220518</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -48406,7 +50204,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -48418,43 +50216,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:nizi:kampala-uga</t>
+          <t>corridor:48:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.003185845864099812</v>
+        <v>0.002899735778643775</v>
       </c>
       <c r="F49">
-        <v>0.008055680196092985</v>
+        <v>0.008156775375274178</v>
       </c>
       <c r="G49">
-        <v>0.007997117456259972</v>
+        <v>0.007168667109143045</v>
       </c>
       <c r="H49">
-        <v>0.020146693276199862</v>
+        <v>0.020086668634671817</v>
       </c>
       <c r="I49">
-        <v>0.0017111961703214886</v>
+        <v>0.001765702714835879</v>
       </c>
       <c r="J49">
-        <v>0.03843501793313703</v>
+        <v>0.039438828983039326</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -48474,7 +50272,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -48486,43 +50284,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:nizi:nebbi-uga</t>
+          <t>corridor:49:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0027950636057349765</v>
+        <v>0.0027436075367688606</v>
       </c>
       <c r="F50">
-        <v>0.008037576849237893</v>
+        <v>0.00813573057807132</v>
       </c>
       <c r="G50">
-        <v>0.007018256519346455</v>
+        <v>0.006783473348184826</v>
       </c>
       <c r="H50">
-        <v>0.02010169499562392</v>
+        <v>0.02003515768678027</v>
       </c>
       <c r="I50">
-        <v>0.0019399331731337372</v>
+        <v>0.0019484543771382619</v>
       </c>
       <c r="J50">
-        <v>0.04644803668949182</v>
+        <v>0.04366249567204285</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -48542,7 +50340,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -48554,43 +50352,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:kilo:beni-cod</t>
+          <t>corridor:50:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D51">
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002821718891003744</v>
+        <v>0.00289673081900102</v>
       </c>
       <c r="F51">
-        <v>0.00803389605052951</v>
+        <v>0.008093538488025936</v>
       </c>
       <c r="G51">
-        <v>0.007085043176923073</v>
+        <v>0.0071612541418274445</v>
       </c>
       <c r="H51">
-        <v>0.020092545647049515</v>
+        <v>0.019931878246767426</v>
       </c>
       <c r="I51">
-        <v>0.0019349047366173573</v>
+        <v>0.0016809985549575749</v>
       </c>
       <c r="J51">
-        <v>0.04003768632169026</v>
+        <v>0.04244857346914838</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -48610,7 +50408,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -48622,43 +50420,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:goma-cod:nebbi-uga</t>
+          <t>corridor:51:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.0028567491561985736</v>
+        <v>0.0029401286142527183</v>
       </c>
       <c r="F52">
-        <v>0.00797006857945673</v>
+        <v>0.008060259325341046</v>
       </c>
       <c r="G52">
-        <v>0.007172809815163245</v>
+        <v>0.0072683082461652004</v>
       </c>
       <c r="H52">
-        <v>0.019933882573881373</v>
+        <v>0.019850402601428535</v>
       </c>
       <c r="I52">
-        <v>0.0017294072526960998</v>
+        <v>0.001797781260891848</v>
       </c>
       <c r="J52">
-        <v>0.042443634852033695</v>
+        <v>0.03851102703520781</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -48678,7 +50476,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -48690,43 +50488,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:nizi:beni-cod</t>
+          <t>corridor:52:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.0030245126948671708</v>
+        <v>0.002865544957359273</v>
       </c>
       <c r="F53">
-        <v>0.00795441234801178</v>
+        <v>0.008007505347331828</v>
       </c>
       <c r="G53">
-        <v>0.007593068348614146</v>
+        <v>0.0070843200252671545</v>
       </c>
       <c r="H53">
-        <v>0.01989496203143168</v>
+        <v>0.019721262395209938</v>
       </c>
       <c r="I53">
-        <v>0.00208860712135866</v>
+        <v>0.0015405355995758848</v>
       </c>
       <c r="J53">
-        <v>0.04390687375830717</v>
+        <v>0.03672115158663102</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -48746,7 +50544,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -48758,43 +50556,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:butembo:kasese-uga</t>
+          <t>corridor:53:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0029631889825048885</v>
+        <v>0.0029536944459469527</v>
       </c>
       <c r="F54">
-        <v>0.00793918577465852</v>
+        <v>0.007960826510511443</v>
       </c>
       <c r="G54">
-        <v>0.007439460946500748</v>
+        <v>0.007301771191140616</v>
       </c>
       <c r="H54">
-        <v>0.019857108285455366</v>
+        <v>0.01960697825032018</v>
       </c>
       <c r="I54">
-        <v>0.001563734909959605</v>
+        <v>0.0016862635592489572</v>
       </c>
       <c r="J54">
-        <v>0.03793928796303533</v>
+        <v>0.045197930386536175</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -48814,7 +50612,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -48826,43 +50624,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:kilo:bundibugyo-uga</t>
+          <t>corridor:54:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0028536624321979787</v>
+        <v>0.0028077086856141686</v>
       </c>
       <c r="F55">
-        <v>0.007897435827033727</v>
+        <v>0.007901485678099562</v>
       </c>
       <c r="G55">
-        <v>0.007165076290699068</v>
+        <v>0.006941632095260497</v>
       </c>
       <c r="H55">
-        <v>0.019753312706144277</v>
+        <v>0.01946168095865239</v>
       </c>
       <c r="I55">
-        <v>0.0021169028283330726</v>
+        <v>0.0021553033511651945</v>
       </c>
       <c r="J55">
-        <v>0.04301862105908695</v>
+        <v>0.04097440772519585</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -48882,7 +50680,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -48894,43 +50692,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:kilo:kasese-uga</t>
+          <t>corridor:55:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.002959971024566438</v>
+        <v>0.0029325884804620728</v>
       </c>
       <c r="F56">
-        <v>0.00787220578285247</v>
+        <v>0.0078658503326898</v>
       </c>
       <c r="G56">
-        <v>0.007431400049636161</v>
+        <v>0.007249708704873986</v>
       </c>
       <c r="H56">
-        <v>0.019690583840609954</v>
+        <v>0.01937442245861365</v>
       </c>
       <c r="I56">
-        <v>0.001641626374744698</v>
+        <v>0.0023275583555744496</v>
       </c>
       <c r="J56">
-        <v>0.040297773039945806</v>
+        <v>0.04310662676624314</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -48950,7 +50748,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -48962,12 +50760,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:goma-cod:kasese-uga</t>
+          <t>corridor:56:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -48979,26 +50777,26 @@
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.0027095766658913334</v>
+        <v>0.002964790671466655</v>
       </c>
       <c r="F57">
-        <v>0.007841647616298908</v>
+        <v>0.007845522849790815</v>
       </c>
       <c r="G57">
-        <v>0.006804043969449947</v>
+        <v>0.007329141803465333</v>
       </c>
       <c r="H57">
-        <v>0.01961460584756758</v>
+        <v>0.019324644695648402</v>
       </c>
       <c r="I57">
-        <v>0.0020235152119086695</v>
+        <v>0.001979182980043831</v>
       </c>
       <c r="J57">
-        <v>0.041393987342476055</v>
+        <v>0.03709606445309815</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -49018,7 +50816,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -49030,43 +50828,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:goma-cod:kampala-uga</t>
+          <t>corridor:57:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.0025110978594395095</v>
+        <v>0.002787974005366123</v>
       </c>
       <c r="F58">
-        <v>0.007818185593694127</v>
+        <v>0.007811983261174604</v>
       </c>
       <c r="G58">
-        <v>0.0063065924718523625</v>
+        <v>0.006892941705632205</v>
       </c>
       <c r="H58">
-        <v>0.019556267594055404</v>
+        <v>0.019242508810321413</v>
       </c>
       <c r="I58">
-        <v>0.0015853366988132862</v>
+        <v>0.0017836493702624218</v>
       </c>
       <c r="J58">
-        <v>0.03742026740783717</v>
+        <v>0.03775589018826164</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -49086,7 +50884,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -49098,43 +50896,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:miti-murhesa:arua-uga</t>
+          <t>corridor:58:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0030156062594385025</v>
+        <v>0.0030397115334472313</v>
       </c>
       <c r="F59">
-        <v>0.007804732379472906</v>
+        <v>0.007798503469288315</v>
       </c>
       <c r="G59">
-        <v>0.007570759922123083</v>
+        <v>0.007513934292532054</v>
       </c>
       <c r="H59">
-        <v>0.019522813800804506</v>
+        <v>0.01920949889117962</v>
       </c>
       <c r="I59">
-        <v>0.001458769241107233</v>
+        <v>0.0016678403853665758</v>
       </c>
       <c r="J59">
-        <v>0.043206799451250055</v>
+        <v>0.03881661822899164</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -49154,7 +50952,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -49166,43 +50964,43 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:bambu:arua-uga</t>
+          <t>corridor:59:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.002681900600504883</v>
+        <v>0.0028279586473544394</v>
       </c>
       <c r="F60">
-        <v>0.0077589260027900175</v>
+        <v>0.007773442977447614</v>
       </c>
       <c r="G60">
-        <v>0.0067346886062866484</v>
+        <v>0.006991592151725234</v>
       </c>
       <c r="H60">
-        <v>0.019408912083272584</v>
+        <v>0.019148124794601235</v>
       </c>
       <c r="I60">
-        <v>0.001316839496169825</v>
+        <v>0.001626485696169075</v>
       </c>
       <c r="J60">
-        <v>0.04188008746055827</v>
+        <v>0.04043085112899037</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -49222,7 +51020,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -49234,43 +51032,43 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:miti-murhesa:nebbi-uga</t>
+          <t>corridor:60:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.0029216317002188907</v>
+        <v>0.0029787064606684455</v>
       </c>
       <c r="F61">
-        <v>0.007737159174179331</v>
+        <v>0.007727723579566553</v>
       </c>
       <c r="G61">
-        <v>0.007335357553010069</v>
+        <v>0.007363466593160867</v>
       </c>
       <c r="H61">
-        <v>0.0193547831266003</v>
+        <v>0.01903614948937532</v>
       </c>
       <c r="I61">
-        <v>0.0021616580283129877</v>
+        <v>0.002161627379220277</v>
       </c>
       <c r="J61">
-        <v>0.038276210708016935</v>
+        <v>0.040700080739514</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -49290,7 +51088,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -49302,43 +51100,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:bambu:bundibugyo-uga</t>
+          <t>corridor:61:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0030176500050449473</v>
+        <v>0.002794253883045994</v>
       </c>
       <c r="F62">
-        <v>0.007734491501665053</v>
+        <v>0.007726643785385345</v>
       </c>
       <c r="G62">
-        <v>0.0075758786333554595</v>
+        <v>0.006908435854105138</v>
       </c>
       <c r="H62">
-        <v>0.019348148843720964</v>
+        <v>0.019033505698469483</v>
       </c>
       <c r="I62">
-        <v>0.0019946892098529428</v>
+        <v>0.0017974249505340796</v>
       </c>
       <c r="J62">
-        <v>0.044163146423054585</v>
+        <v>0.040761246701666295</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -49358,7 +51156,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -49370,43 +51168,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:miti-murhesa:kasese-uga</t>
+          <t>corridor:62:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0027185906083667943</v>
+        <v>0.0027895356588024944</v>
       </c>
       <c r="F63">
-        <v>0.007723897502855653</v>
+        <v>0.007708922084123715</v>
       </c>
       <c r="G63">
-        <v>0.006826633017774586</v>
+        <v>0.0068967939985309645</v>
       </c>
       <c r="H63">
-        <v>0.01932180334913558</v>
+        <v>0.018990099864912985</v>
       </c>
       <c r="I63">
-        <v>0.001326890680265347</v>
+        <v>0.0013975388045409515</v>
       </c>
       <c r="J63">
-        <v>0.044931486478670124</v>
+        <v>0.042391251021321644</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -49426,7 +51224,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -49438,43 +51236,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:miti-murhesa:beni-cod</t>
+          <t>corridor:63:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0027329214469088425</v>
+        <v>0.0024745761411364142</v>
       </c>
       <c r="F64">
-        <v>0.007653410571739322</v>
+        <v>0.007569959524086317</v>
       </c>
       <c r="G64">
-        <v>0.0068625427804339945</v>
+        <v>0.00611952005219521</v>
       </c>
       <c r="H64">
-        <v>0.019146499430329145</v>
+        <v>0.01864970148957265</v>
       </c>
       <c r="I64">
-        <v>0.001510923662171504</v>
+        <v>0.001552318276025716</v>
       </c>
       <c r="J64">
-        <v>0.04151791854720881</v>
+        <v>0.034976270348434146</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -49494,7 +51292,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -49506,12 +51304,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:nizi:bundibugyo-uga</t>
+          <t>corridor:64:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -49523,26 +51321,26 @@
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0028089304317990282</v>
+        <v>0.0028359961308326576</v>
       </c>
       <c r="F65">
-        <v>0.007651463995398566</v>
+        <v>0.00756961435820569</v>
       </c>
       <c r="G65">
-        <v>0.007053001153893956</v>
+        <v>0.007011421744851615</v>
       </c>
       <c r="H65">
-        <v>0.019141661110745445</v>
+        <v>0.018648855869933034</v>
       </c>
       <c r="I65">
-        <v>0.0017533987795390561</v>
+        <v>0.0011273495847349967</v>
       </c>
       <c r="J65">
-        <v>0.04071220585407649</v>
+        <v>0.037299073210084584</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -49562,7 +51360,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -49574,7 +51372,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:goma-cod:bundibugyo-uga</t>
+          <t>corridor:65:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -49584,33 +51382,33 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.0027894808005398397</v>
+        <v>0.002833861264198795</v>
       </c>
       <c r="F66">
-        <v>0.007505535288456183</v>
+        <v>0.007547888001259828</v>
       </c>
       <c r="G66">
-        <v>0.00700426804677709</v>
+        <v>0.007006154836616929</v>
       </c>
       <c r="H66">
-        <v>0.018778672919181755</v>
+        <v>0.018595628743809794</v>
       </c>
       <c r="I66">
-        <v>0.001405618489354124</v>
+        <v>0.00218933896549888</v>
       </c>
       <c r="J66">
-        <v>0.038891998237858</v>
+        <v>0.04012855964424418</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -49630,7 +51428,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -49642,43 +51440,43 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:goma-cod:beni-cod</t>
+          <t>corridor:66:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.002691745671106749</v>
+        <v>0.0028713896563432317</v>
       </c>
       <c r="F67">
-        <v>0.007306343783265612</v>
+        <v>0.007546538100174749</v>
       </c>
       <c r="G67">
-        <v>0.00675936068384736</v>
+        <v>0.007098739218278277</v>
       </c>
       <c r="H67">
-        <v>0.018283072120277938</v>
+        <v>0.018592320839906473</v>
       </c>
       <c r="I67">
-        <v>0.00182661275920816</v>
+        <v>0.002009283025009237</v>
       </c>
       <c r="J67">
-        <v>0.03743852328668568</v>
+        <v>0.035894482626523734</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -49698,7 +51496,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -49836,7 +51634,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -49888,7 +51686,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -49942,7 +51740,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -49996,7 +51794,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -50050,7 +51848,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -50104,7 +51902,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -50158,7 +51956,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -50185,10 +51983,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.3974126026144006</v>
+        <v>0.4036352802540115</v>
       </c>
       <c r="F9">
-        <v>0.4586317958944394</v>
+        <v>0.46215932894360784</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -50212,7 +52010,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -50239,10 +52037,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>3.1380822768917134</v>
+        <v>2.5636921180997643</v>
       </c>
       <c r="F10">
-        <v>13.124786655735885</v>
+        <v>12.502589644513742</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -50266,7 +52064,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -50293,10 +52091,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="F11">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -50320,7 +52118,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -50374,7 +52172,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L12"/>
@@ -50422,7 +52220,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -50474,7 +52272,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -50526,7 +52324,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -50552,7 +52350,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -50578,7 +52376,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -50604,7 +52402,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.03</v>
+        <v>0.018</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -50630,7 +52428,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -50656,7 +52454,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.962</v>
+        <v>0.979</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -50682,7 +52480,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -50736,7 +52534,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L19"/>
@@ -50786,7 +52584,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L20"/>
@@ -50864,7 +52662,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"confirmed": 106, "deaths": 179, "suspected": 904}</t>
+          <t>{"confirmed": 112, "deaths": 223, "suspected": 906}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -50902,12 +52700,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"confirmed": 106, "suspected": 904}</t>
+          <t>{"confirmed": 112, "suspected": 906}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"confirmation_backlog_50": [462, 720], "reporting_completeness_50": [0.3974126026144006, 0.4586317958944394]}</t>
+          <t>{"confirmation_backlog_50": [455, 725], "reporting_completeness_50": [0.4036352802540115, 0.46215932894360784]}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50936,12 +52734,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"confirmed_endpoint": 106, "reporting_completeness_50": [0.3974126026144006, 0.4586317958944394]}</t>
+          <t>{"confirmed_endpoint": 112, "reporting_completeness_50": [0.4036352802540115, 0.46215932894360784]}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"endpoint_confirmable_50": [231, 267]}</t>
+          <t>{"endpoint_confirmable_50": [242, 277]}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50970,7 +52768,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"deaths": 179}</t>
+          <t>{"deaths": 223}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -50980,7 +52778,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The 179-death input updates the snapshot-level sensitivity calculation, but the source lacks a data/report date, so it must be rendered as a publication-clock endpoint rather than a connected dated trajectory point.</t>
+          <t>The 223-death input comes from the US CDC Current Situation 25 May, a dated-report source, so it updates the snapshot-level sensitivity calculation as a connected dated trajectory point. The DRC MoH dashboard aggregate (179, 24 May) and the ECDC 25 May figure (119) are held as conflict anchors and are not promoted, so no publication-clock-only endpoint is rendered.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -51008,7 +52806,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"confirmed": 106}</t>
+          <t>{"confirmed": 112}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -51042,7 +52840,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"headline_confirmed": 106, "unallocated_headline_confirmed": 27, "zone_attributed_confirmed": 79}</t>
+          <t>{"headline_confirmed": 112, "unallocated_headline_confirmed": 33, "zone_attributed_confirmed": 79}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.1% lower bounds and 1.9-49.1% upper bounds.</t>
+          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.2% lower bounds and 1.8-48.2% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -47020,7 +47020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:beni-cod</t>
+          <t>corridor:01:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -47030,29 +47030,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.08705872476656829</v>
+        <v>0.0861708114385285</v>
       </c>
       <c r="F2">
-        <v>0.23849877729636965</v>
+        <v>0.23315469335620254</v>
       </c>
       <c r="G2">
-        <v>0.20200901575875693</v>
+        <v>0.20028631694823662</v>
       </c>
       <c r="H2">
-        <v>0.490855636804455</v>
+        <v>0.48234065943233195</v>
       </c>
       <c r="I2">
-        <v>0.05827234299127523</v>
+        <v>0.06427581319980569</v>
       </c>
       <c r="J2">
-        <v>0.7360585970208364</v>
+        <v>0.7474537035483133</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -47088,7 +47088,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:kampala-uga</t>
+          <t>corridor:02:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -47098,29 +47098,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.09106071850782033</v>
+        <v>0.08768171124595683</v>
       </c>
       <c r="F3">
-        <v>0.23180304927763629</v>
+        <v>0.2275794037963691</v>
       </c>
       <c r="G3">
-        <v>0.21064783365598588</v>
+        <v>0.2035618016305265</v>
       </c>
       <c r="H3">
-        <v>0.47969244396961136</v>
+        <v>0.47295633103988544</v>
       </c>
       <c r="I3">
-        <v>0.05967373659336905</v>
+        <v>0.04459460740614488</v>
       </c>
       <c r="J3">
-        <v>0.7123311692401879</v>
+        <v>0.7478981260349676</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -47156,7 +47156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:nebbi-uga</t>
+          <t>corridor:03:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -47166,29 +47166,29 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08277521513409741</v>
+        <v>0.08233054224498484</v>
       </c>
       <c r="F4">
-        <v>0.22641515556489766</v>
+        <v>0.22543492066869397</v>
       </c>
       <c r="G4">
-        <v>0.19270105652080258</v>
+        <v>0.19192499609422323</v>
       </c>
       <c r="H4">
-        <v>0.47060445029291187</v>
+        <v>0.46931800011005115</v>
       </c>
       <c r="I4">
-        <v>0.058851102281542125</v>
+        <v>0.06964130796312437</v>
       </c>
       <c r="J4">
-        <v>0.7381007215516742</v>
+        <v>0.6990237917928565</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:kasese-uga</t>
+          <t>corridor:04:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -47234,29 +47234,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.0777667177980044</v>
+        <v>0.08664306873590838</v>
       </c>
       <c r="F5">
-        <v>0.22125498504359012</v>
+        <v>0.222887038238157</v>
       </c>
       <c r="G5">
-        <v>0.18173566771392538</v>
+        <v>0.20131080198240825</v>
       </c>
       <c r="H5">
-        <v>0.46181259202543024</v>
+        <v>0.4649794327839667</v>
       </c>
       <c r="I5">
-        <v>0.04687532836669559</v>
+        <v>0.05425688863966508</v>
       </c>
       <c r="J5">
-        <v>0.7431942191372538</v>
+        <v>0.7101842045533336</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:bundibugyo-uga</t>
+          <t>corridor:05:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -47302,29 +47302,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08994167609221052</v>
+        <v>0.09176382815314144</v>
       </c>
       <c r="F6">
-        <v>0.21814102710172356</v>
+        <v>0.2196720235905948</v>
       </c>
       <c r="G6">
-        <v>0.2082377356100764</v>
+        <v>0.2123714082943657</v>
       </c>
       <c r="H6">
-        <v>0.4564648825278334</v>
+        <v>0.45947010738720273</v>
       </c>
       <c r="I6">
-        <v>0.06843498725883312</v>
+        <v>0.0602209036243418</v>
       </c>
       <c r="J6">
-        <v>0.7351838704184875</v>
+        <v>0.7146926481656625</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corridor:06:rwampara:arua-uga</t>
+          <t>corridor:06:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -47370,29 +47370,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08738592639250203</v>
+        <v>0.08396936085735776</v>
       </c>
       <c r="F7">
-        <v>0.21691539014958308</v>
+        <v>0.2119043283318027</v>
       </c>
       <c r="G7">
-        <v>0.20271776834032668</v>
+        <v>0.19549948212877702</v>
       </c>
       <c r="H7">
-        <v>0.4543515172508829</v>
+        <v>0.44602874389977687</v>
       </c>
       <c r="I7">
-        <v>0.0606006699211846</v>
+        <v>0.056360235565877555</v>
       </c>
       <c r="J7">
-        <v>0.7294259710737864</v>
+        <v>0.7142786607680277</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -47428,43 +47428,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:bunia:kampala-uga</t>
+          <t>corridor:07:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.04246356113673297</v>
+        <v>0.03855467933328152</v>
       </c>
       <c r="F8">
-        <v>0.11942130278737001</v>
+        <v>0.11620932868289471</v>
       </c>
       <c r="G8">
-        <v>0.10192493852909751</v>
+        <v>0.09291440432184914</v>
       </c>
       <c r="H8">
-        <v>0.270266609097878</v>
+        <v>0.2639086114886541</v>
       </c>
       <c r="I8">
-        <v>0.028409667809219823</v>
+        <v>0.025175207094245807</v>
       </c>
       <c r="J8">
-        <v>0.46391565999619183</v>
+        <v>0.46361890390099453</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -47496,7 +47496,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:bundibugyo-uga</t>
+          <t>corridor:08:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -47506,29 +47506,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04372720174962935</v>
+        <v>0.04147908524423352</v>
       </c>
       <c r="F9">
-        <v>0.11776659374999701</v>
+        <v>0.11562806950949953</v>
       </c>
       <c r="G9">
-        <v>0.10485843323233299</v>
+        <v>0.09974219409345544</v>
       </c>
       <c r="H9">
-        <v>0.2668648630838556</v>
+        <v>0.2627072705721946</v>
       </c>
       <c r="I9">
-        <v>0.024824081936019447</v>
+        <v>0.025907663365721464</v>
       </c>
       <c r="J9">
-        <v>0.47074791691760753</v>
+        <v>0.4462554570998926</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:beni-cod</t>
+          <t>corridor:09:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -47574,29 +47574,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.043721416421617726</v>
+        <v>0.04179480816556652</v>
       </c>
       <c r="F10">
-        <v>0.11772211441413447</v>
+        <v>0.11558245421258095</v>
       </c>
       <c r="G10">
-        <v>0.1048450145946053</v>
+        <v>0.10047743392001213</v>
       </c>
       <c r="H10">
-        <v>0.2667733722448983</v>
+        <v>0.26261295488077974</v>
       </c>
       <c r="I10">
-        <v>0.03158643596552796</v>
+        <v>0.027913949480659363</v>
       </c>
       <c r="J10">
-        <v>0.4736878533835456</v>
+        <v>0.4647552683750245</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -47649,22 +47649,22 @@
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.0444155412592947</v>
+        <v>0.04186956091160368</v>
       </c>
       <c r="F11">
-        <v>0.11571118127048804</v>
+        <v>0.11539491748492897</v>
       </c>
       <c r="G11">
-        <v>0.10645391938867926</v>
+        <v>0.10065158442248001</v>
       </c>
       <c r="H11">
-        <v>0.2626253665816084</v>
+        <v>0.26222507759010427</v>
       </c>
       <c r="I11">
-        <v>0.03078606866593397</v>
+        <v>0.021242880051839726</v>
       </c>
       <c r="J11">
-        <v>0.4883461510873249</v>
+        <v>0.46678607844486947</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -47700,12 +47700,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:bunia:kasese-uga</t>
+          <t>corridor:11:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -47717,26 +47717,26 @@
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.04410979236313228</v>
+        <v>0.04042920346327944</v>
       </c>
       <c r="F12">
-        <v>0.11505461271845879</v>
+        <v>0.11242435593909272</v>
       </c>
       <c r="G12">
-        <v>0.10574531651674063</v>
+        <v>0.09729451222456448</v>
       </c>
       <c r="H12">
-        <v>0.26126870223516685</v>
+        <v>0.2560645676658191</v>
       </c>
       <c r="I12">
-        <v>0.028827859136638982</v>
+        <v>0.027413735537554062</v>
       </c>
       <c r="J12">
-        <v>0.4349056791496498</v>
+        <v>0.43705126759089724</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -47768,7 +47768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:arua-uga</t>
+          <t>corridor:12:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -47778,29 +47778,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.04061609325636212</v>
+        <v>0.04024586283096926</v>
       </c>
       <c r="F13">
-        <v>0.11396739072964437</v>
+        <v>0.11159467152136757</v>
       </c>
       <c r="G13">
-        <v>0.09762606642203506</v>
+        <v>0.09686667859605977</v>
       </c>
       <c r="H13">
-        <v>0.25901826950891554</v>
+        <v>0.25433876336268857</v>
       </c>
       <c r="I13">
-        <v>0.02387539752522782</v>
+        <v>0.03067229187569909</v>
       </c>
       <c r="J13">
-        <v>0.4461622227370582</v>
+        <v>0.4576157180833162</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -47836,7 +47836,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:beni-cod</t>
+          <t>corridor:13:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -47846,29 +47846,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.03710996846095013</v>
+        <v>0.04066526892293623</v>
       </c>
       <c r="F14">
-        <v>0.10964681236938656</v>
+        <v>0.11152320362817797</v>
       </c>
       <c r="G14">
-        <v>0.08943382811819442</v>
+        <v>0.09784524147753831</v>
       </c>
       <c r="H14">
-        <v>0.250034224844084</v>
+        <v>0.254190125108517</v>
       </c>
       <c r="I14">
-        <v>0.03385391457147437</v>
+        <v>0.026605224754838577</v>
       </c>
       <c r="J14">
-        <v>0.46993004228955715</v>
+        <v>0.46394166684739413</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -47904,43 +47904,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:mongbwalu:nebbi-uga</t>
+          <t>corridor:14:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.042080228665137914</v>
+        <v>0.043769887053943884</v>
       </c>
       <c r="F15">
-        <v>0.10683766833988695</v>
+        <v>0.11103027985574987</v>
       </c>
       <c r="G15">
-        <v>0.10103406480576219</v>
+        <v>0.10506919313252691</v>
       </c>
       <c r="H15">
-        <v>0.24415829376737277</v>
+        <v>0.2531634176228099</v>
       </c>
       <c r="I15">
-        <v>0.027024110522923</v>
+        <v>0.024326153776741695</v>
       </c>
       <c r="J15">
-        <v>0.4126434945709156</v>
+        <v>0.44860424323610526</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -47972,7 +47972,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:15:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -47982,29 +47982,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.04202426525540365</v>
+        <v>0.03750471405393857</v>
       </c>
       <c r="F16">
-        <v>0.10608468442723934</v>
+        <v>0.10749948779872281</v>
       </c>
       <c r="G16">
-        <v>0.10090394584352139</v>
+        <v>0.09045541125798737</v>
       </c>
       <c r="H16">
-        <v>0.24257853052369338</v>
+        <v>0.24578444055142545</v>
       </c>
       <c r="I16">
-        <v>0.025730387416915464</v>
+        <v>0.027237694409312466</v>
       </c>
       <c r="J16">
-        <v>0.4196281916748507</v>
+        <v>0.4271444488438072</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -48040,43 +48040,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:arua-uga</t>
+          <t>corridor:16:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.03933542211197083</v>
+        <v>0.04228950663900796</v>
       </c>
       <c r="F17">
-        <v>0.10546729596630738</v>
+        <v>0.10704031678368539</v>
       </c>
       <c r="G17">
-        <v>0.09463884639695044</v>
+        <v>0.10162893993380431</v>
       </c>
       <c r="H17">
-        <v>0.24128195279119546</v>
+        <v>0.24482175888282368</v>
       </c>
       <c r="I17">
-        <v>0.024899713049719586</v>
+        <v>0.026598690800271954</v>
       </c>
       <c r="J17">
-        <v>0.45412776873008587</v>
+        <v>0.4232379895804849</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -48108,7 +48108,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:kasese-uga</t>
+          <t>corridor:17:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -48118,29 +48118,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.03674677955972819</v>
+        <v>0.03798452079077774</v>
       </c>
       <c r="F18">
-        <v>0.10253826350865747</v>
+        <v>0.1055578744412985</v>
       </c>
       <c r="G18">
-        <v>0.08858269196104879</v>
+        <v>0.09157962059775004</v>
       </c>
       <c r="H18">
-        <v>0.2351121722828113</v>
+        <v>0.24170839592150667</v>
       </c>
       <c r="I18">
-        <v>0.02446060018301769</v>
+        <v>0.0239669463086208</v>
       </c>
       <c r="J18">
-        <v>0.43434320993589176</v>
+        <v>0.4664322846035496</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:kampala-uga</t>
+          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -48186,29 +48186,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.03673769680232783</v>
+        <v>0.03778298943272401</v>
       </c>
       <c r="F19">
-        <v>0.10176519464035952</v>
+        <v>0.10384450964700326</v>
       </c>
       <c r="G19">
-        <v>0.08856139661635878</v>
+        <v>0.09110754488962608</v>
       </c>
       <c r="H19">
-        <v>0.23347872961217356</v>
+        <v>0.23810062900458037</v>
       </c>
       <c r="I19">
-        <v>0.019766568129704724</v>
+        <v>0.027747327225511372</v>
       </c>
       <c r="J19">
-        <v>0.45173277256401556</v>
+        <v>0.39188625277934763</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:nebbi-uga</t>
+          <t>corridor:19:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -48254,29 +48254,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.02943619547001522</v>
+        <v>0.031304381068294335</v>
       </c>
       <c r="F20">
-        <v>0.08644089973446445</v>
+        <v>0.08779786212598711</v>
       </c>
       <c r="G20">
-        <v>0.07134929740790441</v>
+        <v>0.07585358277896675</v>
       </c>
       <c r="H20">
-        <v>0.20067080506318333</v>
+        <v>0.2038133127969261</v>
       </c>
       <c r="I20">
-        <v>0.017249897635217455</v>
+        <v>0.017690770792813504</v>
       </c>
       <c r="J20">
-        <v>0.37720643415082816</v>
+        <v>0.3619871650097016</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:kampala-uga</t>
+          <t>corridor:20:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -48322,29 +48322,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03143620060038951</v>
+        <v>0.03171837340940942</v>
       </c>
       <c r="F21">
-        <v>0.08597135121230412</v>
+        <v>0.08476753807336304</v>
       </c>
       <c r="G21">
-        <v>0.0760830743974528</v>
+        <v>0.07683287603147732</v>
       </c>
       <c r="H21">
-        <v>0.19965252253419963</v>
+        <v>0.19723709872212672</v>
       </c>
       <c r="I21">
-        <v>0.026413643415756798</v>
+        <v>0.0227792144919888</v>
       </c>
       <c r="J21">
-        <v>0.3875565167376865</v>
+        <v>0.3495642294984912</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -48380,7 +48380,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:bundibugyo-uga</t>
+          <t>corridor:21:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -48390,29 +48390,29 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.033545219747423194</v>
+        <v>0.030540418665822744</v>
       </c>
       <c r="F22">
-        <v>0.08571847788474835</v>
+        <v>0.08438962198493272</v>
       </c>
       <c r="G22">
-        <v>0.08105927552190084</v>
+        <v>0.07404478785217791</v>
       </c>
       <c r="H22">
-        <v>0.19910390583267018</v>
+        <v>0.19641470100450442</v>
       </c>
       <c r="I22">
-        <v>0.02488466056117501</v>
+        <v>0.019203507671592176</v>
       </c>
       <c r="J22">
-        <v>0.3750758008783629</v>
+        <v>0.3838230566411262</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:arua-uga</t>
+          <t>corridor:22:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -48458,29 +48458,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.03209426849587091</v>
+        <v>0.030399316276041116</v>
       </c>
       <c r="F23">
-        <v>0.08294965297286142</v>
+        <v>0.08407821789447709</v>
       </c>
       <c r="G23">
-        <v>0.07763750605795702</v>
+        <v>0.07371053738981273</v>
       </c>
       <c r="H23">
-        <v>0.19308102183167064</v>
+        <v>0.19573661412777732</v>
       </c>
       <c r="I23">
-        <v>0.01788217072461529</v>
+        <v>0.021457583298788</v>
       </c>
       <c r="J23">
-        <v>0.34301640031334013</v>
+        <v>0.358453978352833</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:beni-cod</t>
+          <t>corridor:23:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -48526,29 +48526,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.02866534159045145</v>
+        <v>0.030329334773183142</v>
       </c>
       <c r="F24">
-        <v>0.08246390394965086</v>
+        <v>0.08357711531060097</v>
       </c>
       <c r="G24">
-        <v>0.0695208928496309</v>
+        <v>0.07354468946695608</v>
       </c>
       <c r="H24">
-        <v>0.19202205699078656</v>
+        <v>0.19464486287655744</v>
       </c>
       <c r="I24">
-        <v>0.016730935405880526</v>
+        <v>0.014570952055622657</v>
       </c>
       <c r="J24">
-        <v>0.364088590258062</v>
+        <v>0.32281669746439295</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:kasese-uga</t>
+          <t>corridor:24:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -48594,29 +48594,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.03081565613688028</v>
+        <v>0.028578262502321705</v>
       </c>
       <c r="F25">
-        <v>0.08049341862637019</v>
+        <v>0.0757669915923353</v>
       </c>
       <c r="G25">
-        <v>0.07461586978106036</v>
+        <v>0.06938957908843438</v>
       </c>
       <c r="H25">
-        <v>0.18771637107786493</v>
+        <v>0.17751379634539563</v>
       </c>
       <c r="I25">
-        <v>0.026248954426468973</v>
+        <v>0.021112935786516</v>
       </c>
       <c r="J25">
-        <v>0.3381175600724034</v>
+        <v>0.3190059046148159</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:nebbi-uga</t>
+          <t>corridor:25:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -48662,29 +48662,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.006029262723708073</v>
+        <v>0.006127400208913586</v>
       </c>
       <c r="F26">
-        <v>0.017114033671260853</v>
+        <v>0.0168408512437718</v>
       </c>
       <c r="G26">
-        <v>0.014870934354623777</v>
+        <v>0.015128788346279537</v>
       </c>
       <c r="H26">
-        <v>0.04186515305349886</v>
+        <v>0.04125072266262608</v>
       </c>
       <c r="I26">
-        <v>0.004470615331371439</v>
+        <v>0.004388490481047946</v>
       </c>
       <c r="J26">
-        <v>0.0770842786162016</v>
+        <v>0.08183093712788367</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -48720,7 +48720,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:arua-uga</t>
+          <t>corridor:26:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -48730,29 +48730,29 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.005522357235792252</v>
+        <v>0.00556423388622837</v>
       </c>
       <c r="F27">
-        <v>0.016224882815260827</v>
+        <v>0.01656759676464939</v>
       </c>
       <c r="G27">
-        <v>0.013625786217095454</v>
+        <v>0.013744050643107991</v>
       </c>
       <c r="H27">
-        <v>0.039716335710117456</v>
+        <v>0.04058965567523373</v>
       </c>
       <c r="I27">
-        <v>0.0035817052958976416</v>
+        <v>0.003889156206565628</v>
       </c>
       <c r="J27">
-        <v>0.07992818660808958</v>
+        <v>0.08557353521823044</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:bundibugyo-uga</t>
+          <t>corridor:27:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -48798,29 +48798,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.005763485989899592</v>
+        <v>0.00571138519466724</v>
       </c>
       <c r="F28">
-        <v>0.015897712364671857</v>
+        <v>0.016458424878468436</v>
       </c>
       <c r="G28">
-        <v>0.01421820486301828</v>
+        <v>0.014105980367321913</v>
       </c>
       <c r="H28">
-        <v>0.038924937410599686</v>
+        <v>0.04032548046029999</v>
       </c>
       <c r="I28">
-        <v>0.00412817012599338</v>
+        <v>0.0032961116192571803</v>
       </c>
       <c r="J28">
-        <v>0.07530722471772157</v>
+        <v>0.08227064654779426</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -48856,7 +48856,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:kasese-uga</t>
+          <t>corridor:28:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -48866,29 +48866,29 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.00569825474665156</v>
+        <v>0.005665299126924983</v>
       </c>
       <c r="F29">
-        <v>0.015708110329420072</v>
+        <v>0.016137547052658407</v>
       </c>
       <c r="G29">
-        <v>0.014057962115334166</v>
+        <v>0.01399263950136656</v>
       </c>
       <c r="H29">
-        <v>0.03846612710006386</v>
+        <v>0.039548733878884995</v>
       </c>
       <c r="I29">
-        <v>0.0030738801757677933</v>
+        <v>0.0033705192295240497</v>
       </c>
       <c r="J29">
-        <v>0.08554865711076257</v>
+        <v>0.0787241376496719</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -48924,7 +48924,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:beni-cod</t>
+          <t>corridor:29:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -48934,29 +48934,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.006051188152445097</v>
+        <v>0.005760920437457601</v>
       </c>
       <c r="F30">
-        <v>0.01568874267670098</v>
+        <v>0.01564371888735397</v>
       </c>
       <c r="G30">
-        <v>0.014924768457324877</v>
+        <v>0.014227802835785092</v>
       </c>
       <c r="H30">
-        <v>0.03841925323098799</v>
+        <v>0.03835261291771347</v>
       </c>
       <c r="I30">
-        <v>0.003838228121916951</v>
+        <v>0.004405736887256273</v>
       </c>
       <c r="J30">
-        <v>0.08215270653449197</v>
+        <v>0.07717071840257644</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -48992,7 +48992,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:kampala-uga</t>
+          <t>corridor:30:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -49002,29 +49002,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005782262522765952</v>
+        <v>0.005519371147358398</v>
       </c>
       <c r="F31">
-        <v>0.015216280256187209</v>
+        <v>0.01552589721826908</v>
       </c>
       <c r="G31">
-        <v>0.014264327261309523</v>
+        <v>0.013633690221780848</v>
       </c>
       <c r="H31">
-        <v>0.03727535911897989</v>
+        <v>0.03806709980880993</v>
       </c>
       <c r="I31">
-        <v>0.0033384218962603934</v>
+        <v>0.003119740043250069</v>
       </c>
       <c r="J31">
-        <v>0.07811576042493965</v>
+        <v>0.07892668631060598</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -49060,39 +49060,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:bambu:beni-cod</t>
+          <t>corridor:31:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.0031221041967082197</v>
+        <v>0.002911020622911431</v>
       </c>
       <c r="F32">
-        <v>0.008698068132782094</v>
+        <v>0.008708366339810258</v>
       </c>
       <c r="G32">
-        <v>0.007717131898621776</v>
+        <v>0.007204585754623377</v>
       </c>
       <c r="H32">
-        <v>0.021411044648201427</v>
+        <v>0.021460131514392883</v>
       </c>
       <c r="I32">
-        <v>0.0017828154968101114</v>
+        <v>0.002213739571223128</v>
       </c>
       <c r="J32">
-        <v>0.0431818978878234</v>
+        <v>0.04056094344785632</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -49128,39 +49128,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:miti-murhesa:beni-cod</t>
+          <t>corridor:32:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.003256550077390147</v>
+        <v>0.0027769798502101373</v>
       </c>
       <c r="F33">
-        <v>0.008690654774771961</v>
+        <v>0.008633599440103473</v>
       </c>
       <c r="G33">
-        <v>0.008048651456418393</v>
+        <v>0.006873526257886398</v>
       </c>
       <c r="H33">
-        <v>0.02139291864359122</v>
+        <v>0.021277062424142124</v>
       </c>
       <c r="I33">
-        <v>0.002208850691779005</v>
+        <v>0.0016525413787399719</v>
       </c>
       <c r="J33">
-        <v>0.0397230321776111</v>
+        <v>0.03899275669757771</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -49196,39 +49196,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:goma-cod:arua-uga</t>
+          <t>corridor:33:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.0029781199558879257</v>
+        <v>0.0029900129594525315</v>
       </c>
       <c r="F34">
-        <v>0.008646396347219365</v>
+        <v>0.00847697711451803</v>
       </c>
       <c r="G34">
-        <v>0.00736201964546096</v>
+        <v>0.007399652921270428</v>
       </c>
       <c r="H34">
-        <v>0.021284669747048707</v>
+        <v>0.020893505827646625</v>
       </c>
       <c r="I34">
-        <v>0.001720505229708283</v>
+        <v>0.0017305897295624153</v>
       </c>
       <c r="J34">
-        <v>0.038678795905731755</v>
+        <v>0.04136198023793251</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -49264,39 +49264,39 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:goma-cod:kampala-uga</t>
+          <t>corridor:34:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003111181616698544</v>
+        <v>0.003004206625567968</v>
       </c>
       <c r="F35">
-        <v>0.008628383148852753</v>
+        <v>0.008424640775256842</v>
       </c>
       <c r="G35">
-        <v>0.007690196297224505</v>
+        <v>0.007434701480319217</v>
       </c>
       <c r="H35">
-        <v>0.021240605916741817</v>
+        <v>0.02076531908923876</v>
       </c>
       <c r="I35">
-        <v>0.0016110230461111126</v>
+        <v>0.0014445621581179958</v>
       </c>
       <c r="J35">
-        <v>0.043150308180892</v>
+        <v>0.03973256156228256</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -49332,12 +49332,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:bambu:bundibugyo-uga</t>
+          <t>corridor:35:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -49349,22 +49349,22 @@
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.0030884074123188887</v>
+        <v>0.003111941625778658</v>
       </c>
       <c r="F36">
-        <v>0.008588026182462571</v>
+        <v>0.008402719753006271</v>
       </c>
       <c r="G36">
-        <v>0.007634031778964906</v>
+        <v>0.0077007053534820236</v>
       </c>
       <c r="H36">
-        <v>0.02114189671152855</v>
+        <v>0.020711624541566498</v>
       </c>
       <c r="I36">
-        <v>0.0020051565560971376</v>
+        <v>0.0017674417542844795</v>
       </c>
       <c r="J36">
-        <v>0.03964300574013423</v>
+        <v>0.038221794937289805</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:butembo:bundibugyo-uga</t>
+          <t>corridor:36:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -49410,29 +49410,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.003025775628822114</v>
+        <v>0.002898657102272467</v>
       </c>
       <c r="F37">
-        <v>0.008571115858547917</v>
+        <v>0.00831048662323794</v>
       </c>
       <c r="G37">
-        <v>0.007479562809800805</v>
+        <v>0.0071740522491085534</v>
       </c>
       <c r="H37">
-        <v>0.021100531187123267</v>
+        <v>0.020485685215592936</v>
       </c>
       <c r="I37">
-        <v>0.0021199327441538463</v>
+        <v>0.0024156585156788397</v>
       </c>
       <c r="J37">
-        <v>0.04196071647036671</v>
+        <v>0.03953263154110449</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -49468,39 +49468,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:nizi:bundibugyo-uga</t>
+          <t>corridor:37:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D38">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.002797267917861973</v>
+        <v>0.0027125515817747747</v>
       </c>
       <c r="F38">
-        <v>0.00846270517529632</v>
+        <v>0.008284511161890662</v>
       </c>
       <c r="G38">
-        <v>0.006915872271437584</v>
+        <v>0.006714374614320118</v>
       </c>
       <c r="H38">
-        <v>0.020835318333113584</v>
+        <v>0.020422048400997733</v>
       </c>
       <c r="I38">
-        <v>0.0018633454289880586</v>
+        <v>0.0015261556624343033</v>
       </c>
       <c r="J38">
-        <v>0.04328965085234269</v>
+        <v>0.04121550107288618</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -49536,12 +49536,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:bambu:nebbi-uga</t>
+          <t>corridor:38:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -49553,22 +49553,22 @@
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.0027165842894116</v>
+        <v>0.002681493416460179</v>
       </c>
       <c r="F39">
-        <v>0.008462033120420043</v>
+        <v>0.008183525990654555</v>
       </c>
       <c r="G39">
-        <v>0.006716793549505717</v>
+        <v>0.0066376497183083805</v>
       </c>
       <c r="H39">
-        <v>0.020833674557079906</v>
+        <v>0.020174624300513644</v>
       </c>
       <c r="I39">
-        <v>0.0020833936544929683</v>
+        <v>0.0014926750968995012</v>
       </c>
       <c r="J39">
-        <v>0.03946198024192364</v>
+        <v>0.039228799255843605</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -49604,39 +49604,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:kilo:kampala-uga</t>
+          <t>corridor:39:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.002827091182153685</v>
+        <v>0.0028326663994584778</v>
       </c>
       <c r="F40">
-        <v>0.00844775188405536</v>
+        <v>0.00815823939873217</v>
       </c>
       <c r="G40">
-        <v>0.00698945216246713</v>
+        <v>0.00701107122667835</v>
       </c>
       <c r="H40">
-        <v>0.020798732145144022</v>
+        <v>0.020112663896618338</v>
       </c>
       <c r="I40">
-        <v>0.002402073067513322</v>
+        <v>0.0015343125999103453</v>
       </c>
       <c r="J40">
-        <v>0.04203889492505474</v>
+        <v>0.04046059631457021</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -49672,12 +49672,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:goma-cod:kasese-uga</t>
+          <t>corridor:40:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -49689,22 +49689,22 @@
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.003098245083166251</v>
+        <v>0.002747567807505402</v>
       </c>
       <c r="F41">
-        <v>0.008421295606099832</v>
+        <v>0.008154445449094133</v>
       </c>
       <c r="G41">
-        <v>0.007658292806589306</v>
+        <v>0.006800874406568735</v>
       </c>
       <c r="H41">
-        <v>0.02073400424273225</v>
+        <v>0.020103367023304758</v>
       </c>
       <c r="I41">
-        <v>0.0019012551291241716</v>
+        <v>0.0016545850906405566</v>
       </c>
       <c r="J41">
-        <v>0.043972182665138686</v>
+        <v>0.04190231971566359</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -49740,39 +49740,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:nizi:kasese-uga</t>
+          <t>corridor:41:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0028569543753373394</v>
+        <v>0.0029994938796520376</v>
       </c>
       <c r="F42">
-        <v>0.008399426913836133</v>
+        <v>0.008147226747461322</v>
       </c>
       <c r="G42">
-        <v>0.007063127009692638</v>
+        <v>0.007423064501010185</v>
       </c>
       <c r="H42">
-        <v>0.02068049618046927</v>
+        <v>0.020085678474308588</v>
       </c>
       <c r="I42">
-        <v>0.001940933593041583</v>
+        <v>0.0019885435545158206</v>
       </c>
       <c r="J42">
-        <v>0.043335795648454876</v>
+        <v>0.03889536735459872</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -49808,39 +49808,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:kilo:beni-cod</t>
+          <t>corridor:42:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.003208969909536785</v>
+        <v>0.003061304197971737</v>
       </c>
       <c r="F43">
-        <v>0.008396225534473778</v>
+        <v>0.00814381727681368</v>
       </c>
       <c r="G43">
-        <v>0.007931333169932525</v>
+        <v>0.00757568403154249</v>
       </c>
       <c r="H43">
-        <v>0.020672662243381656</v>
+        <v>0.020077321716829383</v>
       </c>
       <c r="I43">
-        <v>0.002451028146972545</v>
+        <v>0.0016647585017794454</v>
       </c>
       <c r="J43">
-        <v>0.03828745231097391</v>
+        <v>0.03886426325038798</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -49876,39 +49876,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:miti-murhesa:kasese-uga</t>
+          <t>corridor:43:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.0029666436131503826</v>
+        <v>0.0031340416283216765</v>
       </c>
       <c r="F44">
-        <v>0.008357295677379833</v>
+        <v>0.008075152624742232</v>
       </c>
       <c r="G44">
-        <v>0.007333712327801806</v>
+        <v>0.00775526629452003</v>
       </c>
       <c r="H44">
-        <v>0.020577406853998614</v>
+        <v>0.01990905693022571</v>
       </c>
       <c r="I44">
-        <v>0.0017909766821187448</v>
+        <v>0.002243955437822981</v>
       </c>
       <c r="J44">
-        <v>0.04221199332021168</v>
+        <v>0.03925743592923069</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:nebbi-uga</t>
+          <t>corridor:44:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -49954,29 +49954,29 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.002842466144925393</v>
+        <v>0.0027076980614253177</v>
       </c>
       <c r="F45">
-        <v>0.008306902670088073</v>
+        <v>0.008070258181662043</v>
       </c>
       <c r="G45">
-        <v>0.007027383918706276</v>
+        <v>0.006702384988596155</v>
       </c>
       <c r="H45">
-        <v>0.02045409216417554</v>
+        <v>0.019897061858827808</v>
       </c>
       <c r="I45">
-        <v>0.001971915409122316</v>
+        <v>0.0018949255081115225</v>
       </c>
       <c r="J45">
-        <v>0.040177434293513725</v>
+        <v>0.03846409821761752</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -50012,39 +50012,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:nizi:arua-uga</t>
+          <t>corridor:45:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D46">
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.0029776446786048127</v>
+        <v>0.0029941551171358827</v>
       </c>
       <c r="F46">
-        <v>0.00827436066103368</v>
+        <v>0.008062710206497403</v>
       </c>
       <c r="G46">
-        <v>0.007360847692718359</v>
+        <v>0.007409881598903129</v>
       </c>
       <c r="H46">
-        <v>0.020374455899091842</v>
+        <v>0.019878564189878323</v>
       </c>
       <c r="I46">
-        <v>0.0020194029902177533</v>
+        <v>0.0023605934928140225</v>
       </c>
       <c r="J46">
-        <v>0.0390744440809115</v>
+        <v>0.03849962672911588</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -50080,39 +50080,39 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:butembo:kampala-uga</t>
+          <t>corridor:46:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.0027549525104297867</v>
+        <v>0.002966610048958429</v>
       </c>
       <c r="F47">
-        <v>0.008222628255700165</v>
+        <v>0.008058011311337127</v>
       </c>
       <c r="G47">
-        <v>0.006811466224796531</v>
+        <v>0.007341863257414205</v>
       </c>
       <c r="H47">
-        <v>0.020247848860154932</v>
+        <v>0.01986704842779069</v>
       </c>
       <c r="I47">
-        <v>0.002002134515076684</v>
+        <v>0.00193425911064469</v>
       </c>
       <c r="J47">
-        <v>0.042430507815804784</v>
+        <v>0.03944581553096073</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -50148,39 +50148,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:goma-cod:bundibugyo-uga</t>
+          <t>corridor:47:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002882502947612553</v>
+        <v>0.002837150359859514</v>
       </c>
       <c r="F48">
-        <v>0.008194900129801702</v>
+        <v>0.008035393220128945</v>
       </c>
       <c r="G48">
-        <v>0.0071261552896609015</v>
+        <v>0.007022145861493551</v>
       </c>
       <c r="H48">
-        <v>0.02017998389325623</v>
+        <v>0.019811615320896397</v>
       </c>
       <c r="I48">
-        <v>0.0014343817285406735</v>
+        <v>0.0016272804773103918</v>
       </c>
       <c r="J48">
-        <v>0.03991556549220518</v>
+        <v>0.0417257099987222</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -50216,39 +50216,39 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:butembo:kasese-uga</t>
+          <t>corridor:48:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.002899735778643775</v>
+        <v>0.0027221893165624844</v>
       </c>
       <c r="F49">
-        <v>0.008156775375274178</v>
+        <v>0.008025112676473323</v>
       </c>
       <c r="G49">
-        <v>0.007168667109143045</v>
+        <v>0.006738183364620509</v>
       </c>
       <c r="H49">
-        <v>0.020086668634671817</v>
+        <v>0.019786420160049306</v>
       </c>
       <c r="I49">
-        <v>0.001765702714835879</v>
+        <v>0.0018923716266919608</v>
       </c>
       <c r="J49">
-        <v>0.039438828983039326</v>
+        <v>0.04067091464985655</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -50284,12 +50284,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:goma-cod:beni-cod</t>
+          <t>corridor:49:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -50301,22 +50301,22 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0027436075367688606</v>
+        <v>0.0029779299971779694</v>
       </c>
       <c r="F50">
-        <v>0.00813573057807132</v>
+        <v>0.007993848855793961</v>
       </c>
       <c r="G50">
-        <v>0.006783473348184826</v>
+        <v>0.007369816645196731</v>
       </c>
       <c r="H50">
-        <v>0.02003515768678027</v>
+        <v>0.019709793462212938</v>
       </c>
       <c r="I50">
-        <v>0.0019484543771382619</v>
+        <v>0.00181708380560561</v>
       </c>
       <c r="J50">
-        <v>0.04366249567204285</v>
+        <v>0.03931941479325931</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -50352,12 +50352,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:butembo:arua-uga</t>
+          <t>corridor:50:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -50369,22 +50369,22 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.00289673081900102</v>
+        <v>0.002573515092590184</v>
       </c>
       <c r="F51">
-        <v>0.008093538488025936</v>
+        <v>0.007966550348283807</v>
       </c>
       <c r="G51">
-        <v>0.0071612541418274445</v>
+        <v>0.006370874666990878</v>
       </c>
       <c r="H51">
-        <v>0.019931878246767426</v>
+        <v>0.01964288498845579</v>
       </c>
       <c r="I51">
-        <v>0.0016809985549575749</v>
+        <v>0.0019758723489192026</v>
       </c>
       <c r="J51">
-        <v>0.04244857346914838</v>
+        <v>0.042497226842963434</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -50420,39 +50420,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:miti-murhesa:kampala-uga</t>
+          <t>corridor:51:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.0029401286142527183</v>
+        <v>0.00270874962073242</v>
       </c>
       <c r="F52">
-        <v>0.008060259325341046</v>
+        <v>0.007945705918331214</v>
       </c>
       <c r="G52">
-        <v>0.0072683082461652004</v>
+        <v>0.006704981285868744</v>
       </c>
       <c r="H52">
-        <v>0.019850402601428535</v>
+        <v>0.019591793108546057</v>
       </c>
       <c r="I52">
-        <v>0.001797781260891848</v>
+        <v>0.0017099558870529636</v>
       </c>
       <c r="J52">
-        <v>0.03851102703520781</v>
+        <v>0.040311579752921115</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -50488,39 +50488,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:bambu:arua-uga</t>
+          <t>corridor:52:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.002865544957359273</v>
+        <v>0.002937977495464733</v>
       </c>
       <c r="F53">
-        <v>0.008007505347331828</v>
+        <v>0.00791077263458917</v>
       </c>
       <c r="G53">
-        <v>0.0070843200252671545</v>
+        <v>0.007271156988672728</v>
       </c>
       <c r="H53">
-        <v>0.019721262395209938</v>
+        <v>0.019506162869570853</v>
       </c>
       <c r="I53">
-        <v>0.0015405355995758848</v>
+        <v>0.0015259490592032937</v>
       </c>
       <c r="J53">
-        <v>0.03672115158663102</v>
+        <v>0.04355956758414158</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -50556,12 +50556,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:miti-murhesa:nebbi-uga</t>
+          <t>corridor:53:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -50573,22 +50573,22 @@
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0029536944459469527</v>
+        <v>0.0025676185126164985</v>
       </c>
       <c r="F54">
-        <v>0.007960826510511443</v>
+        <v>0.007868621059145403</v>
       </c>
       <c r="G54">
-        <v>0.007301771191140616</v>
+        <v>0.0063563051772850265</v>
       </c>
       <c r="H54">
-        <v>0.01960697825032018</v>
+        <v>0.01940283456752373</v>
       </c>
       <c r="I54">
-        <v>0.0016862635592489572</v>
+        <v>0.0016564750458324922</v>
       </c>
       <c r="J54">
-        <v>0.045197930386536175</v>
+        <v>0.03677402473147005</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -50624,39 +50624,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:bambu:kampala-uga</t>
+          <t>corridor:54:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0028077086856141686</v>
+        <v>0.0027868684736187532</v>
       </c>
       <c r="F55">
-        <v>0.007901485678099562</v>
+        <v>0.007841801348761585</v>
       </c>
       <c r="G55">
-        <v>0.006941632095260497</v>
+        <v>0.00689795184472039</v>
       </c>
       <c r="H55">
-        <v>0.01946168095865239</v>
+        <v>0.019337083521810405</v>
       </c>
       <c r="I55">
-        <v>0.0021553033511651945</v>
+        <v>0.0017127846529912062</v>
       </c>
       <c r="J55">
-        <v>0.04097440772519585</v>
+        <v>0.03838966632456429</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -50692,39 +50692,39 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:butembo:beni-cod</t>
+          <t>corridor:55:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.0029325884804620728</v>
+        <v>0.002695763743499391</v>
       </c>
       <c r="F56">
-        <v>0.0078658503326898</v>
+        <v>0.007827990157414616</v>
       </c>
       <c r="G56">
-        <v>0.007249708704873986</v>
+        <v>0.006672903334783625</v>
       </c>
       <c r="H56">
-        <v>0.01937442245861365</v>
+        <v>0.0193032265603717</v>
       </c>
       <c r="I56">
-        <v>0.0023275583555744496</v>
+        <v>0.0021490354133257674</v>
       </c>
       <c r="J56">
-        <v>0.04310662676624314</v>
+        <v>0.04054210634480244</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -50760,7 +50760,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:kilo:kasese-uga</t>
+          <t>corridor:56:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -50770,29 +50770,29 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.002964790671466655</v>
+        <v>0.003089733434463643</v>
       </c>
       <c r="F57">
-        <v>0.007845522849790815</v>
+        <v>0.007797896708572921</v>
       </c>
       <c r="G57">
-        <v>0.007329141803465333</v>
+        <v>0.007645875573836641</v>
       </c>
       <c r="H57">
-        <v>0.019324644695648402</v>
+        <v>0.019229449244770908</v>
       </c>
       <c r="I57">
-        <v>0.001979182980043831</v>
+        <v>0.0016800255774773844</v>
       </c>
       <c r="J57">
-        <v>0.03709606445309815</v>
+        <v>0.034479825340189424</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -50828,39 +50828,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:miti-murhesa:arua-uga</t>
+          <t>corridor:57:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.002787974005366123</v>
+        <v>0.002629641493342244</v>
       </c>
       <c r="F58">
-        <v>0.007811983261174604</v>
+        <v>0.0077950978062735765</v>
       </c>
       <c r="G58">
-        <v>0.006892941705632205</v>
+        <v>0.006509547825961637</v>
       </c>
       <c r="H58">
-        <v>0.019242508810321413</v>
+        <v>0.019222587126321078</v>
       </c>
       <c r="I58">
-        <v>0.0017836493702624218</v>
+        <v>0.0013601473368735656</v>
       </c>
       <c r="J58">
-        <v>0.03775589018826164</v>
+        <v>0.03643059423991454</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -50896,39 +50896,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:nizi:kampala-uga</t>
+          <t>corridor:58:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0030397115334472313</v>
+        <v>0.0028404048325195996</v>
       </c>
       <c r="F59">
-        <v>0.007798503469288315</v>
+        <v>0.007786957767991598</v>
       </c>
       <c r="G59">
-        <v>0.007513934292532054</v>
+        <v>0.007030184083863106</v>
       </c>
       <c r="H59">
-        <v>0.01920949889117962</v>
+        <v>0.019202630017290306</v>
       </c>
       <c r="I59">
-        <v>0.0016678403853665758</v>
+        <v>0.0018407478578635922</v>
       </c>
       <c r="J59">
-        <v>0.03881661822899164</v>
+        <v>0.041169590401536636</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -50964,12 +50964,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:nizi:beni-cod</t>
+          <t>corridor:59:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -50981,22 +50981,22 @@
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.0028279586473544394</v>
+        <v>0.0030164649861187665</v>
       </c>
       <c r="F60">
-        <v>0.007773442977447614</v>
+        <v>0.007772299321732512</v>
       </c>
       <c r="G60">
-        <v>0.006991592151725234</v>
+        <v>0.0074649703248304</v>
       </c>
       <c r="H60">
-        <v>0.019148124794601235</v>
+        <v>0.01916669022271858</v>
       </c>
       <c r="I60">
-        <v>0.001626485696169075</v>
+        <v>0.0017745338814096486</v>
       </c>
       <c r="J60">
-        <v>0.04043085112899037</v>
+        <v>0.04144693368617039</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -51032,39 +51032,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:bambu:kasese-uga</t>
+          <t>corridor:60:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.0029787064606684455</v>
+        <v>0.002780055599183956</v>
       </c>
       <c r="F61">
-        <v>0.007727723579566553</v>
+        <v>0.0077543800748747505</v>
       </c>
       <c r="G61">
-        <v>0.007363466593160867</v>
+        <v>0.006881123372275866</v>
       </c>
       <c r="H61">
-        <v>0.01903614948937532</v>
+        <v>0.01912275597116167</v>
       </c>
       <c r="I61">
-        <v>0.002161627379220277</v>
+        <v>0.001731233807528232</v>
       </c>
       <c r="J61">
-        <v>0.040700080739514</v>
+        <v>0.03818702256228324</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -51100,39 +51100,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:butembo:nebbi-uga</t>
+          <t>corridor:61:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.002794253883045994</v>
+        <v>0.0026587921388565305</v>
       </c>
       <c r="F62">
-        <v>0.007726643785385345</v>
+        <v>0.007745510300115388</v>
       </c>
       <c r="G62">
-        <v>0.006908435854105138</v>
+        <v>0.006581566727665494</v>
       </c>
       <c r="H62">
-        <v>0.019033505698469483</v>
+        <v>0.0191010070867213</v>
       </c>
       <c r="I62">
-        <v>0.0017974249505340796</v>
+        <v>0.0015209453885095762</v>
       </c>
       <c r="J62">
-        <v>0.040761246701666295</v>
+        <v>0.040091153412378705</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -51168,39 +51168,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:kilo:arua-uga</t>
+          <t>corridor:62:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0027895356588024944</v>
+        <v>0.0027361329624540076</v>
       </c>
       <c r="F63">
-        <v>0.007708922084123715</v>
+        <v>0.0075987291180549255</v>
       </c>
       <c r="G63">
-        <v>0.0068967939985309645</v>
+        <v>0.006772627856763858</v>
       </c>
       <c r="H63">
-        <v>0.018990099864912985</v>
+        <v>0.018741077563372677</v>
       </c>
       <c r="I63">
-        <v>0.0013975388045409515</v>
+        <v>0.0013777102458249037</v>
       </c>
       <c r="J63">
-        <v>0.042391251021321644</v>
+        <v>0.043087769872402426</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -51236,39 +51236,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:kilo:bundibugyo-uga</t>
+          <t>corridor:63:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0024745761411364142</v>
+        <v>0.0028258568215484003</v>
       </c>
       <c r="F64">
-        <v>0.007569959524086317</v>
+        <v>0.007552854340310916</v>
       </c>
       <c r="G64">
-        <v>0.00611952005219521</v>
+        <v>0.006994252131591605</v>
       </c>
       <c r="H64">
-        <v>0.01864970148957265</v>
+        <v>0.018628569089331942</v>
       </c>
       <c r="I64">
-        <v>0.001552318276025716</v>
+        <v>0.0018339497806420303</v>
       </c>
       <c r="J64">
-        <v>0.034976270348434146</v>
+        <v>0.0447125896493108</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -51304,12 +51304,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:64:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -51321,22 +51321,22 @@
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0028359961308326576</v>
+        <v>0.002862546240653324</v>
       </c>
       <c r="F65">
-        <v>0.00756961435820569</v>
+        <v>0.0075168412354912895</v>
       </c>
       <c r="G65">
-        <v>0.007011421744851615</v>
+        <v>0.007084869280098771</v>
       </c>
       <c r="H65">
-        <v>0.018648855869933034</v>
+        <v>0.0185402409724002</v>
       </c>
       <c r="I65">
-        <v>0.0011273495847349967</v>
+        <v>0.0017601300993422223</v>
       </c>
       <c r="J65">
-        <v>0.037299073210084584</v>
+        <v>0.04281508413149316</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -51372,39 +51372,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:goma-cod:nebbi-uga</t>
+          <t>corridor:65:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.002833861264198795</v>
+        <v>0.002806475854065099</v>
       </c>
       <c r="F66">
-        <v>0.007547888001259828</v>
+        <v>0.007390944356303691</v>
       </c>
       <c r="G66">
-        <v>0.007006154836616929</v>
+        <v>0.006946382389732636</v>
       </c>
       <c r="H66">
-        <v>0.018595628743809794</v>
+        <v>0.018231416239954695</v>
       </c>
       <c r="I66">
-        <v>0.00218933896549888</v>
+        <v>0.00208300583836101</v>
       </c>
       <c r="J66">
-        <v>0.04012855964424418</v>
+        <v>0.03944316706094814</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -51440,39 +51440,39 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:nizi:nebbi-uga</t>
+          <t>corridor:66:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.0028713896563432317</v>
+        <v>0.0028636196069686815</v>
       </c>
       <c r="F67">
-        <v>0.007546538100174749</v>
+        <v>0.007245116575636645</v>
       </c>
       <c r="G67">
-        <v>0.007098739218278277</v>
+        <v>0.0070875198104265735</v>
       </c>
       <c r="H67">
-        <v>0.018592320839906473</v>
+        <v>0.017873638059777402</v>
       </c>
       <c r="I67">
-        <v>0.002009283025009237</v>
+        <v>0.001885099074969826</v>
       </c>
       <c r="J67">
-        <v>0.035894482626523734</v>
+        <v>0.04037313015728034</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -51983,10 +51983,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.4036352802540115</v>
+        <v>0.4031809300428392</v>
       </c>
       <c r="F9">
-        <v>0.46215932894360784</v>
+        <v>0.4637985606142611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -52037,10 +52037,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>2.5636921180997643</v>
+        <v>2.658988714502407</v>
       </c>
       <c r="F10">
-        <v>12.502589644513742</v>
+        <v>12.09131304558839</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -52091,10 +52091,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="F11">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -52402,7 +52402,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -52454,7 +52454,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.979</v>
+        <v>0.973</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -52705,7 +52705,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"confirmation_backlog_50": [455, 725], "reporting_completeness_50": [0.4036352802540115, 0.46215932894360784]}</t>
+          <t>{"confirmation_backlog_50": [468, 712], "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -52734,12 +52734,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"confirmed_endpoint": 112, "reporting_completeness_50": [0.4036352802540115, 0.46215932894360784]}</t>
+          <t>{"confirmed_endpoint": 112, "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"endpoint_confirmable_50": [242, 277]}</t>
+          <t>{"endpoint_confirmable_50": [241, 278]}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
     </row>
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -819,7 +819,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (761 to 1171 at deaths 179), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 761 to 1171 at deaths 179, CFR 40 to 26</t>
+          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 948 to 1458 at deaths 223, CFR 40 to 26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 761 to 1171 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
+          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 948 to 1458 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 106; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 27 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.4% lower bounds and 1.8-46.9% upper bounds.</t>
+          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.2% lower bounds and 1.8-48.2% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed cumulative table exists, keep the 27 cases unallocated and do not derive corridor risks from the 106 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
+          <t>Before any later snapshot, first refresh official per-zone source-load evidence. If no newer officially zone-attributed cumulative table exists, keep the 33 cases unallocated and do not derive corridor risks from the 112 headline aggregate. Do not present current-outbreak corridor constants as fitted or literature-grounded until BDBV-specific or outbreak-specific calibration is added.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1353,47 +1353,94 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Bdbv may25 official release</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>The May 25 public snapshot supersedes the May 24 snapshot by fix-forward (a new dated snapshot, not an in-place re-cut) and uses the US CDC Current Situation page (25 May) as the highest valid primary on the latest date for suspected, confirmed, and deaths. ECDC (25 May), the DRC MoH all-published-bulletins dashboard aggregate (24 May), and WHO DG (22 May) are retained as dated conflict anchors. The endpoint takes the higher valid primary and does not average across sources or down-revise to a lower peer.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>US CDC 25 May reports 906 suspected DRC cases, 112 confirmed (105 DRC + 7 Uganda), 223 suspected DRC deaths, ten confirmed DRC deaths, and one Uganda death. ECDC 25 May reports 101 confirmed, 904 suspected, and 119 suspected deaths. The DRC MoH 24 May dashboard aggregate reports 854 reported cases, 112 confirmed DRC cases, and 179 registered deaths. The reconciled endpoint takes CDC's 906 suspected, 112 confirmed, and 223 deaths; the lower or source-review figures 179, 119, and 177 are dated conflict anchors.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>US CDC. Ebola Disease: Current Situation, 25 May 2026.; European Centre for Disease Prevention and Control. Ebola virus disease outbreak in the DRC and Uganda, outbreak page, 25 May 2026.; data/bundibugyo-2026/manifest.json entries cdc-current-situation-2026-05-25 and ecdc-bdbv-drc-uga-2026-05-25-live.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html; https://www.ecdc.europa.eu/en/ebola-virus-disease; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Keep the May 25 snapshot as review-ready evidence-backed state. Hold public release for the founder go-signal. Revisit the deaths endpoint if a later official PDF or table reconciles the CDC-versus-ECDC suspected-death spread.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-028</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Bdbv may25 source review boundary</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>May 25 source-review evidence can be archived for audit and partner context without creating a May 25 public snapshot route or promoting non-primary/watch claims into scored counts.</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>ECDC 25 May is accepted as regional cross-check only (snapshot_trigger=false); WHO AFRO hub is official context/readiness only (snapshot_trigger=false); IFRC requires browser/AIR capture when plain HTTP is challenged; Wikipedia remains watch-only unless confirmed by public-health authority.</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>supported</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>ECDC. Ebola virus disease outbreak in the Democratic Republic of the Congo and Uganda. Page last updated 25 May 2026 16:30.; WHO Regional Office for Africa. Ongoing outbreak in the Democratic Republic of the Congo / Bundibugyo virus disease outbreak hub. Updated 24 May 2026.; IFRC. Ebola: IFRC scales up response in eastern DRC as regional risks grow. 21 May 2026.; Wikipedia contributors. 2026 Ituri Province Ebola epidemic, live page observed by 25 May 2026 freshness check.; data/external_sources/freshness/bdbv-2026-2026-05-25.json generated by source_ingest.py --live-check --as-of 2026-05-25.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026; https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26; https://www.ifrc.org/press-release/ebola-ifrc-scales-response-eastern-drc-regional-risks-grow; https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic; restricted-local-review-not-redistributed</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Keep May 24 as the current publication-state route. Continue source review for DRC MoH table semantics, CDC traveler context, and future primary WHO/DRC/Uganda/CDC updates before any May 25 snapshot promotion.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Detailed audit IDs and review locators are withheld from this public export.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I26"/>
 </worksheet>
 </file>
 
@@ -3750,8 +3797,66 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>US Centers for Disease Control and Prevention</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-25T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-05-25T22:17:34Z</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="J41"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L40"/>
+  <autoFilter ref="A1:L41"/>
 </worksheet>
 </file>
 
@@ -8260,7 +8365,7 @@
       <c r="I10"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (761 to 1171 at deaths 179), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11081,12 +11186,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
       <c r="E2"/>
@@ -11120,7 +11225,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="D3"/>
@@ -16124,8 +16229,141 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>source_data_report_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D122"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>source_publication_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D123"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-05-25T22:17:34Z</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>official CDC headline/source-review input for global COD+UGA counts; can update headline confirmed/suspected only after source-review, and does not by itself update DRC MoH zone-attributed corridor source load.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>official_cdc</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I121"/>
+  <autoFilter ref="A1:I124"/>
 </worksheet>
 </file>
 
@@ -32851,34 +33089,34 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D212"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F212">
-        <v>904</v>
-      </c>
-      <c r="G212">
-        <v>395</v>
-      </c>
-      <c r="H212">
-        <v>904</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="G212"/>
+      <c r="H212"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>count</t>
@@ -32886,27 +33124,23 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K212"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O212" t="inlineStr">
@@ -32916,7 +33150,7 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -32934,12 +33168,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -32947,21 +33181,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D213"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-05-24T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F213">
-        <v>106</v>
-      </c>
-      <c r="G213">
-        <v>10</v>
-      </c>
-      <c r="H213">
-        <v>106</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G213"/>
+      <c r="H213"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>count</t>
@@ -32969,27 +33203,23 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24</t>
-        </is>
-      </c>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K213"/>
       <c r="L213" t="inlineStr">
         <is>
-          <t>BDBV-CLAIM-026</t>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -32999,7 +33229,7 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>b33e81ab0e2af289ccde2ed4685a4a380f3397693ed2f6864e54a0f65227dc7d</t>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -33012,97 +33242,1053 @@
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+      <c r="S213"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F214">
+        <v>112</v>
+      </c>
+      <c r="G214"/>
+      <c r="H214"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K214"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F215">
+        <v>7</v>
+      </c>
+      <c r="G215"/>
+      <c r="H215"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K215"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K216"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F217">
+        <v>906</v>
+      </c>
+      <c r="G217"/>
+      <c r="H217"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K217"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F218">
+        <v>906</v>
+      </c>
+      <c r="G218"/>
+      <c r="H218"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K218"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F219">
+        <v>10</v>
+      </c>
+      <c r="G219"/>
+      <c r="H219"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K219"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F220">
+        <v>223</v>
+      </c>
+      <c r="G220"/>
+      <c r="H220"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K220"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S220"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F221">
+        <v>223</v>
+      </c>
+      <c r="G221"/>
+      <c r="H221"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K221"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222"/>
+      <c r="H222"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K222"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>source:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F223">
+        <v>200</v>
+      </c>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K223"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D224"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F224">
+        <v>906</v>
+      </c>
+      <c r="G224">
+        <v>395</v>
+      </c>
+      <c r="H224">
+        <v>906</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D225"/>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F225">
+        <v>112</v>
+      </c>
+      <c r="G225">
+        <v>10</v>
+      </c>
+      <c r="H225">
+        <v>112</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D214"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>2026-05-24T23:59:59Z</t>
-        </is>
-      </c>
-      <c r="F214">
-        <v>179</v>
-      </c>
-      <c r="G214">
+      <c r="D226"/>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F226">
+        <v>223</v>
+      </c>
+      <c r="G226">
         <v>106</v>
       </c>
-      <c r="H214">
-        <v>179</v>
-      </c>
-      <c r="I214" t="inlineStr">
+      <c r="H226">
+        <v>223</v>
+      </c>
+      <c r="I226" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>BDBV-CLAIM-026</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr">
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N214" t="inlineStr">
+      <c r="N226" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>https://administration.sante.gouv.cd/graphql</t>
-        </is>
-      </c>
-      <c r="P214" t="inlineStr">
-        <is>
-          <t>f3d5149176d77cbf28d15c79bb7449b1a516c6b855ffe28d51b2adaef0f4bff5</t>
-        </is>
-      </c>
-      <c r="Q214" t="inlineStr">
-        <is>
-          <t>private_restricted_bytes</t>
-        </is>
-      </c>
-      <c r="R214" t="inlineStr">
-        <is>
-          <t>publisher-terms-not-confirmed</t>
-        </is>
-      </c>
-      <c r="S214"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S226"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S214"/>
+  <autoFilter ref="A1:S226"/>
 </worksheet>
 </file>
 
@@ -43897,8 +45083,620 @@
       </c>
       <c r="K211"/>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D212">
+        <v>112</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D213">
+        <v>105</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D214">
+        <v>112</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K214"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D215">
+        <v>7</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_confirmed_united_states</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D217">
+        <v>10</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D218">
+        <v>223</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D219">
+        <v>223</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D220">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K220"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D221">
+        <v>200</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D222">
+        <v>906</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>906</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K223"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K211"/>
+  <autoFilter ref="A1:K223"/>
 </worksheet>
 </file>
 
@@ -45222,7 +47020,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:arua-uga</t>
+          <t>corridor:01:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -45232,33 +47030,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.0912163373057068</v>
+        <v>0.0861708114385285</v>
       </c>
       <c r="F2">
-        <v>0.2226702397521661</v>
+        <v>0.23315469335620254</v>
       </c>
       <c r="G2">
-        <v>0.21390472120489915</v>
+        <v>0.20028631694823662</v>
       </c>
       <c r="H2">
-        <v>0.4694422290811111</v>
+        <v>0.48234065943233195</v>
       </c>
       <c r="I2">
-        <v>0.04532749822980132</v>
+        <v>0.06427581319980569</v>
       </c>
       <c r="J2">
-        <v>0.6911278013787443</v>
+        <v>0.7474537035483133</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -45278,7 +47076,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -45290,7 +47088,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:nebbi-uga</t>
+          <t>corridor:02:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -45300,33 +47098,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08452455181245988</v>
+        <v>0.08768171124595683</v>
       </c>
       <c r="F3">
-        <v>0.22265814712920945</v>
+        <v>0.2275794037963691</v>
       </c>
       <c r="G3">
-        <v>0.19925818749831423</v>
+        <v>0.2035618016305265</v>
       </c>
       <c r="H3">
-        <v>0.4694209392975942</v>
+        <v>0.47295633103988544</v>
       </c>
       <c r="I3">
-        <v>0.06671907792458477</v>
+        <v>0.04459460740614488</v>
       </c>
       <c r="J3">
-        <v>0.7039957005098051</v>
+        <v>0.7478981260349676</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -45346,7 +47144,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -45358,7 +47156,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:kampala-uga</t>
+          <t>corridor:03:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -45368,33 +47166,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.0837536879207027</v>
+        <v>0.08233054224498484</v>
       </c>
       <c r="F4">
-        <v>0.22263658502383896</v>
+        <v>0.22543492066869397</v>
       </c>
       <c r="G4">
-        <v>0.19756045935788125</v>
+        <v>0.19192499609422323</v>
       </c>
       <c r="H4">
-        <v>0.46938420491713334</v>
+        <v>0.46931800011005115</v>
       </c>
       <c r="I4">
-        <v>0.049090364064060366</v>
+        <v>0.06964130796312437</v>
       </c>
       <c r="J4">
-        <v>0.7378909709414584</v>
+        <v>0.6990237917928565</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -45414,7 +47212,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -45443,26 +47241,26 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08539306320934745</v>
+        <v>0.08664306873590838</v>
       </c>
       <c r="F5">
-        <v>0.21732595153426423</v>
+        <v>0.222887038238157</v>
       </c>
       <c r="G5">
-        <v>0.20116768514208086</v>
+        <v>0.20131080198240825</v>
       </c>
       <c r="H5">
-        <v>0.4602154648850442</v>
+        <v>0.4649794327839667</v>
       </c>
       <c r="I5">
-        <v>0.06296500819577727</v>
+        <v>0.05425688863966508</v>
       </c>
       <c r="J5">
-        <v>0.6925655607803819</v>
+        <v>0.7101842045533336</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -45482,7 +47280,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -45494,7 +47292,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:bundibugyo-uga</t>
+          <t>corridor:05:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -45504,33 +47302,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08585999321999954</v>
+        <v>0.09176382815314144</v>
       </c>
       <c r="F6">
-        <v>0.2142466100194772</v>
+        <v>0.2196720235905948</v>
       </c>
       <c r="G6">
-        <v>0.20219412729622327</v>
+        <v>0.2123714082943657</v>
       </c>
       <c r="H6">
-        <v>0.45485593395145274</v>
+        <v>0.45947010738720273</v>
       </c>
       <c r="I6">
-        <v>0.06638378793530512</v>
+        <v>0.0602209036243418</v>
       </c>
       <c r="J6">
-        <v>0.7375416502530325</v>
+        <v>0.7146926481656625</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -45550,7 +47348,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -45562,7 +47360,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corridor:06:rwampara:kasese-uga</t>
+          <t>corridor:06:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -45572,33 +47370,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08862360450035126</v>
+        <v>0.08396936085735776</v>
       </c>
       <c r="F7">
-        <v>0.21187297147959527</v>
+        <v>0.2119043283318027</v>
       </c>
       <c r="G7">
-        <v>0.20824918095316647</v>
+        <v>0.19549948212877702</v>
       </c>
       <c r="H7">
-        <v>0.45070261253386334</v>
+        <v>0.44602874389977687</v>
       </c>
       <c r="I7">
-        <v>0.04755485008790408</v>
+        <v>0.056360235565877555</v>
       </c>
       <c r="J7">
-        <v>0.712627902824087</v>
+        <v>0.7142786607680277</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -45618,7 +47416,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -45630,43 +47428,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:bunia:arua-uga</t>
+          <t>corridor:07:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.04135954827362884</v>
+        <v>0.03855467933328152</v>
       </c>
       <c r="F8">
-        <v>0.11983328959815714</v>
+        <v>0.11620932868289471</v>
       </c>
       <c r="G8">
-        <v>0.10083207797214216</v>
+        <v>0.09291440432184914</v>
       </c>
       <c r="H8">
-        <v>0.2747126636812153</v>
+        <v>0.2639086114886541</v>
       </c>
       <c r="I8">
-        <v>0.029212073563033354</v>
+        <v>0.025175207094245807</v>
       </c>
       <c r="J8">
-        <v>0.4662213001716538</v>
+        <v>0.46361890390099453</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -45686,7 +47484,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -45698,7 +47496,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:nebbi-uga</t>
+          <t>corridor:08:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -45708,33 +47506,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04398227300651175</v>
+        <v>0.04147908524423352</v>
       </c>
       <c r="F9">
-        <v>0.11642476266588117</v>
+        <v>0.11562806950949953</v>
       </c>
       <c r="G9">
-        <v>0.10700893044190996</v>
+        <v>0.09974219409345544</v>
       </c>
       <c r="H9">
-        <v>0.26762425390736977</v>
+        <v>0.2627072705721946</v>
       </c>
       <c r="I9">
-        <v>0.03323309459346699</v>
+        <v>0.025907663365721464</v>
       </c>
       <c r="J9">
-        <v>0.48792183288806773</v>
+        <v>0.4462554570998926</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -45754,7 +47552,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -45766,7 +47564,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:kampala-uga</t>
+          <t>corridor:09:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -45776,33 +47574,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04216514495541318</v>
+        <v>0.04179480816556652</v>
       </c>
       <c r="F10">
-        <v>0.11487490058729838</v>
+        <v>0.11558245421258095</v>
       </c>
       <c r="G10">
-        <v>0.10273220880627104</v>
+        <v>0.10047743392001213</v>
       </c>
       <c r="H10">
-        <v>0.26438756064883345</v>
+        <v>0.26261295488077974</v>
       </c>
       <c r="I10">
-        <v>0.033514354068220314</v>
+        <v>0.027913949480659363</v>
       </c>
       <c r="J10">
-        <v>0.4600121524453567</v>
+        <v>0.4647552683750245</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -45822,7 +47620,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -45834,7 +47632,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:beni-cod</t>
+          <t>corridor:10:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -45844,33 +47642,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.038990402689660864</v>
+        <v>0.04186956091160368</v>
       </c>
       <c r="F11">
-        <v>0.11434892428716492</v>
+        <v>0.11539491748492897</v>
       </c>
       <c r="G11">
-        <v>0.09522978243904648</v>
+        <v>0.10065158442248001</v>
       </c>
       <c r="H11">
-        <v>0.2632867689300544</v>
+        <v>0.26222507759010427</v>
       </c>
       <c r="I11">
-        <v>0.029063057329189432</v>
+        <v>0.021242880051839726</v>
       </c>
       <c r="J11">
-        <v>0.4767924217921794</v>
+        <v>0.46678607844486947</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -45890,7 +47688,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -45902,7 +47700,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:arua-uga</t>
+          <t>corridor:11:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -45912,33 +47710,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.03536372093507828</v>
+        <v>0.04042920346327944</v>
       </c>
       <c r="F12">
-        <v>0.11162698694924067</v>
+        <v>0.11242435593909272</v>
       </c>
       <c r="G12">
-        <v>0.08661374204772454</v>
+        <v>0.09729451222456448</v>
       </c>
       <c r="H12">
-        <v>0.25757649648927927</v>
+        <v>0.2560645676658191</v>
       </c>
       <c r="I12">
-        <v>0.02600635405233129</v>
+        <v>0.027413735537554062</v>
       </c>
       <c r="J12">
-        <v>0.4314625171558782</v>
+        <v>0.43705126759089724</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -45958,7 +47756,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -45970,7 +47768,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:bundibugyo-uga</t>
+          <t>corridor:12:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -45980,33 +47778,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.041168739753125294</v>
+        <v>0.04024586283096926</v>
       </c>
       <c r="F13">
-        <v>0.1107501387756348</v>
+        <v>0.11159467152136757</v>
       </c>
       <c r="G13">
-        <v>0.10038168382708493</v>
+        <v>0.09686667859605977</v>
       </c>
       <c r="H13">
-        <v>0.25573121824365375</v>
+        <v>0.25433876336268857</v>
       </c>
       <c r="I13">
-        <v>0.02427074965026969</v>
+        <v>0.03067229187569909</v>
       </c>
       <c r="J13">
-        <v>0.4571962132606071</v>
+        <v>0.4576157180833162</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -46026,7 +47824,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -46055,26 +47853,26 @@
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.03840747902562522</v>
+        <v>0.04066526892293623</v>
       </c>
       <c r="F14">
-        <v>0.11022468214471043</v>
+        <v>0.11152320362817797</v>
       </c>
       <c r="G14">
-        <v>0.09384836785268524</v>
+        <v>0.09784524147753831</v>
       </c>
       <c r="H14">
-        <v>0.2546240929072371</v>
+        <v>0.254190125108517</v>
       </c>
       <c r="I14">
-        <v>0.02339760290109348</v>
+        <v>0.026605224754838577</v>
       </c>
       <c r="J14">
-        <v>0.45366135584564343</v>
+        <v>0.46394166684739413</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -46094,7 +47892,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -46106,12 +47904,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:14:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -46123,26 +47921,26 @@
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.042622724856425986</v>
+        <v>0.043769887053943884</v>
       </c>
       <c r="F15">
-        <v>0.10994385490859934</v>
+        <v>0.11103027985574987</v>
       </c>
       <c r="G15">
-        <v>0.1038104281778379</v>
+        <v>0.10506919313252691</v>
       </c>
       <c r="H15">
-        <v>0.25403199640798074</v>
+        <v>0.2531634176228099</v>
       </c>
       <c r="I15">
-        <v>0.028277498811380836</v>
+        <v>0.024326153776741695</v>
       </c>
       <c r="J15">
-        <v>0.4533285985841223</v>
+        <v>0.44860424323610526</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -46162,7 +47960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -46174,43 +47972,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:bunia:kasese-uga</t>
+          <t>corridor:15:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.039893708218035395</v>
+        <v>0.03750471405393857</v>
       </c>
       <c r="F16">
-        <v>0.10839783417298046</v>
+        <v>0.10749948779872281</v>
       </c>
       <c r="G16">
-        <v>0.09736829629570376</v>
+        <v>0.09045541125798737</v>
       </c>
       <c r="H16">
-        <v>0.25076635038617995</v>
+        <v>0.24578444055142545</v>
       </c>
       <c r="I16">
-        <v>0.022945425424494254</v>
+        <v>0.027237694409312466</v>
       </c>
       <c r="J16">
-        <v>0.45584132979198283</v>
+        <v>0.4271444488438072</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -46230,7 +48028,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -46242,43 +48040,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:nebbi-uga</t>
+          <t>corridor:16:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.03885897551186415</v>
+        <v>0.04228950663900796</v>
       </c>
       <c r="F17">
-        <v>0.10809533543848754</v>
+        <v>0.10704031678368539</v>
       </c>
       <c r="G17">
-        <v>0.09491863955491664</v>
+        <v>0.10162893993380431</v>
       </c>
       <c r="H17">
-        <v>0.25012728395195716</v>
+        <v>0.24482175888282368</v>
       </c>
       <c r="I17">
-        <v>0.029075868004294698</v>
+        <v>0.026598690800271954</v>
       </c>
       <c r="J17">
-        <v>0.4187443071247904</v>
+        <v>0.4232379895804849</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -46298,7 +48096,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -46310,7 +48108,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:kasese-uga</t>
+          <t>corridor:17:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -46320,33 +48118,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.040512046777299554</v>
+        <v>0.03798452079077774</v>
       </c>
       <c r="F18">
-        <v>0.1055105651614231</v>
+        <v>0.1055578744412985</v>
       </c>
       <c r="G18">
-        <v>0.09883047424769487</v>
+        <v>0.09157962059775004</v>
       </c>
       <c r="H18">
-        <v>0.24464677320153547</v>
+        <v>0.24170839592150667</v>
       </c>
       <c r="I18">
-        <v>0.02918801892369734</v>
+        <v>0.0239669463086208</v>
       </c>
       <c r="J18">
-        <v>0.4609928209129825</v>
+        <v>0.4664322846035496</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -46366,7 +48164,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -46378,7 +48176,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:beni-cod</t>
+          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -46388,33 +48186,33 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.039473762203850765</v>
+        <v>0.03778298943272401</v>
       </c>
       <c r="F19">
-        <v>0.10362489156884852</v>
+        <v>0.10384450964700326</v>
       </c>
       <c r="G19">
-        <v>0.09637461819714294</v>
+        <v>0.09110754488962608</v>
       </c>
       <c r="H19">
-        <v>0.24063384235105276</v>
+        <v>0.23810062900458037</v>
       </c>
       <c r="I19">
-        <v>0.023570590511507086</v>
+        <v>0.027747327225511372</v>
       </c>
       <c r="J19">
-        <v>0.4323792575072521</v>
+        <v>0.39188625277934763</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -46434,7 +48232,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -46446,7 +48244,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:bundibugyo-uga</t>
+          <t>corridor:19:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -46456,33 +48254,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.03571317240808905</v>
+        <v>0.031304381068294335</v>
       </c>
       <c r="F20">
-        <v>0.08858542009424464</v>
+        <v>0.08779786212598711</v>
       </c>
       <c r="G20">
-        <v>0.08744601480295106</v>
+        <v>0.07585358277896675</v>
       </c>
       <c r="H20">
-        <v>0.20816581788193778</v>
+        <v>0.2038133127969261</v>
       </c>
       <c r="I20">
-        <v>0.02794960657154857</v>
+        <v>0.017690770792813504</v>
       </c>
       <c r="J20">
-        <v>0.3464635789222376</v>
+        <v>0.3619871650097016</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -46502,7 +48300,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -46514,7 +48312,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:arua-uga</t>
+          <t>corridor:20:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -46524,33 +48322,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03264229590569645</v>
+        <v>0.03171837340940942</v>
       </c>
       <c r="F21">
-        <v>0.08586088011945975</v>
+        <v>0.08476753807336304</v>
       </c>
       <c r="G21">
-        <v>0.08011583054612229</v>
+        <v>0.07683287603147732</v>
       </c>
       <c r="H21">
-        <v>0.20219610083896622</v>
+        <v>0.19723709872212672</v>
       </c>
       <c r="I21">
-        <v>0.023533108201656935</v>
+        <v>0.0227792144919888</v>
       </c>
       <c r="J21">
-        <v>0.35610832817909704</v>
+        <v>0.3495642294984912</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -46570,7 +48368,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -46599,26 +48397,26 @@
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.029377911723571293</v>
+        <v>0.030540418665822744</v>
       </c>
       <c r="F22">
-        <v>0.08201035370872972</v>
+        <v>0.08438962198493272</v>
       </c>
       <c r="G22">
-        <v>0.07228482019525184</v>
+        <v>0.07404478785217791</v>
       </c>
       <c r="H22">
-        <v>0.19371312977138444</v>
+        <v>0.19641470100450442</v>
       </c>
       <c r="I22">
-        <v>0.01774942777466498</v>
+        <v>0.019203507671592176</v>
       </c>
       <c r="J22">
-        <v>0.378011129181644</v>
+        <v>0.3838230566411262</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -46638,7 +48436,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -46650,7 +48448,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:beni-cod</t>
+          <t>corridor:22:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -46660,33 +48458,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.029460858829418568</v>
+        <v>0.030399316276041116</v>
       </c>
       <c r="F23">
-        <v>0.08095304945678247</v>
+        <v>0.08407821789447709</v>
       </c>
       <c r="G23">
-        <v>0.07248432245564349</v>
+        <v>0.07371053738981273</v>
       </c>
       <c r="H23">
-        <v>0.1913742950989335</v>
+        <v>0.19573661412777732</v>
       </c>
       <c r="I23">
-        <v>0.019818390626375203</v>
+        <v>0.021457583298788</v>
       </c>
       <c r="J23">
-        <v>0.3257214893602651</v>
+        <v>0.358453978352833</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -46706,7 +48504,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -46718,7 +48516,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:kasese-uga</t>
+          <t>corridor:23:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -46728,33 +48526,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.030671572216132148</v>
+        <v>0.030329334773183142</v>
       </c>
       <c r="F24">
-        <v>0.08068683653973213</v>
+        <v>0.08357711531060097</v>
       </c>
       <c r="G24">
-        <v>0.07539301823448152</v>
+        <v>0.07354468946695608</v>
       </c>
       <c r="H24">
-        <v>0.19078484133652965</v>
+        <v>0.19464486287655744</v>
       </c>
       <c r="I24">
-        <v>0.019185526848990185</v>
+        <v>0.014570952055622657</v>
       </c>
       <c r="J24">
-        <v>0.36091283002425634</v>
+        <v>0.32281669746439295</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -46774,7 +48572,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -46786,7 +48584,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:nebbi-uga</t>
+          <t>corridor:24:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -46796,33 +48594,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.030591361644302484</v>
+        <v>0.028578262502321705</v>
       </c>
       <c r="F25">
-        <v>0.08048830355982659</v>
+        <v>0.0757669915923353</v>
       </c>
       <c r="G25">
-        <v>0.07520043792455658</v>
+        <v>0.06938957908843438</v>
       </c>
       <c r="H25">
-        <v>0.190345024854301</v>
+        <v>0.17751379634539563</v>
       </c>
       <c r="I25">
-        <v>0.021021863745825663</v>
+        <v>0.021112935786516</v>
       </c>
       <c r="J25">
-        <v>0.350237662341076</v>
+        <v>0.3190059046148159</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -46842,7 +48640,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -46854,7 +48652,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:kasese-uga</t>
+          <t>corridor:25:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -46864,33 +48662,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.00566357846163032</v>
+        <v>0.006127400208913586</v>
       </c>
       <c r="F26">
-        <v>0.0168189945872127</v>
+        <v>0.0168408512437718</v>
       </c>
       <c r="G26">
-        <v>0.014189997894389739</v>
+        <v>0.015128788346279537</v>
       </c>
       <c r="H26">
-        <v>0.04178316258612558</v>
+        <v>0.04125072266262608</v>
       </c>
       <c r="I26">
-        <v>0.003642365369538583</v>
+        <v>0.004388490481047946</v>
       </c>
       <c r="J26">
-        <v>0.08338795718242407</v>
+        <v>0.08183093712788367</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -46910,7 +48708,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -46922,7 +48720,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:kampala-uga</t>
+          <t>corridor:26:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -46932,33 +48730,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.005570451792462239</v>
+        <v>0.00556423388622837</v>
       </c>
       <c r="F27">
-        <v>0.016523396691662473</v>
+        <v>0.01656759676464939</v>
       </c>
       <c r="G27">
-        <v>0.013957658459393757</v>
+        <v>0.013744050643107991</v>
       </c>
       <c r="H27">
-        <v>0.04105807768030023</v>
+        <v>0.04058965567523373</v>
       </c>
       <c r="I27">
-        <v>0.004065924990798628</v>
+        <v>0.003889156206565628</v>
       </c>
       <c r="J27">
-        <v>0.0783570979599987</v>
+        <v>0.08557353521823044</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -46978,7 +48776,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -46990,7 +48788,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:nebbi-uga</t>
+          <t>corridor:27:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -47000,33 +48798,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.0058766644079958075</v>
+        <v>0.00571138519466724</v>
       </c>
       <c r="F28">
-        <v>0.015576503650650497</v>
+        <v>0.016458424878468436</v>
       </c>
       <c r="G28">
-        <v>0.014721496800445155</v>
+        <v>0.014105980367321913</v>
       </c>
       <c r="H28">
-        <v>0.03873315623063381</v>
+        <v>0.04032548046029999</v>
       </c>
       <c r="I28">
-        <v>0.0031251689189409713</v>
+        <v>0.0032961116192571803</v>
       </c>
       <c r="J28">
-        <v>0.08111023604042748</v>
+        <v>0.08227064654779426</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -47046,7 +48844,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -47075,26 +48873,26 @@
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.0056457725950707915</v>
+        <v>0.005665299126924983</v>
       </c>
       <c r="F29">
-        <v>0.015271156168351285</v>
+        <v>0.016137547052658407</v>
       </c>
       <c r="G29">
-        <v>0.014145577133137133</v>
+        <v>0.01399263950136656</v>
       </c>
       <c r="H29">
-        <v>0.03798273499621879</v>
+        <v>0.039548733878884995</v>
       </c>
       <c r="I29">
-        <v>0.003856294606997707</v>
+        <v>0.0033705192295240497</v>
       </c>
       <c r="J29">
-        <v>0.07660375034507658</v>
+        <v>0.0787241376496719</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -47114,7 +48912,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -47126,7 +48924,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:bundibugyo-uga</t>
+          <t>corridor:29:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -47136,33 +48934,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.0049699088501186095</v>
+        <v>0.005760920437457601</v>
       </c>
       <c r="F30">
-        <v>0.015117858841951992</v>
+        <v>0.01564371888735397</v>
       </c>
       <c r="G30">
-        <v>0.01245858544077938</v>
+        <v>0.014227802835785092</v>
       </c>
       <c r="H30">
-        <v>0.03760584808099718</v>
+        <v>0.03835261291771347</v>
       </c>
       <c r="I30">
-        <v>0.004351318719822542</v>
+        <v>0.004405736887256273</v>
       </c>
       <c r="J30">
-        <v>0.07699905023307309</v>
+        <v>0.07717071840257644</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -47182,7 +48980,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -47194,7 +48992,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:arua-uga</t>
+          <t>corridor:30:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -47204,33 +49002,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005409534124622251</v>
+        <v>0.005519371147358398</v>
       </c>
       <c r="F31">
-        <v>0.01477439647878373</v>
+        <v>0.01552589721826908</v>
       </c>
       <c r="G31">
-        <v>0.013556110803496668</v>
+        <v>0.013633690221780848</v>
       </c>
       <c r="H31">
-        <v>0.0367611052860419</v>
+        <v>0.03806709980880993</v>
       </c>
       <c r="I31">
-        <v>0.0038099731375384363</v>
+        <v>0.003119740043250069</v>
       </c>
       <c r="J31">
-        <v>0.07985048552615662</v>
+        <v>0.07892668631060598</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -47250,7 +49048,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -47262,43 +49060,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:butembo:bundibugyo-uga</t>
+          <t>corridor:31:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.0029668846561548</v>
+        <v>0.002911020622911431</v>
       </c>
       <c r="F32">
-        <v>0.008648404569959522</v>
+        <v>0.008708366339810258</v>
       </c>
       <c r="G32">
-        <v>0.00744871853801346</v>
+        <v>0.007204585754623377</v>
       </c>
       <c r="H32">
-        <v>0.021619303752781205</v>
+        <v>0.021460131514392883</v>
       </c>
       <c r="I32">
-        <v>0.0017127776636171044</v>
+        <v>0.002213739571223128</v>
       </c>
       <c r="J32">
-        <v>0.03867924896503808</v>
+        <v>0.04056094344785632</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -47318,7 +49116,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -47330,43 +49128,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:nizi:kasese-uga</t>
+          <t>corridor:32:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.00286779665502937</v>
+        <v>0.0027769798502101373</v>
       </c>
       <c r="F33">
-        <v>0.008456716056206709</v>
+        <v>0.008633599440103473</v>
       </c>
       <c r="G33">
-        <v>0.007200487783166232</v>
+        <v>0.006873526257886398</v>
       </c>
       <c r="H33">
-        <v>0.021143201820719187</v>
+        <v>0.021277062424142124</v>
       </c>
       <c r="I33">
-        <v>0.0016031328739968375</v>
+        <v>0.0016525413787399719</v>
       </c>
       <c r="J33">
-        <v>0.04124369346445676</v>
+        <v>0.03899275669757771</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -47386,7 +49184,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -47398,43 +49196,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:bambu:beni-cod</t>
+          <t>corridor:33:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.003013732647334205</v>
+        <v>0.0029900129594525315</v>
       </c>
       <c r="F34">
-        <v>0.008437658403657261</v>
+        <v>0.00847697711451803</v>
       </c>
       <c r="G34">
-        <v>0.007566060778216588</v>
+        <v>0.007399652921270428</v>
       </c>
       <c r="H34">
-        <v>0.021095861835840557</v>
+        <v>0.020893505827646625</v>
       </c>
       <c r="I34">
-        <v>0.0014900168661657197</v>
+        <v>0.0017305897295624153</v>
       </c>
       <c r="J34">
-        <v>0.04002250253804156</v>
+        <v>0.04136198023793251</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -47454,7 +49252,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -47466,7 +49264,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:butembo:nebbi-uga</t>
+          <t>corridor:34:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -47476,33 +49274,33 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003046128650042168</v>
+        <v>0.003004206625567968</v>
       </c>
       <c r="F35">
-        <v>0.008413631722209353</v>
+        <v>0.008424640775256842</v>
       </c>
       <c r="G35">
-        <v>0.007647210019176343</v>
+        <v>0.007434701480319217</v>
       </c>
       <c r="H35">
-        <v>0.02103617594229515</v>
+        <v>0.02076531908923876</v>
       </c>
       <c r="I35">
-        <v>0.0019978706910661645</v>
+        <v>0.0014445621581179958</v>
       </c>
       <c r="J35">
-        <v>0.040842162929054585</v>
+        <v>0.03973256156228256</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -47522,7 +49320,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -47534,43 +49332,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:bambu:kampala-uga</t>
+          <t>corridor:35:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.002803891071768233</v>
+        <v>0.003111941625778658</v>
       </c>
       <c r="F36">
-        <v>0.008410470868929015</v>
+        <v>0.008402719753006271</v>
       </c>
       <c r="G36">
-        <v>0.007040374520295156</v>
+        <v>0.0077007053534820236</v>
       </c>
       <c r="H36">
-        <v>0.021028323783931435</v>
+        <v>0.020711624541566498</v>
       </c>
       <c r="I36">
-        <v>0.001983808750996477</v>
+        <v>0.0017674417542844795</v>
       </c>
       <c r="J36">
-        <v>0.04221535551667012</v>
+        <v>0.038221794937289805</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -47590,7 +49388,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -47602,43 +49400,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:36:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.0030254703539086825</v>
+        <v>0.002898657102272467</v>
       </c>
       <c r="F37">
-        <v>0.008302024512592543</v>
+        <v>0.00831048662323794</v>
       </c>
       <c r="G37">
-        <v>0.007595467076894652</v>
+        <v>0.0071740522491085534</v>
       </c>
       <c r="H37">
-        <v>0.020758892754370956</v>
+        <v>0.020485685215592936</v>
       </c>
       <c r="I37">
-        <v>0.0019239494772106266</v>
+        <v>0.0024156585156788397</v>
       </c>
       <c r="J37">
-        <v>0.03967236765955354</v>
+        <v>0.03953263154110449</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -47658,7 +49456,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -47670,43 +49468,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:bambu:kasese-uga</t>
+          <t>corridor:37:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D38">
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.003143077793635596</v>
+        <v>0.0027125515817747747</v>
       </c>
       <c r="F38">
-        <v>0.00824148730856386</v>
+        <v>0.008284511161890662</v>
       </c>
       <c r="G38">
-        <v>0.007890017121025772</v>
+        <v>0.006714374614320118</v>
       </c>
       <c r="H38">
-        <v>0.02060847054148296</v>
+        <v>0.020422048400997733</v>
       </c>
       <c r="I38">
-        <v>0.0022432737764674915</v>
+        <v>0.0015261556624343033</v>
       </c>
       <c r="J38">
-        <v>0.043110322723682405</v>
+        <v>0.04121550107288618</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -47726,7 +49524,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -47738,7 +49536,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:nizi:arua-uga</t>
+          <t>corridor:38:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -47748,33 +49546,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.002912215693761211</v>
+        <v>0.002681493416460179</v>
       </c>
       <c r="F39">
-        <v>0.008224729039250062</v>
+        <v>0.008183525990654555</v>
       </c>
       <c r="G39">
-        <v>0.0073117689802146835</v>
+        <v>0.0066376497183083805</v>
       </c>
       <c r="H39">
-        <v>0.020566822397248136</v>
+        <v>0.020174624300513644</v>
       </c>
       <c r="I39">
-        <v>0.0020761411962235826</v>
+        <v>0.0014926750968995012</v>
       </c>
       <c r="J39">
-        <v>0.04050042360943858</v>
+        <v>0.039228799255843605</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -47794,7 +49592,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -47806,43 +49604,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:kilo:kampala-uga</t>
+          <t>corridor:39:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.00278351825972617</v>
+        <v>0.0028326663994584778</v>
       </c>
       <c r="F40">
-        <v>0.008218801697601641</v>
+        <v>0.00815823939873217</v>
       </c>
       <c r="G40">
-        <v>0.006989327711157262</v>
+        <v>0.00701107122667835</v>
       </c>
       <c r="H40">
-        <v>0.020552098310094136</v>
+        <v>0.020112663896618338</v>
       </c>
       <c r="I40">
-        <v>0.0020186656917254436</v>
+        <v>0.0015343125999103453</v>
       </c>
       <c r="J40">
-        <v>0.04178167469755334</v>
+        <v>0.04046059631457021</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -47862,7 +49660,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -47874,43 +49672,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:miti-murhesa:kampala-uga</t>
+          <t>corridor:40:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.002917199157010275</v>
+        <v>0.002747567807505402</v>
       </c>
       <c r="F41">
-        <v>0.008210588027216303</v>
+        <v>0.008154445449094133</v>
       </c>
       <c r="G41">
-        <v>0.007324252868381925</v>
+        <v>0.006800874406568735</v>
       </c>
       <c r="H41">
-        <v>0.0205316862710912</v>
+        <v>0.020103367023304758</v>
       </c>
       <c r="I41">
-        <v>0.0018646941450676275</v>
+        <v>0.0016545850906405566</v>
       </c>
       <c r="J41">
-        <v>0.039202128673268916</v>
+        <v>0.04190231971566359</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -47930,7 +49728,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -47942,12 +49740,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:goma-cod:arua-uga</t>
+          <t>corridor:41:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -47959,26 +49757,26 @@
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0029229943219314103</v>
+        <v>0.0029994938796520376</v>
       </c>
       <c r="F42">
-        <v>0.008200076441295834</v>
+        <v>0.008147226747461322</v>
       </c>
       <c r="G42">
-        <v>0.0073387711057757155</v>
+        <v>0.007423064501010185</v>
       </c>
       <c r="H42">
-        <v>0.02050556570307871</v>
+        <v>0.020085678474308588</v>
       </c>
       <c r="I42">
-        <v>0.002416971899848838</v>
+        <v>0.0019885435545158206</v>
       </c>
       <c r="J42">
-        <v>0.0399238123747093</v>
+        <v>0.03889536735459872</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -47998,7 +49796,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -48010,12 +49808,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:bambu:nebbi-uga</t>
+          <t>corridor:42:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -48027,26 +49825,26 @@
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.0029578847553219656</v>
+        <v>0.003061304197971737</v>
       </c>
       <c r="F43">
-        <v>0.008182077561825735</v>
+        <v>0.00814381727681368</v>
       </c>
       <c r="G43">
-        <v>0.007426173507821376</v>
+        <v>0.00757568403154249</v>
       </c>
       <c r="H43">
-        <v>0.020460836970333962</v>
+        <v>0.020077321716829383</v>
       </c>
       <c r="I43">
-        <v>0.0019204820773748386</v>
+        <v>0.0016647585017794454</v>
       </c>
       <c r="J43">
-        <v>0.03736221748994108</v>
+        <v>0.03886426325038798</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -48066,7 +49864,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -48078,43 +49876,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:butembo:kampala-uga</t>
+          <t>corridor:43:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.002809220150436914</v>
+        <v>0.0031340416283216765</v>
       </c>
       <c r="F44">
-        <v>0.008167798887166844</v>
+        <v>0.008075152624742232</v>
       </c>
       <c r="G44">
-        <v>0.007053727044364355</v>
+        <v>0.00775526629452003</v>
       </c>
       <c r="H44">
-        <v>0.02042535229876477</v>
+        <v>0.01990905693022571</v>
       </c>
       <c r="I44">
-        <v>0.002021133668671976</v>
+        <v>0.002243955437822981</v>
       </c>
       <c r="J44">
-        <v>0.041858581949275345</v>
+        <v>0.03925743592923069</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -48134,7 +49932,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -48146,7 +49944,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:arua-uga</t>
+          <t>corridor:44:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -48156,33 +49954,33 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.003018664226666662</v>
+        <v>0.0027076980614253177</v>
       </c>
       <c r="F45">
-        <v>0.008165091988575929</v>
+        <v>0.008070258181662043</v>
       </c>
       <c r="G45">
-        <v>0.0075784187553437354</v>
+        <v>0.006702384988596155</v>
       </c>
       <c r="H45">
-        <v>0.02041862413740289</v>
+        <v>0.019897061858827808</v>
       </c>
       <c r="I45">
-        <v>0.0020682252418399495</v>
+        <v>0.0018949255081115225</v>
       </c>
       <c r="J45">
-        <v>0.04398886439373007</v>
+        <v>0.03846409821761752</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -48202,7 +50000,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -48214,43 +50012,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:butembo:arua-uga</t>
+          <t>corridor:45:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D46">
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.002806560204559716</v>
+        <v>0.0029941551171358827</v>
       </c>
       <c r="F46">
-        <v>0.008123680596680921</v>
+        <v>0.008062710206497403</v>
       </c>
       <c r="G46">
-        <v>0.007047062151783884</v>
+        <v>0.007409881598903129</v>
       </c>
       <c r="H46">
-        <v>0.020315706599612765</v>
+        <v>0.019878564189878323</v>
       </c>
       <c r="I46">
-        <v>0.0017574721703900373</v>
+        <v>0.0023605934928140225</v>
       </c>
       <c r="J46">
-        <v>0.04275438546425416</v>
+        <v>0.03849962672911588</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -48270,7 +50068,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -48282,43 +50080,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:butembo:beni-cod</t>
+          <t>corridor:46:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.002679528990868457</v>
+        <v>0.002966610048958429</v>
       </c>
       <c r="F47">
-        <v>0.008108904295966224</v>
+        <v>0.008058011311337127</v>
       </c>
       <c r="G47">
-        <v>0.006728745228450933</v>
+        <v>0.007341863257414205</v>
       </c>
       <c r="H47">
-        <v>0.02027898210665266</v>
+        <v>0.01986704842779069</v>
       </c>
       <c r="I47">
-        <v>0.00201859998001081</v>
+        <v>0.00193425911064469</v>
       </c>
       <c r="J47">
-        <v>0.039852226938007426</v>
+        <v>0.03944581553096073</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -48338,7 +50136,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -48350,43 +50148,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:kilo:nebbi-uga</t>
+          <t>corridor:47:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.0030217714965165288</v>
+        <v>0.002837150359859514</v>
       </c>
       <c r="F48">
-        <v>0.008088559543497742</v>
+        <v>0.008035393220128945</v>
       </c>
       <c r="G48">
-        <v>0.007586202236514322</v>
+        <v>0.007022145861493551</v>
       </c>
       <c r="H48">
-        <v>0.020228416398239663</v>
+        <v>0.019811615320896397</v>
       </c>
       <c r="I48">
-        <v>0.0013824992306557622</v>
+        <v>0.0016272804773103918</v>
       </c>
       <c r="J48">
-        <v>0.04298876053352871</v>
+        <v>0.0417257099987222</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -48406,7 +50204,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -48418,43 +50216,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:nizi:kampala-uga</t>
+          <t>corridor:48:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.003185845864099812</v>
+        <v>0.0027221893165624844</v>
       </c>
       <c r="F49">
-        <v>0.008055680196092985</v>
+        <v>0.008025112676473323</v>
       </c>
       <c r="G49">
-        <v>0.007997117456259972</v>
+        <v>0.006738183364620509</v>
       </c>
       <c r="H49">
-        <v>0.020146693276199862</v>
+        <v>0.019786420160049306</v>
       </c>
       <c r="I49">
-        <v>0.0017111961703214886</v>
+        <v>0.0018923716266919608</v>
       </c>
       <c r="J49">
-        <v>0.03843501793313703</v>
+        <v>0.04067091464985655</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -48474,7 +50272,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -48486,43 +50284,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:nizi:nebbi-uga</t>
+          <t>corridor:49:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0027950636057349765</v>
+        <v>0.0029779299971779694</v>
       </c>
       <c r="F50">
-        <v>0.008037576849237893</v>
+        <v>0.007993848855793961</v>
       </c>
       <c r="G50">
-        <v>0.007018256519346455</v>
+        <v>0.007369816645196731</v>
       </c>
       <c r="H50">
-        <v>0.02010169499562392</v>
+        <v>0.019709793462212938</v>
       </c>
       <c r="I50">
-        <v>0.0019399331731337372</v>
+        <v>0.00181708380560561</v>
       </c>
       <c r="J50">
-        <v>0.04644803668949182</v>
+        <v>0.03931941479325931</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -48542,7 +50340,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -48554,43 +50352,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:kilo:beni-cod</t>
+          <t>corridor:50:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D51">
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002821718891003744</v>
+        <v>0.002573515092590184</v>
       </c>
       <c r="F51">
-        <v>0.00803389605052951</v>
+        <v>0.007966550348283807</v>
       </c>
       <c r="G51">
-        <v>0.007085043176923073</v>
+        <v>0.006370874666990878</v>
       </c>
       <c r="H51">
-        <v>0.020092545647049515</v>
+        <v>0.01964288498845579</v>
       </c>
       <c r="I51">
-        <v>0.0019349047366173573</v>
+        <v>0.0019758723489192026</v>
       </c>
       <c r="J51">
-        <v>0.04003768632169026</v>
+        <v>0.042497226842963434</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -48610,7 +50408,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -48622,43 +50420,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:goma-cod:nebbi-uga</t>
+          <t>corridor:51:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.0028567491561985736</v>
+        <v>0.00270874962073242</v>
       </c>
       <c r="F52">
-        <v>0.00797006857945673</v>
+        <v>0.007945705918331214</v>
       </c>
       <c r="G52">
-        <v>0.007172809815163245</v>
+        <v>0.006704981285868744</v>
       </c>
       <c r="H52">
-        <v>0.019933882573881373</v>
+        <v>0.019591793108546057</v>
       </c>
       <c r="I52">
-        <v>0.0017294072526960998</v>
+        <v>0.0017099558870529636</v>
       </c>
       <c r="J52">
-        <v>0.042443634852033695</v>
+        <v>0.040311579752921115</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -48678,7 +50476,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -48690,43 +50488,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:nizi:beni-cod</t>
+          <t>corridor:52:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.0030245126948671708</v>
+        <v>0.002937977495464733</v>
       </c>
       <c r="F53">
-        <v>0.00795441234801178</v>
+        <v>0.00791077263458917</v>
       </c>
       <c r="G53">
-        <v>0.007593068348614146</v>
+        <v>0.007271156988672728</v>
       </c>
       <c r="H53">
-        <v>0.01989496203143168</v>
+        <v>0.019506162869570853</v>
       </c>
       <c r="I53">
-        <v>0.00208860712135866</v>
+        <v>0.0015259490592032937</v>
       </c>
       <c r="J53">
-        <v>0.04390687375830717</v>
+        <v>0.04355956758414158</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -48746,7 +50544,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -48758,43 +50556,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:butembo:kasese-uga</t>
+          <t>corridor:53:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0029631889825048885</v>
+        <v>0.0025676185126164985</v>
       </c>
       <c r="F54">
-        <v>0.00793918577465852</v>
+        <v>0.007868621059145403</v>
       </c>
       <c r="G54">
-        <v>0.007439460946500748</v>
+        <v>0.0063563051772850265</v>
       </c>
       <c r="H54">
-        <v>0.019857108285455366</v>
+        <v>0.01940283456752373</v>
       </c>
       <c r="I54">
-        <v>0.001563734909959605</v>
+        <v>0.0016564750458324922</v>
       </c>
       <c r="J54">
-        <v>0.03793928796303533</v>
+        <v>0.03677402473147005</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -48814,7 +50612,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -48826,43 +50624,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:kilo:bundibugyo-uga</t>
+          <t>corridor:54:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0028536624321979787</v>
+        <v>0.0027868684736187532</v>
       </c>
       <c r="F55">
-        <v>0.007897435827033727</v>
+        <v>0.007841801348761585</v>
       </c>
       <c r="G55">
-        <v>0.007165076290699068</v>
+        <v>0.00689795184472039</v>
       </c>
       <c r="H55">
-        <v>0.019753312706144277</v>
+        <v>0.019337083521810405</v>
       </c>
       <c r="I55">
-        <v>0.0021169028283330726</v>
+        <v>0.0017127846529912062</v>
       </c>
       <c r="J55">
-        <v>0.04301862105908695</v>
+        <v>0.03838966632456429</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -48882,7 +50680,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -48894,43 +50692,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:kilo:kasese-uga</t>
+          <t>corridor:55:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.002959971024566438</v>
+        <v>0.002695763743499391</v>
       </c>
       <c r="F56">
-        <v>0.00787220578285247</v>
+        <v>0.007827990157414616</v>
       </c>
       <c r="G56">
-        <v>0.007431400049636161</v>
+        <v>0.006672903334783625</v>
       </c>
       <c r="H56">
-        <v>0.019690583840609954</v>
+        <v>0.0193032265603717</v>
       </c>
       <c r="I56">
-        <v>0.001641626374744698</v>
+        <v>0.0021490354133257674</v>
       </c>
       <c r="J56">
-        <v>0.040297773039945806</v>
+        <v>0.04054210634480244</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -48950,7 +50748,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -48962,43 +50760,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:goma-cod:kasese-uga</t>
+          <t>corridor:56:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.0027095766658913334</v>
+        <v>0.003089733434463643</v>
       </c>
       <c r="F57">
-        <v>0.007841647616298908</v>
+        <v>0.007797896708572921</v>
       </c>
       <c r="G57">
-        <v>0.006804043969449947</v>
+        <v>0.007645875573836641</v>
       </c>
       <c r="H57">
-        <v>0.01961460584756758</v>
+        <v>0.019229449244770908</v>
       </c>
       <c r="I57">
-        <v>0.0020235152119086695</v>
+        <v>0.0016800255774773844</v>
       </c>
       <c r="J57">
-        <v>0.041393987342476055</v>
+        <v>0.034479825340189424</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -49018,7 +50816,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -49030,43 +50828,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:goma-cod:kampala-uga</t>
+          <t>corridor:57:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.0025110978594395095</v>
+        <v>0.002629641493342244</v>
       </c>
       <c r="F58">
-        <v>0.007818185593694127</v>
+        <v>0.0077950978062735765</v>
       </c>
       <c r="G58">
-        <v>0.0063065924718523625</v>
+        <v>0.006509547825961637</v>
       </c>
       <c r="H58">
-        <v>0.019556267594055404</v>
+        <v>0.019222587126321078</v>
       </c>
       <c r="I58">
-        <v>0.0015853366988132862</v>
+        <v>0.0013601473368735656</v>
       </c>
       <c r="J58">
-        <v>0.03742026740783717</v>
+        <v>0.03643059423991454</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -49086,7 +50884,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -49098,12 +50896,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:miti-murhesa:arua-uga</t>
+          <t>corridor:58:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -49115,26 +50913,26 @@
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0030156062594385025</v>
+        <v>0.0028404048325195996</v>
       </c>
       <c r="F59">
-        <v>0.007804732379472906</v>
+        <v>0.007786957767991598</v>
       </c>
       <c r="G59">
-        <v>0.007570759922123083</v>
+        <v>0.007030184083863106</v>
       </c>
       <c r="H59">
-        <v>0.019522813800804506</v>
+        <v>0.019202630017290306</v>
       </c>
       <c r="I59">
-        <v>0.001458769241107233</v>
+        <v>0.0018407478578635922</v>
       </c>
       <c r="J59">
-        <v>0.043206799451250055</v>
+        <v>0.041169590401536636</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -49154,7 +50952,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -49166,7 +50964,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:bambu:arua-uga</t>
+          <t>corridor:59:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -49176,33 +50974,33 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.002681900600504883</v>
+        <v>0.0030164649861187665</v>
       </c>
       <c r="F60">
-        <v>0.0077589260027900175</v>
+        <v>0.007772299321732512</v>
       </c>
       <c r="G60">
-        <v>0.0067346886062866484</v>
+        <v>0.0074649703248304</v>
       </c>
       <c r="H60">
-        <v>0.019408912083272584</v>
+        <v>0.01916669022271858</v>
       </c>
       <c r="I60">
-        <v>0.001316839496169825</v>
+        <v>0.0017745338814096486</v>
       </c>
       <c r="J60">
-        <v>0.04188008746055827</v>
+        <v>0.04144693368617039</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -49222,7 +51020,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -49234,7 +51032,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:miti-murhesa:nebbi-uga</t>
+          <t>corridor:60:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -49244,33 +51042,33 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.0029216317002188907</v>
+        <v>0.002780055599183956</v>
       </c>
       <c r="F61">
-        <v>0.007737159174179331</v>
+        <v>0.0077543800748747505</v>
       </c>
       <c r="G61">
-        <v>0.007335357553010069</v>
+        <v>0.006881123372275866</v>
       </c>
       <c r="H61">
-        <v>0.0193547831266003</v>
+        <v>0.01912275597116167</v>
       </c>
       <c r="I61">
-        <v>0.0021616580283129877</v>
+        <v>0.001731233807528232</v>
       </c>
       <c r="J61">
-        <v>0.038276210708016935</v>
+        <v>0.03818702256228324</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -49290,7 +51088,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -49302,43 +51100,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:bambu:bundibugyo-uga</t>
+          <t>corridor:61:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0030176500050449473</v>
+        <v>0.0026587921388565305</v>
       </c>
       <c r="F62">
-        <v>0.007734491501665053</v>
+        <v>0.007745510300115388</v>
       </c>
       <c r="G62">
-        <v>0.0075758786333554595</v>
+        <v>0.006581566727665494</v>
       </c>
       <c r="H62">
-        <v>0.019348148843720964</v>
+        <v>0.0191010070867213</v>
       </c>
       <c r="I62">
-        <v>0.0019946892098529428</v>
+        <v>0.0015209453885095762</v>
       </c>
       <c r="J62">
-        <v>0.044163146423054585</v>
+        <v>0.040091153412378705</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -49358,7 +51156,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -49370,43 +51168,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:miti-murhesa:kasese-uga</t>
+          <t>corridor:62:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0027185906083667943</v>
+        <v>0.0027361329624540076</v>
       </c>
       <c r="F63">
-        <v>0.007723897502855653</v>
+        <v>0.0075987291180549255</v>
       </c>
       <c r="G63">
-        <v>0.006826633017774586</v>
+        <v>0.006772627856763858</v>
       </c>
       <c r="H63">
-        <v>0.01932180334913558</v>
+        <v>0.018741077563372677</v>
       </c>
       <c r="I63">
-        <v>0.001326890680265347</v>
+        <v>0.0013777102458249037</v>
       </c>
       <c r="J63">
-        <v>0.044931486478670124</v>
+        <v>0.043087769872402426</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -49426,7 +51224,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -49438,43 +51236,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:miti-murhesa:beni-cod</t>
+          <t>corridor:63:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0027329214469088425</v>
+        <v>0.0028258568215484003</v>
       </c>
       <c r="F64">
-        <v>0.007653410571739322</v>
+        <v>0.007552854340310916</v>
       </c>
       <c r="G64">
-        <v>0.0068625427804339945</v>
+        <v>0.006994252131591605</v>
       </c>
       <c r="H64">
-        <v>0.019146499430329145</v>
+        <v>0.018628569089331942</v>
       </c>
       <c r="I64">
-        <v>0.001510923662171504</v>
+        <v>0.0018339497806420303</v>
       </c>
       <c r="J64">
-        <v>0.04151791854720881</v>
+        <v>0.0447125896493108</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -49494,7 +51292,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -49506,12 +51304,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:nizi:bundibugyo-uga</t>
+          <t>corridor:64:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -49523,26 +51321,26 @@
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0028089304317990282</v>
+        <v>0.002862546240653324</v>
       </c>
       <c r="F65">
-        <v>0.007651463995398566</v>
+        <v>0.0075168412354912895</v>
       </c>
       <c r="G65">
-        <v>0.007053001153893956</v>
+        <v>0.007084869280098771</v>
       </c>
       <c r="H65">
-        <v>0.019141661110745445</v>
+        <v>0.0185402409724002</v>
       </c>
       <c r="I65">
-        <v>0.0017533987795390561</v>
+        <v>0.0017601300993422223</v>
       </c>
       <c r="J65">
-        <v>0.04071220585407649</v>
+        <v>0.04281508413149316</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -49562,7 +51360,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -49574,12 +51372,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:goma-cod:bundibugyo-uga</t>
+          <t>corridor:65:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -49591,26 +51389,26 @@
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.0027894808005398397</v>
+        <v>0.002806475854065099</v>
       </c>
       <c r="F66">
-        <v>0.007505535288456183</v>
+        <v>0.007390944356303691</v>
       </c>
       <c r="G66">
-        <v>0.00700426804677709</v>
+        <v>0.006946382389732636</v>
       </c>
       <c r="H66">
-        <v>0.018778672919181755</v>
+        <v>0.018231416239954695</v>
       </c>
       <c r="I66">
-        <v>0.001405618489354124</v>
+        <v>0.00208300583836101</v>
       </c>
       <c r="J66">
-        <v>0.038891998237858</v>
+        <v>0.03944316706094814</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -49630,7 +51428,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -49642,43 +51440,43 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:goma-cod:beni-cod</t>
+          <t>corridor:66:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.002691745671106749</v>
+        <v>0.0028636196069686815</v>
       </c>
       <c r="F67">
-        <v>0.007306343783265612</v>
+        <v>0.007245116575636645</v>
       </c>
       <c r="G67">
-        <v>0.00675936068384736</v>
+        <v>0.0070875198104265735</v>
       </c>
       <c r="H67">
-        <v>0.018283072120277938</v>
+        <v>0.017873638059777402</v>
       </c>
       <c r="I67">
-        <v>0.00182661275920816</v>
+        <v>0.001885099074969826</v>
       </c>
       <c r="J67">
-        <v>0.03743852328668568</v>
+        <v>0.04037313015728034</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.52× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -49698,7 +51496,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -49836,7 +51634,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -49888,7 +51686,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -49942,7 +51740,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -49996,7 +51794,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -50050,7 +51848,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -50104,7 +51902,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -50158,7 +51956,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -50185,10 +51983,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.3974126026144006</v>
+        <v>0.4031809300428392</v>
       </c>
       <c r="F9">
-        <v>0.4586317958944394</v>
+        <v>0.4637985606142611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -50212,7 +52010,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -50239,10 +52037,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>3.1380822768917134</v>
+        <v>2.658988714502407</v>
       </c>
       <c r="F10">
-        <v>13.124786655735885</v>
+        <v>12.09131304558839</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -50266,7 +52064,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -50293,10 +52091,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="F11">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -50320,7 +52118,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -50374,7 +52172,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L12"/>
@@ -50422,7 +52220,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -50474,7 +52272,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -50526,7 +52324,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -50578,7 +52376,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -50604,7 +52402,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.03</v>
+        <v>0.019</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -50630,7 +52428,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -50656,7 +52454,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.962</v>
+        <v>0.973</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -50682,7 +52480,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -50736,7 +52534,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L19"/>
@@ -50786,7 +52584,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L20"/>
@@ -50864,7 +52662,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"confirmed": 106, "deaths": 179, "suspected": 904}</t>
+          <t>{"confirmed": 112, "deaths": 223, "suspected": 906}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -50902,12 +52700,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"confirmed": 106, "suspected": 904}</t>
+          <t>{"confirmed": 112, "suspected": 906}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"confirmation_backlog_50": [462, 720], "reporting_completeness_50": [0.3974126026144006, 0.4586317958944394]}</t>
+          <t>{"confirmation_backlog_50": [468, 712], "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -50936,12 +52734,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"confirmed_endpoint": 106, "reporting_completeness_50": [0.3974126026144006, 0.4586317958944394]}</t>
+          <t>{"confirmed_endpoint": 112, "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"endpoint_confirmable_50": [231, 267]}</t>
+          <t>{"endpoint_confirmable_50": [241, 278]}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -50970,7 +52768,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"deaths": 179}</t>
+          <t>{"deaths": 223}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -50980,7 +52778,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The 179-death input updates the snapshot-level sensitivity calculation, but the source lacks a data/report date, so it must be rendered as a publication-clock endpoint rather than a connected dated trajectory point.</t>
+          <t>The 223-death input comes from the US CDC Current Situation 25 May, a dated-report source, so it updates the snapshot-level sensitivity calculation as a connected dated trajectory point. The DRC MoH dashboard aggregate (179, 24 May) and the ECDC 25 May figure (119) are held as conflict anchors and are not promoted, so no publication-clock-only endpoint is rendered.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -51008,7 +52806,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"confirmed": 106}</t>
+          <t>{"confirmed": 112}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -51042,7 +52840,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"headline_confirmed": 106, "unallocated_headline_confirmed": 27, "zone_attributed_confirmed": 79}</t>
+          <t>{"headline_confirmed": 112, "unallocated_headline_confirmed": 33, "zone_attributed_confirmed": 79}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1439,8 +1439,102 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-029</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Source attribution lag</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The May 25 headline confirmed-count primary is ahead of the latest officially zone-attributed cumulative table, so the corridor source-load total remains 79 and the unallocated headline context is 33. This is a named source-attribution lag, not a lost public claim audit or a down-revision.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>headline_confirmed_total=112 from CDC 25 May; zone_attributed_confirmed_total=79 from DRC MoH SitRep 007 cumulative Table IV; unallocated_confirmed_total=33 computed as 112 - 79.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>US CDC Ebola Disease: Current Situation page, archived 25 May 2026.; DRC Ministry of Health SitRep MVE N 007/MVB_17/2026 PDF cumulative Table IV, data as of 21 May 2026 and published 22 May 2026.; data/snapshot_contract.json confirmed_case_partition.; NUMBERS_AUDIT.md source-attribution lag and confirmed-case partition section.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html; https://administration.sante.gouv.cd/wp-content/uploads/2026/05/SitRep_MVE_RDC_20260512-FDv2_IM.pdf; restricted-local-review-not-redistributed; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Keep the confirmed-case partition explicit in snapshot_contract and NUMBERS_AUDIT. Promote newer zone-attributed rows only after a cumulative official table/PDF or validated equivalent is archived.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-030</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bdbv may26 source review boundary</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The 26 May sweep found one count-bearing official source update that should be archived for audit: ECDC 26 May. Its count tuple corroborates the CDC 25 May endpoint but carries separate page, count-source, and retrieval clocks, so it must not be treated as a new data-date-only trajectory point or as a generic deaths replacement.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ECDC page publication/as-of date=2026-05-26; ECDC count source label=DRC Ministry of Health on 2026-05-25; DRC confirmed=105, DRC suspected=906, DRC confirmed deaths=10, DRC suspected deaths=223, Uganda confirmed=7, Uganda deaths=1; computed country-pair confirmed=112.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ECDC. Ebola virus disease outbreak in the Democratic Republic of the Congo and Uganda. Live page captured 26 May 2026.; WHO Regional Office for Africa. Ongoing outbreak in the Democratic Republic of the Congo / Bundibugyo virus disease outbreak hub. Movement detected by the 26 May freshness check.; US CDC returning-travelers public information page. Context update detected by the 26 May freshness check.; Wikipedia contributors. 2026 Ituri Province Ebola epidemic, live page observed by 26 May 2026 freshness check.; data/external_sources/freshness/bdbv-2026-2026-05-26.json generated by source_ingest.py --live-check --as-of 2026-05-26.; data/bundibugyo-2026/manifest.json entry ecdc-bdbv-drc-uga-2026-05-26-live.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026; https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26; https://www.cdc.gov/viral-hemorrhagic-fevers/travel-to-us/index.html; https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic; restricted-local-review-not-redistributed; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Keep the May 26 ECDC archive as evidence-backed cross-check input. Do not publish, promote preview, or alter the public endpoint until the May 26 snapshot/release gate resolves date semantics and the DRC MoH/CDC/ECDC death-metric concepts are reviewed.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I28"/>
 </worksheet>
 </file>
 
@@ -3855,8 +3949,66 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>European Centre for Disease Prevention and Control</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-26T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-26T22:13:28Z</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="J42"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L42"/>
 </worksheet>
 </file>
 
@@ -11225,7 +11377,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D3"/>
@@ -16362,8 +16514,141 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>source_data_report_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D125"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>source_publication_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D126"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-26T22:13:28Z</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I124"/>
+  <autoFilter ref="A1:I127"/>
 </worksheet>
 </file>
 
@@ -34037,34 +34322,34 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D224"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F224">
-        <v>906</v>
-      </c>
-      <c r="G224">
-        <v>395</v>
-      </c>
-      <c r="H224">
-        <v>906</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G224"/>
+      <c r="H224"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>count</t>
@@ -34072,37 +34357,33 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K224"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -34112,7 +34393,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="S224"/>
@@ -34120,12 +34401,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_total</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -34133,21 +34414,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D225"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F225">
         <v>112</v>
       </c>
-      <c r="G225">
-        <v>10</v>
-      </c>
-      <c r="H225">
-        <v>112</v>
-      </c>
+      <c r="G225"/>
+      <c r="H225"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>count</t>
@@ -34155,37 +34436,33 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K225"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -34195,100 +34472,819 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
-        </is>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S225"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F226">
+        <v>7</v>
+      </c>
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K226"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F227">
+        <v>906</v>
+      </c>
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K227"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F228">
+        <v>10</v>
+      </c>
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K228"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F229">
+        <v>223</v>
+      </c>
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K229"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K230"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:http_status</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F231">
+        <v>200</v>
+      </c>
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K231"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S231"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:suspected_cases_italy</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K232"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S232"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D233"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F233">
+        <v>906</v>
+      </c>
+      <c r="G233">
+        <v>395</v>
+      </c>
+      <c r="H233">
+        <v>906</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S233"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D234"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F234">
+        <v>112</v>
+      </c>
+      <c r="G234">
+        <v>10</v>
+      </c>
+      <c r="H234">
+        <v>112</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D226"/>
-      <c r="E226" t="inlineStr">
+      <c r="D235"/>
+      <c r="E235" t="inlineStr">
         <is>
           <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
-      <c r="F226">
+      <c r="F235">
         <v>223</v>
       </c>
-      <c r="G226">
+      <c r="G235">
         <v>106</v>
       </c>
-      <c r="H226">
+      <c r="H235">
         <v>223</v>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I235" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
+      <c r="J235" t="inlineStr">
         <is>
           <t>cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K235" t="inlineStr">
         <is>
           <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t>PUBLIC-SOURCE-AUDIT</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N235" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O235" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr">
+      <c r="P235" t="inlineStr">
         <is>
           <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
+      <c r="Q235" t="inlineStr">
         <is>
           <t>public_bytes</t>
         </is>
       </c>
-      <c r="R226" t="inlineStr">
+      <c r="R235" t="inlineStr">
         <is>
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="S226"/>
+      <c r="S235"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S226"/>
+  <autoFilter ref="A1:S235"/>
 </worksheet>
 </file>
 
@@ -45341,7 +46337,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -45351,11 +46347,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D217">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -45364,27 +46360,27 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K217"/>
@@ -45392,7 +46388,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_total</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -45402,11 +46398,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D218">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -45415,27 +46411,27 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K218"/>
@@ -45443,7 +46439,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_uganda</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -45453,11 +46449,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D219">
-        <v>223</v>
+        <v>7</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -45466,27 +46462,27 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K219"/>
@@ -45494,7 +46490,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -45508,7 +46504,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -45545,7 +46541,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -45555,11 +46551,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>http_status</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D221">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -45596,7 +46592,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -45606,11 +46602,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D222">
-        <v>906</v>
+        <v>223</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -45647,56 +46643,515 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D224">
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D225">
+        <v>223</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K225"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D227">
+        <v>200</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:http_status</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D228">
+        <v>200</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D229">
+        <v>906</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
           <t>timeline:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>suspected_cases</t>
         </is>
       </c>
-      <c r="D223">
+      <c r="D230">
         <v>906</v>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
+      <c r="J230" t="inlineStr">
         <is>
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="K223"/>
+      <c r="K230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D231">
+        <v>906</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K231"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:suspected_cases_italy</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D232">
+        <v>2</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K232"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K223"/>
+  <autoFilter ref="A1:K232"/>
 </worksheet>
 </file>
 
@@ -47037,22 +48492,22 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.0861708114385285</v>
+        <v>0.09445951733436075</v>
       </c>
       <c r="F2">
-        <v>0.23315469335620254</v>
+        <v>0.24002055285686827</v>
       </c>
       <c r="G2">
-        <v>0.20028631694823662</v>
+        <v>0.21815681374976198</v>
       </c>
       <c r="H2">
-        <v>0.48234065943233195</v>
+        <v>0.49376090747255597</v>
       </c>
       <c r="I2">
-        <v>0.06427581319980569</v>
+        <v>0.06319702466996217</v>
       </c>
       <c r="J2">
-        <v>0.7474537035483133</v>
+        <v>0.719264702591034</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -47088,7 +48543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:kasese-uga</t>
+          <t>corridor:02:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -47098,29 +48553,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08768171124595683</v>
+        <v>0.08273781175301806</v>
       </c>
       <c r="F3">
-        <v>0.2275794037963691</v>
+        <v>0.2284874731887681</v>
       </c>
       <c r="G3">
-        <v>0.2035618016305265</v>
+        <v>0.1928142001378063</v>
       </c>
       <c r="H3">
-        <v>0.47295633103988544</v>
+        <v>0.4744917795152871</v>
       </c>
       <c r="I3">
-        <v>0.04459460740614488</v>
+        <v>0.06730851508774321</v>
       </c>
       <c r="J3">
-        <v>0.7478981260349676</v>
+        <v>0.7564576627228864</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -47173,22 +48628,22 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08233054224498484</v>
+        <v>0.09048464357894637</v>
       </c>
       <c r="F4">
-        <v>0.22543492066869397</v>
+        <v>0.22273556590441385</v>
       </c>
       <c r="G4">
-        <v>0.19192499609422323</v>
+        <v>0.20961712897740686</v>
       </c>
       <c r="H4">
-        <v>0.46931800011005115</v>
+        <v>0.4647202826386523</v>
       </c>
       <c r="I4">
-        <v>0.06964130796312437</v>
+        <v>0.04977612451622361</v>
       </c>
       <c r="J4">
-        <v>0.6990237917928565</v>
+        <v>0.7106528036367321</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -47224,7 +48679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:beni-cod</t>
+          <t>corridor:04:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -47234,29 +48689,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08664306873590838</v>
+        <v>0.08565218814006142</v>
       </c>
       <c r="F5">
-        <v>0.222887038238157</v>
+        <v>0.22029891605266969</v>
       </c>
       <c r="G5">
-        <v>0.20131080198240825</v>
+        <v>0.19916026506380355</v>
       </c>
       <c r="H5">
-        <v>0.4649794327839667</v>
+        <v>0.4605488463027082</v>
       </c>
       <c r="I5">
-        <v>0.05425688863966508</v>
+        <v>0.07273190347723515</v>
       </c>
       <c r="J5">
-        <v>0.7101842045533336</v>
+        <v>0.7278051232264949</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -47292,7 +48747,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:arua-uga</t>
+          <t>corridor:05:rwampara:goma-cod</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -47302,29 +48757,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.09176382815314144</v>
+        <v>0.08761720560139294</v>
       </c>
       <c r="F6">
-        <v>0.2196720235905948</v>
+        <v>0.21936354051325144</v>
       </c>
       <c r="G6">
-        <v>0.2123714082943657</v>
+        <v>0.20342220318959423</v>
       </c>
       <c r="H6">
-        <v>0.45947010738720273</v>
+        <v>0.4589425069655363</v>
       </c>
       <c r="I6">
-        <v>0.0602209036243418</v>
+        <v>0.06886739376279995</v>
       </c>
       <c r="J6">
-        <v>0.7146926481656625</v>
+        <v>0.743152794738482</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -47377,22 +48832,22 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08396936085735776</v>
+        <v>0.08287569990928895</v>
       </c>
       <c r="F7">
-        <v>0.2119043283318027</v>
+        <v>0.21243842944956587</v>
       </c>
       <c r="G7">
-        <v>0.19549948212877702</v>
+        <v>0.1931151059217136</v>
       </c>
       <c r="H7">
-        <v>0.44602874389977687</v>
+        <v>0.4469590270913051</v>
       </c>
       <c r="I7">
-        <v>0.056360235565877555</v>
+        <v>0.05292524916825545</v>
       </c>
       <c r="J7">
-        <v>0.7142786607680277</v>
+        <v>0.7528903131888608</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -47428,43 +48883,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:mongbwalu:nebbi-uga</t>
+          <t>corridor:07:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>rwampara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.03855467933328152</v>
+        <v>0.0813030320518214</v>
       </c>
       <c r="F8">
-        <v>0.11620932868289471</v>
+        <v>0.2120036212731276</v>
       </c>
       <c r="G8">
-        <v>0.09291440432184914</v>
+        <v>0.18967897671798614</v>
       </c>
       <c r="H8">
-        <v>0.2639086114886541</v>
+        <v>0.44620129623757115</v>
       </c>
       <c r="I8">
-        <v>0.025175207094245807</v>
+        <v>0.05853988867330033</v>
       </c>
       <c r="J8">
-        <v>0.46361890390099453</v>
+        <v>0.721341036531536</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -47496,7 +48951,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:kampala-uga</t>
+          <t>corridor:08:bunia:goma-cod</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -47506,29 +48961,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04147908524423352</v>
+        <v>0.04260859167640518</v>
       </c>
       <c r="F9">
-        <v>0.11562806950949953</v>
+        <v>0.11766030943420233</v>
       </c>
       <c r="G9">
-        <v>0.09974219409345544</v>
+        <v>0.10237107937830753</v>
       </c>
       <c r="H9">
-        <v>0.2627072705721946</v>
+        <v>0.26690234529353574</v>
       </c>
       <c r="I9">
-        <v>0.025907663365721464</v>
+        <v>0.03562848758295974</v>
       </c>
       <c r="J9">
-        <v>0.4462554570998926</v>
+        <v>0.4539173649760259</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -47564,7 +49019,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:arua-uga</t>
+          <t>corridor:09:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -47574,29 +49029,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04179480816556652</v>
+        <v>0.04147908524423352</v>
       </c>
       <c r="F10">
-        <v>0.11558245421258095</v>
+        <v>0.11562806950949953</v>
       </c>
       <c r="G10">
-        <v>0.10047743392001213</v>
+        <v>0.09974219409345544</v>
       </c>
       <c r="H10">
-        <v>0.26261295488077974</v>
+        <v>0.2627072705721946</v>
       </c>
       <c r="I10">
-        <v>0.027913949480659363</v>
+        <v>0.025907663365721464</v>
       </c>
       <c r="J10">
-        <v>0.4647552683750245</v>
+        <v>0.4462554570998926</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -47632,7 +49087,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:nebbi-uga</t>
+          <t>corridor:10:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -47642,29 +49097,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.04186956091160368</v>
+        <v>0.04179480816556652</v>
       </c>
       <c r="F11">
-        <v>0.11539491748492897</v>
+        <v>0.11558245421258095</v>
       </c>
       <c r="G11">
-        <v>0.10065158442248001</v>
+        <v>0.10047743392001213</v>
       </c>
       <c r="H11">
-        <v>0.26222507759010427</v>
+        <v>0.26261295488077974</v>
       </c>
       <c r="I11">
-        <v>0.021242880051839726</v>
+        <v>0.027913949480659363</v>
       </c>
       <c r="J11">
-        <v>0.46678607844486947</v>
+        <v>0.4647552683750245</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -47700,43 +49155,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:kasese-uga</t>
+          <t>corridor:11:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.04042920346327944</v>
+        <v>0.040430218691513475</v>
       </c>
       <c r="F12">
-        <v>0.11242435593909272</v>
+        <v>0.11557548317625271</v>
       </c>
       <c r="G12">
-        <v>0.09729451222456448</v>
+        <v>0.09729691190408213</v>
       </c>
       <c r="H12">
-        <v>0.2560645676658191</v>
+        <v>0.26259850203465634</v>
       </c>
       <c r="I12">
-        <v>0.027413735537554062</v>
+        <v>0.024532453328788482</v>
       </c>
       <c r="J12">
-        <v>0.43705126759089724</v>
+        <v>0.4737244474950434</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -47768,7 +49223,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:kasese-uga</t>
+          <t>corridor:12:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -47778,29 +49233,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.04024586283096926</v>
+        <v>0.04186956091160368</v>
       </c>
       <c r="F13">
-        <v>0.11159467152136757</v>
+        <v>0.11539491748492897</v>
       </c>
       <c r="G13">
-        <v>0.09686667859605977</v>
+        <v>0.10065158442248001</v>
       </c>
       <c r="H13">
-        <v>0.25433876336268857</v>
+        <v>0.26222507759010427</v>
       </c>
       <c r="I13">
-        <v>0.03067229187569909</v>
+        <v>0.021242880051839726</v>
       </c>
       <c r="J13">
-        <v>0.4576157180833162</v>
+        <v>0.46678607844486947</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -47836,7 +49291,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:kampala-uga</t>
+          <t>corridor:13:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -47846,29 +49301,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.04066526892293623</v>
+        <v>0.04269679620853847</v>
       </c>
       <c r="F14">
-        <v>0.11152320362817797</v>
+        <v>0.1114239910693812</v>
       </c>
       <c r="G14">
-        <v>0.09784524147753831</v>
+        <v>0.1025762389475964</v>
       </c>
       <c r="H14">
-        <v>0.254190125108517</v>
+        <v>0.25398350476377357</v>
       </c>
       <c r="I14">
-        <v>0.026605224754838577</v>
+        <v>0.024461896089849052</v>
       </c>
       <c r="J14">
-        <v>0.46394166684739413</v>
+        <v>0.42050488842189776</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -47904,7 +49359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:bunia:bundibugyo-uga</t>
+          <t>corridor:14:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -47914,7 +49369,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D15">
@@ -47972,7 +49427,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:beni-cod</t>
+          <t>corridor:15:mongbwalu:goma-cod</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -47982,29 +49437,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.03750471405393857</v>
+        <v>0.03967055365389441</v>
       </c>
       <c r="F16">
-        <v>0.10749948779872281</v>
+        <v>0.11037528493444154</v>
       </c>
       <c r="G16">
-        <v>0.09045541125798737</v>
+        <v>0.09552333993090975</v>
       </c>
       <c r="H16">
-        <v>0.24578444055142545</v>
+        <v>0.2517977687861897</v>
       </c>
       <c r="I16">
-        <v>0.027237694409312466</v>
+        <v>0.02246092821507834</v>
       </c>
       <c r="J16">
-        <v>0.4271444488438072</v>
+        <v>0.4355790666314244</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -48040,43 +49495,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:bunia:beni-cod</t>
+          <t>corridor:16:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.04228950663900796</v>
+        <v>0.036893545042157305</v>
       </c>
       <c r="F17">
-        <v>0.10704031678368539</v>
+        <v>0.10867014828748978</v>
       </c>
       <c r="G17">
-        <v>0.10162893993380431</v>
+        <v>0.08902229938514877</v>
       </c>
       <c r="H17">
-        <v>0.24482175888282368</v>
+        <v>0.2482358877081989</v>
       </c>
       <c r="I17">
-        <v>0.026598690800271954</v>
+        <v>0.020695892757526077</v>
       </c>
       <c r="J17">
-        <v>0.4232379895804849</v>
+        <v>0.4289255637849178</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -48108,7 +49563,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:arua-uga</t>
+          <t>corridor:17:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -48118,29 +49573,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.03798452079077774</v>
+        <v>0.038935353978377885</v>
       </c>
       <c r="F18">
-        <v>0.1055578744412985</v>
+        <v>0.10835196082870574</v>
       </c>
       <c r="G18">
-        <v>0.09157962059775004</v>
+        <v>0.09380493517661201</v>
       </c>
       <c r="H18">
-        <v>0.24170839592150667</v>
+        <v>0.2475701272178043</v>
       </c>
       <c r="I18">
-        <v>0.0239669463086208</v>
+        <v>0.021267428986718424</v>
       </c>
       <c r="J18">
-        <v>0.4664322846035496</v>
+        <v>0.43910667718208657</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -48176,12 +49631,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:18:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -48193,26 +49648,26 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.03778298943272401</v>
+        <v>0.04228950663900796</v>
       </c>
       <c r="F19">
-        <v>0.10384450964700326</v>
+        <v>0.10704031678368539</v>
       </c>
       <c r="G19">
-        <v>0.09110754488962608</v>
+        <v>0.10162893993380431</v>
       </c>
       <c r="H19">
-        <v>0.23810062900458037</v>
+        <v>0.24482175888282368</v>
       </c>
       <c r="I19">
-        <v>0.027747327225511372</v>
+        <v>0.026598690800271954</v>
       </c>
       <c r="J19">
-        <v>0.39188625277934763</v>
+        <v>0.4232379895804849</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -48244,43 +49699,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:kasese-uga</t>
+          <t>corridor:19:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.031304381068294335</v>
+        <v>0.035432678170503384</v>
       </c>
       <c r="F20">
-        <v>0.08779786212598711</v>
+        <v>0.10593636188070824</v>
       </c>
       <c r="G20">
-        <v>0.07585358277896675</v>
+        <v>0.08559121466787023</v>
       </c>
       <c r="H20">
-        <v>0.2038133127969261</v>
+        <v>0.24250404576809376</v>
       </c>
       <c r="I20">
-        <v>0.017690770792813504</v>
+        <v>0.027309488663839657</v>
       </c>
       <c r="J20">
-        <v>0.3619871650097016</v>
+        <v>0.4555467010005905</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -48312,43 +49767,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:beni-cod</t>
+          <t>corridor:20:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03171837340940942</v>
+        <v>0.03763199658508454</v>
       </c>
       <c r="F21">
-        <v>0.08476753807336304</v>
+        <v>0.10128422532010978</v>
       </c>
       <c r="G21">
-        <v>0.07683287603147732</v>
+        <v>0.09075375258925547</v>
       </c>
       <c r="H21">
-        <v>0.19723709872212672</v>
+        <v>0.23269034583576234</v>
       </c>
       <c r="I21">
-        <v>0.0227792144919888</v>
+        <v>0.019116090021161606</v>
       </c>
       <c r="J21">
-        <v>0.3495642294984912</v>
+        <v>0.4602236579125214</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -48380,43 +49835,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:kampala-uga</t>
+          <t>corridor:21:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.030540418665822744</v>
+        <v>0.038843460236694466</v>
       </c>
       <c r="F22">
-        <v>0.08438962198493272</v>
+        <v>0.10070243265367404</v>
       </c>
       <c r="G22">
-        <v>0.07404478785217791</v>
+        <v>0.0935899840239344</v>
       </c>
       <c r="H22">
-        <v>0.19641470100450442</v>
+        <v>0.23145773577863957</v>
       </c>
       <c r="I22">
-        <v>0.019203507671592176</v>
+        <v>0.025371459529098615</v>
       </c>
       <c r="J22">
-        <v>0.3838230566411262</v>
+        <v>0.4729197264386862</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -48448,7 +49903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:bundibugyo-uga</t>
+          <t>corridor:22:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -48458,29 +49913,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.030399316276041116</v>
+        <v>0.03146929822468722</v>
       </c>
       <c r="F23">
-        <v>0.08407821789447709</v>
+        <v>0.08989853663383654</v>
       </c>
       <c r="G23">
-        <v>0.07371053738981273</v>
+        <v>0.07624375486519391</v>
       </c>
       <c r="H23">
-        <v>0.19573661412777732</v>
+        <v>0.20835308906693198</v>
       </c>
       <c r="I23">
-        <v>0.021457583298788</v>
+        <v>0.023297869762629386</v>
       </c>
       <c r="J23">
-        <v>0.358453978352833</v>
+        <v>0.3863428563442163</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -48516,7 +49971,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:nebbi-uga</t>
+          <t>corridor:23:nyankunde:goma-cod</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -48526,29 +49981,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.030329334773183142</v>
+        <v>0.032748675469615296</v>
       </c>
       <c r="F24">
-        <v>0.08357711531060097</v>
+        <v>0.08856563497530315</v>
       </c>
       <c r="G24">
-        <v>0.07354468946695608</v>
+        <v>0.07926732761392977</v>
       </c>
       <c r="H24">
-        <v>0.19464486287655744</v>
+        <v>0.2054744022745903</v>
       </c>
       <c r="I24">
-        <v>0.014570952055622657</v>
+        <v>0.020503468439890822</v>
       </c>
       <c r="J24">
-        <v>0.32281669746439295</v>
+        <v>0.34571427438684454</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -48584,7 +50039,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:arua-uga</t>
+          <t>corridor:24:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -48594,29 +50049,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.028578262502321705</v>
+        <v>0.030026997527813626</v>
       </c>
       <c r="F25">
-        <v>0.0757669915923353</v>
+        <v>0.08665812766707617</v>
       </c>
       <c r="G25">
-        <v>0.06938957908843438</v>
+        <v>0.07282808208366084</v>
       </c>
       <c r="H25">
-        <v>0.17751379634539563</v>
+        <v>0.2013434496623271</v>
       </c>
       <c r="I25">
-        <v>0.021112935786516</v>
+        <v>0.025288863375360248</v>
       </c>
       <c r="J25">
-        <v>0.3190059046148159</v>
+        <v>0.34693271100874334</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -48652,43 +50107,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:bundibugyo-uga</t>
+          <t>corridor:25:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.006127400208913586</v>
+        <v>0.03075884987706151</v>
       </c>
       <c r="F26">
-        <v>0.0168408512437718</v>
+        <v>0.08599999997606922</v>
       </c>
       <c r="G26">
-        <v>0.015128788346279537</v>
+        <v>0.07456220134186478</v>
       </c>
       <c r="H26">
-        <v>0.04125072266262608</v>
+        <v>0.19991563107642202</v>
       </c>
       <c r="I26">
-        <v>0.004388490481047946</v>
+        <v>0.023982280525205277</v>
       </c>
       <c r="J26">
-        <v>0.08183093712788367</v>
+        <v>0.3479361411653973</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -48720,43 +50175,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:kasese-uga</t>
+          <t>corridor:26:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.00556423388622837</v>
+        <v>0.03164694763292836</v>
       </c>
       <c r="F27">
-        <v>0.01656759676464939</v>
+        <v>0.08559300950103177</v>
       </c>
       <c r="G27">
-        <v>0.013744050643107991</v>
+        <v>0.07666392163091817</v>
       </c>
       <c r="H27">
-        <v>0.04058965567523373</v>
+        <v>0.19903170204824353</v>
       </c>
       <c r="I27">
-        <v>0.003889156206565628</v>
+        <v>0.01960014940850209</v>
       </c>
       <c r="J27">
-        <v>0.08557353521823044</v>
+        <v>0.35567826316219087</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -48788,43 +50243,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:kampala-uga</t>
+          <t>corridor:27:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.00571138519466724</v>
+        <v>0.03415616913117603</v>
       </c>
       <c r="F28">
-        <v>0.016458424878468436</v>
+        <v>0.0843769399835359</v>
       </c>
       <c r="G28">
-        <v>0.014105980367321913</v>
+        <v>0.0825868002754413</v>
       </c>
       <c r="H28">
-        <v>0.04032548046029999</v>
+        <v>0.1963870895325143</v>
       </c>
       <c r="I28">
-        <v>0.0032961116192571803</v>
+        <v>0.023187377364693004</v>
       </c>
       <c r="J28">
-        <v>0.08227064654779426</v>
+        <v>0.3421266345564783</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -48856,43 +50311,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:beni-cod</t>
+          <t>corridor:28:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.005665299126924983</v>
+        <v>0.03357687364916134</v>
       </c>
       <c r="F29">
-        <v>0.016137547052658407</v>
+        <v>0.08425270479805413</v>
       </c>
       <c r="G29">
-        <v>0.01399263950136656</v>
+        <v>0.08122145623779894</v>
       </c>
       <c r="H29">
-        <v>0.039548733878884995</v>
+        <v>0.196116146145421</v>
       </c>
       <c r="I29">
-        <v>0.0033705192295240497</v>
+        <v>0.02179834248652243</v>
       </c>
       <c r="J29">
-        <v>0.0787241376496719</v>
+        <v>0.35919822012550795</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -48924,7 +50379,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:arua-uga</t>
+          <t>corridor:29:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -48934,29 +50389,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.005760920437457601</v>
+        <v>0.005665299126924983</v>
       </c>
       <c r="F30">
-        <v>0.01564371888735397</v>
+        <v>0.016137547052658407</v>
       </c>
       <c r="G30">
-        <v>0.014227802835785092</v>
+        <v>0.01399263950136656</v>
       </c>
       <c r="H30">
-        <v>0.03835261291771347</v>
+        <v>0.039548733878884995</v>
       </c>
       <c r="I30">
-        <v>0.004405736887256273</v>
+        <v>0.0033705192295240497</v>
       </c>
       <c r="J30">
-        <v>0.07717071840257644</v>
+        <v>0.0787241376496719</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -48992,7 +50447,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:nebbi-uga</t>
+          <t>corridor:30:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -49002,29 +50457,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005519371147358398</v>
+        <v>0.005408064245022548</v>
       </c>
       <c r="F31">
-        <v>0.01552589721826908</v>
+        <v>0.016075387130097485</v>
       </c>
       <c r="G31">
-        <v>0.013633690221780848</v>
+        <v>0.013359846492850574</v>
       </c>
       <c r="H31">
-        <v>0.03806709980880993</v>
+        <v>0.039398229649427796</v>
       </c>
       <c r="I31">
-        <v>0.003119740043250069</v>
+        <v>0.0037862601247234534</v>
       </c>
       <c r="J31">
-        <v>0.07892668631060598</v>
+        <v>0.07544870631338906</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -49060,43 +50515,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:goma-cod:kasese-uga</t>
+          <t>corridor:31:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.002911020622911431</v>
+        <v>0.005760920437457601</v>
       </c>
       <c r="F32">
-        <v>0.008708366339810258</v>
+        <v>0.01564371888735397</v>
       </c>
       <c r="G32">
-        <v>0.007204585754623377</v>
+        <v>0.014227802835785092</v>
       </c>
       <c r="H32">
-        <v>0.021460131514392883</v>
+        <v>0.03835261291771347</v>
       </c>
       <c r="I32">
-        <v>0.002213739571223128</v>
+        <v>0.004405736887256273</v>
       </c>
       <c r="J32">
-        <v>0.04056094344785632</v>
+        <v>0.07717071840257644</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -49128,43 +50583,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:butembo:nebbi-uga</t>
+          <t>corridor:32:katwa:goma-cod</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.0027769798502101373</v>
+        <v>0.006169920398082257</v>
       </c>
       <c r="F33">
-        <v>0.008633599440103473</v>
+        <v>0.01553498621898089</v>
       </c>
       <c r="G33">
-        <v>0.006873526257886398</v>
+        <v>0.01523329162375131</v>
       </c>
       <c r="H33">
-        <v>0.021277062424142124</v>
+        <v>0.03808912674070569</v>
       </c>
       <c r="I33">
-        <v>0.0016525413787399719</v>
+        <v>0.003357225433652031</v>
       </c>
       <c r="J33">
-        <v>0.03899275669757771</v>
+        <v>0.06777077505091869</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -49196,43 +50651,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:miti-murhesa:kasese-uga</t>
+          <t>corridor:33:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.0029900129594525315</v>
+        <v>0.005252367922210843</v>
       </c>
       <c r="F34">
-        <v>0.00847697711451803</v>
+        <v>0.015529432038009494</v>
       </c>
       <c r="G34">
-        <v>0.007399652921270428</v>
+        <v>0.012976721133270863</v>
       </c>
       <c r="H34">
-        <v>0.020893505827646625</v>
+        <v>0.038075666248175294</v>
       </c>
       <c r="I34">
-        <v>0.0017305897295624153</v>
+        <v>0.002718444578993254</v>
       </c>
       <c r="J34">
-        <v>0.04136198023793251</v>
+        <v>0.07153399444934289</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -49264,43 +50719,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:butembo:arua-uga</t>
+          <t>corridor:34:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003004206625567968</v>
+        <v>0.005519371147358398</v>
       </c>
       <c r="F35">
-        <v>0.008424640775256842</v>
+        <v>0.01552589721826908</v>
       </c>
       <c r="G35">
-        <v>0.007434701480319217</v>
+        <v>0.013633690221780848</v>
       </c>
       <c r="H35">
-        <v>0.02076531908923876</v>
+        <v>0.03806709980880993</v>
       </c>
       <c r="I35">
-        <v>0.0014445621581179958</v>
+        <v>0.003119740043250069</v>
       </c>
       <c r="J35">
-        <v>0.03973256156228256</v>
+        <v>0.07892668631060598</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -49332,43 +50787,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:nizi:bundibugyo-uga</t>
+          <t>corridor:35:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.003111941625778658</v>
+        <v>0.005719038632820889</v>
       </c>
       <c r="F36">
-        <v>0.008402719753006271</v>
+        <v>0.01443774068944173</v>
       </c>
       <c r="G36">
-        <v>0.0077007053534820236</v>
+        <v>0.014124805074243657</v>
       </c>
       <c r="H36">
-        <v>0.020711624541566498</v>
+        <v>0.03542780468093812</v>
       </c>
       <c r="I36">
-        <v>0.0017674417542844795</v>
+        <v>0.0037666445426507516</v>
       </c>
       <c r="J36">
-        <v>0.038221794937289805</v>
+        <v>0.07911590609890654</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -49400,39 +50855,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:butembo:kampala-uga</t>
+          <t>corridor:36:miti-murhesa:goma-cod</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.002898657102272467</v>
+        <v>0.002804459043458968</v>
       </c>
       <c r="F37">
-        <v>0.00831048662323794</v>
+        <v>0.00878511499370449</v>
       </c>
       <c r="G37">
-        <v>0.0071740522491085534</v>
+        <v>0.0069414009149691425</v>
       </c>
       <c r="H37">
-        <v>0.020485685215592936</v>
+        <v>0.021648029980746247</v>
       </c>
       <c r="I37">
-        <v>0.0024156585156788397</v>
+        <v>0.0018195961747441535</v>
       </c>
       <c r="J37">
-        <v>0.03953263154110449</v>
+        <v>0.04351969089202276</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -49468,12 +50923,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:goma-cod:arua-uga</t>
+          <t>corridor:37:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49485,22 +50940,22 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.0027125515817747747</v>
+        <v>0.002911020622911431</v>
       </c>
       <c r="F38">
-        <v>0.008284511161890662</v>
+        <v>0.008708366339810258</v>
       </c>
       <c r="G38">
-        <v>0.006714374614320118</v>
+        <v>0.007204585754623377</v>
       </c>
       <c r="H38">
-        <v>0.020422048400997733</v>
+        <v>0.021460131514392883</v>
       </c>
       <c r="I38">
-        <v>0.0015261556624343033</v>
+        <v>0.002213739571223128</v>
       </c>
       <c r="J38">
-        <v>0.04121550107288618</v>
+        <v>0.04056094344785632</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -49536,39 +50991,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:nizi:nebbi-uga</t>
+          <t>corridor:38:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.002681493416460179</v>
+        <v>0.0027769798502101373</v>
       </c>
       <c r="F39">
-        <v>0.008183525990654555</v>
+        <v>0.008633599440103473</v>
       </c>
       <c r="G39">
-        <v>0.0066376497183083805</v>
+        <v>0.006873526257886398</v>
       </c>
       <c r="H39">
-        <v>0.020174624300513644</v>
+        <v>0.021277062424142124</v>
       </c>
       <c r="I39">
-        <v>0.0014926750968995012</v>
+        <v>0.0016525413787399719</v>
       </c>
       <c r="J39">
-        <v>0.039228799255843605</v>
+        <v>0.03899275669757771</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -49604,39 +51059,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:nizi:beni-cod</t>
+          <t>corridor:39:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.0028326663994584778</v>
+        <v>0.002943458801597104</v>
       </c>
       <c r="F40">
-        <v>0.00815823939873217</v>
+        <v>0.00848250804610165</v>
       </c>
       <c r="G40">
-        <v>0.00701107122667835</v>
+        <v>0.00728469284319036</v>
       </c>
       <c r="H40">
-        <v>0.020112663896618338</v>
+        <v>0.020907051259871884</v>
       </c>
       <c r="I40">
-        <v>0.0015343125999103453</v>
+        <v>0.0019834988729835134</v>
       </c>
       <c r="J40">
-        <v>0.04046059631457021</v>
+        <v>0.04021049895847632</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -49672,39 +51127,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:butembo:kasese-uga</t>
+          <t>corridor:40:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.002747567807505402</v>
+        <v>0.0029900129594525315</v>
       </c>
       <c r="F41">
-        <v>0.008154445449094133</v>
+        <v>0.00847697711451803</v>
       </c>
       <c r="G41">
-        <v>0.006800874406568735</v>
+        <v>0.007399652921270428</v>
       </c>
       <c r="H41">
-        <v>0.020103367023304758</v>
+        <v>0.020893505827646625</v>
       </c>
       <c r="I41">
-        <v>0.0016545850906405566</v>
+        <v>0.0017305897295624153</v>
       </c>
       <c r="J41">
-        <v>0.04190231971566359</v>
+        <v>0.04136198023793251</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -49740,39 +51195,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:bambu:arua-uga</t>
+          <t>corridor:41:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0029994938796520376</v>
+        <v>0.0030684076719234843</v>
       </c>
       <c r="F42">
-        <v>0.008147226747461322</v>
+        <v>0.008456179104640776</v>
       </c>
       <c r="G42">
-        <v>0.007423064501010185</v>
+        <v>0.007593222717078629</v>
       </c>
       <c r="H42">
-        <v>0.020085678474308588</v>
+        <v>0.02084256764572595</v>
       </c>
       <c r="I42">
-        <v>0.0019885435545158206</v>
+        <v>0.002196657973502822</v>
       </c>
       <c r="J42">
-        <v>0.03889536735459872</v>
+        <v>0.041788827485054</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -49808,39 +51263,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:miti-murhesa:nebbi-uga</t>
+          <t>corridor:42:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.003061304197971737</v>
+        <v>0.003004206625567968</v>
       </c>
       <c r="F43">
-        <v>0.00814381727681368</v>
+        <v>0.008424640775256842</v>
       </c>
       <c r="G43">
-        <v>0.00757568403154249</v>
+        <v>0.007434701480319217</v>
       </c>
       <c r="H43">
-        <v>0.020077321716829383</v>
+        <v>0.02076531908923876</v>
       </c>
       <c r="I43">
-        <v>0.0016647585017794454</v>
+        <v>0.0014445621581179958</v>
       </c>
       <c r="J43">
-        <v>0.03886426325038798</v>
+        <v>0.03973256156228256</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -49876,39 +51331,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:goma-cod:nebbi-uga</t>
+          <t>corridor:43:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.0031340416283216765</v>
+        <v>0.002960980933083057</v>
       </c>
       <c r="F44">
-        <v>0.008075152624742232</v>
+        <v>0.008410627383326874</v>
       </c>
       <c r="G44">
-        <v>0.00775526629452003</v>
+        <v>0.007327962889187772</v>
       </c>
       <c r="H44">
-        <v>0.01990905693022571</v>
+        <v>0.02073099435361825</v>
       </c>
       <c r="I44">
-        <v>0.002243955437822981</v>
+        <v>0.0019244758288322094</v>
       </c>
       <c r="J44">
-        <v>0.03925743592923069</v>
+        <v>0.04355962661351945</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -49944,39 +51399,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:kasese-uga</t>
+          <t>corridor:44:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.0027076980614253177</v>
+        <v>0.0027859978355153636</v>
       </c>
       <c r="F45">
-        <v>0.008070258181662043</v>
+        <v>0.008318397055267795</v>
       </c>
       <c r="G45">
-        <v>0.006702384988596155</v>
+        <v>0.006895801362401172</v>
       </c>
       <c r="H45">
-        <v>0.019897061858827808</v>
+        <v>0.020505061460188434</v>
       </c>
       <c r="I45">
-        <v>0.0018949255081115225</v>
+        <v>0.0019464730520260044</v>
       </c>
       <c r="J45">
-        <v>0.03846409821761752</v>
+        <v>0.0437435227905687</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -50012,12 +51467,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:bambu:nebbi-uga</t>
+          <t>corridor:45:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -50029,22 +51484,22 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.0029941551171358827</v>
+        <v>0.002955828840965319</v>
       </c>
       <c r="F46">
-        <v>0.008062710206497403</v>
+        <v>0.008295276156943115</v>
       </c>
       <c r="G46">
-        <v>0.007409881598903129</v>
+        <v>0.00731524012555157</v>
       </c>
       <c r="H46">
-        <v>0.019878564189878323</v>
+        <v>0.020448421900859687</v>
       </c>
       <c r="I46">
-        <v>0.0023605934928140225</v>
+        <v>0.0014705155925033963</v>
       </c>
       <c r="J46">
-        <v>0.03849962672911588</v>
+        <v>0.04349024336692712</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -50080,7 +51535,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:goma-cod:bundibugyo-uga</t>
+          <t>corridor:46:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -50090,29 +51545,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.002966610048958429</v>
+        <v>0.0027125515817747747</v>
       </c>
       <c r="F47">
-        <v>0.008058011311337127</v>
+        <v>0.008284511161890662</v>
       </c>
       <c r="G47">
-        <v>0.007341863257414205</v>
+        <v>0.006714374614320118</v>
       </c>
       <c r="H47">
-        <v>0.01986704842779069</v>
+        <v>0.020422048400997733</v>
       </c>
       <c r="I47">
-        <v>0.00193425911064469</v>
+        <v>0.0015261556624343033</v>
       </c>
       <c r="J47">
-        <v>0.03944581553096073</v>
+        <v>0.04121550107288618</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -50148,39 +51603,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:miti-murhesa:beni-cod</t>
+          <t>corridor:47:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002837150359859514</v>
+        <v>0.002859782073699718</v>
       </c>
       <c r="F48">
-        <v>0.008035393220128945</v>
+        <v>0.008263354150150004</v>
       </c>
       <c r="G48">
-        <v>0.007022145861493551</v>
+        <v>0.0070780413459651526</v>
       </c>
       <c r="H48">
-        <v>0.019811615320896397</v>
+        <v>0.02037021424485949</v>
       </c>
       <c r="I48">
-        <v>0.0016272804773103918</v>
+        <v>0.001649416108444149</v>
       </c>
       <c r="J48">
-        <v>0.0417257099987222</v>
+        <v>0.042018168525404104</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -50216,7 +51671,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:bambu:bundibugyo-uga</t>
+          <t>corridor:48:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -50226,29 +51681,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.0027221893165624844</v>
+        <v>0.0029994938796520376</v>
       </c>
       <c r="F49">
-        <v>0.008025112676473323</v>
+        <v>0.008147226747461322</v>
       </c>
       <c r="G49">
-        <v>0.006738183364620509</v>
+        <v>0.007423064501010185</v>
       </c>
       <c r="H49">
-        <v>0.019786420160049306</v>
+        <v>0.020085678474308588</v>
       </c>
       <c r="I49">
-        <v>0.0018923716266919608</v>
+        <v>0.0019885435545158206</v>
       </c>
       <c r="J49">
-        <v>0.04067091464985655</v>
+        <v>0.03889536735459872</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -50284,39 +51739,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:butembo:beni-cod</t>
+          <t>corridor:49:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0029779299971779694</v>
+        <v>0.003061304197971737</v>
       </c>
       <c r="F50">
-        <v>0.007993848855793961</v>
+        <v>0.00814381727681368</v>
       </c>
       <c r="G50">
-        <v>0.007369816645196731</v>
+        <v>0.00757568403154249</v>
       </c>
       <c r="H50">
-        <v>0.019709793462212938</v>
+        <v>0.020077321716829383</v>
       </c>
       <c r="I50">
-        <v>0.00181708380560561</v>
+        <v>0.0016647585017794454</v>
       </c>
       <c r="J50">
-        <v>0.03931941479325931</v>
+        <v>0.03886426325038798</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -50352,12 +51807,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:nizi:arua-uga</t>
+          <t>corridor:50:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -50369,22 +51824,22 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002573515092590184</v>
+        <v>0.002726713106049522</v>
       </c>
       <c r="F51">
-        <v>0.007966550348283807</v>
+        <v>0.008090540628411913</v>
       </c>
       <c r="G51">
-        <v>0.006370874666990878</v>
+        <v>0.00674935818047237</v>
       </c>
       <c r="H51">
-        <v>0.01964288498845579</v>
+        <v>0.019946766455073678</v>
       </c>
       <c r="I51">
-        <v>0.0019758723489192026</v>
+        <v>0.001970594123010397</v>
       </c>
       <c r="J51">
-        <v>0.042497226842963434</v>
+        <v>0.0390130390539575</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -50420,39 +51875,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:bambu:kasese-uga</t>
+          <t>corridor:51:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.00270874962073242</v>
+        <v>0.0031340416283216765</v>
       </c>
       <c r="F52">
-        <v>0.007945705918331214</v>
+        <v>0.008075152624742232</v>
       </c>
       <c r="G52">
-        <v>0.006704981285868744</v>
+        <v>0.00775526629452003</v>
       </c>
       <c r="H52">
-        <v>0.019591793108546057</v>
+        <v>0.01990905693022571</v>
       </c>
       <c r="I52">
-        <v>0.0017099558870529636</v>
+        <v>0.002243955437822981</v>
       </c>
       <c r="J52">
-        <v>0.040311579752921115</v>
+        <v>0.03925743592923069</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -50488,39 +51943,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:goma-cod:kampala-uga</t>
+          <t>corridor:52:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.002937977495464733</v>
+        <v>0.0029941551171358827</v>
       </c>
       <c r="F53">
-        <v>0.00791077263458917</v>
+        <v>0.008062710206497403</v>
       </c>
       <c r="G53">
-        <v>0.007271156988672728</v>
+        <v>0.007409881598903129</v>
       </c>
       <c r="H53">
-        <v>0.019506162869570853</v>
+        <v>0.019878564189878323</v>
       </c>
       <c r="I53">
-        <v>0.0015259490592032937</v>
+        <v>0.0023605934928140225</v>
       </c>
       <c r="J53">
-        <v>0.04355956758414158</v>
+        <v>0.03849962672911588</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -50556,39 +52011,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:kilo:nebbi-uga</t>
+          <t>corridor:53:butembo:goma-cod</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0025676185126164985</v>
+        <v>0.002966610048958429</v>
       </c>
       <c r="F54">
-        <v>0.007868621059145403</v>
+        <v>0.008058011311337127</v>
       </c>
       <c r="G54">
-        <v>0.0063563051772850265</v>
+        <v>0.007341863257414205</v>
       </c>
       <c r="H54">
-        <v>0.01940283456752373</v>
+        <v>0.01986704842779069</v>
       </c>
       <c r="I54">
-        <v>0.0016564750458324922</v>
+        <v>0.00193425911064469</v>
       </c>
       <c r="J54">
-        <v>0.03677402473147005</v>
+        <v>0.03944581553096073</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -50624,39 +52079,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:miti-murhesa:arua-uga</t>
+          <t>corridor:54:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0027868684736187532</v>
+        <v>0.002837150359859514</v>
       </c>
       <c r="F55">
-        <v>0.007841801348761585</v>
+        <v>0.008035393220128945</v>
       </c>
       <c r="G55">
-        <v>0.00689795184472039</v>
+        <v>0.007022145861493551</v>
       </c>
       <c r="H55">
-        <v>0.019337083521810405</v>
+        <v>0.019811615320896397</v>
       </c>
       <c r="I55">
-        <v>0.0017127846529912062</v>
+        <v>0.0016272804773103918</v>
       </c>
       <c r="J55">
-        <v>0.03838966632456429</v>
+        <v>0.0417257099987222</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -50692,7 +52147,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:bambu:kampala-uga</t>
+          <t>corridor:55:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -50702,29 +52157,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.002695763743499391</v>
+        <v>0.0027221893165624844</v>
       </c>
       <c r="F56">
-        <v>0.007827990157414616</v>
+        <v>0.008025112676473323</v>
       </c>
       <c r="G56">
-        <v>0.006672903334783625</v>
+        <v>0.006738183364620509</v>
       </c>
       <c r="H56">
-        <v>0.0193032265603717</v>
+        <v>0.019786420160049306</v>
       </c>
       <c r="I56">
-        <v>0.0021490354133257674</v>
+        <v>0.0018923716266919608</v>
       </c>
       <c r="J56">
-        <v>0.04054210634480244</v>
+        <v>0.04067091464985655</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -50760,39 +52215,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:kilo:beni-cod</t>
+          <t>corridor:56:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.003089733434463643</v>
+        <v>0.0029259199934389135</v>
       </c>
       <c r="F57">
-        <v>0.007797896708572921</v>
+        <v>0.008020137561744467</v>
       </c>
       <c r="G57">
-        <v>0.007645875573836641</v>
+        <v>0.007241380772000483</v>
       </c>
       <c r="H57">
-        <v>0.019229449244770908</v>
+        <v>0.019774226740906592</v>
       </c>
       <c r="I57">
-        <v>0.0016800255774773844</v>
+        <v>0.0020925966217400726</v>
       </c>
       <c r="J57">
-        <v>0.034479825340189424</v>
+        <v>0.03834918307680624</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -50828,39 +52283,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:kilo:bundibugyo-uga</t>
+          <t>corridor:57:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.002629641493342244</v>
+        <v>0.0029779299971779694</v>
       </c>
       <c r="F58">
-        <v>0.0077950978062735765</v>
+        <v>0.007993848855793961</v>
       </c>
       <c r="G58">
-        <v>0.006509547825961637</v>
+        <v>0.007369816645196731</v>
       </c>
       <c r="H58">
-        <v>0.019222587126321078</v>
+        <v>0.019709793462212938</v>
       </c>
       <c r="I58">
-        <v>0.0013601473368735656</v>
+        <v>0.00181708380560561</v>
       </c>
       <c r="J58">
-        <v>0.03643059423991454</v>
+        <v>0.03931941479325931</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -50896,39 +52351,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:kilo:arua-uga</t>
+          <t>corridor:58:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0028404048325195996</v>
+        <v>0.0028157111278240277</v>
       </c>
       <c r="F59">
-        <v>0.007786957767991598</v>
+        <v>0.007982907485630852</v>
       </c>
       <c r="G59">
-        <v>0.007030184083863106</v>
+        <v>0.00696919271112631</v>
       </c>
       <c r="H59">
-        <v>0.019202630017290306</v>
+        <v>0.01968297753862283</v>
       </c>
       <c r="I59">
-        <v>0.0018407478578635922</v>
+        <v>0.0017612060420275717</v>
       </c>
       <c r="J59">
-        <v>0.041169590401536636</v>
+        <v>0.04306536711443636</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -50964,39 +52419,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:bambu:beni-cod</t>
+          <t>corridor:59:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.0030164649861187665</v>
+        <v>0.0028025163740137693</v>
       </c>
       <c r="F60">
-        <v>0.007772299321732512</v>
+        <v>0.007952241687691819</v>
       </c>
       <c r="G60">
-        <v>0.0074649703248304</v>
+        <v>0.006936602546891185</v>
       </c>
       <c r="H60">
-        <v>0.01916669022271858</v>
+        <v>0.019607812760897347</v>
       </c>
       <c r="I60">
-        <v>0.0017745338814096486</v>
+        <v>0.0019699792558314196</v>
       </c>
       <c r="J60">
-        <v>0.04144693368617039</v>
+        <v>0.03954925963547096</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -51032,39 +52487,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:miti-murhesa:kampala-uga</t>
+          <t>corridor:60:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.002780055599183956</v>
+        <v>0.00270874962073242</v>
       </c>
       <c r="F61">
-        <v>0.0077543800748747505</v>
+        <v>0.007945705918331214</v>
       </c>
       <c r="G61">
-        <v>0.006881123372275866</v>
+        <v>0.006704981285868744</v>
       </c>
       <c r="H61">
-        <v>0.01912275597116167</v>
+        <v>0.019591793108546057</v>
       </c>
       <c r="I61">
-        <v>0.001731233807528232</v>
+        <v>0.0017099558870529636</v>
       </c>
       <c r="J61">
-        <v>0.03818702256228324</v>
+        <v>0.040311579752921115</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -51100,39 +52555,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:goma-cod:beni-cod</t>
+          <t>corridor:61:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0026587921388565305</v>
+        <v>0.0027622307839203497</v>
       </c>
       <c r="F62">
-        <v>0.007745510300115388</v>
+        <v>0.007936559977572588</v>
       </c>
       <c r="G62">
-        <v>0.006581566727665494</v>
+        <v>0.0068370944013670665</v>
       </c>
       <c r="H62">
-        <v>0.0191010070867213</v>
+        <v>0.019569374185153948</v>
       </c>
       <c r="I62">
-        <v>0.0015209453885095762</v>
+        <v>0.0017312928849019195</v>
       </c>
       <c r="J62">
-        <v>0.040091153412378705</v>
+        <v>0.043878198155480545</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -51168,39 +52623,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:nizi:kampala-uga</t>
+          <t>corridor:62:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0027361329624540076</v>
+        <v>0.002937977495464733</v>
       </c>
       <c r="F63">
-        <v>0.0075987291180549255</v>
+        <v>0.00791077263458917</v>
       </c>
       <c r="G63">
-        <v>0.006772627856763858</v>
+        <v>0.007271156988672728</v>
       </c>
       <c r="H63">
-        <v>0.018741077563372677</v>
+        <v>0.019506162869570853</v>
       </c>
       <c r="I63">
-        <v>0.0013777102458249037</v>
+        <v>0.0015259490592032937</v>
       </c>
       <c r="J63">
-        <v>0.043087769872402426</v>
+        <v>0.04355956758414158</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -51236,7 +52691,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:nizi:kasese-uga</t>
+          <t>corridor:63:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -51246,29 +52701,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0028258568215484003</v>
+        <v>0.0027959740199166583</v>
       </c>
       <c r="F64">
-        <v>0.007552854340310916</v>
+        <v>0.007902911626123776</v>
       </c>
       <c r="G64">
-        <v>0.006994252131591605</v>
+        <v>0.006920442727769538</v>
       </c>
       <c r="H64">
-        <v>0.018628569089331942</v>
+        <v>0.019486894130341964</v>
       </c>
       <c r="I64">
-        <v>0.0018339497806420303</v>
+        <v>0.0013335076635186461</v>
       </c>
       <c r="J64">
-        <v>0.0447125896493108</v>
+        <v>0.03481721986752081</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -51304,39 +52759,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:butembo:bundibugyo-uga</t>
+          <t>corridor:64:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D65">
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.002862546240653324</v>
+        <v>0.0025676185126164985</v>
       </c>
       <c r="F65">
-        <v>0.0075168412354912895</v>
+        <v>0.007868621059145403</v>
       </c>
       <c r="G65">
-        <v>0.007084869280098771</v>
+        <v>0.0063563051772850265</v>
       </c>
       <c r="H65">
-        <v>0.0185402409724002</v>
+        <v>0.01940283456752373</v>
       </c>
       <c r="I65">
-        <v>0.0017601300993422223</v>
+        <v>0.0016564750458324922</v>
       </c>
       <c r="J65">
-        <v>0.04281508413149316</v>
+        <v>0.03677402473147005</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -51372,39 +52827,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:65:bambu:goma-cod</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.002806475854065099</v>
+        <v>0.002734796227902181</v>
       </c>
       <c r="F66">
-        <v>0.007390944356303691</v>
+        <v>0.007857450301785557</v>
       </c>
       <c r="G66">
-        <v>0.006946382389732636</v>
+        <v>0.006769325733142567</v>
       </c>
       <c r="H66">
-        <v>0.018231416239954695</v>
+        <v>0.01937544941239916</v>
       </c>
       <c r="I66">
-        <v>0.00208300583836101</v>
+        <v>0.0020746804621469632</v>
       </c>
       <c r="J66">
-        <v>0.03944316706094814</v>
+        <v>0.039964857141121454</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -51440,7 +52895,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:kilo:kampala-uga</t>
+          <t>corridor:66:kilo:goma-cod</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -51450,29 +52905,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.0028636196069686815</v>
+        <v>0.0027868684736187532</v>
       </c>
       <c r="F67">
-        <v>0.007245116575636645</v>
+        <v>0.007841801348761585</v>
       </c>
       <c r="G67">
-        <v>0.0070875198104265735</v>
+        <v>0.00689795184472039</v>
       </c>
       <c r="H67">
-        <v>0.017873638059777402</v>
+        <v>0.019337083521810405</v>
       </c>
       <c r="I67">
-        <v>0.001885099074969826</v>
+        <v>0.0017127846529912062</v>
       </c>
       <c r="J67">
-        <v>0.04037313015728034</v>
+        <v>0.03838966632456429</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -51505,8 +52960,688 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>corridor:67:bambu:kampala-uga</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bambu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kampala-uga</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>30</v>
+      </c>
+      <c r="E68">
+        <v>0.002695763743499391</v>
+      </c>
+      <c r="F68">
+        <v>0.007827990157414616</v>
+      </c>
+      <c r="G68">
+        <v>0.006672903334783625</v>
+      </c>
+      <c r="H68">
+        <v>0.0193032265603717</v>
+      </c>
+      <c r="I68">
+        <v>0.0021490354133257674</v>
+      </c>
+      <c r="J68">
+        <v>0.04054210634480244</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>corridor:68:miti-murhesa:beni-cod</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>miti-murhesa</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69">
+        <v>0.002747310022513244</v>
+      </c>
+      <c r="F69">
+        <v>0.007800938064515872</v>
+      </c>
+      <c r="G69">
+        <v>0.006800237623896643</v>
+      </c>
+      <c r="H69">
+        <v>0.019236905708309188</v>
+      </c>
+      <c r="I69">
+        <v>0.002007951916882189</v>
+      </c>
+      <c r="J69">
+        <v>0.03490534363617388</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>corridor:69:kilo:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>30</v>
+      </c>
+      <c r="E70">
+        <v>0.0028404048325195996</v>
+      </c>
+      <c r="F70">
+        <v>0.007786957767991598</v>
+      </c>
+      <c r="G70">
+        <v>0.007030184083863106</v>
+      </c>
+      <c r="H70">
+        <v>0.019202630017290306</v>
+      </c>
+      <c r="I70">
+        <v>0.0018407478578635922</v>
+      </c>
+      <c r="J70">
+        <v>0.041169590401536636</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>corridor:70:bambu:beni-cod</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bambu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71">
+        <v>0.0030164649861187665</v>
+      </c>
+      <c r="F71">
+        <v>0.007772299321732512</v>
+      </c>
+      <c r="G71">
+        <v>0.0074649703248304</v>
+      </c>
+      <c r="H71">
+        <v>0.01916669022271858</v>
+      </c>
+      <c r="I71">
+        <v>0.0017745338814096486</v>
+      </c>
+      <c r="J71">
+        <v>0.04144693368617039</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>corridor:71:kilo:beni-cod</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+      <c r="E72">
+        <v>0.002780055599183956</v>
+      </c>
+      <c r="F72">
+        <v>0.0077543800748747505</v>
+      </c>
+      <c r="G72">
+        <v>0.006881123372275866</v>
+      </c>
+      <c r="H72">
+        <v>0.01912275597116167</v>
+      </c>
+      <c r="I72">
+        <v>0.001731233807528232</v>
+      </c>
+      <c r="J72">
+        <v>0.03818702256228324</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>corridor:72:goma-cod:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>30</v>
+      </c>
+      <c r="E73">
+        <v>0.0026587921388565305</v>
+      </c>
+      <c r="F73">
+        <v>0.007745510300115388</v>
+      </c>
+      <c r="G73">
+        <v>0.006581566727665494</v>
+      </c>
+      <c r="H73">
+        <v>0.0191010070867213</v>
+      </c>
+      <c r="I73">
+        <v>0.0015209453885095762</v>
+      </c>
+      <c r="J73">
+        <v>0.040091153412378705</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>corridor:73:nizi:goma-cod</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nizi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74">
+        <v>0.002825210964649716</v>
+      </c>
+      <c r="F74">
+        <v>0.00765236996976712</v>
+      </c>
+      <c r="G74">
+        <v>0.006992656995719604</v>
+      </c>
+      <c r="H74">
+        <v>0.01887262263985079</v>
+      </c>
+      <c r="I74">
+        <v>0.001869567731866642</v>
+      </c>
+      <c r="J74">
+        <v>0.03961175754580763</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>corridor:74:butembo:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>butembo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75">
+        <v>0.002862546240653324</v>
+      </c>
+      <c r="F75">
+        <v>0.0075168412354912895</v>
+      </c>
+      <c r="G75">
+        <v>0.007084869280098771</v>
+      </c>
+      <c r="H75">
+        <v>0.0185402409724002</v>
+      </c>
+      <c r="I75">
+        <v>0.0017601300993422223</v>
+      </c>
+      <c r="J75">
+        <v>0.04281508413149316</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>corridor:75:kilo:arua-uga</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>arua-uga</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>30</v>
+      </c>
+      <c r="E76">
+        <v>0.002806475854065099</v>
+      </c>
+      <c r="F76">
+        <v>0.007390944356303691</v>
+      </c>
+      <c r="G76">
+        <v>0.006946382389732636</v>
+      </c>
+      <c r="H76">
+        <v>0.018231416239954695</v>
+      </c>
+      <c r="I76">
+        <v>0.00208300583836101</v>
+      </c>
+      <c r="J76">
+        <v>0.03944316706094814</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>corridor:76:nizi:beni-cod</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>nizi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77">
+        <v>0.002632399314454331</v>
+      </c>
+      <c r="F77">
+        <v>0.007137232739807736</v>
+      </c>
+      <c r="G77">
+        <v>0.00651636145090756</v>
+      </c>
+      <c r="H77">
+        <v>0.017608901019654427</v>
+      </c>
+      <c r="I77">
+        <v>0.0019380433985584896</v>
+      </c>
+      <c r="J77">
+        <v>0.034324531074020156</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P67"/>
+  <autoFilter ref="A1:P77"/>
 </worksheet>
 </file>
 
@@ -53757,7 +55892,205 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>bunia -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>bunia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I14">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>0.1024</v>
+      </c>
+      <c r="K14">
+        <v>0.2669</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-02</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rwampara -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rwampara</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>0.2034</v>
+      </c>
+      <c r="K15">
+        <v>0.4589</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-03</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>mongbwalu -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>mongbwalu</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I16">
+        <v>30</v>
+      </c>
+      <c r="J16">
+        <v>0.0955</v>
+      </c>
+      <c r="K16">
+        <v>0.2518</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N16"/>
 </worksheet>
 </file>
--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.2% lower bounds and 1.8-48.2% upper bounds.</t>
+          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 76-corridor adjusted 50% range is 0.6-21.8% lower bounds and 1.8-49.4% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ministere de la Sante Publique, Hygiene et Prevoyance sociale, Democratic Republic of the Congo. SitRep MVE N 007/MVB_17/2026 official PDF, cumulative Table IV, data as of 21 May 2026 / published 22 May 2026.; US CDC. Ebola Disease: Current Situation, 24 May 2026.; data/snapshot_contract.json generated from data/live-bdbv-2026-output.json by lovs/snapshot_contract.py.; lovs/lovs_next_zone.py source-load selection and corridor driver generation.; Evidence chain PUBLIC-CLAIM-AUDIT and public claim audit row BDBV-CLAIM-005.</t>
+          <t>Ministere de la Sante Publique, Hygiene et Prevoyance sociale, Democratic Republic of the Congo. SitRep MVE N 007/MVB_17/2026 official PDF, cumulative Table IV, data as of 21 May 2026 / published 22 May 2026.; US CDC. Ebola Disease: Current Situation, 25 May 2026.; data/snapshot_contract.json generated from data/live-bdbv-2026-output.json by lovs/snapshot_contract.py.; lovs/lovs_next_zone.py source-load selection and corridor driver generation.; Evidence chain PUBLIC-CLAIM-AUDIT and public claim audit row BDBV-CLAIM-005.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -135,7 +135,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 66-corridor adjusted 50% range is 0.6-21.2% lower bounds and 1.8-48.2% upper bounds.</t>
+          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 76-corridor adjusted 50% range is 0.6-21.8% lower bounds and 1.8-49.4% upper bounds.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ministere de la Sante Publique, Hygiene et Prevoyance sociale, Democratic Republic of the Congo. SitRep MVE N 007/MVB_17/2026 official PDF, cumulative Table IV, data as of 21 May 2026 / published 22 May 2026.; US CDC. Ebola Disease: Current Situation, 24 May 2026.; data/snapshot_contract.json generated from data/live-bdbv-2026-output.json by lovs/snapshot_contract.py.; lovs/lovs_next_zone.py source-load selection and corridor driver generation.; Evidence chain PUBLIC-CLAIM-AUDIT and public claim audit row BDBV-CLAIM-005.</t>
+          <t>Ministere de la Sante Publique, Hygiene et Prevoyance sociale, Democratic Republic of the Congo. SitRep MVE N 007/MVB_17/2026 official PDF, cumulative Table IV, data as of 21 May 2026 / published 22 May 2026.; US CDC. Ebola Disease: Current Situation, 25 May 2026.; data/snapshot_contract.json generated from data/live-bdbv-2026-output.json by lovs/snapshot_contract.py.; lovs/lovs_next_zone.py source-load selection and corridor driver generation.; Evidence chain PUBLIC-CLAIM-AUDIT and public claim audit row BDBV-CLAIM-005.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1439,8 +1439,102 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-029</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Source attribution lag</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The May 25 headline confirmed-count primary is ahead of the latest officially zone-attributed cumulative table, so the corridor source-load total remains 79 and the unallocated headline context is 33. This is a named source-attribution lag, not a lost public claim audit or a down-revision.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>headline_confirmed_total=112 from CDC 25 May; zone_attributed_confirmed_total=79 from DRC MoH SitRep 007 cumulative Table IV; unallocated_confirmed_total=33 computed as 112 - 79.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>US CDC Ebola Disease: Current Situation page, archived 25 May 2026.; DRC Ministry of Health SitRep MVE N 007/MVB_17/2026 PDF cumulative Table IV, data as of 21 May 2026 and published 22 May 2026.; data/snapshot_contract.json confirmed_case_partition.; NUMBERS_AUDIT.md source-attribution lag and confirmed-case partition section.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html; https://administration.sante.gouv.cd/wp-content/uploads/2026/05/SitRep_MVE_RDC_20260512-FDv2_IM.pdf; restricted-local-review-not-redistributed; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Keep the confirmed-case partition explicit in snapshot_contract and NUMBERS_AUDIT. Promote newer zone-attributed rows only after a cumulative official table/PDF or validated equivalent is archived.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-030</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bdbv may26 source review boundary</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>The 26 May sweep found one count-bearing official source update that should be archived for audit: ECDC 26 May. Its count tuple corroborates the CDC 25 May endpoint but carries separate page, count-source, and retrieval clocks, so it must not be treated as a new data-date-only trajectory point or as a generic deaths replacement.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ECDC page publication/as-of date=2026-05-26; ECDC count source label=DRC Ministry of Health on 2026-05-25; DRC confirmed=105, DRC suspected=906, DRC confirmed deaths=10, DRC suspected deaths=223, Uganda confirmed=7, Uganda deaths=1; computed country-pair confirmed=112.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>supported</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ECDC. Ebola virus disease outbreak in the Democratic Republic of the Congo and Uganda. Live page captured 26 May 2026.; WHO Regional Office for Africa. Ongoing outbreak in the Democratic Republic of the Congo / Bundibugyo virus disease outbreak hub. Movement detected by the 26 May freshness check.; US CDC returning-travelers public information page. Context update detected by the 26 May freshness check.; Wikipedia contributors. 2026 Ituri Province Ebola epidemic, live page observed by 26 May 2026 freshness check.; data/external_sources/freshness/bdbv-2026-2026-05-26.json generated by source_ingest.py --live-check --as-of 2026-05-26.; data/bundibugyo-2026/manifest.json entry ecdc-bdbv-drc-uga-2026-05-26-live.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026; https://www.afro.who.int/health-topics/ebola-disease/outbreak-drc-26; https://www.cdc.gov/viral-hemorrhagic-fevers/travel-to-us/index.html; https://en.wikipedia.org/wiki/2026_Ituri_Province_Ebola_epidemic; restricted-local-review-not-redistributed; restricted-local-review-not-redistributed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Keep the May 26 ECDC archive as evidence-backed cross-check input. Do not publish, promote preview, or alter the public endpoint until the May 26 snapshot/release gate resolves date semantics and the DRC MoH/CDC/ECDC death-metric concepts are reviewed.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Detailed audit IDs and review locators are withheld from this public export.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I28"/>
 </worksheet>
 </file>
 
@@ -3855,8 +3949,66 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>European Centre for Disease Prevention and Control</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-05-26T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-05-26T22:13:28Z</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="J42"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L41"/>
+  <autoFilter ref="A1:L42"/>
 </worksheet>
 </file>
 
@@ -11225,7 +11377,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D3"/>
@@ -16362,8 +16514,141 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>source_data_report_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D125"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>source_publication_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D126"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-05-26T22:13:28Z</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>regional cross-check and source-review input; values corroborate the CDC 2026-05-25 country-pair endpoint but do not independently change the published May 25 headline tuple</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I124"/>
+  <autoFilter ref="A1:I127"/>
 </worksheet>
 </file>
 
@@ -34037,34 +34322,34 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D224"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F224">
-        <v>906</v>
-      </c>
-      <c r="G224">
-        <v>395</v>
-      </c>
-      <c r="H224">
-        <v>906</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="G224"/>
+      <c r="H224"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>count</t>
@@ -34072,37 +34357,33 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K224"/>
       <c r="L224" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -34112,7 +34393,7 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="S224"/>
@@ -34120,12 +34401,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_total</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -34133,21 +34414,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D225"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F225">
         <v>112</v>
       </c>
-      <c r="G225">
-        <v>10</v>
-      </c>
-      <c r="H225">
-        <v>112</v>
-      </c>
+      <c r="G225"/>
+      <c r="H225"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>count</t>
@@ -34155,37 +34436,33 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K225"/>
       <c r="L225" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -34195,100 +34472,819 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
-        </is>
-      </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S225"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F226">
+        <v>7</v>
+      </c>
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K226"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F227">
+        <v>906</v>
+      </c>
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K227"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F228">
+        <v>10</v>
+      </c>
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K228"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F229">
+        <v>223</v>
+      </c>
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K229"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F230">
+        <v>1</v>
+      </c>
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K230"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:http_status</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F231">
+        <v>200</v>
+      </c>
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K231"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S231"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-26-live:suspected_cases_italy</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="K232"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S232"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D233"/>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F233">
+        <v>906</v>
+      </c>
+      <c r="G233">
+        <v>395</v>
+      </c>
+      <c r="H233">
+        <v>906</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S233"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D234"/>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-05-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F234">
+        <v>112</v>
+      </c>
+      <c r="G234">
+        <v>10</v>
+      </c>
+      <c r="H234">
+        <v>112</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B235" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C235" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D226"/>
-      <c r="E226" t="inlineStr">
+      <c r="D235"/>
+      <c r="E235" t="inlineStr">
         <is>
           <t>2026-05-25T23:59:59Z</t>
         </is>
       </c>
-      <c r="F226">
+      <c r="F235">
         <v>223</v>
       </c>
-      <c r="G226">
+      <c r="G235">
         <v>106</v>
       </c>
-      <c r="H226">
+      <c r="H235">
         <v>223</v>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I235" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
+      <c r="J235" t="inlineStr">
         <is>
           <t>cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K235" t="inlineStr">
         <is>
           <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t>PUBLIC-SOURCE-AUDIT</t>
         </is>
       </c>
-      <c r="M226" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N235" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O235" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr">
+      <c r="P235" t="inlineStr">
         <is>
           <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
-      <c r="Q226" t="inlineStr">
+      <c r="Q235" t="inlineStr">
         <is>
           <t>public_bytes</t>
         </is>
       </c>
-      <c r="R226" t="inlineStr">
+      <c r="R235" t="inlineStr">
         <is>
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="S226"/>
+      <c r="S235"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S226"/>
+  <autoFilter ref="A1:S235"/>
 </worksheet>
 </file>
 
@@ -45341,7 +46337,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -45351,11 +46347,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D217">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -45364,27 +46360,27 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K217"/>
@@ -45392,7 +46388,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_total</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -45402,11 +46398,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D218">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -45415,27 +46411,27 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K218"/>
@@ -45443,7 +46439,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_confirmed_uganda</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -45453,11 +46449,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>deaths</t>
+          <t>confirmed_cases</t>
         </is>
       </c>
       <c r="D219">
-        <v>223</v>
+        <v>7</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -45466,27 +46462,27 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="K219"/>
@@ -45494,7 +46490,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_confirmed_drc</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -45508,7 +46504,7 @@
         </is>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -45545,7 +46541,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -45555,11 +46551,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>http_status</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D221">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -45596,7 +46592,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_suspected_drc</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -45606,11 +46602,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
+          <t>deaths</t>
         </is>
       </c>
       <c r="D222">
-        <v>906</v>
+        <v>223</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -45647,56 +46643,515 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>timeline:cdc-current-situation-2026-05-25:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D224">
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D225">
+        <v>223</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K225"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D226">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:http_status</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D227">
+        <v>200</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:http_status</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D228">
+        <v>200</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>timeline:cdc-current-situation-2026-05-25:cases_suspected</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D229">
+        <v>906</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>source_manifest:cdc-current-situation-2026-05-25</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>public-domain-us-gov</t>
+        </is>
+      </c>
+      <c r="K229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
           <t>timeline:cdc-current-situation-2026-05-25:cases_suspected_drc</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C230" t="inlineStr">
         <is>
           <t>suspected_cases</t>
         </is>
       </c>
-      <c r="D223">
+      <c r="D230">
         <v>906</v>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G230" t="inlineStr">
         <is>
           <t>source_manifest:cdc-current-situation-2026-05-25</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H230" t="inlineStr">
         <is>
           <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I230" t="inlineStr">
         <is>
           <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
+      <c r="J230" t="inlineStr">
         <is>
           <t>public-domain-us-gov</t>
         </is>
       </c>
-      <c r="K223"/>
+      <c r="K230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D231">
+        <v>906</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K231"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-26-live:suspected_cases_italy</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D232">
+        <v>2</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-26-live</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>d455dcaca4e5239f23951ef82dec77211ff9de963cfd6e2c12ecf7c3d8378977</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K232"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K223"/>
+  <autoFilter ref="A1:K232"/>
 </worksheet>
 </file>
 
@@ -47037,22 +48492,22 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.0861708114385285</v>
+        <v>0.09445951733436075</v>
       </c>
       <c r="F2">
-        <v>0.23315469335620254</v>
+        <v>0.24002055285686827</v>
       </c>
       <c r="G2">
-        <v>0.20028631694823662</v>
+        <v>0.21815681374976198</v>
       </c>
       <c r="H2">
-        <v>0.48234065943233195</v>
+        <v>0.49376090747255597</v>
       </c>
       <c r="I2">
-        <v>0.06427581319980569</v>
+        <v>0.06319702466996217</v>
       </c>
       <c r="J2">
-        <v>0.7474537035483133</v>
+        <v>0.719264702591034</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -47088,7 +48543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:kasese-uga</t>
+          <t>corridor:02:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -47098,29 +48553,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08768171124595683</v>
+        <v>0.08273781175301806</v>
       </c>
       <c r="F3">
-        <v>0.2275794037963691</v>
+        <v>0.2284874731887681</v>
       </c>
       <c r="G3">
-        <v>0.2035618016305265</v>
+        <v>0.1928142001378063</v>
       </c>
       <c r="H3">
-        <v>0.47295633103988544</v>
+        <v>0.4744917795152871</v>
       </c>
       <c r="I3">
-        <v>0.04459460740614488</v>
+        <v>0.06730851508774321</v>
       </c>
       <c r="J3">
-        <v>0.7478981260349676</v>
+        <v>0.7564576627228864</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -47173,22 +48628,22 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08233054224498484</v>
+        <v>0.09048464357894637</v>
       </c>
       <c r="F4">
-        <v>0.22543492066869397</v>
+        <v>0.22273556590441385</v>
       </c>
       <c r="G4">
-        <v>0.19192499609422323</v>
+        <v>0.20961712897740686</v>
       </c>
       <c r="H4">
-        <v>0.46931800011005115</v>
+        <v>0.4647202826386523</v>
       </c>
       <c r="I4">
-        <v>0.06964130796312437</v>
+        <v>0.04977612451622361</v>
       </c>
       <c r="J4">
-        <v>0.6990237917928565</v>
+        <v>0.7106528036367321</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -47224,7 +48679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:beni-cod</t>
+          <t>corridor:04:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -47234,29 +48689,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08664306873590838</v>
+        <v>0.08565218814006142</v>
       </c>
       <c r="F5">
-        <v>0.222887038238157</v>
+        <v>0.22029891605266969</v>
       </c>
       <c r="G5">
-        <v>0.20131080198240825</v>
+        <v>0.19916026506380355</v>
       </c>
       <c r="H5">
-        <v>0.4649794327839667</v>
+        <v>0.4605488463027082</v>
       </c>
       <c r="I5">
-        <v>0.05425688863966508</v>
+        <v>0.07273190347723515</v>
       </c>
       <c r="J5">
-        <v>0.7101842045533336</v>
+        <v>0.7278051232264949</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -47292,7 +48747,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:arua-uga</t>
+          <t>corridor:05:rwampara:goma-cod</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -47302,29 +48757,29 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.09176382815314144</v>
+        <v>0.08761720560139294</v>
       </c>
       <c r="F6">
-        <v>0.2196720235905948</v>
+        <v>0.21936354051325144</v>
       </c>
       <c r="G6">
-        <v>0.2123714082943657</v>
+        <v>0.20342220318959423</v>
       </c>
       <c r="H6">
-        <v>0.45947010738720273</v>
+        <v>0.4589425069655363</v>
       </c>
       <c r="I6">
-        <v>0.0602209036243418</v>
+        <v>0.06886739376279995</v>
       </c>
       <c r="J6">
-        <v>0.7146926481656625</v>
+        <v>0.743152794738482</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -47377,22 +48832,22 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08396936085735776</v>
+        <v>0.08287569990928895</v>
       </c>
       <c r="F7">
-        <v>0.2119043283318027</v>
+        <v>0.21243842944956587</v>
       </c>
       <c r="G7">
-        <v>0.19549948212877702</v>
+        <v>0.1931151059217136</v>
       </c>
       <c r="H7">
-        <v>0.44602874389977687</v>
+        <v>0.4469590270913051</v>
       </c>
       <c r="I7">
-        <v>0.056360235565877555</v>
+        <v>0.05292524916825545</v>
       </c>
       <c r="J7">
-        <v>0.7142786607680277</v>
+        <v>0.7528903131888608</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -47428,43 +48883,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:mongbwalu:nebbi-uga</t>
+          <t>corridor:07:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>rwampara</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.03855467933328152</v>
+        <v>0.0813030320518214</v>
       </c>
       <c r="F8">
-        <v>0.11620932868289471</v>
+        <v>0.2120036212731276</v>
       </c>
       <c r="G8">
-        <v>0.09291440432184914</v>
+        <v>0.18967897671798614</v>
       </c>
       <c r="H8">
-        <v>0.2639086114886541</v>
+        <v>0.44620129623757115</v>
       </c>
       <c r="I8">
-        <v>0.025175207094245807</v>
+        <v>0.05853988867330033</v>
       </c>
       <c r="J8">
-        <v>0.46361890390099453</v>
+        <v>0.721341036531536</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -47496,7 +48951,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:kampala-uga</t>
+          <t>corridor:08:bunia:goma-cod</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -47506,29 +48961,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04147908524423352</v>
+        <v>0.04260859167640518</v>
       </c>
       <c r="F9">
-        <v>0.11562806950949953</v>
+        <v>0.11766030943420233</v>
       </c>
       <c r="G9">
-        <v>0.09974219409345544</v>
+        <v>0.10237107937830753</v>
       </c>
       <c r="H9">
-        <v>0.2627072705721946</v>
+        <v>0.26690234529353574</v>
       </c>
       <c r="I9">
-        <v>0.025907663365721464</v>
+        <v>0.03562848758295974</v>
       </c>
       <c r="J9">
-        <v>0.4462554570998926</v>
+        <v>0.4539173649760259</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -47564,7 +49019,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:arua-uga</t>
+          <t>corridor:09:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -47574,29 +49029,29 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04179480816556652</v>
+        <v>0.04147908524423352</v>
       </c>
       <c r="F10">
-        <v>0.11558245421258095</v>
+        <v>0.11562806950949953</v>
       </c>
       <c r="G10">
-        <v>0.10047743392001213</v>
+        <v>0.09974219409345544</v>
       </c>
       <c r="H10">
-        <v>0.26261295488077974</v>
+        <v>0.2627072705721946</v>
       </c>
       <c r="I10">
-        <v>0.027913949480659363</v>
+        <v>0.025907663365721464</v>
       </c>
       <c r="J10">
-        <v>0.4647552683750245</v>
+        <v>0.4462554570998926</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -47632,7 +49087,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:nebbi-uga</t>
+          <t>corridor:10:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -47642,29 +49097,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.04186956091160368</v>
+        <v>0.04179480816556652</v>
       </c>
       <c r="F11">
-        <v>0.11539491748492897</v>
+        <v>0.11558245421258095</v>
       </c>
       <c r="G11">
-        <v>0.10065158442248001</v>
+        <v>0.10047743392001213</v>
       </c>
       <c r="H11">
-        <v>0.26222507759010427</v>
+        <v>0.26261295488077974</v>
       </c>
       <c r="I11">
-        <v>0.021242880051839726</v>
+        <v>0.027913949480659363</v>
       </c>
       <c r="J11">
-        <v>0.46678607844486947</v>
+        <v>0.4647552683750245</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -47700,43 +49155,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:mongbwalu:kasese-uga</t>
+          <t>corridor:11:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.04042920346327944</v>
+        <v>0.040430218691513475</v>
       </c>
       <c r="F12">
-        <v>0.11242435593909272</v>
+        <v>0.11557548317625271</v>
       </c>
       <c r="G12">
-        <v>0.09729451222456448</v>
+        <v>0.09729691190408213</v>
       </c>
       <c r="H12">
-        <v>0.2560645676658191</v>
+        <v>0.26259850203465634</v>
       </c>
       <c r="I12">
-        <v>0.027413735537554062</v>
+        <v>0.024532453328788482</v>
       </c>
       <c r="J12">
-        <v>0.43705126759089724</v>
+        <v>0.4737244474950434</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -47768,7 +49223,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:kasese-uga</t>
+          <t>corridor:12:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -47778,29 +49233,29 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.04024586283096926</v>
+        <v>0.04186956091160368</v>
       </c>
       <c r="F13">
-        <v>0.11159467152136757</v>
+        <v>0.11539491748492897</v>
       </c>
       <c r="G13">
-        <v>0.09686667859605977</v>
+        <v>0.10065158442248001</v>
       </c>
       <c r="H13">
-        <v>0.25433876336268857</v>
+        <v>0.26222507759010427</v>
       </c>
       <c r="I13">
-        <v>0.03067229187569909</v>
+        <v>0.021242880051839726</v>
       </c>
       <c r="J13">
-        <v>0.4576157180833162</v>
+        <v>0.46678607844486947</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -47836,7 +49291,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:kampala-uga</t>
+          <t>corridor:13:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -47846,29 +49301,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.04066526892293623</v>
+        <v>0.04269679620853847</v>
       </c>
       <c r="F14">
-        <v>0.11152320362817797</v>
+        <v>0.1114239910693812</v>
       </c>
       <c r="G14">
-        <v>0.09784524147753831</v>
+        <v>0.1025762389475964</v>
       </c>
       <c r="H14">
-        <v>0.254190125108517</v>
+        <v>0.25398350476377357</v>
       </c>
       <c r="I14">
-        <v>0.026605224754838577</v>
+        <v>0.024461896089849052</v>
       </c>
       <c r="J14">
-        <v>0.46394166684739413</v>
+        <v>0.42050488842189776</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -47904,7 +49359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:bunia:bundibugyo-uga</t>
+          <t>corridor:14:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -47914,7 +49369,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D15">
@@ -47972,7 +49427,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:beni-cod</t>
+          <t>corridor:15:mongbwalu:goma-cod</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -47982,29 +49437,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.03750471405393857</v>
+        <v>0.03967055365389441</v>
       </c>
       <c r="F16">
-        <v>0.10749948779872281</v>
+        <v>0.11037528493444154</v>
       </c>
       <c r="G16">
-        <v>0.09045541125798737</v>
+        <v>0.09552333993090975</v>
       </c>
       <c r="H16">
-        <v>0.24578444055142545</v>
+        <v>0.2517977687861897</v>
       </c>
       <c r="I16">
-        <v>0.027237694409312466</v>
+        <v>0.02246092821507834</v>
       </c>
       <c r="J16">
-        <v>0.4271444488438072</v>
+        <v>0.4355790666314244</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -48040,43 +49495,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:bunia:beni-cod</t>
+          <t>corridor:16:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.04228950663900796</v>
+        <v>0.036893545042157305</v>
       </c>
       <c r="F17">
-        <v>0.10704031678368539</v>
+        <v>0.10867014828748978</v>
       </c>
       <c r="G17">
-        <v>0.10162893993380431</v>
+        <v>0.08902229938514877</v>
       </c>
       <c r="H17">
-        <v>0.24482175888282368</v>
+        <v>0.2482358877081989</v>
       </c>
       <c r="I17">
-        <v>0.026598690800271954</v>
+        <v>0.020695892757526077</v>
       </c>
       <c r="J17">
-        <v>0.4232379895804849</v>
+        <v>0.4289255637849178</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -48108,7 +49563,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:arua-uga</t>
+          <t>corridor:17:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -48118,29 +49573,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.03798452079077774</v>
+        <v>0.038935353978377885</v>
       </c>
       <c r="F18">
-        <v>0.1055578744412985</v>
+        <v>0.10835196082870574</v>
       </c>
       <c r="G18">
-        <v>0.09157962059775004</v>
+        <v>0.09380493517661201</v>
       </c>
       <c r="H18">
-        <v>0.24170839592150667</v>
+        <v>0.2475701272178043</v>
       </c>
       <c r="I18">
-        <v>0.0239669463086208</v>
+        <v>0.021267428986718424</v>
       </c>
       <c r="J18">
-        <v>0.4664322846035496</v>
+        <v>0.43910667718208657</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -48176,12 +49631,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:18:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -48193,26 +49648,26 @@
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.03778298943272401</v>
+        <v>0.04228950663900796</v>
       </c>
       <c r="F19">
-        <v>0.10384450964700326</v>
+        <v>0.10704031678368539</v>
       </c>
       <c r="G19">
-        <v>0.09110754488962608</v>
+        <v>0.10162893993380431</v>
       </c>
       <c r="H19">
-        <v>0.23810062900458037</v>
+        <v>0.24482175888282368</v>
       </c>
       <c r="I19">
-        <v>0.027747327225511372</v>
+        <v>0.026598690800271954</v>
       </c>
       <c r="J19">
-        <v>0.39188625277934763</v>
+        <v>0.4232379895804849</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -48244,43 +49699,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:nyankunde:kasese-uga</t>
+          <t>corridor:19:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.031304381068294335</v>
+        <v>0.035432678170503384</v>
       </c>
       <c r="F20">
-        <v>0.08779786212598711</v>
+        <v>0.10593636188070824</v>
       </c>
       <c r="G20">
-        <v>0.07585358277896675</v>
+        <v>0.08559121466787023</v>
       </c>
       <c r="H20">
-        <v>0.2038133127969261</v>
+        <v>0.24250404576809376</v>
       </c>
       <c r="I20">
-        <v>0.017690770792813504</v>
+        <v>0.027309488663839657</v>
       </c>
       <c r="J20">
-        <v>0.3619871650097016</v>
+        <v>0.4555467010005905</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -48312,43 +49767,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:nyankunde:beni-cod</t>
+          <t>corridor:20:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03171837340940942</v>
+        <v>0.03763199658508454</v>
       </c>
       <c r="F21">
-        <v>0.08476753807336304</v>
+        <v>0.10128422532010978</v>
       </c>
       <c r="G21">
-        <v>0.07683287603147732</v>
+        <v>0.09075375258925547</v>
       </c>
       <c r="H21">
-        <v>0.19723709872212672</v>
+        <v>0.23269034583576234</v>
       </c>
       <c r="I21">
-        <v>0.0227792144919888</v>
+        <v>0.019116090021161606</v>
       </c>
       <c r="J21">
-        <v>0.3495642294984912</v>
+        <v>0.4602236579125214</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -48380,43 +49835,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:nyankunde:kampala-uga</t>
+          <t>corridor:21:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nyankunde</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.030540418665822744</v>
+        <v>0.038843460236694466</v>
       </c>
       <c r="F22">
-        <v>0.08438962198493272</v>
+        <v>0.10070243265367404</v>
       </c>
       <c r="G22">
-        <v>0.07404478785217791</v>
+        <v>0.0935899840239344</v>
       </c>
       <c r="H22">
-        <v>0.19641470100450442</v>
+        <v>0.23145773577863957</v>
       </c>
       <c r="I22">
-        <v>0.019203507671592176</v>
+        <v>0.025371459529098615</v>
       </c>
       <c r="J22">
-        <v>0.3838230566411262</v>
+        <v>0.4729197264386862</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -48448,7 +49903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>corridor:22:nyankunde:bundibugyo-uga</t>
+          <t>corridor:22:nyankunde:beni-cod</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -48458,29 +49913,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D23">
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.030399316276041116</v>
+        <v>0.03146929822468722</v>
       </c>
       <c r="F23">
-        <v>0.08407821789447709</v>
+        <v>0.08989853663383654</v>
       </c>
       <c r="G23">
-        <v>0.07371053738981273</v>
+        <v>0.07624375486519391</v>
       </c>
       <c r="H23">
-        <v>0.19573661412777732</v>
+        <v>0.20835308906693198</v>
       </c>
       <c r="I23">
-        <v>0.021457583298788</v>
+        <v>0.023297869762629386</v>
       </c>
       <c r="J23">
-        <v>0.358453978352833</v>
+        <v>0.3863428563442163</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -48516,7 +49971,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:nebbi-uga</t>
+          <t>corridor:23:nyankunde:goma-cod</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -48526,29 +49981,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.030329334773183142</v>
+        <v>0.032748675469615296</v>
       </c>
       <c r="F24">
-        <v>0.08357711531060097</v>
+        <v>0.08856563497530315</v>
       </c>
       <c r="G24">
-        <v>0.07354468946695608</v>
+        <v>0.07926732761392977</v>
       </c>
       <c r="H24">
-        <v>0.19464486287655744</v>
+        <v>0.2054744022745903</v>
       </c>
       <c r="I24">
-        <v>0.014570952055622657</v>
+        <v>0.020503468439890822</v>
       </c>
       <c r="J24">
-        <v>0.32281669746439295</v>
+        <v>0.34571427438684454</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -48584,7 +50039,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:arua-uga</t>
+          <t>corridor:24:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -48594,29 +50049,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.028578262502321705</v>
+        <v>0.030026997527813626</v>
       </c>
       <c r="F25">
-        <v>0.0757669915923353</v>
+        <v>0.08665812766707617</v>
       </c>
       <c r="G25">
-        <v>0.06938957908843438</v>
+        <v>0.07282808208366084</v>
       </c>
       <c r="H25">
-        <v>0.17751379634539563</v>
+        <v>0.2013434496623271</v>
       </c>
       <c r="I25">
-        <v>0.021112935786516</v>
+        <v>0.025288863375360248</v>
       </c>
       <c r="J25">
-        <v>0.3190059046148159</v>
+        <v>0.34693271100874334</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -48652,43 +50107,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:katwa:bundibugyo-uga</t>
+          <t>corridor:25:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.006127400208913586</v>
+        <v>0.03075884987706151</v>
       </c>
       <c r="F26">
-        <v>0.0168408512437718</v>
+        <v>0.08599999997606922</v>
       </c>
       <c r="G26">
-        <v>0.015128788346279537</v>
+        <v>0.07456220134186478</v>
       </c>
       <c r="H26">
-        <v>0.04125072266262608</v>
+        <v>0.19991563107642202</v>
       </c>
       <c r="I26">
-        <v>0.004388490481047946</v>
+        <v>0.023982280525205277</v>
       </c>
       <c r="J26">
-        <v>0.08183093712788367</v>
+        <v>0.3479361411653973</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -48720,43 +50175,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:katwa:kasese-uga</t>
+          <t>corridor:26:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.00556423388622837</v>
+        <v>0.03164694763292836</v>
       </c>
       <c r="F27">
-        <v>0.01656759676464939</v>
+        <v>0.08559300950103177</v>
       </c>
       <c r="G27">
-        <v>0.013744050643107991</v>
+        <v>0.07666392163091817</v>
       </c>
       <c r="H27">
-        <v>0.04058965567523373</v>
+        <v>0.19903170204824353</v>
       </c>
       <c r="I27">
-        <v>0.003889156206565628</v>
+        <v>0.01960014940850209</v>
       </c>
       <c r="J27">
-        <v>0.08557353521823044</v>
+        <v>0.35567826316219087</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -48788,43 +50243,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:katwa:kampala-uga</t>
+          <t>corridor:27:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.00571138519466724</v>
+        <v>0.03415616913117603</v>
       </c>
       <c r="F28">
-        <v>0.016458424878468436</v>
+        <v>0.0843769399835359</v>
       </c>
       <c r="G28">
-        <v>0.014105980367321913</v>
+        <v>0.0825868002754413</v>
       </c>
       <c r="H28">
-        <v>0.04032548046029999</v>
+        <v>0.1963870895325143</v>
       </c>
       <c r="I28">
-        <v>0.0032961116192571803</v>
+        <v>0.023187377364693004</v>
       </c>
       <c r="J28">
-        <v>0.08227064654779426</v>
+        <v>0.3421266345564783</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -48856,43 +50311,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:katwa:beni-cod</t>
+          <t>corridor:28:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>katwa</t>
+          <t>nyankunde</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.005665299126924983</v>
+        <v>0.03357687364916134</v>
       </c>
       <c r="F29">
-        <v>0.016137547052658407</v>
+        <v>0.08425270479805413</v>
       </c>
       <c r="G29">
-        <v>0.01399263950136656</v>
+        <v>0.08122145623779894</v>
       </c>
       <c r="H29">
-        <v>0.039548733878884995</v>
+        <v>0.196116146145421</v>
       </c>
       <c r="I29">
-        <v>0.0033705192295240497</v>
+        <v>0.02179834248652243</v>
       </c>
       <c r="J29">
-        <v>0.0787241376496719</v>
+        <v>0.35919822012550795</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -48924,7 +50379,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:arua-uga</t>
+          <t>corridor:29:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -48934,29 +50389,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.005760920437457601</v>
+        <v>0.005665299126924983</v>
       </c>
       <c r="F30">
-        <v>0.01564371888735397</v>
+        <v>0.016137547052658407</v>
       </c>
       <c r="G30">
-        <v>0.014227802835785092</v>
+        <v>0.01399263950136656</v>
       </c>
       <c r="H30">
-        <v>0.03835261291771347</v>
+        <v>0.039548733878884995</v>
       </c>
       <c r="I30">
-        <v>0.004405736887256273</v>
+        <v>0.0033705192295240497</v>
       </c>
       <c r="J30">
-        <v>0.07717071840257644</v>
+        <v>0.0787241376496719</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -48992,7 +50447,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:nebbi-uga</t>
+          <t>corridor:30:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -49002,29 +50457,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005519371147358398</v>
+        <v>0.005408064245022548</v>
       </c>
       <c r="F31">
-        <v>0.01552589721826908</v>
+        <v>0.016075387130097485</v>
       </c>
       <c r="G31">
-        <v>0.013633690221780848</v>
+        <v>0.013359846492850574</v>
       </c>
       <c r="H31">
-        <v>0.03806709980880993</v>
+        <v>0.039398229649427796</v>
       </c>
       <c r="I31">
-        <v>0.003119740043250069</v>
+        <v>0.0037862601247234534</v>
       </c>
       <c r="J31">
-        <v>0.07892668631060598</v>
+        <v>0.07544870631338906</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -49060,43 +50515,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:goma-cod:kasese-uga</t>
+          <t>corridor:31:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.002911020622911431</v>
+        <v>0.005760920437457601</v>
       </c>
       <c r="F32">
-        <v>0.008708366339810258</v>
+        <v>0.01564371888735397</v>
       </c>
       <c r="G32">
-        <v>0.007204585754623377</v>
+        <v>0.014227802835785092</v>
       </c>
       <c r="H32">
-        <v>0.021460131514392883</v>
+        <v>0.03835261291771347</v>
       </c>
       <c r="I32">
-        <v>0.002213739571223128</v>
+        <v>0.004405736887256273</v>
       </c>
       <c r="J32">
-        <v>0.04056094344785632</v>
+        <v>0.07717071840257644</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -49128,43 +50583,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:butembo:nebbi-uga</t>
+          <t>corridor:32:katwa:goma-cod</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.0027769798502101373</v>
+        <v>0.006169920398082257</v>
       </c>
       <c r="F33">
-        <v>0.008633599440103473</v>
+        <v>0.01553498621898089</v>
       </c>
       <c r="G33">
-        <v>0.006873526257886398</v>
+        <v>0.01523329162375131</v>
       </c>
       <c r="H33">
-        <v>0.021277062424142124</v>
+        <v>0.03808912674070569</v>
       </c>
       <c r="I33">
-        <v>0.0016525413787399719</v>
+        <v>0.003357225433652031</v>
       </c>
       <c r="J33">
-        <v>0.03899275669757771</v>
+        <v>0.06777077505091869</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -49196,43 +50651,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>corridor:33:miti-murhesa:kasese-uga</t>
+          <t>corridor:33:katwa:nebbi-uga</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D34">
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.0029900129594525315</v>
+        <v>0.005252367922210843</v>
       </c>
       <c r="F34">
-        <v>0.00847697711451803</v>
+        <v>0.015529432038009494</v>
       </c>
       <c r="G34">
-        <v>0.007399652921270428</v>
+        <v>0.012976721133270863</v>
       </c>
       <c r="H34">
-        <v>0.020893505827646625</v>
+        <v>0.038075666248175294</v>
       </c>
       <c r="I34">
-        <v>0.0017305897295624153</v>
+        <v>0.002718444578993254</v>
       </c>
       <c r="J34">
-        <v>0.04136198023793251</v>
+        <v>0.07153399444934289</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -49264,43 +50719,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>corridor:34:butembo:arua-uga</t>
+          <t>corridor:34:katwa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D35">
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.003004206625567968</v>
+        <v>0.005519371147358398</v>
       </c>
       <c r="F35">
-        <v>0.008424640775256842</v>
+        <v>0.01552589721826908</v>
       </c>
       <c r="G35">
-        <v>0.007434701480319217</v>
+        <v>0.013633690221780848</v>
       </c>
       <c r="H35">
-        <v>0.02076531908923876</v>
+        <v>0.03806709980880993</v>
       </c>
       <c r="I35">
-        <v>0.0014445621581179958</v>
+        <v>0.003119740043250069</v>
       </c>
       <c r="J35">
-        <v>0.03973256156228256</v>
+        <v>0.07892668631060598</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -49332,43 +50787,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:nizi:bundibugyo-uga</t>
+          <t>corridor:35:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>katwa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.003111941625778658</v>
+        <v>0.005719038632820889</v>
       </c>
       <c r="F36">
-        <v>0.008402719753006271</v>
+        <v>0.01443774068944173</v>
       </c>
       <c r="G36">
-        <v>0.0077007053534820236</v>
+        <v>0.014124805074243657</v>
       </c>
       <c r="H36">
-        <v>0.020711624541566498</v>
+        <v>0.03542780468093812</v>
       </c>
       <c r="I36">
-        <v>0.0017674417542844795</v>
+        <v>0.0037666445426507516</v>
       </c>
       <c r="J36">
-        <v>0.038221794937289805</v>
+        <v>0.07911590609890654</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -49400,39 +50855,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:butembo:kampala-uga</t>
+          <t>corridor:36:miti-murhesa:goma-cod</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.002898657102272467</v>
+        <v>0.002804459043458968</v>
       </c>
       <c r="F37">
-        <v>0.00831048662323794</v>
+        <v>0.00878511499370449</v>
       </c>
       <c r="G37">
-        <v>0.0071740522491085534</v>
+        <v>0.0069414009149691425</v>
       </c>
       <c r="H37">
-        <v>0.020485685215592936</v>
+        <v>0.021648029980746247</v>
       </c>
       <c r="I37">
-        <v>0.0024156585156788397</v>
+        <v>0.0018195961747441535</v>
       </c>
       <c r="J37">
-        <v>0.03953263154110449</v>
+        <v>0.04351969089202276</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -49468,12 +50923,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>corridor:37:goma-cod:arua-uga</t>
+          <t>corridor:37:butembo:arua-uga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49485,22 +50940,22 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.0027125515817747747</v>
+        <v>0.002911020622911431</v>
       </c>
       <c r="F38">
-        <v>0.008284511161890662</v>
+        <v>0.008708366339810258</v>
       </c>
       <c r="G38">
-        <v>0.006714374614320118</v>
+        <v>0.007204585754623377</v>
       </c>
       <c r="H38">
-        <v>0.020422048400997733</v>
+        <v>0.021460131514392883</v>
       </c>
       <c r="I38">
-        <v>0.0015261556624343033</v>
+        <v>0.002213739571223128</v>
       </c>
       <c r="J38">
-        <v>0.04121550107288618</v>
+        <v>0.04056094344785632</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -49536,39 +50991,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:nizi:nebbi-uga</t>
+          <t>corridor:38:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.002681493416460179</v>
+        <v>0.0027769798502101373</v>
       </c>
       <c r="F39">
-        <v>0.008183525990654555</v>
+        <v>0.008633599440103473</v>
       </c>
       <c r="G39">
-        <v>0.0066376497183083805</v>
+        <v>0.006873526257886398</v>
       </c>
       <c r="H39">
-        <v>0.020174624300513644</v>
+        <v>0.021277062424142124</v>
       </c>
       <c r="I39">
-        <v>0.0014926750968995012</v>
+        <v>0.0016525413787399719</v>
       </c>
       <c r="J39">
-        <v>0.039228799255843605</v>
+        <v>0.03899275669757771</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -49604,39 +51059,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:nizi:beni-cod</t>
+          <t>corridor:39:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.0028326663994584778</v>
+        <v>0.002943458801597104</v>
       </c>
       <c r="F40">
-        <v>0.00815823939873217</v>
+        <v>0.00848250804610165</v>
       </c>
       <c r="G40">
-        <v>0.00701107122667835</v>
+        <v>0.00728469284319036</v>
       </c>
       <c r="H40">
-        <v>0.020112663896618338</v>
+        <v>0.020907051259871884</v>
       </c>
       <c r="I40">
-        <v>0.0015343125999103453</v>
+        <v>0.0019834988729835134</v>
       </c>
       <c r="J40">
-        <v>0.04046059631457021</v>
+        <v>0.04021049895847632</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -49672,39 +51127,39 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:butembo:kasese-uga</t>
+          <t>corridor:40:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.002747567807505402</v>
+        <v>0.0029900129594525315</v>
       </c>
       <c r="F41">
-        <v>0.008154445449094133</v>
+        <v>0.00847697711451803</v>
       </c>
       <c r="G41">
-        <v>0.006800874406568735</v>
+        <v>0.007399652921270428</v>
       </c>
       <c r="H41">
-        <v>0.020103367023304758</v>
+        <v>0.020893505827646625</v>
       </c>
       <c r="I41">
-        <v>0.0016545850906405566</v>
+        <v>0.0017305897295624153</v>
       </c>
       <c r="J41">
-        <v>0.04190231971566359</v>
+        <v>0.04136198023793251</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -49740,39 +51195,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:bambu:arua-uga</t>
+          <t>corridor:41:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0029994938796520376</v>
+        <v>0.0030684076719234843</v>
       </c>
       <c r="F42">
-        <v>0.008147226747461322</v>
+        <v>0.008456179104640776</v>
       </c>
       <c r="G42">
-        <v>0.007423064501010185</v>
+        <v>0.007593222717078629</v>
       </c>
       <c r="H42">
-        <v>0.020085678474308588</v>
+        <v>0.02084256764572595</v>
       </c>
       <c r="I42">
-        <v>0.0019885435545158206</v>
+        <v>0.002196657973502822</v>
       </c>
       <c r="J42">
-        <v>0.03889536735459872</v>
+        <v>0.041788827485054</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -49808,39 +51263,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:miti-murhesa:nebbi-uga</t>
+          <t>corridor:42:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.003061304197971737</v>
+        <v>0.003004206625567968</v>
       </c>
       <c r="F43">
-        <v>0.00814381727681368</v>
+        <v>0.008424640775256842</v>
       </c>
       <c r="G43">
-        <v>0.00757568403154249</v>
+        <v>0.007434701480319217</v>
       </c>
       <c r="H43">
-        <v>0.020077321716829383</v>
+        <v>0.02076531908923876</v>
       </c>
       <c r="I43">
-        <v>0.0016647585017794454</v>
+        <v>0.0014445621581179958</v>
       </c>
       <c r="J43">
-        <v>0.03886426325038798</v>
+        <v>0.03973256156228256</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -49876,39 +51331,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:goma-cod:nebbi-uga</t>
+          <t>corridor:43:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.0031340416283216765</v>
+        <v>0.002960980933083057</v>
       </c>
       <c r="F44">
-        <v>0.008075152624742232</v>
+        <v>0.008410627383326874</v>
       </c>
       <c r="G44">
-        <v>0.00775526629452003</v>
+        <v>0.007327962889187772</v>
       </c>
       <c r="H44">
-        <v>0.01990905693022571</v>
+        <v>0.02073099435361825</v>
       </c>
       <c r="I44">
-        <v>0.002243955437822981</v>
+        <v>0.0019244758288322094</v>
       </c>
       <c r="J44">
-        <v>0.03925743592923069</v>
+        <v>0.04355962661351945</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -49944,39 +51399,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:kilo:kasese-uga</t>
+          <t>corridor:44:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.0027076980614253177</v>
+        <v>0.0027859978355153636</v>
       </c>
       <c r="F45">
-        <v>0.008070258181662043</v>
+        <v>0.008318397055267795</v>
       </c>
       <c r="G45">
-        <v>0.006702384988596155</v>
+        <v>0.006895801362401172</v>
       </c>
       <c r="H45">
-        <v>0.019897061858827808</v>
+        <v>0.020505061460188434</v>
       </c>
       <c r="I45">
-        <v>0.0018949255081115225</v>
+        <v>0.0019464730520260044</v>
       </c>
       <c r="J45">
-        <v>0.03846409821761752</v>
+        <v>0.0437435227905687</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -50012,12 +51467,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:bambu:nebbi-uga</t>
+          <t>corridor:45:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -50029,22 +51484,22 @@
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.0029941551171358827</v>
+        <v>0.002955828840965319</v>
       </c>
       <c r="F46">
-        <v>0.008062710206497403</v>
+        <v>0.008295276156943115</v>
       </c>
       <c r="G46">
-        <v>0.007409881598903129</v>
+        <v>0.00731524012555157</v>
       </c>
       <c r="H46">
-        <v>0.019878564189878323</v>
+        <v>0.020448421900859687</v>
       </c>
       <c r="I46">
-        <v>0.0023605934928140225</v>
+        <v>0.0014705155925033963</v>
       </c>
       <c r="J46">
-        <v>0.03849962672911588</v>
+        <v>0.04349024336692712</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -50080,7 +51535,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:goma-cod:bundibugyo-uga</t>
+          <t>corridor:46:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -50090,29 +51545,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.002966610048958429</v>
+        <v>0.0027125515817747747</v>
       </c>
       <c r="F47">
-        <v>0.008058011311337127</v>
+        <v>0.008284511161890662</v>
       </c>
       <c r="G47">
-        <v>0.007341863257414205</v>
+        <v>0.006714374614320118</v>
       </c>
       <c r="H47">
-        <v>0.01986704842779069</v>
+        <v>0.020422048400997733</v>
       </c>
       <c r="I47">
-        <v>0.00193425911064469</v>
+        <v>0.0015261556624343033</v>
       </c>
       <c r="J47">
-        <v>0.03944581553096073</v>
+        <v>0.04121550107288618</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -50148,39 +51603,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:miti-murhesa:beni-cod</t>
+          <t>corridor:47:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002837150359859514</v>
+        <v>0.002859782073699718</v>
       </c>
       <c r="F48">
-        <v>0.008035393220128945</v>
+        <v>0.008263354150150004</v>
       </c>
       <c r="G48">
-        <v>0.007022145861493551</v>
+        <v>0.0070780413459651526</v>
       </c>
       <c r="H48">
-        <v>0.019811615320896397</v>
+        <v>0.02037021424485949</v>
       </c>
       <c r="I48">
-        <v>0.0016272804773103918</v>
+        <v>0.001649416108444149</v>
       </c>
       <c r="J48">
-        <v>0.0417257099987222</v>
+        <v>0.042018168525404104</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -50216,7 +51671,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:bambu:bundibugyo-uga</t>
+          <t>corridor:48:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -50226,29 +51681,29 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.0027221893165624844</v>
+        <v>0.0029994938796520376</v>
       </c>
       <c r="F49">
-        <v>0.008025112676473323</v>
+        <v>0.008147226747461322</v>
       </c>
       <c r="G49">
-        <v>0.006738183364620509</v>
+        <v>0.007423064501010185</v>
       </c>
       <c r="H49">
-        <v>0.019786420160049306</v>
+        <v>0.020085678474308588</v>
       </c>
       <c r="I49">
-        <v>0.0018923716266919608</v>
+        <v>0.0019885435545158206</v>
       </c>
       <c r="J49">
-        <v>0.04067091464985655</v>
+        <v>0.03889536735459872</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -50284,39 +51739,39 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:butembo:beni-cod</t>
+          <t>corridor:49:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D50">
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.0029779299971779694</v>
+        <v>0.003061304197971737</v>
       </c>
       <c r="F50">
-        <v>0.007993848855793961</v>
+        <v>0.00814381727681368</v>
       </c>
       <c r="G50">
-        <v>0.007369816645196731</v>
+        <v>0.00757568403154249</v>
       </c>
       <c r="H50">
-        <v>0.019709793462212938</v>
+        <v>0.020077321716829383</v>
       </c>
       <c r="I50">
-        <v>0.00181708380560561</v>
+        <v>0.0016647585017794454</v>
       </c>
       <c r="J50">
-        <v>0.03931941479325931</v>
+        <v>0.03886426325038798</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -50352,12 +51807,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:nizi:arua-uga</t>
+          <t>corridor:50:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -50369,22 +51824,22 @@
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002573515092590184</v>
+        <v>0.002726713106049522</v>
       </c>
       <c r="F51">
-        <v>0.007966550348283807</v>
+        <v>0.008090540628411913</v>
       </c>
       <c r="G51">
-        <v>0.006370874666990878</v>
+        <v>0.00674935818047237</v>
       </c>
       <c r="H51">
-        <v>0.01964288498845579</v>
+        <v>0.019946766455073678</v>
       </c>
       <c r="I51">
-        <v>0.0019758723489192026</v>
+        <v>0.001970594123010397</v>
       </c>
       <c r="J51">
-        <v>0.042497226842963434</v>
+        <v>0.0390130390539575</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -50420,39 +51875,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:bambu:kasese-uga</t>
+          <t>corridor:51:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.00270874962073242</v>
+        <v>0.0031340416283216765</v>
       </c>
       <c r="F52">
-        <v>0.007945705918331214</v>
+        <v>0.008075152624742232</v>
       </c>
       <c r="G52">
-        <v>0.006704981285868744</v>
+        <v>0.00775526629452003</v>
       </c>
       <c r="H52">
-        <v>0.019591793108546057</v>
+        <v>0.01990905693022571</v>
       </c>
       <c r="I52">
-        <v>0.0017099558870529636</v>
+        <v>0.002243955437822981</v>
       </c>
       <c r="J52">
-        <v>0.040311579752921115</v>
+        <v>0.03925743592923069</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -50488,39 +51943,39 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:goma-cod:kampala-uga</t>
+          <t>corridor:52:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.002937977495464733</v>
+        <v>0.0029941551171358827</v>
       </c>
       <c r="F53">
-        <v>0.00791077263458917</v>
+        <v>0.008062710206497403</v>
       </c>
       <c r="G53">
-        <v>0.007271156988672728</v>
+        <v>0.007409881598903129</v>
       </c>
       <c r="H53">
-        <v>0.019506162869570853</v>
+        <v>0.019878564189878323</v>
       </c>
       <c r="I53">
-        <v>0.0015259490592032937</v>
+        <v>0.0023605934928140225</v>
       </c>
       <c r="J53">
-        <v>0.04355956758414158</v>
+        <v>0.03849962672911588</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -50556,39 +52011,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:kilo:nebbi-uga</t>
+          <t>corridor:53:butembo:goma-cod</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.0025676185126164985</v>
+        <v>0.002966610048958429</v>
       </c>
       <c r="F54">
-        <v>0.007868621059145403</v>
+        <v>0.008058011311337127</v>
       </c>
       <c r="G54">
-        <v>0.0063563051772850265</v>
+        <v>0.007341863257414205</v>
       </c>
       <c r="H54">
-        <v>0.01940283456752373</v>
+        <v>0.01986704842779069</v>
       </c>
       <c r="I54">
-        <v>0.0016564750458324922</v>
+        <v>0.00193425911064469</v>
       </c>
       <c r="J54">
-        <v>0.03677402473147005</v>
+        <v>0.03944581553096073</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -50624,39 +52079,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:miti-murhesa:arua-uga</t>
+          <t>corridor:54:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.0027868684736187532</v>
+        <v>0.002837150359859514</v>
       </c>
       <c r="F55">
-        <v>0.007841801348761585</v>
+        <v>0.008035393220128945</v>
       </c>
       <c r="G55">
-        <v>0.00689795184472039</v>
+        <v>0.007022145861493551</v>
       </c>
       <c r="H55">
-        <v>0.019337083521810405</v>
+        <v>0.019811615320896397</v>
       </c>
       <c r="I55">
-        <v>0.0017127846529912062</v>
+        <v>0.0016272804773103918</v>
       </c>
       <c r="J55">
-        <v>0.03838966632456429</v>
+        <v>0.0417257099987222</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -50692,7 +52147,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:bambu:kampala-uga</t>
+          <t>corridor:55:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -50702,29 +52157,29 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.002695763743499391</v>
+        <v>0.0027221893165624844</v>
       </c>
       <c r="F56">
-        <v>0.007827990157414616</v>
+        <v>0.008025112676473323</v>
       </c>
       <c r="G56">
-        <v>0.006672903334783625</v>
+        <v>0.006738183364620509</v>
       </c>
       <c r="H56">
-        <v>0.0193032265603717</v>
+        <v>0.019786420160049306</v>
       </c>
       <c r="I56">
-        <v>0.0021490354133257674</v>
+        <v>0.0018923716266919608</v>
       </c>
       <c r="J56">
-        <v>0.04054210634480244</v>
+        <v>0.04067091464985655</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -50760,39 +52215,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:kilo:beni-cod</t>
+          <t>corridor:56:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.003089733434463643</v>
+        <v>0.0029259199934389135</v>
       </c>
       <c r="F57">
-        <v>0.007797896708572921</v>
+        <v>0.008020137561744467</v>
       </c>
       <c r="G57">
-        <v>0.007645875573836641</v>
+        <v>0.007241380772000483</v>
       </c>
       <c r="H57">
-        <v>0.019229449244770908</v>
+        <v>0.019774226740906592</v>
       </c>
       <c r="I57">
-        <v>0.0016800255774773844</v>
+        <v>0.0020925966217400726</v>
       </c>
       <c r="J57">
-        <v>0.034479825340189424</v>
+        <v>0.03834918307680624</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -50828,39 +52283,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:kilo:bundibugyo-uga</t>
+          <t>corridor:57:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.002629641493342244</v>
+        <v>0.0029779299971779694</v>
       </c>
       <c r="F58">
-        <v>0.0077950978062735765</v>
+        <v>0.007993848855793961</v>
       </c>
       <c r="G58">
-        <v>0.006509547825961637</v>
+        <v>0.007369816645196731</v>
       </c>
       <c r="H58">
-        <v>0.019222587126321078</v>
+        <v>0.019709793462212938</v>
       </c>
       <c r="I58">
-        <v>0.0013601473368735656</v>
+        <v>0.00181708380560561</v>
       </c>
       <c r="J58">
-        <v>0.03643059423991454</v>
+        <v>0.03931941479325931</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -50896,39 +52351,39 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:kilo:arua-uga</t>
+          <t>corridor:58:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0028404048325195996</v>
+        <v>0.0028157111278240277</v>
       </c>
       <c r="F59">
-        <v>0.007786957767991598</v>
+        <v>0.007982907485630852</v>
       </c>
       <c r="G59">
-        <v>0.007030184083863106</v>
+        <v>0.00696919271112631</v>
       </c>
       <c r="H59">
-        <v>0.019202630017290306</v>
+        <v>0.01968297753862283</v>
       </c>
       <c r="I59">
-        <v>0.0018407478578635922</v>
+        <v>0.0017612060420275717</v>
       </c>
       <c r="J59">
-        <v>0.041169590401536636</v>
+        <v>0.04306536711443636</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -50964,39 +52419,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:bambu:beni-cod</t>
+          <t>corridor:59:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.0030164649861187665</v>
+        <v>0.0028025163740137693</v>
       </c>
       <c r="F60">
-        <v>0.007772299321732512</v>
+        <v>0.007952241687691819</v>
       </c>
       <c r="G60">
-        <v>0.0074649703248304</v>
+        <v>0.006936602546891185</v>
       </c>
       <c r="H60">
-        <v>0.01916669022271858</v>
+        <v>0.019607812760897347</v>
       </c>
       <c r="I60">
-        <v>0.0017745338814096486</v>
+        <v>0.0019699792558314196</v>
       </c>
       <c r="J60">
-        <v>0.04144693368617039</v>
+        <v>0.03954925963547096</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -51032,39 +52487,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:miti-murhesa:kampala-uga</t>
+          <t>corridor:60:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.002780055599183956</v>
+        <v>0.00270874962073242</v>
       </c>
       <c r="F61">
-        <v>0.0077543800748747505</v>
+        <v>0.007945705918331214</v>
       </c>
       <c r="G61">
-        <v>0.006881123372275866</v>
+        <v>0.006704981285868744</v>
       </c>
       <c r="H61">
-        <v>0.01912275597116167</v>
+        <v>0.019591793108546057</v>
       </c>
       <c r="I61">
-        <v>0.001731233807528232</v>
+        <v>0.0017099558870529636</v>
       </c>
       <c r="J61">
-        <v>0.03818702256228324</v>
+        <v>0.040311579752921115</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -51100,39 +52555,39 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:goma-cod:beni-cod</t>
+          <t>corridor:61:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0026587921388565305</v>
+        <v>0.0027622307839203497</v>
       </c>
       <c r="F62">
-        <v>0.007745510300115388</v>
+        <v>0.007936559977572588</v>
       </c>
       <c r="G62">
-        <v>0.006581566727665494</v>
+        <v>0.0068370944013670665</v>
       </c>
       <c r="H62">
-        <v>0.0191010070867213</v>
+        <v>0.019569374185153948</v>
       </c>
       <c r="I62">
-        <v>0.0015209453885095762</v>
+        <v>0.0017312928849019195</v>
       </c>
       <c r="J62">
-        <v>0.040091153412378705</v>
+        <v>0.043878198155480545</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -51168,39 +52623,39 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:nizi:kampala-uga</t>
+          <t>corridor:62:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.0027361329624540076</v>
+        <v>0.002937977495464733</v>
       </c>
       <c r="F63">
-        <v>0.0075987291180549255</v>
+        <v>0.00791077263458917</v>
       </c>
       <c r="G63">
-        <v>0.006772627856763858</v>
+        <v>0.007271156988672728</v>
       </c>
       <c r="H63">
-        <v>0.018741077563372677</v>
+        <v>0.019506162869570853</v>
       </c>
       <c r="I63">
-        <v>0.0013777102458249037</v>
+        <v>0.0015259490592032937</v>
       </c>
       <c r="J63">
-        <v>0.043087769872402426</v>
+        <v>0.04355956758414158</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -51236,7 +52691,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:nizi:kasese-uga</t>
+          <t>corridor:63:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -51246,29 +52701,29 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0028258568215484003</v>
+        <v>0.0027959740199166583</v>
       </c>
       <c r="F64">
-        <v>0.007552854340310916</v>
+        <v>0.007902911626123776</v>
       </c>
       <c r="G64">
-        <v>0.006994252131591605</v>
+        <v>0.006920442727769538</v>
       </c>
       <c r="H64">
-        <v>0.018628569089331942</v>
+        <v>0.019486894130341964</v>
       </c>
       <c r="I64">
-        <v>0.0018339497806420303</v>
+        <v>0.0013335076635186461</v>
       </c>
       <c r="J64">
-        <v>0.0447125896493108</v>
+        <v>0.03481721986752081</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -51304,39 +52759,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:butembo:bundibugyo-uga</t>
+          <t>corridor:64:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D65">
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.002862546240653324</v>
+        <v>0.0025676185126164985</v>
       </c>
       <c r="F65">
-        <v>0.0075168412354912895</v>
+        <v>0.007868621059145403</v>
       </c>
       <c r="G65">
-        <v>0.007084869280098771</v>
+        <v>0.0063563051772850265</v>
       </c>
       <c r="H65">
-        <v>0.0185402409724002</v>
+        <v>0.01940283456752373</v>
       </c>
       <c r="I65">
-        <v>0.0017601300993422223</v>
+        <v>0.0016564750458324922</v>
       </c>
       <c r="J65">
-        <v>0.04281508413149316</v>
+        <v>0.03677402473147005</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -51372,39 +52827,39 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:65:bambu:goma-cod</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.002806475854065099</v>
+        <v>0.002734796227902181</v>
       </c>
       <c r="F66">
-        <v>0.007390944356303691</v>
+        <v>0.007857450301785557</v>
       </c>
       <c r="G66">
-        <v>0.006946382389732636</v>
+        <v>0.006769325733142567</v>
       </c>
       <c r="H66">
-        <v>0.018231416239954695</v>
+        <v>0.01937544941239916</v>
       </c>
       <c r="I66">
-        <v>0.00208300583836101</v>
+        <v>0.0020746804621469632</v>
       </c>
       <c r="J66">
-        <v>0.03944316706094814</v>
+        <v>0.039964857141121454</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -51440,7 +52895,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:kilo:kampala-uga</t>
+          <t>corridor:66:kilo:goma-cod</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -51450,29 +52905,29 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.0028636196069686815</v>
+        <v>0.0027868684736187532</v>
       </c>
       <c r="F67">
-        <v>0.007245116575636645</v>
+        <v>0.007841801348761585</v>
       </c>
       <c r="G67">
-        <v>0.0070875198104265735</v>
+        <v>0.00689795184472039</v>
       </c>
       <c r="H67">
-        <v>0.017873638059777402</v>
+        <v>0.019337083521810405</v>
       </c>
       <c r="I67">
-        <v>0.001885099074969826</v>
+        <v>0.0017127846529912062</v>
       </c>
       <c r="J67">
-        <v>0.04037313015728034</v>
+        <v>0.03838966632456429</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -51505,8 +52960,688 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>corridor:67:bambu:kampala-uga</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>bambu</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>kampala-uga</t>
+        </is>
+      </c>
+      <c r="D68">
+        <v>30</v>
+      </c>
+      <c r="E68">
+        <v>0.002695763743499391</v>
+      </c>
+      <c r="F68">
+        <v>0.007827990157414616</v>
+      </c>
+      <c r="G68">
+        <v>0.006672903334783625</v>
+      </c>
+      <c r="H68">
+        <v>0.0193032265603717</v>
+      </c>
+      <c r="I68">
+        <v>0.0021490354133257674</v>
+      </c>
+      <c r="J68">
+        <v>0.04054210634480244</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>corridor:68:miti-murhesa:beni-cod</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>miti-murhesa</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69">
+        <v>0.002747310022513244</v>
+      </c>
+      <c r="F69">
+        <v>0.007800938064515872</v>
+      </c>
+      <c r="G69">
+        <v>0.006800237623896643</v>
+      </c>
+      <c r="H69">
+        <v>0.019236905708309188</v>
+      </c>
+      <c r="I69">
+        <v>0.002007951916882189</v>
+      </c>
+      <c r="J69">
+        <v>0.03490534363617388</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>corridor:69:kilo:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D70">
+        <v>30</v>
+      </c>
+      <c r="E70">
+        <v>0.0028404048325195996</v>
+      </c>
+      <c r="F70">
+        <v>0.007786957767991598</v>
+      </c>
+      <c r="G70">
+        <v>0.007030184083863106</v>
+      </c>
+      <c r="H70">
+        <v>0.019202630017290306</v>
+      </c>
+      <c r="I70">
+        <v>0.0018407478578635922</v>
+      </c>
+      <c r="J70">
+        <v>0.041169590401536636</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>corridor:70:bambu:beni-cod</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>bambu</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71">
+        <v>0.0030164649861187665</v>
+      </c>
+      <c r="F71">
+        <v>0.007772299321732512</v>
+      </c>
+      <c r="G71">
+        <v>0.0074649703248304</v>
+      </c>
+      <c r="H71">
+        <v>0.01916669022271858</v>
+      </c>
+      <c r="I71">
+        <v>0.0017745338814096486</v>
+      </c>
+      <c r="J71">
+        <v>0.04144693368617039</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>corridor:71:kilo:beni-cod</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+      <c r="E72">
+        <v>0.002780055599183956</v>
+      </c>
+      <c r="F72">
+        <v>0.0077543800748747505</v>
+      </c>
+      <c r="G72">
+        <v>0.006881123372275866</v>
+      </c>
+      <c r="H72">
+        <v>0.01912275597116167</v>
+      </c>
+      <c r="I72">
+        <v>0.001731233807528232</v>
+      </c>
+      <c r="J72">
+        <v>0.03818702256228324</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>corridor:72:goma-cod:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D73">
+        <v>30</v>
+      </c>
+      <c r="E73">
+        <v>0.0026587921388565305</v>
+      </c>
+      <c r="F73">
+        <v>0.007745510300115388</v>
+      </c>
+      <c r="G73">
+        <v>0.006581566727665494</v>
+      </c>
+      <c r="H73">
+        <v>0.0191010070867213</v>
+      </c>
+      <c r="I73">
+        <v>0.0015209453885095762</v>
+      </c>
+      <c r="J73">
+        <v>0.040091153412378705</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>corridor:73:nizi:goma-cod</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nizi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74">
+        <v>0.002825210964649716</v>
+      </c>
+      <c r="F74">
+        <v>0.00765236996976712</v>
+      </c>
+      <c r="G74">
+        <v>0.006992656995719604</v>
+      </c>
+      <c r="H74">
+        <v>0.01887262263985079</v>
+      </c>
+      <c r="I74">
+        <v>0.001869567731866642</v>
+      </c>
+      <c r="J74">
+        <v>0.03961175754580763</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>corridor:74:butembo:kasese-uga</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>butembo</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>kasese-uga</t>
+        </is>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75">
+        <v>0.002862546240653324</v>
+      </c>
+      <c r="F75">
+        <v>0.0075168412354912895</v>
+      </c>
+      <c r="G75">
+        <v>0.007084869280098771</v>
+      </c>
+      <c r="H75">
+        <v>0.0185402409724002</v>
+      </c>
+      <c r="I75">
+        <v>0.0017601300993422223</v>
+      </c>
+      <c r="J75">
+        <v>0.04281508413149316</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>corridor:75:kilo:arua-uga</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>kilo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>arua-uga</t>
+        </is>
+      </c>
+      <c r="D76">
+        <v>30</v>
+      </c>
+      <c r="E76">
+        <v>0.002806475854065099</v>
+      </c>
+      <c r="F76">
+        <v>0.007390944356303691</v>
+      </c>
+      <c r="G76">
+        <v>0.006946382389732636</v>
+      </c>
+      <c r="H76">
+        <v>0.018231416239954695</v>
+      </c>
+      <c r="I76">
+        <v>0.00208300583836101</v>
+      </c>
+      <c r="J76">
+        <v>0.03944316706094814</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>corridor:76:nizi:beni-cod</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>nizi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>beni-cod</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77">
+        <v>0.002632399314454331</v>
+      </c>
+      <c r="F77">
+        <v>0.007137232739807736</v>
+      </c>
+      <c r="G77">
+        <v>0.00651636145090756</v>
+      </c>
+      <c r="H77">
+        <v>0.017608901019654427</v>
+      </c>
+      <c r="I77">
+        <v>0.0019380433985584896</v>
+      </c>
+      <c r="J77">
+        <v>0.034324531074020156</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>BDBV-CLAIM-005</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>derived_model_output_with_unsupported_exponent_attribution</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>pinned_snapshot_model_output</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Descriptive watch-point interval, not a forecast or response recommendation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P67"/>
+  <autoFilter ref="A1:P77"/>
 </worksheet>
 </file>
 
@@ -53757,7 +55892,205 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-01</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>bunia -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>bunia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I14">
+        <v>30</v>
+      </c>
+      <c r="J14">
+        <v>0.1024</v>
+      </c>
+      <c r="K14">
+        <v>0.2669</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-02</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>rwampara -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rwampara</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>0.2034</v>
+      </c>
+      <c r="K15">
+        <v>0.4589</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>calibration-block:bdbv-uga-cod-2026:2026-05-26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-25T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>public-calibration-point-2026-05-26-03</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>mongbwalu -&gt; goma-cod</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>mongbwalu</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>goma-cod</t>
+        </is>
+      </c>
+      <c r="I16">
+        <v>30</v>
+      </c>
+      <c r="J16">
+        <v>0.0955</v>
+      </c>
+      <c r="K16">
+        <v>0.2518</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>PUBLIC-CALIBRATION-LEDGER</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pre_committed_carry_forward</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Third calibration block. Graduates Goma (goma-cod) from geographic-anchor-not-in-calibration to a pinned candidate target on 2026-05-26 per founder direction (see .process/2026-05-26-pre-refresh-decisions/follow-up-after-pushback.md, Thread 2 path A). Pins the three Ituri source HZs -&gt; goma-cod corridors at the ascertainment-adjusted 50% intervals from the 2026-05-26 pipeline run with goma-cod added to candidate_target_zones. Pre-pin prior context (NOT a resolution event): one laboratory-confirmed BDBV case in Goma on 2026-05-17, a woman who travelled from Ituri Province (per data/zones.json:goma-cod and data/external_sources/bdbv-2026.observed.json). Doctrine[4] early-lock will fire only on a new lab-confirmed case landing in Goma strictly inside [2026-05-26, 2026-06-25T23:59:59Z]; the 17-May case is outside that window and is therefore not a doctrine[4] trigger. Carried forward unchanged on every later refresh; scored against public reports on 2026-06-25.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N13"/>
+  <autoFilter ref="A1:N16"/>
 </worksheet>
 </file>
--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -114,7 +114,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-26T23:59:59Z</t>
         </is>
       </c>
     </row>
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -819,7 +819,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1012 to 1556 at deaths 238), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 948 to 1458 at deaths 223, CFR 40 to 26</t>
+          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 1012 to 1556 at deaths 238, CFR 40 to 26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>headline confirmed total 112; officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones; 33 confirmed cases remain unallocated headline context; current 76-corridor adjusted 50% range is 0.6-21.8% lower bounds and 1.8-49.4% upper bounds.</t>
+          <t>headline confirmed total 128 (121 DRC per ECDC 27 May citing DRC MoH 26 May + 7 Uganda per CDC 25 May; INRB build-2026-05-27 cross-corroborates the DRC component); officially zone-attributed corridor source-load total 79 across 11 DRC MoH source zones (carry-forward from SitRep MVE N 007/MVB_17/2026 PDF because no newer official cumulative health-zone table has been published); 49 confirmed cases remain unallocated headline context; current 76-corridor adjusted 50% range is 0.7-20.4% lower bounds and 1.8-49.3% upper bounds. The May-26 cycle prior was headline confirmed 112 / 33 unallocated / 0.6-21.8% lower / 1.8-49.4% upper; the headline advance from 112 to 128 reflects the DRC MoH 26 May release (16 new confirmed DRC cases) without changing the SitRep 007 source-load vector, so the corridor watchlist is not the current headline confirmed aggregate.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4007,8 +4007,124 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Institut National de Recherche Biomedicale (INRB), Institut National de Sante Publique (INSP), and Unite de Modelisation et Intelligence Epidemique (UMIE)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/Ebola_DRC_2026/releases/download/build-2026-05-27-059661a/build-2026-05-27-059661a.tar.gz</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-05-27T14:33:41Z</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:57:33Z</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>6d13fed81a6305c1d7ac12d53c86da40718d37470352c885b9f79a097ed7aaf9</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>private_restricted_bytes</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>publisher-terms-not-confirmed</t>
+        </is>
+      </c>
+      <c r="J43"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>European Centre for Disease Prevention and Control</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-05-27T00:00:00Z</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-05-27T17:25:00Z</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="J44"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L42"/>
+  <autoFilter ref="A1:L44"/>
 </worksheet>
 </file>
 
@@ -8517,7 +8633,7 @@
       <c r="I10"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (948 to 1458 at deaths 223), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1012 to 1556 at deaths 238), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -11338,12 +11454,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-26T23:59:59Z</t>
         </is>
       </c>
       <c r="E2"/>
@@ -11377,7 +11493,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D3"/>
@@ -16647,8 +16763,274 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>source_data_report_date:inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D128"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>source_publication_date:inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D129"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-05-27T15:57:33Z</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>source_data_report_date:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D131"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Primary regional cross-corroboration of the DRC MoH 26 May release; in concert with INRB build-2026-05-27 (DRC-only national_moh), supports promotion of DRC MoH 26 May to headline count endpoint for the May-27 publication-state snapshot. CDC May-26 retained as dated conflict anchor (105/906/10/223).</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>source_publication_date:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D132"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Primary regional cross-corroboration of the DRC MoH 26 May release; in concert with INRB build-2026-05-27 (DRC-only national_moh), supports promotion of DRC MoH 26 May to headline count endpoint for the May-27 publication-state snapshot. CDC May-26 retained as dated conflict anchor (105/906/10/223).</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-05-27T17:25:00Z</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Primary regional cross-corroboration of the DRC MoH 26 May release; in concert with INRB build-2026-05-27 (DRC-only national_moh), supports promotion of DRC MoH 26 May to headline count endpoint for the May-27 publication-state snapshot. CDC May-26 retained as dated conflict anchor (105/906/10/223).</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>regional_body</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I127"/>
+  <autoFilter ref="A1:I133"/>
 </worksheet>
 </file>
 
@@ -35033,34 +35415,34 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:suspected</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_drc</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>suspected_cases</t>
-        </is>
-      </c>
-      <c r="D233"/>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F233">
-        <v>906</v>
-      </c>
-      <c r="G233">
-        <v>395</v>
-      </c>
-      <c r="H233">
-        <v>906</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="G233"/>
+      <c r="H233"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>count</t>
@@ -35068,37 +35450,33 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K233"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -35108,7 +35486,7 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
+          <t>CC-BY-4.0</t>
         </is>
       </c>
       <c r="S233"/>
@@ -35116,12 +35494,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>snapshot:reported_counts:confirmed</t>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_total</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_metric</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -35129,21 +35507,21 @@
           <t>confirmed_cases</t>
         </is>
       </c>
-      <c r="D234"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>2026-05-25T23:59:59Z</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F234">
-        <v>112</v>
-      </c>
-      <c r="G234">
-        <v>10</v>
-      </c>
-      <c r="H234">
-        <v>112</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G234"/>
+      <c r="H234"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>count</t>
@@ -35151,37 +35529,33 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K234"/>
       <c r="L234" t="inlineStr">
         <is>
-          <t>PUBLIC-SOURCE-AUDIT</t>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>reconciled_from_dated_sources</t>
+          <t>source_manifest_attested</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>snapshot_reconciled_range</t>
+          <t>source_extracted_metric</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
         </is>
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -35191,100 +35565,819 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>public-domain-us-gov</t>
-        </is>
-      </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
-        </is>
-      </c>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S234"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F235">
+        <v>7</v>
+      </c>
+      <c r="G235"/>
+      <c r="H235"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K235"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S235"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F236">
+        <v>1077</v>
+      </c>
+      <c r="G236"/>
+      <c r="H236"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K236"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S236"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F237">
+        <v>17</v>
+      </c>
+      <c r="G237"/>
+      <c r="H237"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K237"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S237"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F238">
+        <v>238</v>
+      </c>
+      <c r="G238"/>
+      <c r="H238"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K238"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S238"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239"/>
+      <c r="H239"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K239"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S239"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:http_status</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F240">
+        <v>200</v>
+      </c>
+      <c r="G240"/>
+      <c r="H240"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K240"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S240"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>source:ecdc-bdbv-drc-uga-2026-05-27-live:uganda_cases_drc_travel_linked</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>uganda_cases_drc_travel_linked</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>COD; UGA</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F241">
+        <v>3</v>
+      </c>
+      <c r="G241"/>
+      <c r="H241"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K241"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>source_manifest_attested</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>source_extracted_metric</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S241"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:suspected</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D242"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-05-26T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F242">
+        <v>1077</v>
+      </c>
+      <c r="G242">
+        <v>395</v>
+      </c>
+      <c r="H242">
+        <v>1077</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S242"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>snapshot:reported_counts:confirmed</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_metric</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D243"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-05-26T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F243">
+        <v>128</v>
+      </c>
+      <c r="G243">
+        <v>10</v>
+      </c>
+      <c r="H243">
+        <v>128</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>PUBLIC-SOURCE-AUDIT</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>reconciled_from_dated_sources</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>snapshot_reconciled_range</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>public_bytes</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>WHO PHEIC deconfirmed the reported Kinshasa case; confirmed minimum excludes Kinshasa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
           <t>snapshot:reported_counts:deaths</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>snapshot_reconciled_metric</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>deaths</t>
         </is>
       </c>
-      <c r="D235"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>2026-05-25T23:59:59Z</t>
-        </is>
-      </c>
-      <c r="F235">
-        <v>223</v>
-      </c>
-      <c r="G235">
+      <c r="D244"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-05-26T23:59:59Z</t>
+        </is>
+      </c>
+      <c r="F244">
+        <v>238</v>
+      </c>
+      <c r="G244">
         <v>106</v>
       </c>
-      <c r="H235">
-        <v>223</v>
-      </c>
-      <c r="I235" t="inlineStr">
+      <c r="H244">
+        <v>238</v>
+      </c>
+      <c r="I244" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>cdc-current-situation-2026-05-25</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
         <is>
           <t>PUBLIC-SOURCE-AUDIT</t>
         </is>
       </c>
-      <c r="M235" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t>reconciled_from_dated_sources</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
+      <c r="N244" t="inlineStr">
         <is>
           <t>snapshot_reconciled_range</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
-        <is>
-          <t>https://www.cdc.gov/ebola/situation-summary/index.html</t>
-        </is>
-      </c>
-      <c r="P235" t="inlineStr">
-        <is>
-          <t>77d396c0a888d13dc3a1cbf6cdd977d5049df73624bbec36a0877a170555a1c9</t>
-        </is>
-      </c>
-      <c r="Q235" t="inlineStr">
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
         <is>
           <t>public_bytes</t>
         </is>
       </c>
-      <c r="R235" t="inlineStr">
-        <is>
-          <t>public-domain-us-gov</t>
-        </is>
-      </c>
-      <c r="S235"/>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="S244"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S235"/>
+  <autoFilter ref="A1:S244"/>
 </worksheet>
 </file>
 
@@ -47150,8 +48243,467 @@
       </c>
       <c r="K232"/>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D233">
+        <v>121</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K233"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_total</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D234">
+        <v>128</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K234"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:cases_confirmed_uganda</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>confirmed_cases</t>
+        </is>
+      </c>
+      <c r="D235">
+        <v>7</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K235"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_confirmed_drc</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D236">
+        <v>17</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K236"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D237">
+        <v>238</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K237"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:deaths_uganda</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>deaths</t>
+        </is>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K238"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:http_status</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>http_status</t>
+        </is>
+      </c>
+      <c r="D239">
+        <v>200</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K239"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:cases_suspected_drc</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>suspected_cases</t>
+        </is>
+      </c>
+      <c r="D240">
+        <v>1077</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K240"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>timeline:ecdc-bdbv-drc-uga-2026-05-27-live:uganda_cases_drc_travel_linked</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>uganda_cases_drc_travel_linked</t>
+        </is>
+      </c>
+      <c r="D241">
+        <v>3</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>source_manifest:ecdc-bdbv-drc-uga-2026-05-27-live</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>CC-BY-4.0</t>
+        </is>
+      </c>
+      <c r="K241"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K232"/>
+  <autoFilter ref="A1:K241"/>
 </worksheet>
 </file>
 
@@ -48475,7 +50027,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:nebbi-uga</t>
+          <t>corridor:01:rwampara:goma-cod</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -48485,33 +50037,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.09445951733436075</v>
+        <v>0.08589962049863303</v>
       </c>
       <c r="F2">
-        <v>0.24002055285686827</v>
+        <v>0.2377669968354101</v>
       </c>
       <c r="G2">
-        <v>0.21815681374976198</v>
+        <v>0.20129270600512006</v>
       </c>
       <c r="H2">
-        <v>0.49376090747255597</v>
+        <v>0.4930960175674681</v>
       </c>
       <c r="I2">
-        <v>0.06319702466996217</v>
+        <v>0.07120480544093157</v>
       </c>
       <c r="J2">
-        <v>0.719264702591034</v>
+        <v>0.7248388454926133</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -48531,7 +50083,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -48543,7 +50095,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:beni-cod</t>
+          <t>corridor:02:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -48553,33 +50105,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08273781175301806</v>
+        <v>0.08505191657867475</v>
       </c>
       <c r="F3">
-        <v>0.2284874731887681</v>
+        <v>0.23121425191013859</v>
       </c>
       <c r="G3">
-        <v>0.1928142001378063</v>
+        <v>0.19943802002803682</v>
       </c>
       <c r="H3">
-        <v>0.4744917795152871</v>
+        <v>0.4821200107370141</v>
       </c>
       <c r="I3">
-        <v>0.06730851508774321</v>
+        <v>0.054059833036011785</v>
       </c>
       <c r="J3">
-        <v>0.7564576627228864</v>
+        <v>0.7483917890968707</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -48599,7 +50151,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -48611,7 +50163,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:bundibugyo-uga</t>
+          <t>corridor:03:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -48621,33 +50173,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.09048464357894637</v>
+        <v>0.08246101760170607</v>
       </c>
       <c r="F4">
-        <v>0.22273556590441385</v>
+        <v>0.22061929395367888</v>
       </c>
       <c r="G4">
-        <v>0.20961712897740686</v>
+        <v>0.19375268176637458</v>
       </c>
       <c r="H4">
-        <v>0.4647202826386523</v>
+        <v>0.4640719973664308</v>
       </c>
       <c r="I4">
-        <v>0.04977612451622361</v>
+        <v>0.046285552997724785</v>
       </c>
       <c r="J4">
-        <v>0.7106528036367321</v>
+        <v>0.7208671523084099</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -48667,7 +50219,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -48679,7 +50231,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:kasese-uga</t>
+          <t>corridor:04:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -48689,33 +50241,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.08565218814006142</v>
+        <v>0.0872098339088937</v>
       </c>
       <c r="F5">
-        <v>0.22029891605266969</v>
+        <v>0.21933684271935094</v>
       </c>
       <c r="G5">
-        <v>0.19916026506380355</v>
+        <v>0.20415468621935687</v>
       </c>
       <c r="H5">
-        <v>0.4605488463027082</v>
+        <v>0.4618632442565608</v>
       </c>
       <c r="I5">
-        <v>0.07273190347723515</v>
+        <v>0.05201982764209262</v>
       </c>
       <c r="J5">
-        <v>0.7278051232264949</v>
+        <v>0.7529772054129632</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -48735,7 +50287,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -48747,7 +50299,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:goma-cod</t>
+          <t>corridor:05:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -48757,33 +50309,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08761720560139294</v>
+        <v>0.08504292783923784</v>
       </c>
       <c r="F6">
-        <v>0.21936354051325144</v>
+        <v>0.21818466263753306</v>
       </c>
       <c r="G6">
-        <v>0.20342220318959423</v>
+        <v>0.19941819443093944</v>
       </c>
       <c r="H6">
-        <v>0.4589425069655363</v>
+        <v>0.4598751196093878</v>
       </c>
       <c r="I6">
-        <v>0.06886739376279995</v>
+        <v>0.05371559052324989</v>
       </c>
       <c r="J6">
-        <v>0.743152794738482</v>
+        <v>0.7436356440277915</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -48803,7 +50355,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -48832,26 +50384,26 @@
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08287569990928895</v>
+        <v>0.08161896053098214</v>
       </c>
       <c r="F7">
-        <v>0.21243842944956587</v>
+        <v>0.21542592859488613</v>
       </c>
       <c r="G7">
-        <v>0.1931151059217136</v>
+        <v>0.19189952767778493</v>
       </c>
       <c r="H7">
-        <v>0.4469590270913051</v>
+        <v>0.4550927331844304</v>
       </c>
       <c r="I7">
-        <v>0.05292524916825545</v>
+        <v>0.04584337260504729</v>
       </c>
       <c r="J7">
-        <v>0.7528903131888608</v>
+        <v>0.7275888838527099</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -48871,7 +50423,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -48883,7 +50435,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:rwampara:arua-uga</t>
+          <t>corridor:07:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -48893,33 +50445,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.0813030320518214</v>
+        <v>0.07903310132360086</v>
       </c>
       <c r="F8">
-        <v>0.2120036212731276</v>
+        <v>0.21005018084173388</v>
       </c>
       <c r="G8">
-        <v>0.18967897671798614</v>
+        <v>0.18619362496919714</v>
       </c>
       <c r="H8">
-        <v>0.44620129623757115</v>
+        <v>0.4456997886549633</v>
       </c>
       <c r="I8">
-        <v>0.05853988867330033</v>
+        <v>0.062493325186918275</v>
       </c>
       <c r="J8">
-        <v>0.721341036531536</v>
+        <v>0.725424432635406</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -48939,7 +50491,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -48951,7 +50503,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:goma-cod</t>
+          <t>corridor:08:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -48961,33 +50513,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04260859167640518</v>
+        <v>0.04729302438764643</v>
       </c>
       <c r="F9">
-        <v>0.11766030943420233</v>
+        <v>0.12370943963454503</v>
       </c>
       <c r="G9">
-        <v>0.10237107937830753</v>
+        <v>0.11417904209164992</v>
       </c>
       <c r="H9">
-        <v>0.26690234529353574</v>
+        <v>0.28141613742977256</v>
       </c>
       <c r="I9">
-        <v>0.03562848758295974</v>
+        <v>0.029207232878451818</v>
       </c>
       <c r="J9">
-        <v>0.4539173649760259</v>
+        <v>0.4920171793027066</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -49007,7 +50559,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -49019,7 +50571,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:kasese-uga</t>
+          <t>corridor:09:bunia:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -49029,33 +50581,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.04147908524423352</v>
+        <v>0.043911160625526746</v>
       </c>
       <c r="F10">
-        <v>0.11562806950949953</v>
+        <v>0.12312573996350779</v>
       </c>
       <c r="G10">
-        <v>0.09974219409345544</v>
+        <v>0.10628910544890177</v>
       </c>
       <c r="H10">
-        <v>0.2627072705721946</v>
+        <v>0.28021748772019517</v>
       </c>
       <c r="I10">
-        <v>0.025907663365721464</v>
+        <v>0.0356239441695431</v>
       </c>
       <c r="J10">
-        <v>0.4462554570998926</v>
+        <v>0.45773855023765087</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -49075,7 +50627,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -49087,7 +50639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:beni-cod</t>
+          <t>corridor:10:bunia:kampala-uga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -49097,33 +50649,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D11">
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.04179480816556652</v>
+        <v>0.03978940807069492</v>
       </c>
       <c r="F11">
-        <v>0.11558245421258095</v>
+        <v>0.1173207414160834</v>
       </c>
       <c r="G11">
-        <v>0.10047743392001213</v>
+        <v>0.09661618012382142</v>
       </c>
       <c r="H11">
-        <v>0.26261295488077974</v>
+        <v>0.2682338954929566</v>
       </c>
       <c r="I11">
-        <v>0.027913949480659363</v>
+        <v>0.029747212124222495</v>
       </c>
       <c r="J11">
-        <v>0.4647552683750245</v>
+        <v>0.5070561528116015</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -49143,7 +50695,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -49155,7 +50707,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:bunia:nebbi-uga</t>
+          <t>corridor:11:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -49165,33 +50717,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.040430218691513475</v>
+        <v>0.0420273929079403</v>
       </c>
       <c r="F12">
-        <v>0.11557548317625271</v>
+        <v>0.11511405461029645</v>
       </c>
       <c r="G12">
-        <v>0.09729691190408213</v>
+        <v>0.10187597894378383</v>
       </c>
       <c r="H12">
-        <v>0.26259850203465634</v>
+        <v>0.263647089428501</v>
       </c>
       <c r="I12">
-        <v>0.024532453328788482</v>
+        <v>0.02819360882235204</v>
       </c>
       <c r="J12">
-        <v>0.4737244474950434</v>
+        <v>0.4840783218842872</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -49211,7 +50763,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -49223,7 +50775,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corridor:12:bunia:arua-uga</t>
+          <t>corridor:12:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -49233,33 +50785,33 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D13">
         <v>30</v>
       </c>
       <c r="E13">
-        <v>0.04186956091160368</v>
+        <v>0.04274652440730639</v>
       </c>
       <c r="F13">
-        <v>0.11539491748492897</v>
+        <v>0.11434447158862063</v>
       </c>
       <c r="G13">
-        <v>0.10065158442248001</v>
+        <v>0.10356227479914651</v>
       </c>
       <c r="H13">
-        <v>0.26222507759010427</v>
+        <v>0.26204345689590547</v>
       </c>
       <c r="I13">
-        <v>0.021242880051839726</v>
+        <v>0.03044678871758952</v>
       </c>
       <c r="J13">
-        <v>0.46678607844486947</v>
+        <v>0.4484607748737422</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -49279,7 +50831,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -49291,7 +50843,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corridor:13:mongbwalu:bundibugyo-uga</t>
+          <t>corridor:13:mongbwalu:kasese-uga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -49301,33 +50853,33 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D14">
         <v>30</v>
       </c>
       <c r="E14">
-        <v>0.04269679620853847</v>
+        <v>0.039939310371646164</v>
       </c>
       <c r="F14">
-        <v>0.1114239910693812</v>
+        <v>0.11344718043981386</v>
       </c>
       <c r="G14">
-        <v>0.1025762389475964</v>
+        <v>0.0969690777153531</v>
       </c>
       <c r="H14">
-        <v>0.25398350476377357</v>
+        <v>0.26017113457605656</v>
       </c>
       <c r="I14">
-        <v>0.024461896089849052</v>
+        <v>0.029113551979605436</v>
       </c>
       <c r="J14">
-        <v>0.42050488842189776</v>
+        <v>0.4360289235710159</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -49347,7 +50899,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -49359,7 +50911,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corridor:14:bunia:kampala-uga</t>
+          <t>corridor:14:bunia:goma-cod</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -49369,33 +50921,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D15">
         <v>30</v>
       </c>
       <c r="E15">
-        <v>0.043769887053943884</v>
+        <v>0.041076420434534744</v>
       </c>
       <c r="F15">
-        <v>0.11103027985574987</v>
+        <v>0.11304415379918484</v>
       </c>
       <c r="G15">
-        <v>0.10506919313252691</v>
+        <v>0.09964326867901607</v>
       </c>
       <c r="H15">
-        <v>0.2531634176228099</v>
+        <v>0.2593292109636347</v>
       </c>
       <c r="I15">
-        <v>0.024326153776741695</v>
+        <v>0.028250398709910075</v>
       </c>
       <c r="J15">
-        <v>0.44860424323610526</v>
+        <v>0.4508698081137886</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -49415,7 +50967,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -49427,43 +50979,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corridor:15:mongbwalu:goma-cod</t>
+          <t>corridor:15:bunia:arua-uga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mongbwalu</t>
+          <t>bunia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D16">
         <v>30</v>
       </c>
       <c r="E16">
-        <v>0.03967055365389441</v>
+        <v>0.04485927078614241</v>
       </c>
       <c r="F16">
-        <v>0.11037528493444154</v>
+        <v>0.11184223470253357</v>
       </c>
       <c r="G16">
-        <v>0.09552333993090975</v>
+        <v>0.10850529581552057</v>
       </c>
       <c r="H16">
-        <v>0.2517977687861897</v>
+        <v>0.25681493622831186</v>
       </c>
       <c r="I16">
-        <v>0.02246092821507834</v>
+        <v>0.024751284236955835</v>
       </c>
       <c r="J16">
-        <v>0.4355790666314244</v>
+        <v>0.49531611361602873</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -49483,7 +51035,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -49495,7 +51047,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corridor:16:mongbwalu:nebbi-uga</t>
+          <t>corridor:16:mongbwalu:beni-cod</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -49505,33 +51057,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D17">
         <v>30</v>
       </c>
       <c r="E17">
-        <v>0.036893545042157305</v>
+        <v>0.04301806763566754</v>
       </c>
       <c r="F17">
-        <v>0.10867014828748978</v>
+        <v>0.11042640860470704</v>
       </c>
       <c r="G17">
-        <v>0.08902229938514877</v>
+        <v>0.10419852291900844</v>
       </c>
       <c r="H17">
-        <v>0.2482358877081989</v>
+        <v>0.253846422063812</v>
       </c>
       <c r="I17">
-        <v>0.020695892757526077</v>
+        <v>0.026469576238533403</v>
       </c>
       <c r="J17">
-        <v>0.4289255637849178</v>
+        <v>0.45608717254290976</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -49551,7 +51103,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -49563,7 +51115,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corridor:17:mongbwalu:beni-cod</t>
+          <t>corridor:17:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -49573,33 +51125,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D18">
         <v>30</v>
       </c>
       <c r="E18">
-        <v>0.038935353978377885</v>
+        <v>0.04151806301681368</v>
       </c>
       <c r="F18">
-        <v>0.10835196082870574</v>
+        <v>0.10815511068592765</v>
       </c>
       <c r="G18">
-        <v>0.09380493517661201</v>
+        <v>0.10068061176617743</v>
       </c>
       <c r="H18">
-        <v>0.2475701272178043</v>
+        <v>0.24906994224721088</v>
       </c>
       <c r="I18">
-        <v>0.021267428986718424</v>
+        <v>0.027065605867335897</v>
       </c>
       <c r="J18">
-        <v>0.43910667718208657</v>
+        <v>0.45249524080602943</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -49619,7 +51171,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -49631,43 +51183,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corridor:18:bunia:bundibugyo-uga</t>
+          <t>corridor:18:mongbwalu:arua-uga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D19">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0.04228950663900796</v>
+        <v>0.04517764440593511</v>
       </c>
       <c r="F19">
-        <v>0.10704031678368539</v>
+        <v>0.10770370920085262</v>
       </c>
       <c r="G19">
-        <v>0.10162893993380431</v>
+        <v>0.10924874396730949</v>
       </c>
       <c r="H19">
-        <v>0.24482175888282368</v>
+        <v>0.24811822952285237</v>
       </c>
       <c r="I19">
-        <v>0.026598690800271954</v>
+        <v>0.02755675796438769</v>
       </c>
       <c r="J19">
-        <v>0.4232379895804849</v>
+        <v>0.4393635609497787</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -49687,7 +51239,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -49699,7 +51251,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>corridor:19:mongbwalu:arua-uga</t>
+          <t>corridor:19:mongbwalu:nebbi-uga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -49709,33 +51261,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D20">
         <v>30</v>
       </c>
       <c r="E20">
-        <v>0.035432678170503384</v>
+        <v>0.03781412755413227</v>
       </c>
       <c r="F20">
-        <v>0.10593636188070824</v>
+        <v>0.10716920248813597</v>
       </c>
       <c r="G20">
-        <v>0.08559121466787023</v>
+        <v>0.09195833138892637</v>
       </c>
       <c r="H20">
-        <v>0.24250404576809376</v>
+        <v>0.2469907006004258</v>
       </c>
       <c r="I20">
-        <v>0.027309488663839657</v>
+        <v>0.0335604551552348</v>
       </c>
       <c r="J20">
-        <v>0.4555467010005905</v>
+        <v>0.44671157509402076</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -49755,7 +51307,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -49767,7 +51319,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>corridor:20:mongbwalu:kampala-uga</t>
+          <t>corridor:20:mongbwalu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -49777,33 +51329,33 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D21">
         <v>30</v>
       </c>
       <c r="E21">
-        <v>0.03763199658508454</v>
+        <v>0.03934606325054965</v>
       </c>
       <c r="F21">
-        <v>0.10128422532010978</v>
+        <v>0.10602360845188871</v>
       </c>
       <c r="G21">
-        <v>0.09075375258925547</v>
+        <v>0.09557201855080028</v>
       </c>
       <c r="H21">
-        <v>0.23269034583576234</v>
+        <v>0.24457009708147964</v>
       </c>
       <c r="I21">
-        <v>0.019116090021161606</v>
+        <v>0.027984932001384973</v>
       </c>
       <c r="J21">
-        <v>0.4602236579125214</v>
+        <v>0.46201575657165617</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -49823,7 +51375,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -49835,7 +51387,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>corridor:21:mongbwalu:kasese-uga</t>
+          <t>corridor:21:mongbwalu:goma-cod</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -49845,33 +51397,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D22">
         <v>30</v>
       </c>
       <c r="E22">
-        <v>0.038843460236694466</v>
+        <v>0.038627166415719366</v>
       </c>
       <c r="F22">
-        <v>0.10070243265367404</v>
+        <v>0.10592423849339813</v>
       </c>
       <c r="G22">
-        <v>0.0935899840239344</v>
+        <v>0.09387731626355811</v>
       </c>
       <c r="H22">
-        <v>0.23145773577863957</v>
+        <v>0.24436042181487633</v>
       </c>
       <c r="I22">
-        <v>0.025371459529098615</v>
+        <v>0.02407334166032219</v>
       </c>
       <c r="J22">
-        <v>0.4729197264386862</v>
+        <v>0.4713848394753903</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -49891,7 +51443,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -49920,26 +51472,26 @@
         <v>30</v>
       </c>
       <c r="E23">
-        <v>0.03146929822468722</v>
+        <v>0.03135748139935121</v>
       </c>
       <c r="F23">
-        <v>0.08989853663383654</v>
+        <v>0.09150990401631812</v>
       </c>
       <c r="G23">
-        <v>0.07624375486519391</v>
+        <v>0.07663299419130262</v>
       </c>
       <c r="H23">
-        <v>0.20835308906693198</v>
+        <v>0.21350373124100783</v>
       </c>
       <c r="I23">
-        <v>0.023297869762629386</v>
+        <v>0.018899520366765413</v>
       </c>
       <c r="J23">
-        <v>0.3863428563442163</v>
+        <v>0.3816000730080578</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -49959,7 +51511,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -49971,7 +51523,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>corridor:23:nyankunde:goma-cod</t>
+          <t>corridor:23:nyankunde:nebbi-uga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -49981,33 +51533,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D24">
         <v>30</v>
       </c>
       <c r="E24">
-        <v>0.032748675469615296</v>
+        <v>0.031774162247601156</v>
       </c>
       <c r="F24">
-        <v>0.08856563497530315</v>
+        <v>0.08869699248391957</v>
       </c>
       <c r="G24">
-        <v>0.07926732761392977</v>
+        <v>0.07762666630951695</v>
       </c>
       <c r="H24">
-        <v>0.2054744022745903</v>
+        <v>0.2073955156202693</v>
       </c>
       <c r="I24">
-        <v>0.020503468439890822</v>
+        <v>0.025654480580084044</v>
       </c>
       <c r="J24">
-        <v>0.34571427438684454</v>
+        <v>0.3732873945401741</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -50027,7 +51579,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -50039,7 +51591,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>corridor:24:nyankunde:kasese-uga</t>
+          <t>corridor:24:nyankunde:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -50049,33 +51601,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D25">
         <v>30</v>
       </c>
       <c r="E25">
-        <v>0.030026997527813626</v>
+        <v>0.030184260059163387</v>
       </c>
       <c r="F25">
-        <v>0.08665812766707617</v>
+        <v>0.08845198525357079</v>
       </c>
       <c r="G25">
-        <v>0.07282808208366084</v>
+        <v>0.07383168246750335</v>
       </c>
       <c r="H25">
-        <v>0.2013434496623271</v>
+        <v>0.20686176295675346</v>
       </c>
       <c r="I25">
-        <v>0.025288863375360248</v>
+        <v>0.01882095254901688</v>
       </c>
       <c r="J25">
-        <v>0.34693271100874334</v>
+        <v>0.3718878829167321</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -50095,7 +51647,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -50107,7 +51659,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>corridor:25:nyankunde:nebbi-uga</t>
+          <t>corridor:25:nyankunde:arua-uga</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -50117,33 +51669,33 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D26">
         <v>30</v>
       </c>
       <c r="E26">
-        <v>0.03075884987706151</v>
+        <v>0.029765462884544208</v>
       </c>
       <c r="F26">
-        <v>0.08599999997606922</v>
+        <v>0.08682234283253074</v>
       </c>
       <c r="G26">
-        <v>0.07456220134186478</v>
+        <v>0.0728305012802403</v>
       </c>
       <c r="H26">
-        <v>0.19991563107642202</v>
+        <v>0.2033089582059392</v>
       </c>
       <c r="I26">
-        <v>0.023982280525205277</v>
+        <v>0.021385648795838562</v>
       </c>
       <c r="J26">
-        <v>0.3479361411653973</v>
+        <v>0.39836965130192753</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -50163,7 +51715,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -50175,7 +51727,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>corridor:26:nyankunde:kampala-uga</t>
+          <t>corridor:26:nyankunde:goma-cod</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -50185,33 +51737,33 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D27">
         <v>30</v>
       </c>
       <c r="E27">
-        <v>0.03164694763292836</v>
+        <v>0.02827845618269012</v>
       </c>
       <c r="F27">
-        <v>0.08559300950103177</v>
+        <v>0.08547394474180545</v>
       </c>
       <c r="G27">
-        <v>0.07666392163091817</v>
+        <v>0.06927035431476608</v>
       </c>
       <c r="H27">
-        <v>0.19903170204824353</v>
+        <v>0.200361785770158</v>
       </c>
       <c r="I27">
-        <v>0.01960014940850209</v>
+        <v>0.017713188168717524</v>
       </c>
       <c r="J27">
-        <v>0.35567826316219087</v>
+        <v>0.37279662736757135</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -50231,7 +51783,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -50243,7 +51795,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>corridor:27:nyankunde:arua-uga</t>
+          <t>corridor:27:nyankunde:kampala-uga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -50253,33 +51805,33 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D28">
         <v>30</v>
       </c>
       <c r="E28">
-        <v>0.03415616913117603</v>
+        <v>0.03231117942521783</v>
       </c>
       <c r="F28">
-        <v>0.0843769399835359</v>
+        <v>0.08412695362430928</v>
       </c>
       <c r="G28">
-        <v>0.0825868002754413</v>
+        <v>0.07890635319122888</v>
       </c>
       <c r="H28">
-        <v>0.1963870895325143</v>
+        <v>0.19741113894251278</v>
       </c>
       <c r="I28">
-        <v>0.023187377364693004</v>
+        <v>0.02371323453231194</v>
       </c>
       <c r="J28">
-        <v>0.3421266345564783</v>
+        <v>0.36955544421315567</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -50299,7 +51851,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -50311,7 +51863,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>corridor:28:nyankunde:bundibugyo-uga</t>
+          <t>corridor:28:nyankunde:kasese-uga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -50321,33 +51873,33 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D29">
         <v>30</v>
       </c>
       <c r="E29">
-        <v>0.03357687364916134</v>
+        <v>0.03177238195869697</v>
       </c>
       <c r="F29">
-        <v>0.08425270479805413</v>
+        <v>0.08268488502423868</v>
       </c>
       <c r="G29">
-        <v>0.08122145623779894</v>
+        <v>0.07762242673024056</v>
       </c>
       <c r="H29">
-        <v>0.196116146145421</v>
+        <v>0.19424473123372044</v>
       </c>
       <c r="I29">
-        <v>0.02179834248652243</v>
+        <v>0.021420932336895075</v>
       </c>
       <c r="J29">
-        <v>0.35919822012550795</v>
+        <v>0.39167754781866554</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 11 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -50367,7 +51919,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -50379,7 +51931,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>corridor:29:katwa:kasese-uga</t>
+          <t>corridor:29:katwa:goma-cod</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -50389,33 +51941,33 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D30">
         <v>30</v>
       </c>
       <c r="E30">
-        <v>0.005665299126924983</v>
+        <v>0.006223097122961846</v>
       </c>
       <c r="F30">
-        <v>0.016137547052658407</v>
+        <v>0.016924941785747494</v>
       </c>
       <c r="G30">
-        <v>0.01399263950136656</v>
+        <v>0.015500515331297121</v>
       </c>
       <c r="H30">
-        <v>0.039548733878884995</v>
+        <v>0.04181751882886131</v>
       </c>
       <c r="I30">
-        <v>0.0033705192295240497</v>
+        <v>0.0038645912994317356</v>
       </c>
       <c r="J30">
-        <v>0.0787241376496719</v>
+        <v>0.08238737967183987</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -50435,7 +51987,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -50447,7 +51999,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>corridor:30:katwa:beni-cod</t>
+          <t>corridor:30:katwa:arua-uga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -50457,33 +52009,33 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D31">
         <v>30</v>
       </c>
       <c r="E31">
-        <v>0.005408064245022548</v>
+        <v>0.006000659519297985</v>
       </c>
       <c r="F31">
-        <v>0.016075387130097485</v>
+        <v>0.016472204886329667</v>
       </c>
       <c r="G31">
-        <v>0.013359846492850574</v>
+        <v>0.01494897128714559</v>
       </c>
       <c r="H31">
-        <v>0.039398229649427796</v>
+        <v>0.040712854128774956</v>
       </c>
       <c r="I31">
-        <v>0.0037862601247234534</v>
+        <v>0.004253787831869915</v>
       </c>
       <c r="J31">
-        <v>0.07544870631338906</v>
+        <v>0.08215720574820966</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -50503,7 +52055,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -50515,7 +52067,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>corridor:31:katwa:kampala-uga</t>
+          <t>corridor:31:katwa:beni-cod</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -50525,33 +52077,33 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D32">
         <v>30</v>
       </c>
       <c r="E32">
-        <v>0.005760920437457601</v>
+        <v>0.006294691018966403</v>
       </c>
       <c r="F32">
-        <v>0.01564371888735397</v>
+        <v>0.016451154965313713</v>
       </c>
       <c r="G32">
-        <v>0.014227802835785092</v>
+        <v>0.015677996476171574</v>
       </c>
       <c r="H32">
-        <v>0.03835261291771347</v>
+        <v>0.04066147497465977</v>
       </c>
       <c r="I32">
-        <v>0.004405736887256273</v>
+        <v>0.0033035694374994678</v>
       </c>
       <c r="J32">
-        <v>0.07717071840257644</v>
+        <v>0.0753414208876655</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -50571,7 +52123,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -50583,7 +52135,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>corridor:32:katwa:goma-cod</t>
+          <t>corridor:32:katwa:kasese-uga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -50593,33 +52145,33 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D33">
         <v>30</v>
       </c>
       <c r="E33">
-        <v>0.006169920398082257</v>
+        <v>0.005351798554195902</v>
       </c>
       <c r="F33">
-        <v>0.01553498621898089</v>
+        <v>0.015895181258903462</v>
       </c>
       <c r="G33">
-        <v>0.01523329162375131</v>
+        <v>0.013339030937020296</v>
       </c>
       <c r="H33">
-        <v>0.03808912674070569</v>
+        <v>0.03930382476548039</v>
       </c>
       <c r="I33">
-        <v>0.003357225433652031</v>
+        <v>0.0038704364436793594</v>
       </c>
       <c r="J33">
-        <v>0.06777077505091869</v>
+        <v>0.06880848728993498</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -50639,7 +52191,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -50668,26 +52220,26 @@
         <v>30</v>
       </c>
       <c r="E34">
-        <v>0.005252367922210843</v>
+        <v>0.006287858773769084</v>
       </c>
       <c r="F34">
-        <v>0.015529432038009494</v>
+        <v>0.01588209066619317</v>
       </c>
       <c r="G34">
-        <v>0.012976721133270863</v>
+        <v>0.015661060204416294</v>
       </c>
       <c r="H34">
-        <v>0.038075666248175294</v>
+        <v>0.03927184670010467</v>
       </c>
       <c r="I34">
-        <v>0.002718444578993254</v>
+        <v>0.0041201575519678735</v>
       </c>
       <c r="J34">
-        <v>0.07153399444934289</v>
+        <v>0.07753553128948343</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -50707,7 +52259,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -50736,26 +52288,26 @@
         <v>30</v>
       </c>
       <c r="E35">
-        <v>0.005519371147358398</v>
+        <v>0.005803328621100556</v>
       </c>
       <c r="F35">
-        <v>0.01552589721826908</v>
+        <v>0.015353418169496535</v>
       </c>
       <c r="G35">
-        <v>0.013633690221780848</v>
+        <v>0.01445952468895867</v>
       </c>
       <c r="H35">
-        <v>0.03806709980880993</v>
+        <v>0.037979771291104275</v>
       </c>
       <c r="I35">
-        <v>0.003119740043250069</v>
+        <v>0.004137028317874831</v>
       </c>
       <c r="J35">
-        <v>0.07892668631060598</v>
+        <v>0.07177861580922726</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -50775,7 +52327,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -50787,7 +52339,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>corridor:35:katwa:arua-uga</t>
+          <t>corridor:35:katwa:kampala-uga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -50797,33 +52349,33 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D36">
         <v>30</v>
       </c>
       <c r="E36">
-        <v>0.005719038632820889</v>
+        <v>0.005452431987887363</v>
       </c>
       <c r="F36">
-        <v>0.01443774068944173</v>
+        <v>0.015112456214481512</v>
       </c>
       <c r="G36">
-        <v>0.014124805074243657</v>
+        <v>0.013588823942918687</v>
       </c>
       <c r="H36">
-        <v>0.03542780468093812</v>
+        <v>0.03739051404598287</v>
       </c>
       <c r="I36">
-        <v>0.0037666445426507516</v>
+        <v>0.0024529046166230227</v>
       </c>
       <c r="J36">
-        <v>0.07911590609890654</v>
+        <v>0.07362524106371474</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 2 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -50843,7 +52395,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -50855,43 +52407,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>corridor:36:miti-murhesa:goma-cod</t>
+          <t>corridor:36:nizi:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D37">
         <v>30</v>
       </c>
       <c r="E37">
-        <v>0.002804459043458968</v>
+        <v>0.0029592732098638053</v>
       </c>
       <c r="F37">
-        <v>0.00878511499370449</v>
+        <v>0.008615756855734874</v>
       </c>
       <c r="G37">
-        <v>0.0069414009149691425</v>
+        <v>0.00738909968964363</v>
       </c>
       <c r="H37">
-        <v>0.021648029980746247</v>
+        <v>0.02142150261393619</v>
       </c>
       <c r="I37">
-        <v>0.0018195961747441535</v>
+        <v>0.002042185554189946</v>
       </c>
       <c r="J37">
-        <v>0.04351969089202276</v>
+        <v>0.038141110678055944</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -50911,7 +52463,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -50940,26 +52492,26 @@
         <v>30</v>
       </c>
       <c r="E38">
-        <v>0.002911020622911431</v>
+        <v>0.0030760137011489053</v>
       </c>
       <c r="F38">
-        <v>0.008708366339810258</v>
+        <v>0.00846374971817368</v>
       </c>
       <c r="G38">
-        <v>0.007204585754623377</v>
+        <v>0.007679918180666212</v>
       </c>
       <c r="H38">
-        <v>0.021460131514392883</v>
+        <v>0.021045977274501276</v>
       </c>
       <c r="I38">
-        <v>0.002213739571223128</v>
+        <v>0.00173074091036608</v>
       </c>
       <c r="J38">
-        <v>0.04056094344785632</v>
+        <v>0.0398150153221205</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -50979,7 +52531,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -50991,7 +52543,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>corridor:38:butembo:beni-cod</t>
+          <t>corridor:38:butembo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -51001,33 +52553,33 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D39">
         <v>30</v>
       </c>
       <c r="E39">
-        <v>0.0027769798502101373</v>
+        <v>0.002912025010885999</v>
       </c>
       <c r="F39">
-        <v>0.008633599440103473</v>
+        <v>0.008445323718460435</v>
       </c>
       <c r="G39">
-        <v>0.006873526257886398</v>
+        <v>0.007271381956022477</v>
       </c>
       <c r="H39">
-        <v>0.021277062424142124</v>
+        <v>0.02100045037086254</v>
       </c>
       <c r="I39">
-        <v>0.0016525413787399719</v>
+        <v>0.001833520856173457</v>
       </c>
       <c r="J39">
-        <v>0.03899275669757771</v>
+        <v>0.04218953222929745</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -51047,7 +52599,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -51059,43 +52611,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>corridor:39:miti-murhesa:kampala-uga</t>
+          <t>corridor:39:kilo:nebbi-uga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D40">
         <v>30</v>
       </c>
       <c r="E40">
-        <v>0.002943458801597104</v>
+        <v>0.002644849557592144</v>
       </c>
       <c r="F40">
-        <v>0.00848250804610165</v>
+        <v>0.00841402477375952</v>
       </c>
       <c r="G40">
-        <v>0.00728469284319036</v>
+        <v>0.006605567546016294</v>
       </c>
       <c r="H40">
-        <v>0.020907051259871884</v>
+        <v>0.02092311504898356</v>
       </c>
       <c r="I40">
-        <v>0.0019834988729835134</v>
+        <v>0.0016877685153872948</v>
       </c>
       <c r="J40">
-        <v>0.04021049895847632</v>
+        <v>0.039855086891450967</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -51115,7 +52667,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -51127,43 +52679,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>corridor:40:kilo:bundibugyo-uga</t>
+          <t>corridor:40:nizi:arua-uga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D41">
         <v>30</v>
       </c>
       <c r="E41">
-        <v>0.0029900129594525315</v>
+        <v>0.0030820348829910804</v>
       </c>
       <c r="F41">
-        <v>0.00847697711451803</v>
+        <v>0.008376715845314964</v>
       </c>
       <c r="G41">
-        <v>0.007399652921270428</v>
+        <v>0.00769491637598807</v>
       </c>
       <c r="H41">
-        <v>0.020893505827646625</v>
+        <v>0.020830924607609352</v>
       </c>
       <c r="I41">
-        <v>0.0017305897295624153</v>
+        <v>0.0022723676394841327</v>
       </c>
       <c r="J41">
-        <v>0.04136198023793251</v>
+        <v>0.039075643466061995</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -51183,7 +52735,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -51195,43 +52747,43 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>corridor:41:goma-cod:nebbi-uga</t>
+          <t>corridor:41:kilo:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D42">
         <v>30</v>
       </c>
       <c r="E42">
-        <v>0.0030684076719234843</v>
+        <v>0.002942442848407112</v>
       </c>
       <c r="F42">
-        <v>0.008456179104640776</v>
+        <v>0.008361385509734004</v>
       </c>
       <c r="G42">
-        <v>0.007593222717078629</v>
+        <v>0.007347167717738967</v>
       </c>
       <c r="H42">
-        <v>0.02084256764572595</v>
+        <v>0.02079304273136731</v>
       </c>
       <c r="I42">
-        <v>0.002196657973502822</v>
+        <v>0.0021218835713092354</v>
       </c>
       <c r="J42">
-        <v>0.041788827485054</v>
+        <v>0.046901203273610005</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -51251,7 +52803,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -51263,43 +52815,43 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>corridor:42:butembo:bundibugyo-uga</t>
+          <t>corridor:42:kilo:beni-cod</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D43">
         <v>30</v>
       </c>
       <c r="E43">
-        <v>0.003004206625567968</v>
+        <v>0.003105704299964651</v>
       </c>
       <c r="F43">
-        <v>0.008424640775256842</v>
+        <v>0.00833115388518385</v>
       </c>
       <c r="G43">
-        <v>0.007434701480319217</v>
+        <v>0.007753873862726468</v>
       </c>
       <c r="H43">
-        <v>0.02076531908923876</v>
+        <v>0.020718334796447163</v>
       </c>
       <c r="I43">
-        <v>0.0014445621581179958</v>
+        <v>0.00180424723430071</v>
       </c>
       <c r="J43">
-        <v>0.03973256156228256</v>
+        <v>0.042309271732519416</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -51319,7 +52871,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -51331,43 +52883,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>corridor:43:miti-murhesa:bundibugyo-uga</t>
+          <t>corridor:43:nizi:nebbi-uga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D44">
         <v>30</v>
       </c>
       <c r="E44">
-        <v>0.002960980933083057</v>
+        <v>0.0032288473585799504</v>
       </c>
       <c r="F44">
-        <v>0.008410627383326874</v>
+        <v>0.008287568484861813</v>
       </c>
       <c r="G44">
-        <v>0.007327962889187772</v>
+        <v>0.008060572955575385</v>
       </c>
       <c r="H44">
-        <v>0.02073099435361825</v>
+        <v>0.02061061825846619</v>
       </c>
       <c r="I44">
-        <v>0.0019244758288322094</v>
+        <v>0.0017025043966995032</v>
       </c>
       <c r="J44">
-        <v>0.04355962661351945</v>
+        <v>0.04124595278907633</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -51387,7 +52939,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -51399,43 +52951,43 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>corridor:44:goma-cod:beni-cod</t>
+          <t>corridor:44:bambu:kampala-uga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D45">
         <v>30</v>
       </c>
       <c r="E45">
-        <v>0.0027859978355153636</v>
+        <v>0.0028642776110266444</v>
       </c>
       <c r="F45">
-        <v>0.008318397055267795</v>
+        <v>0.008285310673803281</v>
       </c>
       <c r="G45">
-        <v>0.006895801362401172</v>
+        <v>0.007152413290739373</v>
       </c>
       <c r="H45">
-        <v>0.020505061460188434</v>
+        <v>0.020605040267043073</v>
       </c>
       <c r="I45">
-        <v>0.0019464730520260044</v>
+        <v>0.0019234467935779626</v>
       </c>
       <c r="J45">
-        <v>0.0437435227905687</v>
+        <v>0.03804667762767432</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -51455,7 +53007,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -51467,43 +53019,43 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>corridor:45:nizi:nebbi-uga</t>
+          <t>corridor:45:miti-murhesa:goma-cod</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D46">
         <v>30</v>
       </c>
       <c r="E46">
-        <v>0.002955828840965319</v>
+        <v>0.0030700936509970855</v>
       </c>
       <c r="F46">
-        <v>0.008295276156943115</v>
+        <v>0.008273574483650847</v>
       </c>
       <c r="G46">
-        <v>0.00731524012555157</v>
+        <v>0.007665171628754436</v>
       </c>
       <c r="H46">
-        <v>0.020448421900859687</v>
+        <v>0.020576036682684068</v>
       </c>
       <c r="I46">
-        <v>0.0014705155925033963</v>
+        <v>0.0016400363006218036</v>
       </c>
       <c r="J46">
-        <v>0.04349024336692712</v>
+        <v>0.04226326610167911</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -51523,7 +53075,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -51535,7 +53087,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>corridor:46:goma-cod:kampala-uga</t>
+          <t>corridor:46:goma-cod:kasese-uga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -51545,33 +53097,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D47">
         <v>30</v>
       </c>
       <c r="E47">
-        <v>0.0027125515817747747</v>
+        <v>0.002895090567260117</v>
       </c>
       <c r="F47">
-        <v>0.008284511161890662</v>
+        <v>0.008258041872603511</v>
       </c>
       <c r="G47">
-        <v>0.006714374614320118</v>
+        <v>0.0072291877287435635</v>
       </c>
       <c r="H47">
-        <v>0.020422048400997733</v>
+        <v>0.020537648258010355</v>
       </c>
       <c r="I47">
-        <v>0.0015261556624343033</v>
+        <v>0.0016874666938423294</v>
       </c>
       <c r="J47">
-        <v>0.04121550107288618</v>
+        <v>0.04358877442490046</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -51591,7 +53143,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -51603,43 +53155,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>corridor:47:goma-cod:arua-uga</t>
+          <t>corridor:47:butembo:beni-cod</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D48">
         <v>30</v>
       </c>
       <c r="E48">
-        <v>0.002859782073699718</v>
+        <v>0.002925413184253295</v>
       </c>
       <c r="F48">
-        <v>0.008263354150150004</v>
+        <v>0.008251826237103216</v>
       </c>
       <c r="G48">
-        <v>0.0070780413459651526</v>
+        <v>0.0073047393212719025</v>
       </c>
       <c r="H48">
-        <v>0.02037021424485949</v>
+        <v>0.020522286377206544</v>
       </c>
       <c r="I48">
-        <v>0.001649416108444149</v>
+        <v>0.0012767486976669267</v>
       </c>
       <c r="J48">
-        <v>0.042018168525404104</v>
+        <v>0.04263932005897099</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -51659,7 +53211,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -51671,43 +53223,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>corridor:48:bambu:arua-uga</t>
+          <t>corridor:48:miti-murhesa:kasese-uga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D49">
         <v>30</v>
       </c>
       <c r="E49">
-        <v>0.0029994938796520376</v>
+        <v>0.003034732560570602</v>
       </c>
       <c r="F49">
-        <v>0.008147226747461322</v>
+        <v>0.008209408125756323</v>
       </c>
       <c r="G49">
-        <v>0.007423064501010185</v>
+        <v>0.007577086361605395</v>
       </c>
       <c r="H49">
-        <v>0.020085678474308588</v>
+        <v>0.02041744425170991</v>
       </c>
       <c r="I49">
-        <v>0.0019885435545158206</v>
+        <v>0.0020835935046357172</v>
       </c>
       <c r="J49">
-        <v>0.03889536735459872</v>
+        <v>0.04266046321792653</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -51727,7 +53279,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -51739,12 +53291,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>corridor:49:miti-murhesa:kasese-uga</t>
+          <t>corridor:49:kilo:kasese-uga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -51756,26 +53308,26 @@
         <v>30</v>
       </c>
       <c r="E50">
-        <v>0.003061304197971737</v>
+        <v>0.0027832306587503852</v>
       </c>
       <c r="F50">
-        <v>0.00814381727681368</v>
+        <v>0.008199105874438367</v>
       </c>
       <c r="G50">
-        <v>0.00757568403154249</v>
+        <v>0.006950453512851895</v>
       </c>
       <c r="H50">
-        <v>0.020077321716829383</v>
+        <v>0.020391981269054865</v>
       </c>
       <c r="I50">
-        <v>0.0016647585017794454</v>
+        <v>0.0016841923935629502</v>
       </c>
       <c r="J50">
-        <v>0.03886426325038798</v>
+        <v>0.04307554327594385</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -51795,7 +53347,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -51807,43 +53359,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>corridor:50:miti-murhesa:arua-uga</t>
+          <t>corridor:50:butembo:goma-cod</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D51">
         <v>30</v>
       </c>
       <c r="E51">
-        <v>0.002726713106049522</v>
+        <v>0.0027648254236306846</v>
       </c>
       <c r="F51">
-        <v>0.008090540628411913</v>
+        <v>0.008195144122697173</v>
       </c>
       <c r="G51">
-        <v>0.00674935818047237</v>
+        <v>0.006904586655286371</v>
       </c>
       <c r="H51">
-        <v>0.019946766455073678</v>
+        <v>0.02038218848131071</v>
       </c>
       <c r="I51">
-        <v>0.001970594123010397</v>
+        <v>0.0014050942164623409</v>
       </c>
       <c r="J51">
-        <v>0.0390130390539575</v>
+        <v>0.04106017161770948</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -51863,7 +53415,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -51875,43 +53427,43 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>corridor:51:goma-cod:bundibugyo-uga</t>
+          <t>corridor:51:nizi:kasese-uga</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>0.0031340416283216765</v>
+        <v>0.0031943550671972576</v>
       </c>
       <c r="F52">
-        <v>0.008075152624742232</v>
+        <v>0.0081754483480935</v>
       </c>
       <c r="G52">
-        <v>0.00775526629452003</v>
+        <v>0.007974672417022405</v>
       </c>
       <c r="H52">
-        <v>0.01990905693022571</v>
+        <v>0.02033350318081173</v>
       </c>
       <c r="I52">
-        <v>0.002243955437822981</v>
+        <v>0.001768037554102492</v>
       </c>
       <c r="J52">
-        <v>0.03925743592923069</v>
+        <v>0.04511220698652555</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -51931,7 +53483,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -51943,7 +53495,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>corridor:52:bambu:nebbi-uga</t>
+          <t>corridor:52:bambu:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -51953,33 +53505,33 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D53">
         <v>30</v>
       </c>
       <c r="E53">
-        <v>0.0029941551171358827</v>
+        <v>0.0030705398729851396</v>
       </c>
       <c r="F53">
-        <v>0.008062710206497403</v>
+        <v>0.008175194200462782</v>
       </c>
       <c r="G53">
-        <v>0.007409881598903129</v>
+        <v>0.007666282652852352</v>
       </c>
       <c r="H53">
-        <v>0.019878564189878323</v>
+        <v>0.02033287701705</v>
       </c>
       <c r="I53">
-        <v>0.0023605934928140225</v>
+        <v>0.002096603096319022</v>
       </c>
       <c r="J53">
-        <v>0.03849962672911588</v>
+        <v>0.0453503407288809</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -51999,7 +53551,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -52011,7 +53563,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>corridor:53:butembo:goma-cod</t>
+          <t>corridor:53:butembo:nebbi-uga</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -52021,33 +53573,33 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D54">
         <v>30</v>
       </c>
       <c r="E54">
-        <v>0.002966610048958429</v>
+        <v>0.003086808276466707</v>
       </c>
       <c r="F54">
-        <v>0.008058011311337127</v>
+        <v>0.008168632292612499</v>
       </c>
       <c r="G54">
-        <v>0.007341863257414205</v>
+        <v>0.007706805224713592</v>
       </c>
       <c r="H54">
-        <v>0.01986704842779069</v>
+        <v>0.020316657158229695</v>
       </c>
       <c r="I54">
-        <v>0.00193425911064469</v>
+        <v>0.0017677151510857804</v>
       </c>
       <c r="J54">
-        <v>0.03944581553096073</v>
+        <v>0.04209255271101412</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -52067,7 +53619,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -52079,43 +53631,43 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>corridor:54:kilo:nebbi-uga</t>
+          <t>corridor:54:butembo:kasese-uga</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D55">
         <v>30</v>
       </c>
       <c r="E55">
-        <v>0.002837150359859514</v>
+        <v>0.0028428624159784754</v>
       </c>
       <c r="F55">
-        <v>0.008035393220128945</v>
+        <v>0.008153807402775132</v>
       </c>
       <c r="G55">
-        <v>0.007022145861493551</v>
+        <v>0.0070990515206802995</v>
       </c>
       <c r="H55">
-        <v>0.019811615320896397</v>
+        <v>0.020280011976689355</v>
       </c>
       <c r="I55">
-        <v>0.0016272804773103918</v>
+        <v>0.0016898985684225406</v>
       </c>
       <c r="J55">
-        <v>0.0417257099987222</v>
+        <v>0.04273366966920612</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -52135,7 +53687,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -52147,43 +53699,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>corridor:55:bambu:bundibugyo-uga</t>
+          <t>corridor:55:goma-cod:arua-uga</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D56">
         <v>30</v>
       </c>
       <c r="E56">
-        <v>0.0027221893165624844</v>
+        <v>0.0028841540948570388</v>
       </c>
       <c r="F56">
-        <v>0.008025112676473323</v>
+        <v>0.008147282496173996</v>
       </c>
       <c r="G56">
-        <v>0.006738183364620509</v>
+        <v>0.007201939352445036</v>
       </c>
       <c r="H56">
-        <v>0.019786420160049306</v>
+        <v>0.020263880904754727</v>
       </c>
       <c r="I56">
-        <v>0.0018923716266919608</v>
+        <v>0.0018996362621870682</v>
       </c>
       <c r="J56">
-        <v>0.04067091464985655</v>
+        <v>0.04338100709317285</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -52203,7 +53755,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -52215,43 +53767,43 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>corridor:56:nizi:bundibugyo-uga</t>
+          <t>corridor:56:miti-murhesa:nebbi-uga</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D57">
         <v>30</v>
       </c>
       <c r="E57">
-        <v>0.0029259199934389135</v>
+        <v>0.003193401191017242</v>
       </c>
       <c r="F57">
-        <v>0.008020137561744467</v>
+        <v>0.008079464270198511</v>
       </c>
       <c r="G57">
-        <v>0.007241380772000483</v>
+        <v>0.00797229685581774</v>
       </c>
       <c r="H57">
-        <v>0.019774226740906592</v>
+        <v>0.020096233035192618</v>
       </c>
       <c r="I57">
-        <v>0.0020925966217400726</v>
+        <v>0.0023432734197598257</v>
       </c>
       <c r="J57">
-        <v>0.03834918307680624</v>
+        <v>0.0428393249043879</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -52271,7 +53823,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -52283,43 +53835,43 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>corridor:57:butembo:kampala-uga</t>
+          <t>corridor:57:bambu:arua-uga</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D58">
         <v>30</v>
       </c>
       <c r="E58">
-        <v>0.0029779299971779694</v>
+        <v>0.002848122989708407</v>
       </c>
       <c r="F58">
-        <v>0.007993848855793961</v>
+        <v>0.008075906007655953</v>
       </c>
       <c r="G58">
-        <v>0.007369816645196731</v>
+        <v>0.007112159789265909</v>
       </c>
       <c r="H58">
-        <v>0.019709793462212938</v>
+        <v>0.02008743646896763</v>
       </c>
       <c r="I58">
-        <v>0.00181708380560561</v>
+        <v>0.0024182472420511887</v>
       </c>
       <c r="J58">
-        <v>0.03931941479325931</v>
+        <v>0.04183062725032947</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -52339,7 +53891,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -52351,43 +53903,43 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corridor:58:nizi:kasese-uga</t>
+          <t>corridor:58:bambu:beni-cod</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D59">
         <v>30</v>
       </c>
       <c r="E59">
-        <v>0.0028157111278240277</v>
+        <v>0.0030952404323974225</v>
       </c>
       <c r="F59">
-        <v>0.007982907485630852</v>
+        <v>0.008075478162716199</v>
       </c>
       <c r="G59">
-        <v>0.00696919271112631</v>
+        <v>0.007727810014310055</v>
       </c>
       <c r="H59">
-        <v>0.01968297753862283</v>
+        <v>0.02008637845334793</v>
       </c>
       <c r="I59">
-        <v>0.0017612060420275717</v>
+        <v>0.0023338362268623125</v>
       </c>
       <c r="J59">
-        <v>0.04306536711443636</v>
+        <v>0.03546392623297891</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -52407,7 +53959,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -52419,43 +53971,43 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>corridor:59:nizi:kampala-uga</t>
+          <t>corridor:59:bambu:nebbi-uga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D60">
         <v>30</v>
       </c>
       <c r="E60">
-        <v>0.0028025163740137693</v>
+        <v>0.0027949239664336045</v>
       </c>
       <c r="F60">
-        <v>0.007952241687691819</v>
+        <v>0.008028942087661334</v>
       </c>
       <c r="G60">
-        <v>0.006936602546891185</v>
+        <v>0.006979593542545737</v>
       </c>
       <c r="H60">
-        <v>0.019607812760897347</v>
+        <v>0.019971328098631613</v>
       </c>
       <c r="I60">
-        <v>0.0019699792558314196</v>
+        <v>0.0017261788874016833</v>
       </c>
       <c r="J60">
-        <v>0.03954925963547096</v>
+        <v>0.04091952527451027</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -52475,7 +54027,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -52487,43 +54039,43 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corridor:60:bambu:kasese-uga</t>
+          <t>corridor:60:nizi:goma-cod</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D61">
         <v>30</v>
       </c>
       <c r="E61">
-        <v>0.00270874962073242</v>
+        <v>0.0027489321597127803</v>
       </c>
       <c r="F61">
-        <v>0.007945705918331214</v>
+        <v>0.007970356450367283</v>
       </c>
       <c r="G61">
-        <v>0.006704981285868744</v>
+        <v>0.006864978691071638</v>
       </c>
       <c r="H61">
-        <v>0.019591793108546057</v>
+        <v>0.01982647730141504</v>
       </c>
       <c r="I61">
-        <v>0.0017099558870529636</v>
+        <v>0.0015215654864910754</v>
       </c>
       <c r="J61">
-        <v>0.040311579752921115</v>
+        <v>0.037110908911026086</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -52543,7 +54095,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -52555,43 +54107,43 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corridor:61:miti-murhesa:nebbi-uga</t>
+          <t>corridor:61:goma-cod:kampala-uga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D62">
         <v>30</v>
       </c>
       <c r="E62">
-        <v>0.0027622307839203497</v>
+        <v>0.002699020688463033</v>
       </c>
       <c r="F62">
-        <v>0.007936559977572588</v>
+        <v>0.00796355475811153</v>
       </c>
       <c r="G62">
-        <v>0.0068370944013670665</v>
+        <v>0.0067405865025700895</v>
       </c>
       <c r="H62">
-        <v>0.019569374185153948</v>
+        <v>0.019809659059149054</v>
       </c>
       <c r="I62">
-        <v>0.0017312928849019195</v>
+        <v>0.001280817184118785</v>
       </c>
       <c r="J62">
-        <v>0.043878198155480545</v>
+        <v>0.0411189894125921</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -52611,7 +54163,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -52623,43 +54175,43 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>corridor:62:butembo:nebbi-uga</t>
+          <t>corridor:62:goma-cod:beni-cod</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D63">
         <v>30</v>
       </c>
       <c r="E63">
-        <v>0.002937977495464733</v>
+        <v>0.003083537929685881</v>
       </c>
       <c r="F63">
-        <v>0.00791077263458917</v>
+        <v>0.007923297556548636</v>
       </c>
       <c r="G63">
-        <v>0.007271156988672728</v>
+        <v>0.007698659732552154</v>
       </c>
       <c r="H63">
-        <v>0.019506162869570853</v>
+        <v>0.019710115573578935</v>
       </c>
       <c r="I63">
-        <v>0.0015259490592032937</v>
+        <v>0.002235223758147331</v>
       </c>
       <c r="J63">
-        <v>0.04355956758414158</v>
+        <v>0.0408197910778464</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -52679,7 +54231,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -52691,43 +54243,43 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>corridor:63:nizi:arua-uga</t>
+          <t>corridor:63:butembo:kampala-uga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>butembo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D64">
         <v>30</v>
       </c>
       <c r="E64">
-        <v>0.0027959740199166583</v>
+        <v>0.0030804891814322777</v>
       </c>
       <c r="F64">
-        <v>0.007902911626123776</v>
+        <v>0.007904299533208425</v>
       </c>
       <c r="G64">
-        <v>0.006920442727769538</v>
+        <v>0.007691066214041364</v>
       </c>
       <c r="H64">
-        <v>0.019486894130341964</v>
+        <v>0.01966313522857363</v>
       </c>
       <c r="I64">
-        <v>0.0013335076635186461</v>
+        <v>0.0016889731420921179</v>
       </c>
       <c r="J64">
-        <v>0.03481721986752081</v>
+        <v>0.03684967293553905</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -52747,7 +54299,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -52759,12 +54311,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>corridor:64:kilo:kampala-uga</t>
+          <t>corridor:64:miti-murhesa:kampala-uga</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -52776,26 +54328,26 @@
         <v>30</v>
       </c>
       <c r="E65">
-        <v>0.0025676185126164985</v>
+        <v>0.0031202457914943083</v>
       </c>
       <c r="F65">
-        <v>0.007868621059145403</v>
+        <v>0.007886484835584268</v>
       </c>
       <c r="G65">
-        <v>0.0063563051772850265</v>
+        <v>0.007790093692533279</v>
       </c>
       <c r="H65">
-        <v>0.01940283456752373</v>
+        <v>0.019619084502247225</v>
       </c>
       <c r="I65">
-        <v>0.0016564750458324922</v>
+        <v>0.0020869398134200413</v>
       </c>
       <c r="J65">
-        <v>0.03677402473147005</v>
+        <v>0.04006299241054349</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -52815,7 +54367,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -52827,43 +54379,43 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>corridor:65:bambu:goma-cod</t>
+          <t>corridor:65:miti-murhesa:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D66">
         <v>30</v>
       </c>
       <c r="E66">
-        <v>0.002734796227902181</v>
+        <v>0.002947329694517803</v>
       </c>
       <c r="F66">
-        <v>0.007857450301785557</v>
+        <v>0.007876845063328641</v>
       </c>
       <c r="G66">
-        <v>0.006769325733142567</v>
+        <v>0.007359343662383694</v>
       </c>
       <c r="H66">
-        <v>0.01937544941239916</v>
+        <v>0.019595246186096926</v>
       </c>
       <c r="I66">
-        <v>0.0020746804621469632</v>
+        <v>0.0018831951808189838</v>
       </c>
       <c r="J66">
-        <v>0.039964857141121454</v>
+        <v>0.03800944544371585</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -52883,7 +54435,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -52895,43 +54447,43 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>corridor:66:kilo:goma-cod</t>
+          <t>corridor:66:miti-murhesa:beni-cod</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D67">
         <v>30</v>
       </c>
       <c r="E67">
-        <v>0.0027868684736187532</v>
+        <v>0.002961794494893477</v>
       </c>
       <c r="F67">
-        <v>0.007841801348761585</v>
+        <v>0.007839037276490352</v>
       </c>
       <c r="G67">
-        <v>0.00689795184472039</v>
+        <v>0.007395381044840943</v>
       </c>
       <c r="H67">
-        <v>0.019337083521810405</v>
+        <v>0.019501747456572294</v>
       </c>
       <c r="I67">
-        <v>0.0017127846529912062</v>
+        <v>0.0017434283860939981</v>
       </c>
       <c r="J67">
-        <v>0.03838966632456429</v>
+        <v>0.03912401061388266</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -52951,7 +54503,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -52963,12 +54515,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>corridor:67:bambu:kampala-uga</t>
+          <t>corridor:67:kilo:kampala-uga</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>bambu</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -52980,26 +54532,26 @@
         <v>30</v>
       </c>
       <c r="E68">
-        <v>0.002695763743499391</v>
+        <v>0.0027653371810337224</v>
       </c>
       <c r="F68">
-        <v>0.007827990157414616</v>
+        <v>0.007832592755062706</v>
       </c>
       <c r="G68">
-        <v>0.006672903334783625</v>
+        <v>0.006905862082790759</v>
       </c>
       <c r="H68">
-        <v>0.0193032265603717</v>
+        <v>0.01948580959864818</v>
       </c>
       <c r="I68">
-        <v>0.0021490354133257674</v>
+        <v>0.0014272206925231457</v>
       </c>
       <c r="J68">
-        <v>0.04054210634480244</v>
+        <v>0.036204525194573595</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -53019,7 +54571,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -53031,43 +54583,43 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>corridor:68:miti-murhesa:beni-cod</t>
+          <t>corridor:68:goma-cod:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>miti-murhesa</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D69">
         <v>30</v>
       </c>
       <c r="E69">
-        <v>0.002747310022513244</v>
+        <v>0.0026401409198533454</v>
       </c>
       <c r="F69">
-        <v>0.007800938064515872</v>
+        <v>0.007825833666732673</v>
       </c>
       <c r="G69">
-        <v>0.006800237623896643</v>
+        <v>0.0065938305286122045</v>
       </c>
       <c r="H69">
-        <v>0.019236905708309188</v>
+        <v>0.019469093435240226</v>
       </c>
       <c r="I69">
-        <v>0.002007951916882189</v>
+        <v>0.001866023926107744</v>
       </c>
       <c r="J69">
-        <v>0.03490534363617388</v>
+        <v>0.04124745480706853</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -53087,7 +54639,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -53099,43 +54651,43 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>corridor:69:kilo:kasese-uga</t>
+          <t>corridor:69:nizi:kampala-uga</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D70">
         <v>30</v>
       </c>
       <c r="E70">
-        <v>0.0028404048325195996</v>
+        <v>0.0028226780921865313</v>
       </c>
       <c r="F70">
-        <v>0.007786957767991598</v>
+        <v>0.007817735186569169</v>
       </c>
       <c r="G70">
-        <v>0.007030184083863106</v>
+        <v>0.007048755201963436</v>
       </c>
       <c r="H70">
-        <v>0.019202630017290306</v>
+        <v>0.019449064923741183</v>
       </c>
       <c r="I70">
-        <v>0.0018407478578635922</v>
+        <v>0.001488848936986176</v>
       </c>
       <c r="J70">
-        <v>0.041169590401536636</v>
+        <v>0.037164132361913654</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -53155,7 +54707,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -53167,7 +54719,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>corridor:70:bambu:beni-cod</t>
+          <t>corridor:70:bambu:kasese-uga</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -53177,33 +54729,33 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D71">
         <v>30</v>
       </c>
       <c r="E71">
-        <v>0.0030164649861187665</v>
+        <v>0.0029924559770832804</v>
       </c>
       <c r="F71">
-        <v>0.007772299321732512</v>
+        <v>0.0077847291413389585</v>
       </c>
       <c r="G71">
-        <v>0.0074649703248304</v>
+        <v>0.007471768248279054</v>
       </c>
       <c r="H71">
-        <v>0.01916669022271858</v>
+        <v>0.01936743172704536</v>
       </c>
       <c r="I71">
-        <v>0.0017745338814096486</v>
+        <v>0.0018760549298865252</v>
       </c>
       <c r="J71">
-        <v>0.04144693368617039</v>
+        <v>0.041123623891718</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -53223,7 +54775,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -53235,7 +54787,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>corridor:71:kilo:beni-cod</t>
+          <t>corridor:71:kilo:goma-cod</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -53245,33 +54797,33 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D72">
         <v>30</v>
       </c>
       <c r="E72">
-        <v>0.002780055599183956</v>
+        <v>0.002899935807471027</v>
       </c>
       <c r="F72">
-        <v>0.0077543800748747505</v>
+        <v>0.007752331645413807</v>
       </c>
       <c r="G72">
-        <v>0.006881123372275866</v>
+        <v>0.0072412614880431325</v>
       </c>
       <c r="H72">
-        <v>0.01912275597116167</v>
+        <v>0.019287303838200764</v>
       </c>
       <c r="I72">
-        <v>0.001731233807528232</v>
+        <v>0.002507736294786378</v>
       </c>
       <c r="J72">
-        <v>0.03818702256228324</v>
+        <v>0.03793936486570249</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -53291,7 +54843,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -53303,43 +54855,43 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>corridor:72:goma-cod:kasese-uga</t>
+          <t>corridor:72:miti-murhesa:arua-uga</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>miti-murhesa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D73">
         <v>30</v>
       </c>
       <c r="E73">
-        <v>0.0026587921388565305</v>
+        <v>0.002674108615021542</v>
       </c>
       <c r="F73">
-        <v>0.007745510300115388</v>
+        <v>0.00771382180610003</v>
       </c>
       <c r="G73">
-        <v>0.006581566727665494</v>
+        <v>0.006678494709007221</v>
       </c>
       <c r="H73">
-        <v>0.0191010070867213</v>
+        <v>0.019192050885068423</v>
       </c>
       <c r="I73">
-        <v>0.0015209453885095762</v>
+        <v>0.0021509346891685544</v>
       </c>
       <c r="J73">
-        <v>0.040091153412378705</v>
+        <v>0.03796381972912847</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -53359,7 +54911,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -53371,12 +54923,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>corridor:73:nizi:goma-cod</t>
+          <t>corridor:73:bambu:goma-cod</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>bambu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -53388,26 +54940,26 @@
         <v>30</v>
       </c>
       <c r="E74">
-        <v>0.002825210964649716</v>
+        <v>0.002798146272251445</v>
       </c>
       <c r="F74">
-        <v>0.00765236996976712</v>
+        <v>0.007671887672487665</v>
       </c>
       <c r="G74">
-        <v>0.006992656995719604</v>
+        <v>0.006987623680738353</v>
       </c>
       <c r="H74">
-        <v>0.01887262263985079</v>
+        <v>0.019088321018667948</v>
       </c>
       <c r="I74">
-        <v>0.001869567731866642</v>
+        <v>0.00212823295616803</v>
       </c>
       <c r="J74">
-        <v>0.03961175754580763</v>
+        <v>0.04046810286129031</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -53427,7 +54979,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -53439,43 +54991,43 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>corridor:74:butembo:kasese-uga</t>
+          <t>corridor:74:kilo:arua-uga</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>butembo</t>
+          <t>kilo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D75">
         <v>30</v>
       </c>
       <c r="E75">
-        <v>0.002862546240653324</v>
+        <v>0.002682487199688749</v>
       </c>
       <c r="F75">
-        <v>0.0075168412354912895</v>
+        <v>0.007647054652725971</v>
       </c>
       <c r="G75">
-        <v>0.007084869280098771</v>
+        <v>0.006699378734415562</v>
       </c>
       <c r="H75">
-        <v>0.0185402409724002</v>
+        <v>0.019026890104194144</v>
       </c>
       <c r="I75">
-        <v>0.0017601300993422223</v>
+        <v>0.002020439742511776</v>
       </c>
       <c r="J75">
-        <v>0.04281508413149316</v>
+        <v>0.04291075599057559</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -53495,7 +55047,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -53507,43 +55059,43 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>corridor:75:kilo:arua-uga</t>
+          <t>corridor:75:nizi:beni-cod</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>kilo</t>
+          <t>nizi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D76">
         <v>30</v>
       </c>
       <c r="E76">
-        <v>0.002806475854065099</v>
+        <v>0.0027869576198622237</v>
       </c>
       <c r="F76">
-        <v>0.007390944356303691</v>
+        <v>0.007500512752997485</v>
       </c>
       <c r="G76">
-        <v>0.006946382389732636</v>
+        <v>0.006959741432272071</v>
       </c>
       <c r="H76">
-        <v>0.018231416239954695</v>
+        <v>0.01866432521129177</v>
       </c>
       <c r="I76">
-        <v>0.00208300583836101</v>
+        <v>0.0019031011265957106</v>
       </c>
       <c r="J76">
-        <v>0.03944316706094814</v>
+        <v>0.04120978950730834</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -53563,7 +55115,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -53575,43 +55127,43 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>corridor:76:nizi:beni-cod</t>
+          <t>corridor:76:goma-cod:nebbi-uga</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nizi</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D77">
         <v>30</v>
       </c>
       <c r="E77">
-        <v>0.002632399314454331</v>
+        <v>0.0028476553420893336</v>
       </c>
       <c r="F77">
-        <v>0.007137232739807736</v>
+        <v>0.007386152605672769</v>
       </c>
       <c r="G77">
-        <v>0.00651636145090756</v>
+        <v>0.00711099325851175</v>
       </c>
       <c r="H77">
-        <v>0.017608901019654427</v>
+        <v>0.01838134562858537</v>
       </c>
       <c r="I77">
-        <v>0.0019380433985584896</v>
+        <v>0.0015336262358129989</v>
       </c>
       <c r="J77">
-        <v>0.034324531074020156</v>
+        <v>0.03820180693514552</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.48× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 1 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -53631,7 +55183,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -53769,7 +55321,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -53821,7 +55373,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -53875,7 +55427,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -53929,7 +55481,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -53983,7 +55535,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -54037,7 +55589,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -54091,7 +55643,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -54118,10 +55670,10 @@
       </c>
       <c r="D9"/>
       <c r="E9">
-        <v>0.4031809300428392</v>
+        <v>0.3996018070006698</v>
       </c>
       <c r="F9">
-        <v>0.4637985606142611</v>
+        <v>0.4583964248659597</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -54145,7 +55697,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -54172,10 +55724,10 @@
       </c>
       <c r="D10"/>
       <c r="E10">
-        <v>2.658988714502407</v>
+        <v>3.010371406466874</v>
       </c>
       <c r="F10">
-        <v>12.09131304558839</v>
+        <v>12.993364597456685</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -54199,7 +55751,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -54226,10 +55778,10 @@
       </c>
       <c r="D11"/>
       <c r="E11">
-        <v>468</v>
+        <v>511</v>
       </c>
       <c r="F11">
-        <v>712</v>
+        <v>832</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -54253,7 +55805,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -54307,7 +55859,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L12"/>
@@ -54355,7 +55907,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -54407,7 +55959,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -54459,7 +56011,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -54485,7 +56037,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="E16"/>
       <c r="F16"/>
@@ -54511,7 +56063,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -54537,7 +56089,7 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="E17"/>
       <c r="F17"/>
@@ -54563,7 +56115,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -54589,7 +56141,7 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.973</v>
+        <v>0.975</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -54615,7 +56167,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -54669,7 +56221,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L19"/>
@@ -54719,7 +56271,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="L20"/>
@@ -54797,7 +56349,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"confirmed": 112, "deaths": 223, "suspected": 906}</t>
+          <t>{"confirmed": 128, "deaths": 238, "suspected": 1077}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -54807,7 +56359,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CDC confirmed/suspected counts carry a May 24 data/report date; DRC MoH deaths carry a May 24 publication clock with no dateRapportage, so deaths are a headline input but not an ordinary dated death-trajectory node.</t>
+          <t>ECDC 27 May confirmed/suspected counts carry a May 26 data/report date (attributed to DRC MoH on 26 May); INRB build-2026-05-27 cross-corroborates DRC-only on the same data date. Death counts carry the same May 26 data date with the 238/246 ECDC/INRB conflict noted; deaths are a headline input and an ordinary dated death-trajectory node.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -54815,11 +56367,7 @@
           <t>current_model_or_display_input</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Deaths headline aggregate remains in count reconciliation, but the publication-only endpoint is separated from dated death-line nodes.</t>
-        </is>
-      </c>
+      <c r="G2"/>
       <c r="H2"/>
     </row>
     <row r="3">
@@ -54835,12 +56383,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"confirmed": 112, "suspected": 906}</t>
+          <t>{"confirmed": 128, "suspected": 1077}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{"confirmation_backlog_50": [468, 712], "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
+          <t>{"confirmation_backlog_50": [511, 832], "reporting_completeness_50": [0.3996018070006698, 0.4583964248659597]}</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -54869,17 +56417,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"confirmed_endpoint": 112, "reporting_completeness_50": [0.4031809300428392, 0.4637985606142611]}</t>
+          <t>{"confirmed_endpoint": 128, "reporting_completeness_50": [0.3996018070006698, 0.4583964248659597]}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>{"endpoint_confirmable_50": [241, 278]}</t>
+          <t>{"endpoint_confirmable_50": [279, 320]}</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Confirmed endpoint is dated May 24; the completeness posterior is the current snapshot posterior applied across the displayed confirmed-case series.</t>
+          <t>Confirmed endpoint is dated May 26 (DRC MoH per ECDC + INRB); the completeness posterior is the current snapshot posterior applied across the displayed confirmed-case series.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -54903,7 +56451,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"deaths": 223}</t>
+          <t>{"deaths": 238}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -54913,7 +56461,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The 223-death input comes from the US CDC Current Situation 25 May, a dated-report source, so it updates the snapshot-level sensitivity calculation as a connected dated trajectory point. The DRC MoH dashboard aggregate (179, 24 May) and the ECDC 25 May figure (119) are held as conflict anchors and are not promoted, so no publication-clock-only endpoint is rendered.</t>
+          <t>The 238-death input comes from ECDC 27 May (citing DRC MoH on 26 May), a dated-report source, so it updates the snapshot-level sensitivity calculation as a connected dated trajectory point. The INRB build-2026-05-27 (DRC-only national_moh) reports 246 on the same date and is retained as a slightly-higher DRC-only conflict anchor per NUMBERS_AUDIT Rule 3. CDC 25 May (223), the DRC MoH dashboard aggregate (179, 24 May), and the earlier ECDC 25 May figure (119) are held as conflict anchors and are not promoted, so no publication-clock-only secondary endpoint is rendered for those peers.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -54941,7 +56489,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"confirmed": 112}</t>
+          <t>{"confirmed": 128}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -54975,7 +56523,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"headline_confirmed": 112, "unallocated_headline_confirmed": 33, "zone_attributed_confirmed": 79}</t>
+          <t>{"headline_confirmed": 128, "unallocated_headline_confirmed": 49, "zone_attributed_confirmed": 79}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -54985,7 +56533,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>No reviewed May 24 cumulative health-zone table. The DRC MoH SitRep 009 dashboard rows remain source-review because dateRapportage and the official PDF are absent at capture.</t>
+          <t>No reviewed May 26 cumulative health-zone table. The DRC MoH SitRep 009 dashboard rows and the INRB build-2026-05-27 processed health-zone layers (latest at 2026-05-24) remain source-review because dateRapportage is absent and no official cumulative PDF for the May 26 data date has been published.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -55000,7 +56548,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No reviewed May 24 cumulative health-zone table. The DRC MoH SitRep 009 dashboard rows remain source-review because dateRapportage and the official PDF are absent at capture.</t>
+          <t>No reviewed May 26 cumulative health-zone table. The DRC MoH SitRep 009 dashboard rows and the INRB build-2026-05-27 processed health-zone layers (latest at 2026-05-24) remain source-review because dateRapportage is absent and no official cumulative PDF for the May 26 data date has been published.</t>
         </is>
       </c>
     </row>

--- a/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
+++ b/deliverables/public-health-dataset/lovs-public-health-dataset.xlsx
@@ -125,7 +125,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -819,7 +819,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1012 to 1556 at deaths 238), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1050 to 1615 at deaths 247), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 1012 to 1556 at deaths 238, CFR 40 to 26</t>
+          <t>total_cases = deaths * (1 + r/beta)^alpha / CFR; r = ln(2)/tau; Rosello gamma alpha 4.42, beta 0.388 per day; growth correction 1.7003 at tau=14; snapshot band 1050 to 1615 at deaths 247, CFR 40 to 26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 948 to 1458 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
+          <t>Keep total_cases_from_deaths linked to this audit row. Treat the 1050 to 1615 band as a reproduction on the snapshot death count, not as the Imperial reference. If the Rosello gamma, the doubling-time central, or the snapshot death count changes, update this audit row and NUMBERS_AUDIT together.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4123,8 +4123,66 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Institut National de Recherche Biomedicale (INRB), Institut National de Sante Publique (INSP), and Unite de Modelisation et Intelligence Epidemique (UMIE)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://github.com/INRB-UMIE/Ebola_DRC_2026/releases/download/build-2026-05-27-e40bc9e/build-2026-05-27-e40bc9e.tar.gz</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-05-27T22:00:53Z</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-28T02:41:54Z</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2a9e1b1f4b9a1828846e55bc12850900112709bff6b91b65057d6d99e7f60b44</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>private_restricted_bytes</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>publisher-terms-not-confirmed</t>
+        </is>
+      </c>
+      <c r="J45"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L44"/>
+  <autoFilter ref="A1:L45"/>
 </worksheet>
 </file>
 
@@ -8633,7 +8691,7 @@
       <c r="I10"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1012 to 1556 at deaths 238), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
+          <t>Keep the 400 to 900 reference band linked to this audit row. Byte-archive the 20 May report PDF or capture its figure text to upgrade from needs_primary_source. Do not present 400 to 900 as byte-verified, and do not conflate it with the snapshot's own deaths-back-projection band (1050 to 1615 at deaths 247), which is grounded by PUBLIC-CLAIM-AUDIT.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -16787,7 +16845,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -16830,7 +16888,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -16877,7 +16935,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>primary DRC authority/partner data release for source review and publication-clock routing; DRC-only national fields are preserved as country-specific values and are not generic headline counts.</t>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -17029,8 +17087,141 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>source_data_report_date:inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>source_data_report_date</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D134"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Data/report date the source says the observation describes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>source_publication_date:inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>source_publication_date</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D135"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Date the source made the observation available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>source_retrieval_date:inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>source_retrieval_date</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-05-28T02:41:54Z</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>primary DRC authority/partner data release for national count promotion and publication-clock routing; DRC-only national fields are preserved as country-specific values, and COD+UGA deaths require an explicit Uganda component.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>national_moh</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>recorded</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Archive capture timestamp for this source edition.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I133"/>
+  <autoFilter ref="A1:I136"/>
 </worksheet>
 </file>
 
@@ -36166,7 +36357,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; ecdc-bdbv-drc-uga-2026-05-21-live; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -36249,7 +36440,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+          <t>who-pheic-2026-05-17-live; ecdc-bdbv-drc-uga-2026-05-19-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -36316,13 +36507,13 @@
         </is>
       </c>
       <c r="F244">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G244">
         <v>106</v>
       </c>
       <c r="H244">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -36331,12 +36522,12 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>ecdc-bdbv-drc-uga-2026-05-27-live</t>
+          <t>inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a</t>
+          <t>afro-sitrep-01-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; who-dg-remarks-bdbv-2026-05-22; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; ecdc-bdbv-drc-uga-2026-05-25-live; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -36356,22 +36547,22 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>https://www.ecdc.europa.eu/en/ebola-virus-disease-outbreak-democratic-republic-congo-and-uganda-19-may-2026</t>
+          <t>https://github.com/INRB-UMIE/Ebola_DRC_2026/releases/download/build-2026-05-27-e40bc9e/build-2026-05-27-e40bc9e.tar.gz</t>
         </is>
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>8a63ef5cfde4aa2d6207aa3b9ffd05975dbfcbf773c6c6860df4dbd335cbe097</t>
+          <t>2a9e1b1f4b9a1828846e55bc12850900112709bff6b91b65057d6d99e7f60b44</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>public_bytes</t>
+          <t>private_restricted_bytes</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>publisher-terms-not-confirmed</t>
         </is>
       </c>
       <c r="S244"/>
@@ -50027,7 +50218,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corridor:01:rwampara:goma-cod</t>
+          <t>corridor:01:rwampara:kasese-uga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -50037,33 +50228,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>goma-cod</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2">
-        <v>0.08589962049863303</v>
+        <v>0.09498912685184227</v>
       </c>
       <c r="F2">
-        <v>0.2377669968354101</v>
+        <v>0.23752050489054755</v>
       </c>
       <c r="G2">
-        <v>0.20129270600512006</v>
+        <v>0.22159625087016196</v>
       </c>
       <c r="H2">
-        <v>0.4930960175674681</v>
+        <v>0.49370548523517666</v>
       </c>
       <c r="I2">
-        <v>0.07120480544093157</v>
+        <v>0.05954416677293458</v>
       </c>
       <c r="J2">
-        <v>0.7248388454926133</v>
+        <v>0.6929830536673017</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -50083,7 +50274,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -50095,7 +50286,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corridor:02:rwampara:kasese-uga</t>
+          <t>corridor:02:rwampara:beni-cod</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -50105,33 +50296,33 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D3">
         <v>30</v>
       </c>
       <c r="E3">
-        <v>0.08505191657867475</v>
+        <v>0.08741522336533816</v>
       </c>
       <c r="F3">
-        <v>0.23121425191013859</v>
+        <v>0.2299711000675383</v>
       </c>
       <c r="G3">
-        <v>0.19943802002803682</v>
+        <v>0.20514242072761815</v>
       </c>
       <c r="H3">
-        <v>0.4821200107370141</v>
+        <v>0.4810289335606389</v>
       </c>
       <c r="I3">
-        <v>0.054059833036011785</v>
+        <v>0.05591331409688446</v>
       </c>
       <c r="J3">
-        <v>0.7483917890968707</v>
+        <v>0.7347148239385632</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -50151,7 +50342,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -50163,7 +50354,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corridor:03:rwampara:arua-uga</t>
+          <t>corridor:03:rwampara:nebbi-uga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -50173,33 +50364,33 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>arua-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D4">
         <v>30</v>
       </c>
       <c r="E4">
-        <v>0.08246101760170607</v>
+        <v>0.09490142403586407</v>
       </c>
       <c r="F4">
-        <v>0.22061929395367888</v>
+        <v>0.22859740005765883</v>
       </c>
       <c r="G4">
-        <v>0.19375268176637458</v>
+        <v>0.2214068352769012</v>
       </c>
       <c r="H4">
-        <v>0.4640719973664308</v>
+        <v>0.4787025471726828</v>
       </c>
       <c r="I4">
-        <v>0.046285552997724785</v>
+        <v>0.0643200948074073</v>
       </c>
       <c r="J4">
-        <v>0.7208671523084099</v>
+        <v>0.7118972592616322</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -50219,7 +50410,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -50231,7 +50422,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corridor:04:rwampara:bundibugyo-uga</t>
+          <t>corridor:04:rwampara:arua-uga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -50241,33 +50432,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>arua-uga</t>
         </is>
       </c>
       <c r="D5">
         <v>30</v>
       </c>
       <c r="E5">
-        <v>0.0872098339088937</v>
+        <v>0.08482732194463333</v>
       </c>
       <c r="F5">
-        <v>0.21933684271935094</v>
+        <v>0.22463407851816508</v>
       </c>
       <c r="G5">
-        <v>0.20415468621935687</v>
+        <v>0.19947246150131526</v>
       </c>
       <c r="H5">
-        <v>0.4618632442565608</v>
+        <v>0.47195406011828506</v>
       </c>
       <c r="I5">
-        <v>0.05201982764209262</v>
+        <v>0.06927412765276479</v>
       </c>
       <c r="J5">
-        <v>0.7529772054129632</v>
+        <v>0.7209883849261258</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -50287,7 +50478,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -50299,7 +50490,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corridor:05:rwampara:beni-cod</t>
+          <t>corridor:05:rwampara:kampala-uga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -50309,33 +50500,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>beni-cod</t>
+          <t>kampala-uga</t>
         </is>
       </c>
       <c r="D6">
         <v>30</v>
       </c>
       <c r="E6">
-        <v>0.08504292783923784</v>
+        <v>0.08091983487963272</v>
       </c>
       <c r="F6">
-        <v>0.21818466263753306</v>
+        <v>0.2238698699856885</v>
       </c>
       <c r="G6">
-        <v>0.19941819443093944</v>
+        <v>0.1908663150804557</v>
       </c>
       <c r="H6">
-        <v>0.4598751196093878</v>
+        <v>0.4706465865029134</v>
       </c>
       <c r="I6">
-        <v>0.05371559052324989</v>
+        <v>0.06803439935132871</v>
       </c>
       <c r="J6">
-        <v>0.7436356440277915</v>
+        <v>0.7465098463711646</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -50355,7 +50546,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -50367,7 +50558,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corridor:06:rwampara:kampala-uga</t>
+          <t>corridor:06:rwampara:bundibugyo-uga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -50377,33 +50568,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>kampala-uga</t>
+          <t>bundibugyo-uga</t>
         </is>
       </c>
       <c r="D7">
         <v>30</v>
       </c>
       <c r="E7">
-        <v>0.08161896053098214</v>
+        <v>0.08921332611965974</v>
       </c>
       <c r="F7">
-        <v>0.21542592859488613</v>
+        <v>0.2209187060317813</v>
       </c>
       <c r="G7">
-        <v>0.19189952767778493</v>
+        <v>0.20906729886058256</v>
       </c>
       <c r="H7">
-        <v>0.4550927331844304</v>
+        <v>0.4655803289135554</v>
       </c>
       <c r="I7">
-        <v>0.04584337260504729</v>
+        <v>0.06091464992724125</v>
       </c>
       <c r="J7">
-        <v>0.7275888838527099</v>
+        <v>0.720889101405187</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -50423,7 +50614,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -50435,7 +50626,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corridor:07:rwampara:nebbi-uga</t>
+          <t>corridor:07:rwampara:goma-cod</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -50445,33 +50636,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>goma-cod</t>
         </is>
       </c>
       <c r="D8">
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0.07903310132360086</v>
+        <v>0.07398406156854198</v>
       </c>
       <c r="F8">
-        <v>0.21005018084173388</v>
+        <v>0.21944777973341462</v>
       </c>
       <c r="G8">
-        <v>0.18619362496919714</v>
+        <v>0.17545266812249247</v>
       </c>
       <c r="H8">
-        <v>0.4456997886549633</v>
+        <v>0.4630442265821525</v>
       </c>
       <c r="I8">
-        <v>0.062493325186918275</v>
+        <v>0.041726286704268596</v>
       </c>
       <c r="J8">
-        <v>0.725424432635406</v>
+        <v>0.7194372076943727</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 31 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -50491,7 +50682,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -50503,7 +50694,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corridor:08:bunia:nebbi-uga</t>
+          <t>corridor:08:bunia:beni-cod</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -50513,33 +50704,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nebbi-uga</t>
+          <t>beni-cod</t>
         </is>
       </c>
       <c r="D9">
         <v>30</v>
       </c>
       <c r="E9">
-        <v>0.04729302438764643</v>
+        <v>0.04323600498165517</v>
       </c>
       <c r="F9">
-        <v>0.12370943963454503</v>
+        <v>0.11693129299493701</v>
       </c>
       <c r="G9">
-        <v>0.11417904209164992</v>
+        <v>0.10500250690373125</v>
       </c>
       <c r="H9">
-        <v>0.28141613742977256</v>
+        <v>0.26810127259513455</v>
       </c>
       <c r="I9">
-        <v>0.029207232878451818</v>
+        <v>0.03135328491478113</v>
       </c>
       <c r="J9">
-        <v>0.4920171793027066</v>
+        <v>0.4691946655730641</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -50559,7 +50750,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -50571,7 +50762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corridor:09:bunia:bundibugyo-uga</t>
+          <t>corridor:09:bunia:kasese-uga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -50581,33 +50772,33 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bundibugyo-uga</t>
+          <t>kasese-uga</t>
         </is>
       </c>
       <c r="D10">
         <v>30</v>
       </c>
       <c r="E10">
-        <v>0.043911160625526746</v>
+        <v>0.04162107990584846</v>
       </c>
       <c r="F10">
-        <v>0.12312573996350779</v>
+        <v>0.11540316298981398</v>
       </c>
       <c r="G10">
-        <v>0.10628910544890177</v>
+        <v>0.10120598888468094</v>
       </c>
       <c r="H10">
-        <v>0.28021748772019517</v>
+        <v>0.26491821536289506</v>
       </c>
       <c r="I10">
-        <v>0.0356239441695431</v>
+        <v>0.031393508449463745</v>
       </c>
       <c r="J10">
-        <v>0.45773855023765087</v>
+        <v>0.4709298655687649</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -50627,7 +50818,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -50639,12 +50830,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corridor:10:bunia:kampala-uga</t>
+          <t>corridor:10:mongbwalu:kampala-uga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bunia</t>
+          <t>mongbwalu</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -50656,26 +50847,26 @@
         <v>30</v>
       </c>
       <c r="E11">
-        <v>0.03978940807069492</v>
+        <v>0.03738808016315484</v>
       </c>
       <c r="F11">
-        <v>0.1173207414160834</v>
+        <v>0.11386910938758041</v>
       </c>
       <c r="G11">
-        <v>0.09661618012382142</v>
+        <v>0.09120887984782666</v>
       </c>
       <c r="H11">
-        <v>0.2682338954929566</v>
+        <v>0.26171435944422355</v>
       </c>
       <c r="I11">
-        <v>0.029747212124222495</v>
+        <v>0.023394545747564707</v>
       </c>
       <c r="J11">
-        <v>0.5070561528116015</v>
+        <v>0.46384933748040447</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zone-attributed confirmed count 15 for this source zone; visibility-adjustment factor 2.50× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
+          <t>zone-attributed confirmed count 14 for this source zone; visibility-adjustment factor 2.51× reflects under-reporting in source zone; raw risk likely understates true hazard</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -50695,7 +50886,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-059661a; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
+          <t>who-don602-2026-05-15-live; who-pheic-2026-05-17-live; afro-sitrep-01-2026-05-18-live; afro-sitrep-01-pdf-2026-05-18-live; africa-cdc-phecs-2026-05-18-live; ecdc-bdbv-drc-uga-2026-05-19-live; ecdc-bdbv-drc-uga-2026-05-21-live; wikipedia-2026-ituri-epidemic-2026-05-20-live; who-dg-remarks-bdbv-2026-05-20; cdc-current-situation-2026-05-21; cdc-current-situation-2026-05-23; cdc-current-situation-2026-05-24; who-don603-2026-05-21-live; who-dg-remarks-bdbv-2026-05-22; who-ihr-ec-bdbv-temporary-recommendations-2026-05-22; drc-moh-epidemie-dashboard-sitrep-009-graphql-2026-05-24; cdc-current-situation-2026-05-25; ecdc-bdbv-drc-uga-2026-05-25-live; ecdc-bdbv-drc-uga-2026-05-26-live; ecdc-bdbv-drc-uga-2026-05-27-live; inrb-umie-ebola-drc-2026-build-2026-05-27-e40bc9e; drc-moh-epidemie-dashboard-sitrep-mve-n-007-mvb-17-2026-pdf-2026-05-22</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -50707,7 +50898,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corridor:11:bunia:kasese-uga</t>
+          <t>corridor:11:bunia:nebbi-uga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -50717,33 +50908,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kasese-uga</t>
+          <t>nebbi-uga</t>
         </is>
       </c>
       <c r="D12">
         <v>30</v>
       </c>
       <c r="E12">
-        <v>0.0420273929079403</v>
+        <v>0.041596373029643946</v>
       </c>
       <c r="F12">
-        <v>0.11511405461029645</v>
+        <v>0.11373391588233098</v>
       </c>
       <c r="G12">
-        <v>0.10187597894378383</v>
+        <v>0.101147850